--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10094312\Downloads\DataTables\DataTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BDC48D8-69CC-4DB5-90AD-AF22ED69B03B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E6AF48-CB4D-44C6-8CF1-BED71BC3E19C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Disease" sheetId="1" r:id="rId1"/>
@@ -20,20 +20,7 @@
     <sheet name="Herb" sheetId="5" r:id="rId5"/>
     <sheet name="Book" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -1064,7 +1051,7 @@
 风寒表虚证
 【组成】
 君：桂枝 三钱
-臣：芍药 三钱
+臣：白芍 三钱
 佐：生姜 三钱，大枣 二钱
 使：甘草 二钱
 【配伍】
@@ -1192,7 +1179,7 @@
 【组成】
 君：乌头 二钱
 臣：麻黄 三钱
-佐：芍药三钱，黄芪 三钱
+佐：白芍 三钱，黄芪 三钱
 使：甘草 三钱，蜂蜜 一斤
 【配伍】
 乌头：大辛大热，温经散寒、逐寒湿、止剧痛，专治寒凝痹痛；
@@ -1556,7 +1543,7 @@
 寒凝心脉
 【组成】
 君：当归 四钱
-臣：桂枝 三钱，芍药 三钱
+臣：桂枝 三钱，白芍 三钱
 佐：细辛 一钱，木通 二钱
 使：甘草 二钱，大枣 二钱
 【配伍】
@@ -1584,7 +1571,7 @@
 【组成】
 君：柴胡 二钱
 臣：香附 一钱五分钱，川芎 一钱五分
-佐：陈皮 二钱，枳壳 一钱五分，芍药 一钱五分
+佐：陈皮 二钱，枳壳 一钱五分，白芍 一钱五分
 使：甘草 五分
 【配伍】
 柴胡：疏肝解郁、调畅气机，直入肝胆疏泄郁滞。
@@ -1608,7 +1595,7 @@
 【组成】
 君：熟地黄 四钱
 臣：当归 三钱
-佐：芍药 三钱，川芎 二钱
+佐：白芍 三钱，川芎 二钱
 使：
 【配伍】
 熟地黄：甘温味厚，滋阴补血、填精益髓，为补血之本。
@@ -1919,7 +1906,7 @@
 【组成】
 君：附子 三钱
 臣：茯苓 三钱，白术 三钱
-佐：生姜 二钱，芍药 三钱
+佐：生姜 二钱，白芍 三钱
 使：
 【配伍】
 附子：大辛大热，温补肾阳、散阴寒，助气化以行水。
@@ -1990,7 +1977,7 @@
 心肾不交
 【组成】
 君：黄连 四钱
-臣：黄芩 三钱，芍药 三钱
+臣：黄芩 三钱，白芍 三钱
 佐：阿胶 三钱
 使：鸡子黄 一两
 【配伍】
@@ -2013,7 +2000,7 @@
 肝脾不和（肝郁脾虚）
 【组成】
 君：柴胡 三钱
-臣：当归 三钱，芍药 三钱
+臣：当归 三钱，白芍 三钱
 佐：白术 三钱，茯苓 三钱，生姜 一钱，薄荷 一钱
 使：甘草 一钱五分
 【配伍】
@@ -2480,8 +2467,7 @@
 解表散寒，温中止呕，解鱼蟹毒
 【释名】
 时珍曰：按：许慎《说文》：姜作䕬，云御湿之菜也。
-王安石《字说》云：姜能强御百邪，故谓之姜。
-初生嫩者，其尖微紫，名紫姜，或作子姜；宿根谓之母姜也。
+王安石《字说》云：姜能强御百邪，故谓之姜。初生嫩者，其尖微紫，名紫姜，或作子姜；宿根谓之母姜也。
 【发明】
 成无己曰︰姜、枣味辛、甘，专行脾之津液而和营卫。药中用之，不独专于发散也。
 杲曰︰生姜之用有四︰制半夏、浓朴之毒，一也；发散风寒，二也；与枣同用，辛温益脾胃元气，温中去湿，三也；与芍药同用，温经散寒，四也。孙真人云︰姜为呕家圣药，盖辛以散之。呕乃气逆不散，此药行阳而散气也。或问︰生姜辛温入肺，何以云入胃口？曰︰俗以心下为胃口者，非矣。咽门之下，受有形之物，乃胃之系，便是胃口，与肺系同行，故能入肺而开胃口也。曰︰人云夜间勿食生姜，令人闭气，何也？曰︰生姜辛温主开发。夜则气本收敛，反开发之，则违天道矣。若有病患，则不然也。生姜屑，比之乾姜则不热，比之生姜则不湿。以乾生姜代乾姜者，以其不僭故也。俗言上床萝卜下床姜。姜能开胃，萝卜消食也。
@@ -2512,9 +2498,8 @@
 【主治】
 发汗解表，宣肺平喘，利水消肿
 【释名】
-龙沙（《本经》）、卑相（《别录》）、卑盐（《别录》）
-时珍曰：诸名殊不可解。或云其味麻，其色黄，未审然否？
-张揖《广雅》云：龙沙，麻黄也。狗骨，麻黄根也。不知何以分别如此？
+龙沙（《本经》）、卑相（《别录》）、卑盐（《别录》）。
+时珍曰：诸名殊不可解。或云其味麻，其色黄，未审然否？张揖《广雅》云：龙沙，麻黄也。狗骨，麻黄根也。不知何以分别如此？
 【发明】
 弘景曰︰麻黄疗伤寒，解肌第一药。
 颂曰︰张仲景治伤寒，有麻黄汤及葛根汤、大小青龙汤，皆用麻黄。治肺痿上气，有射干麻黄汤、浓朴麻黄汤，皆大方也。
@@ -2576,8 +2561,7 @@
 【主治】
 止咳平喘，润肠通便
 【释名】
-时珍曰︰杏字篆文象子在木枝之形。或云从口及从可者，并非也。
-《江南录》云︰杨行密改杏名甜梅。
+时珍曰︰杏字篆文象子在木枝之形。或云从口及从可者，并非也。《江南录》云︰杨行密改杏名甜梅。
 【发明】
 元素曰︰杏仁气薄味浓，浊而沉坠，降也、阴也。入手太阴经。其用有三︰润肺也，消食积也，散滞气也。
 杲曰︰杏仁散结润燥，除肺中风热咳嗽。杏仁下喘，治气也；桃仁疗狂，治血也。俱治大便秘，当分气、血。昼则便难，行阳气也；夜则便难，行阴血也。故虚人便闭，不可过泄。脉浮者属气，用杏仁、陈皮；脉沉者属血，用桃仁、陈皮。手阳明与手太阴为表里，贲门主往来，魄门主收闭，为气之通道，故并用陈皮佐之。
@@ -2610,7 +2594,7 @@
 【主治】
 益气补中，清热解毒，祛痰止咳，缓急止痛，调和诸药
 【释名】
-密甘（《别录》）、密草（《别录》）、美草（《别录》）、蕗草（《别录》）、灵通（《记事珠》）、国老（《别录》）
+密甘（《别录》）、密草（《别录》）、美草（《别录》）、蕗草（《别录》）、灵通（《记事珠》）、国老（《别录》）。
 弘景曰︰此草最为众药之主，经方少有不用者，犹如香中有沉香也。国老即帝师之称，虽非君而为君所宗，是以能安和草石而解诸毒也。
 甄权曰︰诸药中甘草为君，治七十二种乳石毒，解一千二百般草木毒，调和众药有功故有国老之号。
 【发明】
@@ -2633,7 +2617,7 @@
     <t>肝|脾</t>
   </si>
   <si>
-    <t>白芍
+    <t>白芍（芍药）
 【气味】
 苦、酸，微寒
 【毒性】
@@ -2643,8 +2627,9 @@
 【主治】
 养血调经，敛阴止汗，柔肝止痛，平抑肝阳
 【释名】
-将离（《纲目》）、犁食（《别录》）、白术（《别录》）、余容（《别录》）、铤（《别录》），白者名金芍药（《图经》）
-时珍曰：芍药，犹约也。约，美好貌。此草花容婥约，故以为名。又《雅翼》言：制食之毒，莫良于芍，故得药名，亦通。郑风诗云：伊其相谑，赠之以芍药。
+将离（《纲目》）、犁食（《别录》）、白术（《别录》）、余容（《别录》）、铤（《别录》），白者名金芍药，赤者名木芍药（《图经》）。
+时珍曰：芍药，犹约也。约，美好貌。此草花容婥约，故以为名。又《雅翼》言：制食之毒，莫良于芍，故得药名，亦通。
+郑风诗云：伊其相谑，赠之以芍药。
 《韩诗外传》云：芍药，离草也。董子云：芍药一名将离，故将别赠之。俗呼其花之千叶者，为小牡丹；赤者为木芍药，与牡丹同名也。
 【发明】
 志曰：赤者，利小便下气；白者，止痛散血。
@@ -2666,7 +2651,7 @@
     <t>赤芍</t>
   </si>
   <si>
-    <t>赤芍
+    <t>赤芍（芍药）
 【气味】
 苦，微寒
 【毒性】
@@ -2676,8 +2661,9 @@
 【主治】
 清热凉血，散瘀止痛，清肝泻火
 【释名】
-将离（《纲目》）、犁食（《别录》）、白术（《别录》）、余容（《别录》）、铤（《别录》），白者名金芍药（《图经》）
-时珍曰：芍药，犹约也。约，美好貌。此草花容婥约，故以为名。又《雅翼》言：制食之毒，莫良于芍，故得药名，亦通。郑风诗云：伊其相谑，赠之以芍药。
+将离（《纲目》）、犁食（《别录》）、白术（《别录》）、余容（《别录》）、铤（《别录》），白者名金芍药，赤者名木芍药（《图经》）。
+时珍曰：芍药，犹约也。约，美好貌。此草花容婥约，故以为名。又《雅翼》言：制食之毒，莫良于芍，故得药名，亦通。
+郑风诗云：伊其相谑，赠之以芍药。
 《韩诗外传》云：芍药，离草也。董子云：芍药一名将离，故将别赠之。俗呼其花之千叶者，为小牡丹；赤者为木芍药，与牡丹同名也。
 【发明】
 志曰：赤者，利小便下气；白者，止痛散血。
@@ -2706,7 +2692,7 @@
 【主治】
 补中益气，养血安神，缓和药性
 【释名】
-干枣（《别录》）、美枣（《别录》）、良枣（《别录》）
+干枣（《别录》）、美枣（《别录》）、良枣（《别录》）。
 《别录》曰︰八月采，曝干。
 瑞曰︰此即晒干大枣也。味最良美，故宜入药。今人亦有用胶枣之肥大者。
 【发明】
@@ -2736,7 +2722,7 @@
 【主治】
 解肌退热，透发麻疹，生津止渴，升阳止泻，通经活络，解酒毒
 【释名】
-鸡齐（《本经》）、鹿藿（《别录》）、黄斤（《别录》）
+鸡齐（《本经》）、鹿藿（《别录》）、黄斤（《别录》）。
 时珍曰︰葛从曷，谐声也。鹿食九草，此其一种，故曰鹿藿。黄斤未详。
 【发明】
 弘景曰︰生葛捣汁饮，解温病发热。五月五日日中时，取根为屑，熬令黄黑，屑末水服方寸匕，疗疟及疮，至良。
@@ -2770,7 +2756,7 @@
 【主治】
 疏散风热，清肺润燥，平抑肝阳，清肝明目，凉血止血
 【释名】
-子名椹
+子名椹（《集韵》）。
 时珍曰︰徐锴《说文解字》云︰桑，音若，东方自然神木之名，其字象形。桑乃蚕所食，异于东方自然之神木，故加木于桑下而别之。
 《典术》云︰桑乃箕星之精。
 【发明】
@@ -2795,7 +2781,7 @@
 【主治】
 疏散风热，平抑肝阳，清肝明目，清热解毒
 【释名】
-节华（《本经》）、女节（《别录》）、女华（《别录》）、女茎（《别录》）、日精（《别录》）、更生（《别录》）、傅延年（《别录》）、治蔷（《尔雅》）、金蕊（《纲目》）、阴成（《别录》）、周盈（《别录》）
+节华（《本经》）、女节（《别录》）、女华（《别录》）、女茎（《别录》）、日精（《别录》）、更生（《别录》）、傅延年（《别录》）、治蔷（《尔雅》）、金蕊（《纲目》）、阴成（《别录》）、周盈（《别录》）。
 时珍曰︰按陆佃《埤雅》云︰菊本作蘜，从鞠。鞠，穷也。
 《月令》︰九月，菊有黄华。华事至此而穷尽，故谓之蘜。节华之名，亦取其应节候也。
 崔实《月令》云︰女节、女华，菊华之名也。治蔷、日精，菊根之名也。
@@ -2818,7 +2804,7 @@
 【主治】
 疏散风热，清利头目，利咽透疹，疏肝行气
 【释名】
-菝（音跋活）、蕃荷菜（蕃，音鄱）、吴菝（《食性》）、南薄荷（《衍义》）、金钱薄荷。
+菝（《食性》）、蕃荷菜（《千金》）、吴菝（《食性》）、南薄荷（《衍义》）、金钱薄荷（《会编》）。
 时珍曰：薄荷，俗称也。陈士良《食性本草》作菝，扬雄《甘泉赋》作茇，吕忱《字林》作茇，则薄荷之为讹称可知矣。
 孙思邈《千金方》作蕃荷，又方音之讹也。今人药用，多以苏州者为胜，故陈士良谓之吴菝，以别胡菝也。
 宗奭曰：世称此为南薄荷，为有一种龙脑薄荷，所以别之。机曰：小儿方多用金钱薄荷，谓其叶小颇圆如钱也，书作金银误矣。
@@ -2849,7 +2835,7 @@
 【主治】
 宣肺利咽，祛痰排脓
 【释名】
-白药（《别录》）、梗草（《别录》）、荠 （《本经》）
+白药（《别录》）、梗草（《别录》）、荠 （《本经》）。
 时珍曰︰此草之根结实而梗直，故名。《吴普本草》一名利如，一名符扈，一名房图，方书并无见，盖亦瘦辞尔。桔梗、荠 乃一类，有甜、苦二种，故《本经》桔梗一名荠 ，而今俗呼荠 为甜桔梗也。至《别录》始出荠 条，分为二物，然其性味功用皆不同，当以《别录》为是。
 【发明】
 好古曰︰桔梗气微温，味苦辛，味浓气轻，阳中之阴，升也。入手太阴肺经气分及足少阴经。
@@ -2871,9 +2857,8 @@
 【主治】
 清热泻火，生津止渴，除烦止呕，利尿
 【释名】
-苇（音伟）、葭（音加），花名
-时珍曰︰按毛苌
-《诗疏》云︰苇之初生曰葭；未秀曰芦；长成曰苇。苇者，伟大也。芦者，色卢黑也。葭者，嘉美也。
+苇（音伟《尔雅》）、葭（音加《尔雅》），花名蓬蕽（《唐本》）、笋名虇（音拳《尔雅》）。
+时珍曰︰按毛苌《诗疏》云︰苇之初生曰葭；未秀曰芦；长成曰苇。苇者，伟大也。芦者，色卢黑也。葭者，嘉美也。
 【发明】
 时珍曰︰按《雷公炮炙论》序云︰益食加觞，须煎芦、朴。注云︰用逆水芦根并浓朴二味等分，煎汤服。盖芦根甘能益胃，寒能降火故也。</t>
   </si>
@@ -2891,7 +2876,7 @@
 【主治】
 清热解毒，疏散风热
 【释名】
-金银藤（《纲目》）、鸳鸯藤（《纲目》）、鹭鸶藤（《纲目》）、老翁须（《纲目》）、左缠藤（《纲目》）、金钗股（《纲目》）、通灵草（《土宿》）、蜜桶藤。
+金银藤（《纲目》）、鸳鸯藤（《纲目》）、鹭鸶藤（《纲目》）、老翁须（《纲目》）、左缠藤（《纲目》）、金钗股（《纲目》）、通灵草（《土宿》）、蜜桶藤（《土宿》）。
 弘景曰︰处处有之。藤生，凌冬不凋，故名忍冬。
 时珍曰︰其花长瓣垂须，黄白相半，而藤左缠，故有金银、鸳鸯以下诸名。金钗股，贵其功也。土宿真君云︰蜜桶藤，阴草也。取汁能伏硫制汞，故有通灵之称。
 【发明】
@@ -2939,7 +2924,7 @@
 【主治】
 疏散风热，宣肺透疹，解毒利咽，滑肠通便
 【释名】
-鼠粘（《别录》）、牛蒡（《别录》）、大力子（《纲目》）、蒡翁菜（《纲目》）、便牵牛（《纲目》）、蝙蝠刺。
+鼠粘（《别录》）、牛蒡（《别录》）、大力子（《纲目》）、蒡翁菜（《纲目》）、便牵牛（《纲目》）、蝙蝠刺（《斗门方》）。
 时珍曰︰其实状恶而多刺钩，故名也。其根叶皆可食，人呼为牛菜，术人隐之呼为大力也。俚人谓之便牵牛。河南人呼为夜叉头。
 颂曰︰实壳多刺，鼠过之则缀惹不可脱，故谓之鼠粘子，亦如羊负来之比。
 【发明】
@@ -2959,7 +2944,7 @@
 【主治】
 解表散风，透疹，利咽消肿，止血
 【释名】
-姜芥（《别录》）、荆芥（《吴普》）、鼠 （《本经》）。
+姜芥（《别录》）、荆芥（《吴普》）、鼠蓂（《本经》）。
 弘景曰︰假苏方药不复用。
 恭曰︰此即菜中荆芥也，姜芥声讹尔。先居草部，今录入菜部。
 士良曰︰荆芥本草呼为假苏。假苏又别是一物。叶锐圆，多野生，以香气似苏，故呼为苏。
@@ -3011,8 +2996,7 @@
 【主治】
 清热泻火，除烦，生津利尿
 【释名】
-时珍曰︰竹字象形。许慎《说文》云︰“竹，冬生草也”。
-故字从倒草。戴凯之《竹谱》云︰植物之中，有名曰竹。不刚不柔，非草非木。小异实虚，大同节目。
+时珍曰︰竹字象形。许慎《说文》云︰“竹，冬生草也”。故字从倒草。戴凯之《竹谱》云︰植物之中，有名曰竹。不刚不柔，非草非木。小异实虚，大同节目。
 【发明】
 弘景曰︰甘竹叶最胜。
 诜曰︰竹叶︰ 、苦、淡、甘之外，馀皆不堪入药，不宜人。淡竹为上，甘竹次之。
@@ -3061,7 +3045,7 @@
 【主治】
 清热润肺，化痰止咳，散结消痈
 【释名】
-（《尔雅》，音萌）、勤母（《别录》）、苦菜（《别录》）、苦花（《别录》）、空草（《本经》）、药实。
+（《尔雅》，音萌）、勤母（《别录》）、苦菜（《别录》）、苦花（《别录》）、空草（《本经》）、药实（《别录》）。
 弘景曰：形似聚贝子，故名贝母。
 时珍曰：《诗》云言采其 ，即此。一作虻，谓根状如虻也。苦菜、药实，与野苦 、黄药子同名。
 【发明】
@@ -3089,10 +3073,8 @@
 【主治】
 清泄肺热，疏散肌表湿热，凉血解毒
 【释名】
-木丹（《本经》）、越桃（《别录》）
-时珍曰︰卮，酒器也。栀子象之，故名。俗作栀。
-司马相如赋云︰鲜支黄砾。注云︰鲜支即支子也。佛书称其花为卜，谢灵运谓之林兰，曾端伯呼为禅友。
-或曰︰卜金色，非栀子也。
+木丹（《本经》）、越桃（《别录》）、鲜支（《纲目》），花名薝蔔（《酉阳杂俎》）。
+时珍曰︰卮，酒器也。栀子象之，故名。俗作栀。司马相如赋云︰鲜支黄砾。注云︰鲜支即支子也。佛书称其花为卜，谢灵运谓之林兰，曾端伯呼为禅友。或曰︰卜金色，非栀子也。
 【发明】
 元素曰︰栀子轻飘而象肺，色赤而象火，故能泻肺中之火。
 其用有四︰心经客热一也，除烦躁二也，去上焦虚热三也，治风四也。
@@ -3118,7 +3100,7 @@
 【主治】
 清心润肺，降火生津，止咳化痰
 【释名】
-快果、果宗、玉乳、蜜父。
+快果（《弘景》）、果宗（《纲目》）、玉乳（《纲目》）、蜜父（《清异录》）。
 震亨曰︰梨者，利也。其性下行流利也。
 弘景曰︰梨种殊多，并皆冷利，多食损人，故俗人谓之快果，不入药用。
 【发明】
@@ -3143,8 +3125,8 @@
 【主治】
 解表散寒，行气和胃
 【释名】
-紫苏（《食疗》）、赤苏（《肘后方》）
-桂荏时珍曰︰苏从酥，音酥，舒畅也。苏性舒畅，行气和血，故谓之苏。曰紫苏者，以别白苏也。苏乃荏类，而味更辛如桂，故《尔 雅》谓之桂荏。
+紫苏（《食疗》）、赤苏（《肘后方》）、桂荏（《尔雅》）。
+时珍曰︰苏从酥，音酥，舒畅也。苏性舒畅，行气和血，故谓之苏。曰紫苏者，以别白苏也。苏乃荏类，而味更辛如桂，故《尔 雅》谓之桂荏。
 【发明】
 颂曰︰若宣通风毒，则单用茎，去节尤良。
 时珍曰︰紫苏，近世要药也。其味辛，入气分；其色紫，入血分。故同橘皮，砂仁，则行气安胎；同藿香、乌药，则温中止痛；同香附、麻黄，则发汗解肌；同芎 、当归则和血散血；同木瓜、浓朴，则散湿解暑，治霍乱、脚气；同桔梗、枳壳，则利膈宽肠；同杏仁、莱菔子，则消痰定喘也。 久则泄人真气焉。
@@ -3167,7 +3149,7 @@
 【主治】
 燥湿化痰，降逆止呕，消痞散结
 【释名】
-守田（《别录》）、水玉（《本经》）
+守田（《别录》）、水玉（《本经》）、地文（《本经》）、和姑（《吴普》）。
 时珍曰︰《礼记‧月令》︰五月半夏生。盖当夏之半也，故名。守田会意，水玉因形。
 【发明】
 权曰︰半夏使也。虚而有痰气，宜加用之。
@@ -3299,8 +3281,8 @@
 【主治】
 祛风解表，胜湿止痛，止痉
 【释名】
-铜芸（《本经》）、茴芸（《吴普》）、茴草（《别录》）、屏风（《别录》）、 根（《别录》）、百枝（《别录》）、百蜚（《吴普》）
-时珍曰：防者，御也。其功疗风最要，故名
+铜芸（《本经》）、茴芸（《吴普》）、茴草（《别录》）、屏风（《别录》）、 根（《别录》）、百枝（《别录》）、百蜚（《吴普》）。
+时珍曰：防者，御也。其功疗风最要，故名。屏风者，防风隐语也。曰芸、曰茴、曰蕳者，其花如茴香，其气如芸蒿、蕳兰也。
 【发明】
 元素曰：防风，治风通用。身半以上风邪用身，身半以下风邪，用梢，治风去湿之仙药也，风能胜湿故尔。能泻肺实，误服泻人上焦元气。杲曰：防风治一身尽痛，乃猝 伍卑贱之职，随所引而至，乃风药中润剂也。若补脾胃，非此引用不能行。凡脊痛项强，不可回顾，腰似折，项似拔者，乃手足太阳证，正当用防风。凡疮在胸膈以上，虽无手足太阳 证，亦当用之，为能散结，去上部风。病患身体拘倦者，风也，诸疮见此证，亦须用之。钱 仲阳泻黄散中倍用防风者，乃于土中泻木也。</t>
   </si>
@@ -3318,7 +3300,7 @@
 【主治】
 祛风湿，清湿热，止痹痛，退虚热
 【释名】
-秦糺（《唐本》）、秦爪（萧炳）
+秦糺（《唐本》）、秦爪（萧炳）。
 恭曰：秦艽，俗作秦胶，本名秦糺，与纠同。
 时珍曰：秦艽出秦中，以根作罗纹交纠者佳，故名秦艽、秦糺。
 【发明】
@@ -3341,8 +3323,9 @@
 【主治】
 补血活血，调经止痛，润肠通便
 【释名】
-干归（《本经》）、山蕲（《尔雅》）、白蕲（《尔雅》）、文无（《纲目》）
-颂曰︰按而粗大。许慎《说文》云︰生山中者，名薜，一名山蕲。然则当归，芹类也。在平地者名芹，生山中粗大者，名当归也。宗奭曰︰今川蜀皆以畦种，尤肥好多脂，不以平地、山中为等差也。
+乾归（《本经》）、山蕲（《尔雅》）、白蕲（《尔雅》）、文无（《纲目》）。
+颂曰︰按而粗大。许慎《说文》云︰生山中者，名薜，一名山蕲。然则当归，芹类也。在平地者名芹，生山中粗大者，名当归也。
+宗奭曰︰今川蜀皆以畦种，尤肥好多脂，不以平地、山中为等差也。
 时珍曰︰当归本非芹类，特以花叶似芹，故得芹名。古人娶妻为嗣续也，当归调血为女人要药，有思夫之意，故有当归之名，正与唐诗胡麻好种无人种，正是归时又不归之旨相同。崔豹《古今注》云，古人相赠以芍药，相招以文无。文无一名当归，芍药一名将离，故也。
 承曰︰当归治妊妇产后恶血上冲，仓猝取效。气血昏乱者，服之即定。能使气血各有所归，恐当归之名必因此出也。
 【发明】
@@ -3371,7 +3354,7 @@
 【主治】
 活血行气，祛风止痛
 【释名】
-胡䓖（《别录》）、川芎（《纲目》）、香果（《别录》）、山鞠穷（《纲目》）
+胡䓖（《别录》）、川芎（《纲目》）、香果（《别录》）、山鞠穷（《纲目》）。
 时珍曰︰芎本作营，名义未详。或云︰人头穹窿穷高，天之象也。此药上行，专治头脑 诸疾，故有芎 之名。以胡戎者为佳，故曰胡芎。古人因其根节状如马衔，谓之马衔芎 。 后世因其状如雀脑，谓之雀脑芎。其出关中者，呼为京芎，亦曰西芎；出蜀中者，为川芎；出天台者，为台芎；出江南者，为抚芎，皆因地而名也。《左传》︰楚人谓萧人曰︰有麦曲乎？ 有山鞠穷乎？河鱼腹疾柰何？二物皆御湿，故以谕之。丹溪朱氏治六郁越鞠丸中用越桃、鞠 穷，故以命名。《金光明经》谓之 莫迦。
 【发明】
 宗奭曰︰今人用此最多，头面风不可缺也，然须以他药佐之。
@@ -3411,8 +3394,7 @@
 乌喙（《本经》，即两头尖）、草乌头（《纲目》）、土附子（《日华》）、奚毒（《本经》）、耿子（《吴普》）、毒公（《吴普》。又名帝秋)、金鸦（《纲目》）、苗名茛（音艮）、芨（音及）、堇（音近）、独白草（《拾遗》）、鸳鸯菊（《纲目》）、汁煎名射罔
 普曰︰乌头，形如乌之头也。有两歧相合如乌之喙者，名曰乌喙。喙即乌之口也。
 恭曰︰乌喙，即乌头异名也。此有三歧者，然两歧者少。若乌头两歧名乌喙，则天雄、附子之两歧者，复何以名之？
-时珍曰︰此即乌头之野生于他处者，俗谓之草乌头，亦曰竹节乌头，出江北者曰淮乌头，《日华子》所谓土附子者是也。乌喙，即偶生两歧者，今俗呼为两头尖，因形而名，其实乃一物也。附子、天雄之偶生两歧者，亦谓之乌喙，功亦同于天雄，非此乌头也。苏恭不知此义，故反疑之。草乌头取汁，晒为毒药，射禽兽，故有射罔之称。《后魏书》言︰辽东塞外秋收乌头为毒药射禽兽，陈藏器所引《续汉五行志》，言西国生独白草，煎为药，敷箭射人即死者，皆此乌头，非川乌头也。
-《菊谱》云︰鸳鸯菊，即乌喙苗也。
+时珍曰︰此即乌头之野生于他处者，俗谓之草乌头，亦曰竹节乌头，出江北者曰淮乌头，《日华子》所谓土附子者是也。乌喙，即偶生两歧者，今俗呼为两头尖，因形而名，其实乃一物也。附子、天雄之偶生两歧者，亦谓之乌喙，功亦同于天雄，非此乌头也。苏恭不知此义，故反疑之。草乌头取汁，晒为毒药，射禽兽，故有射罔之称。《后魏书》言︰辽东塞外秋收乌头为毒药射禽兽，陈藏器所引《续汉五行志》，言西国生独白草，煎为药，敷箭射人即死者，皆此乌头，非川乌头也。《菊谱》云︰鸳鸯菊，即乌喙苗也。
 【发明】
 [川乌]
 宗奭曰︰补虚寒须用附子，风家即多用天雄，大略如此。其乌头、乌喙、附子，则量其材而用之。时珍曰︰按王氏《究原方》云︰附子性重滞，温脾逐寒。川乌头性轻疏，温脾去风。若是寒疾即用附子；风疾即用川乌头。一云︰凡人中风，不可先用风药及乌附。 若先用气药，后用乌附乃宜也。又凡用乌、附药，并宜冷服者，热因寒用也。盖阴寒在下，虚阳上浮。治之以寒，则阴气益甚而病增；治之以热，则拒格而不纳。热药冷冻饮料，下嗌之后，冷体既消，热性便发，而病气随愈。不违其情，而致大益，此反治之妙也。昔张仲景治寒疝 内结，用蜜煎乌头。《近效方》治喉痹，用蜜炙附子，含之咽汁。朱丹溪治疝气，用乌头、栀子。并热因寒用也。李东垣治冯翰林侄阴盛格阳伤寒，面赤目赤，烦渴引饮，脉来七、八至，但按之则散。用姜附东加人参，投半斤服之，得汗而愈。此则神圣之妙也。 吴绶曰︰附子乃阴证要药。凡伤寒传变三阴，及中寒夹阴，虽身大热而脉沉者，必用之。或厥冷腹痛，脉沉细，甚则唇青囊缩者，急须用之，有退阴回阳之力，起死回生之功。近 世阴证伤寒，往往疑似，不敢用附子，直待阴极阳竭而用之，已迟矣。且夹阴伤寒，内外皆阴，阳气顿衰。必须急用人参，健脉以益其原；佐以附子，温经散寒。舍此不用，将何以救 之？
@@ -3471,7 +3453,7 @@
 【主治】
 补中润燥，止痛解毒，外用生肌敛疮
 【释名】
-蜂糖（俗名）生岩石者名石蜜（《本经》）、石饴（同上）、岩蜜。
+蜂糖（俗名）生岩石者名石蜜（《本经》）、石饴（同上）、岩蜜（《拾遗》）。
 时珍曰︰蜜以密成，故谓之蜜。《本经》原作石蜜，盖以生岩石者为良耳，而诸家反致疑辩。今直题曰蜂蜜，正名也。
 【发明】
 弘景曰︰石蜜道家丸饵，莫不须之。仙方亦单炼服食，云致长生不老也。
@@ -3523,7 +3505,7 @@
 【主治】
 解表散寒，祛风除湿，止痛
 【释名】
-羌活（《本经》）、羌青（《本经》）、独摇草（《别录》）、护羌使者（《本经》）、胡王使者（《吴普》）、长生草
+羌活（《本经》）、羌青（《本经》）、独摇草（《别录》）、护羌使者（《本经》）、胡王使者（《吴普》）、长生草（《纲目》）。
 弘景曰：一茎直上，不为风摇，故曰独活。《别录》曰：此草得风不摇，无风自动，故名独摇草。大明曰：独活，是羌活母也。
 时珍曰：独活、羌活乃一类二种，独活以羌中来者为良，故有羌活、胡王使者诸名，乃一物二种也。正如川芎、抚芎，白术、苍术之义，入用
 【发明】
@@ -3544,7 +3526,7 @@
 【主治】
 解表散寒，祛风除湿，止痛
 【释名】
-羌活（《本经》）、羌青（《本经》）、独摇草（《别录》）、护羌使者（《本经》）、胡王使者（《吴普》）、长生草
+羌活（《本经》）、羌青（《本经》）、独摇草（《别录》）、护羌使者（《本经》）、胡王使者（《吴普》）、长生草（《纲目》）。
 弘景曰：一茎直上，不为风摇，故曰独活。《别录》曰：此草得风不摇，无风自动，故名独摇草。大明曰：独活，是羌活母也。
 时珍曰：独活、羌活乃一类二种，独活以羌中来者为良，故有羌活、胡王使者诸名，乃一物二种也。正如川芎、抚芎，白术、苍术之义，入用
 【发明】
@@ -3565,8 +3547,8 @@
 【主治】
 清热泻火，除烦止渴
 【释名】
-细理石（《别录》）、寒水石（《纲目》）
-震享曰︰火 细研醋调，封丹灶，其固密甚于脂膏。此盖兼质与能而得名，正与石脂同意。
+细理石（《别录》）、寒水石（《纲目》）。
+震享曰︰火煅细研醋调，封丹灶，其固密甚于脂膏。此盖兼质与能而得名，正与石脂同意。
 时珍曰︰其纹理细密，故名细理石。其性大寒如水，故名寒水石，与凝水石同名异物。
 【发明】
 成无己曰︰风，阳邪也；寒，阴邪也。风喜伤阳，寒喜伤阴。营卫阴阳，为风寒所伤，则非轻剂所能独散，必须轻重之剂同散之，乃得阴阳之邪俱去，营卫之气俱和。是以大青龙汤，以石膏为使。石膏乃重剂，而又专达肌表也。又云︰热淫所胜，佐以苦甘。知母、石膏之苦甘以散热。
@@ -3620,7 +3602,7 @@
 【主治】
 补中益气，健脾和胃，除烦渴，止泻痢
 【释名】
-（与粳同）
+秔（《说文》与粳同）。
 时珍曰︰粳乃谷稻之总名也，有早、中、晚三收。诸本草独以晚稻为粳者，非矣。粘者为糯，不粘者为粳。糯者懦也，粳者硬也。但入解热药，以晚粳为良尔。
 【发明】
 诜曰︰粳米赤者粒大而香，水渍之有味益人。大抵新熟者动气，经再年者亦发病。惟江南人多收火稻贮仓，烧去毛，至春舂米食之，即不发病宜人，温中益气，补下元也。
@@ -3646,7 +3628,7 @@
 【主治】
 清热化痰，息风定惊
 【释名】
-虎膏（《纲目》）、鬼蒟蒻（《日华》）
+虎膏（《纲目》）、鬼蒟蒻（《日华》）。
 恭曰︰其根四畔有圆牙，看如虎掌，故有此名。
 颂曰︰天南星即本草虎掌也，小者名由跋。古方多用虎掌，不言天南星。南星近出唐人中风痰毒方中用之，乃后人采用，别立此名尔。
 时珍曰︰虎掌因叶形似之，非根也。南星因根圆白，形如老人星状，故名南星，即虎掌也。苏颂说甚明白。宋《开宝》不当重出南星条，今并入。
@@ -3669,7 +3651,7 @@
 润肺化痰，滑肠通便
 【释名】
 果裸（音裸）、栝蒌（《纲目》）、天瓜（《别录》）、黄瓜（《别录》）、地蒌（《本经》）、泽姑（《别录》）
-根名白药（《图经》）、天花粉（《图经》）、瑞雪
+根名白药（《图经》）、天花粉（《图经》）、瑞雪（《赵宜真》）。
 时珍曰︰裸，与蓏同。
 许慎云︰木上曰果，地下曰蓏。此物蔓生附木，故得兼名。《诗》云︰果裸之实，亦施于宇，是矣。栝蒌，即果裸二字音转也，亦作𤫱𤬏，后人又转为栝蒌，愈转愈失其真矣。古者瓜姑同音，故有泽姑之名。齐人谓之天瓜，象形也。雷 《炮炙论》，以圆者为栝，长者为蒌，亦出牵强，但分雌雄可也。其根作粉，洁白如雪，故谓之天花粉。苏颂《图经》重出天花粉，谬矣，今削之。
 【发明】
@@ -3693,7 +3675,7 @@
 【主治】
 清热燥湿，泻火解毒，止血，安胎
 【释名】
-腐肠（《本经》）、空肠（《别录》）、内虚（《别录》）、妒妇（《吴普》）、经芩 （《别录》）、黄文（《别录》）、印头（《吴普》）、苦督邮（《记事》），内实者名子芩（弘景）、条芩（《纲目》）、 尾芩（《唐本》）、鼠尾芩。
+腐肠（《本经》）、空肠（《别录》）、内虚（《别录》）、妒妇（《吴普》）、经芩 （《别录》）、黄文（《别录》）、印头（《吴普》）、苦督邮（《记事》），内实者名子芩（弘景）、条芩（《纲目》）、 尾芩（《唐本》）、鼠尾芩（《纲目》）。
 弘景曰：圆者，名子芩；破者，名宿芩，其腹中皆烂，故名腐肠。
 时珍曰：芩，《说文》作 ，谓其色黄也。或云芩者，黔也，黔乃黄黑之色也。宿芩乃旧根，多中空，外黄内黑，即今所谓片芩，故又有腐肠、妒妇诸名。妒 妇心黯，故以比之。子芩乃新根，多内实，即今所谓条芩。或云西芩多中空而色黔，北芩多内实而深黄。
 【发明】
@@ -3742,9 +3724,7 @@
 大补元气，复脉固脱，益气摄血，生津安神
 【释名】
 人薓（音参。或省作参）、黄参（《吴普》）、血参（《别录》）、人衔（《本经》）、鬼盖（《本经》）、神草（《别录》）、土精（《别录》）、地精（《广雅》）、海腴、皱面还丹（《广雅》）。
-时珍曰︰人薓年深，浸渐长成者，根如人形，有神，故谓之人薓、神草。薓字，从𣹰，亦浸渐之义。𣹰，即浸字，后世因字文繁，遂以参星之字代之，从简便尔。然承误日久，亦不能变矣，惟张仲景《伤寒论》尚作薓字。《别录》一名人微，微乃薓字之讹也。其成有阶级，故曰人衔。其草背阳向阴，故曰鬼盖。其在五参，色黄属土，而补脾胃，生阴血，故有黄参、血参之名。得地之精灵，故有土精、地精之名。
-《广五行记》云︰隋文帝时，上党有人宅后每夜闻人呼声，求之不得。去宅一里许，见人参枝叶异常，掘之入地五尺，得人参，一如人体，四肢毕备，呼声遂绝。观此，则土精之名，尤可证也。《礼斗威仪》云︰下有人参，上有紫气。
-《春秋运斗枢》云︰摇光星散而为人参。人君废山渎之利，则摇光不明，人参不生。观此，则神草之名，又可证矣。
+时珍曰︰人薓年深，浸渐长成者，根如人形，有神，故谓之人薓、神草。薓字，从𣹰，亦浸渐之义。𣹰，即浸字，后世因字文繁，遂以参星之字代之，从简便尔。然承误日久，亦不能变矣，惟张仲景《伤寒论》尚作薓字。《别录》一名人微，微乃薓字之讹也。其成有阶级，故曰人衔。其草背阳向阴，故曰鬼盖。其在五参，色黄属土，而补脾胃，生阴血，故有黄参、血参之名。得地之精灵，故有土精、地精之名。《广五行记》云︰隋文帝时，上党有人宅后每夜闻人呼声，求之不得。去宅一里许，见人参枝叶异常，掘之入地五尺，得人参，一如人体，四肢毕备，呼声遂绝。观此，则土精之名，尤可证也。《礼斗威仪》云︰下有人参，上有紫气。《春秋运斗枢》云︰摇光星散而为人参。人君废山渎之利，则摇光不明，人参不生。观此，则神草之名，又可证矣。
 【发明】
 弘景曰︰人参为药切要，与甘草同功。
 杲曰︰人参甘温，能补肺中元气，肺气旺则四脏之气皆旺，精自生而形自盛，肺主诸气故也。张仲景云︰病患汗后身热、亡血、脉沉迟者，下痢身凉、脉微、血虚者，并加人参。
@@ -3769,7 +3749,7 @@
 【主治】
 补血滋阴，益精填髓
 【释名】
- 芐（音户）、芑（音起）、地髓（本经）
+芐（音户《别录》）、芑（音起《别录》）、地髓（《本经》）。
 大明曰︰生者以水浸验之。浮者名天黄；半浮半沉者名人黄；沉者名地黄。入药沉者为佳，半沉者次之，浮者不堪。
 时珍曰︰《尔雅》云︰ 芐，地黄。郭璞云︰江东呼为芐。罗愿云︰芐以沉下者为贵，故字从下。
 【发明】
@@ -3797,7 +3777,7 @@
 【主治】
 收敛固涩，益气生津，补肾宁心
 【释名】
-荎藸 （《尔雅》，音知除）
+荎藸 （《尔雅》，音知除）、玄及（《别录》）、会及（《别录》）。
 恭曰︰五味，皮、肉甘、酸，核中辛、苦，都有咸味，此则五味具也。《本经》但云味酸，当以木为五行之先也。
 【发明】
 成无己曰︰肺欲收，急食酸以收之，以酸补之。芍药、五味之酸，以收逆气而安肺。
@@ -3824,7 +3804,7 @@
 【主治】
 润肺下气，化痰止咳
 【释名】
-青菀（《别录》）、紫蒨（《别录》）、返魂草（《纲目》）、夜牵牛
+青菀（《别录》）、紫蒨（《别录》）、返魂草（《纲目》）、夜牵牛（《斗门方》）。
 时珍曰︰其根色紫而柔宛，故名许慎《说文》作茈菀。《斗门方》谓之返魂草。
 【发明】</t>
   </si>
@@ -3842,7 +3822,7 @@
 【主治】
 泻肺平喘，利水消肿
 【释名】
-子名椹。
+子名椹（《集韵》）。
 时珍曰︰徐锴《说文解字》云︰桑，音若，东方自然神木之名，其字象形。桑乃蚕所食，异于东方自然之神木，故加木于桑下而别之。《典术》云︰桑乃箕星之精。
 【发明】
 杲曰︰桑白皮，甘以固元气之不足而补虚，辛以泻肺气之有馀而止嗽。又云︰桑白皮泻肺，然性不纯良，不宜多用。
@@ -3863,8 +3843,9 @@
 【主治】
 养阴生津，润肺清心
 【释名】
-冬（音门），韭（《吴普》）阶前草
-时珍曰︰麦须曰 ，此草根似麦而有须，其叶如韭，凌冬不凋，故谓之麦 冬，及有诸韭、忍冬诸名。俗作门冬，便于字也。可以服食断谷，一名仆垒，一名随脂。
+虋冬（音门《尔雅》），秦名羊韭、齐名爱韭、楚名马韭、越名羊耆（并《别录》）。禹韭（《吴普》）、禹余粮（《别录》）、忍冬（《吴普》）、忍凌（《吴普》）、不死药（《吴普》）、阶前草（《梅尧臣诗》）。
+弘景曰：根似穬麦，故谓之麦门冬。
+时珍曰︰麦须曰虋，此草根似麦而有须，其叶如韭，凌冬不凋，故谓之麦 冬，及有诸韭、忍冬诸名。俗作门冬，便于字也。可以服食断谷，一名仆垒，一名随脂。
 【发明】
 宗奭曰︰麦门冬治肺热之功为多，其味苦，但专泄而不专收，寒多人禁服。治心肺虚热及虚劳。与地黄、阿胶、麻仁，同为润经益血、复脉通心之剂；与五味子、枸杞子，同为生脉之剂。
 元素曰︰麦门冬治肺中伏火、脉气欲绝者，加五味子、人参二味为生脉散，补肺中元气不足。
@@ -3909,7 +3890,7 @@
 清热泻火，生津止渴，消肿排脓
 【释名】
 果裸（音裸）、栝蒌（《纲目》）、天瓜（《别录》）、黄瓜（《别录》）、地蒌（《本经》）、泽姑（《别录》）
-根名白药（《图经》）、天花粉（《图经》）、瑞雪
+根名白药（《图经》）、天花粉（《图经》）、瑞雪（《赵宜真》）。
 时珍曰︰裸，与蓏同。
 许慎云︰木上曰果，地下曰蓏。此物蔓生附木，故得兼名。《诗》云︰果裸之实，亦施于宇，是矣。栝蒌，即果裸二字音转也，亦作𤫱𤬏，后人又转为栝蒌，愈转愈失其真矣。古者瓜姑同音，故有泽姑之名。齐人谓之天瓜，象形也。雷 《炮炙论》，以圆者为栝，长者为蒌，亦出牵强，但分雌雄可也。其根作粉，洁白如雪，故谓之天花粉。苏颂《图经》重出天花粉，谬矣，今削之。
 【发明】
@@ -3934,8 +3915,8 @@
 【主治】
 健脾化湿，和中消暑
 【释名】
-沿篱豆（俗）、蛾眉豆。
-时珍曰︰ ，本作扁，荚形扁也。沿篱，蔓延也。蛾眉，象豆脊白路之形也。
+沿篱豆（俗）、蛾眉豆（《纲目》）。
+时珍曰︰ 藊本作扁，荚形扁也。沿篱，蔓延也。蛾眉，象豆脊白路之形也。
 【发明】
 时珍曰︰硬壳白扁豆，其子充实，白而微黄，其气腥香，其性温平，得乎中和，脾之谷也。入太阴气分，通利三焦，能化清降浊，故专治中宫之病，消暑除湿而解毒也。其软壳及黑鹊色者，其性微凉，但可供食，亦调脾胃。</t>
   </si>
@@ -3959,7 +3940,7 @@
 【主治】
 清热凉血，养阴生津
 【释名】
-芐（音户）、芑（音起）、地髓（本经）
+芐（音户《别录》）、芑（音起《别录》）、地髓（《本经》）。
 大明曰︰生者以水浸验之。浮者名天黄；半浮半沉者名人黄；沉者名地黄。入药沉者为佳，半沉者次之，浮者不堪。
 时珍曰︰《尔雅》云︰ 芐，地黄。郭璞云︰江东呼为芐。罗愿云︰芐以沉下者为贵，故字从下。
 【发明】
@@ -3983,10 +3964,9 @@
 【主治】
 养阴润燥，清肺生津
 【释名】
-冬（音门）、颠勒
-禹锡曰︰按︰《尔雅》云︰蔷蘼， 冬。注云︰门冬也，一名满冬。《抱朴子》云︰一名颠棘，或名地门冬，或名筵门冬。在东岳名淫羊藿；在中岳名天门冬；在西岳名管松；在北岳，名无不愈；在南岳名百部；在京陆山阜名颠棘；在越人，名浣草。虽处处有之，其名不同，其实一也。别有百部草，其根有百许如一，而苗小异，其苗似菝 ，惟可治咳，不中服食，须分别之。
-时珍曰︰草之茂者为 ，俗作门。此草蔓茂，而功同麦门冬，故曰天门冬，或曰天棘。
-《尔雅》云︰髦，颠棘也。因其细叶如髦，有细棘也。颠、天，音相近也。按︰《救荒本草》云︰俗名万岁藤，又名娑萝树。其形与治肺之功颇同百部，故亦名百部也。蔷蘼乃营实苗，而《尔雅》指为 冬，盖古书错
+虋冬（音门《尔雅》）、颠勒（《本经》）、天棘（《纲目》）、万岁藤（《救荒》）。
+禹锡曰︰按︰《尔雅》云︰蔷蘼，虋冬。注云︰门冬也，一名满冬。《抱朴子》云︰一名颠棘，或名地门冬，或名筵门冬。在东岳名淫羊藿；在中岳名天门冬；在西岳名管松；在北岳，名无不愈；在南岳名百部；在京陆山阜名颠棘；在越人，名浣草。虽处处有之，其名不同，其实一也。别有百部草，其根有百许如一，而苗小异，其苗似菝 ，惟可治咳，不中服食，须分别之。
+时珍曰︰草之茂者为 ，俗作门。此草蔓茂，而功同麦门冬，故曰天门冬，或曰天棘。《尔雅》云︰髦，颠棘也。因其细叶如髦，有细棘也。颠、天，音相近也。按︰《救荒本草》云︰俗名万岁藤，又名娑萝树。其形与治肺之功颇同百部，故亦名百部也。蔷蘼乃营实苗，而《尔雅》指为虋冬，盖古书错简也。
 【发明】
 权曰︰天门冬冷而能补，患人体虚而热者，宜加用之。和地黄为使，服之耐老头不白。
 宗奭曰︰治肺热之功为多。其味苦，专泄而不专收，寒多人禁服之。
@@ -4038,7 +4018,7 @@
 【主治】
 活血祛瘀，通经止痛，清心除烦，凉血消痈
 【释名】
-赤参（《别录》）、山参（《日华》）、 蝉草（《本经》）、木羊乳（《吴普》）、逐马（弘景）、奔马草。
+赤参（《别录》）、山参（《日华》）、 蝉草（《本经》）、木羊乳（《吴普》）、逐马（弘景）、奔马草（《四声》）。
 时珍曰︰五参五色配五脏。故人参入脾，曰黄参；沙参入肺，曰白参；玄参入肾，曰黑参；牡蒙入肝，曰紫参；丹参入心，曰赤参。其苦参，则右肾命门之药也。古人舍紫参而称苦参，未达此义尔。炳曰︰丹参治风软脚，可逐奔马，故名奔马草。曾用，实有效。
 【发明】
 时珍曰︰丹参色赤味苦，气平而降，阴中之阳也。入手少阴、厥阴之经，心与包络血分药也。按︰《妇人明理论》云︰四物汤治妇人病，不问产前、产后，经水多少，皆可通用。惟一味丹参散，主治与之相同。盖丹参能破宿血，补新血，安生胎，落死胎，止崩中带下，调经脉，其功大类当归、地黄、芎 、芍药故也。</t>
@@ -4083,7 +4063,7 @@
 【主治】
 养心补肝，宁心安神，敛汗生津
 【释名】
-（《尔雅》）、山枣。
+樲（《尔雅》）、山枣（《弘景》）。
 【发明】
 恭曰︰《本经》用实疗不得眠，不言用仁。今方皆用仁。补中益肝，坚筋骨，助阴气，皆酸枣仁之功也。
 宗奭曰︰酸枣，《经》不言用仁，而今天下皆用之。
@@ -4104,7 +4084,7 @@
 【主治】
 养心安神，润肠通便，止汗
 【释名】
-（音菊）、侧柏。
+椈（音菊《尔雅》）、侧柏（《尔雅翼》）。
 李时珍曰︰按︰魏子才《六书精蕴》云︰万木皆向阳，而柏独西指，盖阴木而有贞德者，故字从白。白者，西方也。陆佃《埤雅》云︰柏之指西，犹针之指南也。柏有数种，入药惟取叶扁而侧生者，故曰侧柏。
 寇宗奭曰︰予官陕西，登高望柏，千万株皆一一西指。盖此木至坚，不畏霜雪，得木之正气，他木不及。所以受金之正气所制，一一西指也。
 【发明】
@@ -4172,7 +4152,7 @@
 【主治】
 利尿通淋，清心除烦，通经下乳
 【释名】
-木通（士良）、附支（《本经》）
+木通（士良）、附支（《本经》）、丁翁（《吴普》）、万年藤（甄权），子名燕覆（《唐本》）。
 时珍曰︰有细细孔，两头皆通，故名通草，即今所谓木通也。今之通草，乃古之通脱木也。宋本草混注为一，名实相乱，今分出之。
 【发明】
 杲曰︰本草十剂︰通可去滞，通草、防己之属是也。夫防己大苦寒，能泻血中湿热之滞，又通大便。通草甘淡，能助西方秋气下降，利小便，专泻气滞也。肺受热邪，津液气化之原绝，则寒水断流，膀胱受湿热，癃闭约缩，小便不通，宜此治之。其症胸中烦热，口燥舌干，咽干，大渴引饮，小便淋沥，或闭塞不通，胫酸脚热，并宜通草主之。凡气味与之同者，茯苓、泽泻、灯草、猪苓、琥珀、瞿麦、车前子之类，皆可以渗湿利小便，泄其滞气也。又曰︰木通下行，泄小肠火，利小便，与琥珀同功，无他药可比。
@@ -4195,8 +4175,7 @@
 【主治】
 清热化痰，除烦止呕
 【释名】
-时珍曰︰竹字象形。许慎《说文》云︰“竹，冬生草也”。
-故字从倒草。戴凯之《竹谱》云︰植物之中，有名曰竹。不刚不柔，非草非木。小异实虚，大同节目。
+时珍曰︰竹字象形。许慎《说文》云︰“竹，冬生草也”。故字从倒草。戴凯之《竹谱》云︰植物之中，有名曰竹。不刚不柔，非草非木。小异实虚，大同节目。
 【发明】</t>
   </si>
   <si>
@@ -4213,7 +4192,7 @@
 【主治】
 开窍豁痰，醒神益智，化湿开胃
 【释名】
-昌阳（《本经》）、尧韭（普）、水剑草。
+昌阳（《本经》）、尧韭（普）、水剑草（《纲目》）。
 时珍曰︰菖蒲，乃蒲类之昌盛者，故曰菖蒲。又《吕氏春秋》云︰冬至后五十七日，菖始生。菖者百草之先生者，于是始耕。则菖蒲、昌阳又取此义也。《典术》云︰尧时天降精于庭为韭，感百阴之气为菖蒲。故曰尧韭。方士隐为水剑，因叶形也。
 【发明】
 颂曰︰古方有单服菖蒲法。蜀人治心腹冷气 痛者，取一、二寸捶碎，同吴茱萸煎汤饮之。亦将随行，卒患心痛，嚼一、二寸，热汤或酒送下，亦效。
@@ -4238,7 +4217,7 @@
 【主治】
 清热燥湿，泻火解毒
 【释名】
-王连（《本经》）、支连（《药性》）
+王连（《本经》）、支连（《药性》）。
 时珍曰：其根连珠而色黄，故名。
 【发明】
 元素曰：黄连性寒味苦，气味俱浓，可升可降，阴中阳也，入手少阴经。其用有六：泻心脏火，一也；去中焦湿热，二也；诸疮必用，三也；去风湿，四也；赤眼暴发，五也；止中部见血，六也。张仲景治九种心下痞，五等泻心汤，皆用之。
@@ -4270,7 +4249,7 @@
 【主治】
 解表散寒，祛风止痛，通窍，温肺化饮
 【释名】
-小辛（《本经》）、少辛。
+小辛（《本经》）、少辛（《山海经》）。
 颂曰：华州真细辛，根细而味极辛，故名之曰细辛。
 时珍曰：小辛、少辛，皆此义也。按《山海经》云，浮戏之山多少辛。《管子》云，五沃之土，群药生少辛，是矣。
 【发明】
@@ -4323,7 +4302,7 @@
 【主治】
 疏肝解郁，理气宽中，调经止痛
 【释名】
-雀头香（《唐本》）、草附子（《图经》）、水香棱（《图经》）、水巴戟（《图经》）、水莎（《图经》）、侯莎（《尔雅》）、莎结（《图经》）、夫须（《别录》）、续根草（《图经》）、地毛（《广雅》）
+雀头香（《唐本》）、草附子（《图经》）、水香棱（《图经》）、水巴戟（《图经》）、水莎（《图经》）、侯莎（《尔雅》）、莎结（《图经》）、夫须（《别录》）、续根草（《图经》）、地毛（《广雅》）。
 时珍曰︰《别录》止云莎草，不言用苗用根。后世皆用其根，名香附子，而不知莎草之名也。其草可为笠及雨衣，疏而不沾，故字从草从沙。亦作蓑字，因其为衣垂 ，如孝子衰衣之状，故又从苔乃笠名，贱夫所须也。其根相附连续而生，可以合香，故谓之香附子。上古谓之雀头香。 按《江表传》云︰魏文帝遣使于吴求雀头香，即此。其叶似三棱及巴戟，而生下湿地，故有水三棱、水巴戟之名。俗人呼为雷公头。《金光明经》谓之月萃哆。《记事珠》谓之抱灵居士。
 【发明】
 好古曰︰香附治膀胱两胁气妨，心忪少气，是能益气，乃血中之气药也。本草不言治崩漏，而方中用治崩漏，是能益气而止血也。又能逐去瘀血，是推陈也。正如巴豆治大便不通而又止泄泻同意。又云︰香附阳中之阴，血中之气药，凡气郁血气必用之。炒黑能止血治崩漏，此妇人之仙药也。多服亦能走气。
@@ -4344,7 +4323,7 @@
 【主治】
 清热燥湿，泻肝胆火
 【释名】
-陵游（《本经》）
+陵游（《本经》）。
 志曰：叶如龙葵，味苦如胆，因以为名。
 【发明】
 元素曰：龙胆味苦性寒，气味俱浓，沉而降，阴也，足厥阴、少阳经气分药也。其用有四：除下部风湿，一也；及湿热，二也；脐下至足肿痛，三也；寒湿脚气，四也。 下行之功与防己同，酒浸则能上行，外行以柴胡为主，龙胆为使治眼中疾必用之药。好古曰：益肝胆之气而泄火。
@@ -4364,7 +4343,7 @@
 【主治】
 利小便，清湿热，泄肾浊
 【释名】
-水泻（《本经》）、鹄泻（《本经》）、及泻（《别录》）、蕍（音俞）、芒芋（《本经》）、禹孙
+水泻（《本经》）、鹄泻（《本经》）、及泻（《别录》）、蕍（音俞）、芒芋（《本经》）、禹孙（《侯氏药谱》）。
 时珍曰︰去水曰泻，如泽水之泻也。禹能治水，故曰禹孙。馀未详。
 【发明】
 颂曰︰《素问》治酒风身热汗出，用泽泻、术；《深师方》治支饮，亦用泽泻、术，但煮法小别尔。张仲景治杂病，心下有支饮苦冒，有泽泻汤，治伤寒有大小泽泻汤、五苓散辈，皆用泽泻，行利停水，为最要药。元素曰︰泽泻乃除湿之圣药，入肾经，治小便淋沥，去阴间汗。无此疾服之，令人目
@@ -4390,7 +4369,7 @@
 【主治】
 清热利尿，渗湿止泻，明目，清肺化痰
 【释名】
-当道（《本经》）、芣苡（音浮以）、马舄（音昔）、牛遗（并别录）、牛舌（《诗疏》）、车轮菜（《救荒》）、地衣（纲目）、虾蟆衣（别录） 
+当道（《本经》）、芣苡（音浮以）、马舄（音昔）、牛遗（并《别录》）、牛舌（《诗疏》）、车轮菜（《救荒》）、地衣（《纲目》）、蛤蟆衣（《别录》）。
 时珍曰︰按《尔雅》云︰芣苡，马舄。马舄，车前。陆玑《诗疏》云︰此草牛马迹中，故有车前、当道、马舄、牛遗之名。舄，足履也。幽州人谓之牛舌草。虾蟆喜藏伏于下，故江东称为虾蟆衣。又《韩诗外传》言︰直曰车前；瞿曰芣苡，恐亦强说也生于两旁者。
 【发明】
 弘景曰︰车前子性冷利，仙经亦服饵之，云令人身轻，能跳越岸谷，不老长生也。
@@ -4412,7 +4391,7 @@
 【主治】
 散寒止痛，理气和胃
 【释名】
-茴香，八角珠
+茴香（《图经》），八月珠（《侯氏药谱》）。
 颂曰： 香，北人呼为茴香，声相近也。
 思邈曰：煮臭肉，下少许，即无臭气，臭酱入末亦香，故曰茴香。
 时珍曰：俚俗多怀之衿衽咀嚼，恐 香之名，或以此也。
@@ -4438,7 +4417,7 @@
 【主治】
 滋补肝肾，益精明目
 【释名】
-枸 （《尔雅》。音计。《本经》作枸忌）、枸棘（《衍义》）、苦杞（《诗疏》）、红菜头（《图经》）、天精（《抱朴》）、地骨（《本经》）、地辅（《本经》）、地仙（《日华》）、却暑（《别录》）
+枸 （《尔雅》。音计。《本经》作枸忌）、枸棘（《衍义》）、苦杞（《诗疏》）、红菜头（《图经》）、天精（《抱朴》）、地骨（《本经》）、地辅（《本经》）、地仙（《日华》）、却暑（《别录》）。
 时珍曰︰枸、杞二树名。此物棘如枸之刺，茎如杞之条，故兼名之。道书言︰千载枸杞，其形如犬，故得枸名，未审然否？
 颂曰︰仙人杖有三种︰一是枸杞；一是菜类，叶似苦苣；一是枯死竹竿之色黑者也。
 【发明】
@@ -4463,9 +4442,8 @@
 【主治】
 行气止痛，温肾散寒
 【释名】
-旁其（《拾遗》）
-时珍曰︰乌以色名。其叶状似 鲫鱼，故俗呼为 树。《拾遗》作旁其，方音讹也。
-南人亦呼为矮樟，其气似樟也。
+旁其（《拾遗》）、鳑魮（《纲目》）、矮樟（《纲目》）。
+时珍曰︰乌以色名。其叶状似 鲫鱼，故俗呼为 树。《拾遗》作旁其，方音讹也。南人亦呼为矮樟，其气似樟也。
 【发明】
 宗奭曰︰乌药性和，来气少，走泄多，但不甚刚猛。与沉香同磨作汤点服，治胸腹冷气甚稳当。
 时珍曰︰乌药辛温香窜，能散诸气。故《惠民和剂局方》治中风中气诸证，用乌药顺气散者，先疏其气，气顺则风散也。严用和《济生方》治七情郁结，上气喘急，用四磨汤者，降中兼升，泻中带补也。其方以人参、乌药、沉香、槟榔各磨浓汁七分，合煎，细细咽之。
@@ -4488,7 +4466,7 @@
 【主治】
 行气止痛，温中止呕，纳气平喘
 【释名】
-沉水香（《纲目》）、蜜香
+沉水香（《纲目》）、蜜香（《南越志》）。
 时珍曰︰木之心节置水则沉，故名沉水，亦曰水沉。半沉者为栈香，不沉者为黄熟香。
 《南越志》言︰交州人称为蜜香，谓其气如蜜脾也。梵书名阿迦香。
 【发明】</t>
@@ -4507,7 +4485,7 @@
 【主治】
 疏肝泄热，行气止痛，杀虫
 【释名】
-苦楝（《图经》），实名金铃子
+苦楝（《图经》），实名金铃子（《侯氏药谱》）。
 时珍曰︰按︰罗愿《尔雅翼》云︰楝叶可以练物，故谓之楝。其子如小铃，熟则黄色。名金铃，象形也。
 【发明】
 元素曰︰热厥暴痛，非此不能除。
@@ -4520,7 +4498,7 @@
     <t>钩藤</t>
   </si>
   <si>
-    <t>钩藤
+    <t>钩藤（钓藤）
 【气味】
 味甘，性凉
 【毒性】
@@ -4549,7 +4527,7 @@
 【主治】
 健脾益气，燥湿利水，止汗，安胎
 【释名】
-山蓟（《本经》）、杨桴（音孚）、桴蓟（《尔雅》）、马蓟（《纲目》）、山姜（《别录》）、山连（《别录》）、吃力伽（《日华》）
+山蓟（《本经》）、杨桴（音孚）、桴蓟（《尔雅》）、马蓟（《纲目》）、山姜（《别录》）、山连（《别录》）、吃力伽（《日华》）。
 时珍曰︰按《六书本义》，术字篆文，象其根干枝叶之形。《吴普本草》一名山芥，一名天蓟。因其叶似蓟，而味似姜、芥也。西域谓之吃力伽，故《外台秘要》有吃力伽散。扬州之域多种白术，其状如桴，故有杨桴及桴蓟之名，今人谓之吴术是也。桴乃鼓槌之名。古方二术通用。后人始有苍、白之分，详见下。
 【发明】
 好古曰︰本草无苍、白术之名。近世多用白术，治皮间风，止汗消痞，补胃和发，有汗则止，与黄耆同功。
@@ -4595,9 +4573,8 @@
 【主治】
 芳香化湿，和中止呕，发表解暑
 【释名】
-兜娄婆香
-时珍曰︰豆叶曰藿，其叶似之，故名。《楞严经》云︰坛前以兜娄婆香煎水洗浴。即此。
-《法华经》谓之多摩罗跋香，《金光明经》谓之钵怛罗香，皆兜娄二字梵言也。涅 又谓之迦算香。
+兜娄婆香（《楞严经》）。
+时珍曰︰豆叶曰藿，其叶似之，故名。《楞严经》云︰坛前以兜娄婆香煎水洗浴。即此。《法华经》谓之多摩罗跋香，《金光明经》谓之钵怛罗香，皆兜娄二字梵言也。《涅槃》又谓之迦算香。
 【发明】
 杲曰︰芳香之气助脾胃，故藿香能止呕逆，进饮食。
 好古曰︰手、足太阴之药。 故入顺气乌药散，则补肺；入黄 、四君子汤，则补脾也。</t>
@@ -4616,7 +4593,7 @@
 【主治】
 燥湿消痰，下气除满
 【释名】
-烈朴（《日华》）、赤朴（《别录》）、浓皮（同）、重皮（《广雅》），树名榛（《别录》），子名逐折（《别录》）
+烈朴（《日华》）、赤朴（《别录》）、浓皮（同）、重皮（《广雅》），树名榛（《别录》），子名逐折（《别录》）。
 时珍曰︰其木质朴而皮浓，味辛烈而色紫赤，故有浓朴、烈、赤诸名。
 颂曰︰《广雅》谓之重皮，方书或作浓皮也。
 【发明】
@@ -4640,10 +4617,8 @@
 【主治】
 行气宽中，行水消肿
 【释名】
-宾门（李当之《药对》）、仁频（《上林赋》）、洗瘴丹（《候氏药谱》）
-时珍曰︰宾与郎皆贵客之称。稽含《南方草木状》言︰交广人凡贵胜族客，必先呈此果。
-若邂逅不设，用相嫌恨。则槟榔名义，盖取于此。雷《炮炙论》谓尖者为槟，圆者为榔，亦似强说。又颜师古注《上林赋》云︰仁频即槟榔也。
-诜曰︰闽中呼为橄榄子。
+宾门（李当之《药对》）、仁频（《上林赋》）、洗瘴丹（《候氏药谱》）。
+时珍曰︰宾与郎皆贵客之称。稽含《南方草木状》言︰交广人凡贵胜族客，必先呈此果。若邂逅不设，用相嫌恨。则槟榔名义，盖取于此。雷《炮炙论》谓尖者为槟，圆者为榔，亦似强说。又颜师古注《上林赋》云︰仁频即槟榔也。诜曰︰闽中呼为橄榄子。
 【发明】</t>
   </si>
   <si>
@@ -4663,7 +4638,7 @@
 【主治】
 解表散寒，祛风止痛，宣通鼻窍，燥湿止带，消肿排脓
 【释名】
-白 （音止，又昌海切）、（许骄切）、莞（音官），叶名 麻（音力）、药。
+白茝（音止，又昌海切《别录》）、芳香（《本经》）、泽芬（《别录》）、苻蓠（《别录》）、䖀（许骄切《吴普》）、莞（音官《别录》）；叶名蒚麻（音力《别录》）、药（音约《图经》）。
 时珍曰︰徐锴云︰初生根干为芷，则白芷之义取乎此也。
 王安石《字说》云︰ 香可以养鼻，又可养体，故 字从臣。臣音怡，养也。
 许慎《说文》云︰晋谓之 ，齐谓之 ，楚谓之蓠，又谓之药。生于下泽，芬芳与兰同德，故骚人以兰 为咏，而本草有芬香、泽芬之名，古人谓之香白芷云。
@@ -4688,10 +4663,9 @@
 【主治】
 益气养阴，补脾肺肾，固精止带
 【释名】
-薯藇（音诸预）、土薯（音除）、山薯（《图经》）、山芋（《吴普》）、山药（《衍义》）、玉延
+藷藇（音诸预《山海经》）、土藷（音除《别录》）、山藷（《图经》）、山芋（《吴普》）、山药（《衍义》）、玉延（《吴普》）。
 吴普曰︰薯蓣，一名薯薯，一名儿草，一名修脆。齐、鲁名山芋，郑、越名土薯，秦、楚名玉延。
-颂曰︰江、闽人单呼为薯（音若殊及韶），亦曰山薯。
-《山海经》云︰景山北望少泽，其草多薯藇（音同薯蓣）。则是一种，但字（或音殊，或音诸）不一，或语有轻重，或相传之讹耳。
+颂曰︰江、闽人单呼为薯（音若殊及韶），亦曰山薯。《山海经》云︰景山北望少泽，其草多薯藇（音同薯蓣）。则是一种，但字（或音殊，或音诸）不一，或语有轻重，或相传之讹耳。
 宗奭曰︰薯蓣，因唐代宗名预，避讳改为薯药；又因宋英宗讳署，改为山药。尽失当日本名。恐岁久以山药为别物，故详著之。
 【发明】
 权曰︰凡患人体虚羸者，宜加而用之。
@@ -4714,9 +4688,7 @@
 补脾止泻，止带，益肾涩精，养心安神
 【释名】
 其根藕（《尔雅》），其实莲（《尔雅》），其茎叶荷（《说文》）。
-韩保升曰︰藕生水中，其叶名荷。按︰《尔雅》云︰荷，芙蕖。其茎茄，其叶蕸，其本蔤，其华菡萏，其实莲，其根藕，其中菂，菂中薏。邢昺注云︰芙蕖，总名也，别名芙蓉，江东人呼为荷。菡萏，莲花也。菂，莲实也。薏，菂中青心也。
-郭璞注云︰蔤，乃茎下白蒻在泥中者。莲，乃房也；菂，乃子也；薏，乃中心苦薏也。江东人呼荷花为芙蓉，北人以藕为荷，亦以莲为荷，蜀人以藕为茄，此皆习俗传误也。
-陆机《诗疏》云︰其茎为荷。其花未发为菡萏，已发为芙蕖。其实莲，莲之皮青里白。其子菂，菂为苦薏也。
+韩保升曰︰藕生水中，其叶名荷。按︰《尔雅》云︰荷，芙蕖。其茎茄，其叶蕸，其本蔤，其华菡萏，其实莲，其根藕，其中菂，菂中薏。邢昺注云︰芙蕖，总名也，别名芙蓉，江东人呼为荷。菡萏，莲花也。菂，莲实也。薏，菂中青心也。郭璞注云︰蔤，乃茎下白蒻在泥中者。莲，乃房也；菂，乃子也；薏，乃中心苦薏也。江东人呼荷花为芙蓉，北人以藕为荷，亦以莲为荷，蜀人以藕为茄，此皆习俗传误也。陆机《诗疏》云︰其茎为荷。其花未发为菡萏，已发为芙蕖。其实莲，莲之皮青里白。其子菂，菂为苦薏也。
 时珍曰︰《尔雅》以荷为根名，韩氏以荷为叶名，陆机以荷为茎名。按︰茎乃负叶者也，有负荷之义，当从陆说。蔤乃嫩蒻，如竹之行鞭者。节生二茎，一为叶，一为花，尽处乃生藕，为花、叶、根、实之本。显仁藏用，功成不居，可谓退藏于密矣，故谓之蔤。花叶常偶生，不偶不生，故根曰藕。或云藕善耕泥，故字从耦，耦者耕也。茄音加，加于蔤上也。蕸音遐，远于密也。菡萏，函合未发之意。芙蓉，敷布容艳之意。莲者连也，花实相连而出也。菂者的也，子在房中点点如的也。的乃凡物点注之名。薏，犹意也，含苦在内也。古诗云︰食子心无弃，苦心生意存是矣。
 【发明】
 时珍曰︰莲产于淤泥而不为泥染；居于水中而不为水没。根茎花实，凡品难同；清净济用，群美兼得。自 而节节生茎，生叶，生花，生藕；由菡萏而生蕊，生莲，生 ，生薏。其莲 则始而黄，黄而青，青而绿，绿而黑，中含白肉，内隐青心。石莲坚刚，可历永久。薏藏生意，藕复萌芽，展转生生，造化不息。故释氏用为引譬，妙理具存；医家取为服食，百病可却。盖莲之味甘气温而性啬，禀清芳之气，得稼穑之味，乃脾之果也。脾者，黄宫，所以交媾水、火，会合木、金者也。土为元气之母，母气既和，津液相成，神乃自生，久视耐老，此其权舆也。昔人治心肾不交，劳伤白浊，有清心莲子饮；补心肾，益精血，有瑞莲丸，皆得此理。
@@ -4783,7 +4755,7 @@
 【主治】
 补益肝肾，收涩固脱
 【释名】
-蜀酸枣（《本经》）、肉枣（《纲目》）、矢（《吴普》）
+蜀酸枣（《本经》）、肉枣（《纲目》）、鬾实（《别录》）、鸡足（《吴普》）、鼠矢（《吴普》）。
 宗奭曰︰山茱萸与吴茱萸甚不相类，治疗大不同，未审何缘命此名也？
 时珍曰︰《本经》一名蜀酸枣，今人呼为肉枣，皆象形也。
 【发明】
@@ -4803,7 +4775,7 @@
 【主治】
 清热凉血，活血化瘀，退虚热
 【释名】
-鼠姑（《本经》）、鹿韭（《本经》）、百两金（《唐本》）、木芍药（《纲目》）、花王
+鼠姑（《本经》）、鹿韭（《本经》）、百两金（《唐本》）、木芍药（《纲目》）、花王（《洛阳名园记》）。
 时珍曰︰牡丹，以色丹者为上，虽结子而根上生苗，故谓之牡丹。唐人谓之木芍药，以其花似芍药，而宿干似木也。群花品中，以牡丹第一，芍药第二，故世谓牡丹为花王，芍药为花相。欧阳修《花谱》所载，凡三十馀种。其名或以地，或以人，或以色，或以异，详见本书。
 【发明】
 元素曰︰牡丹乃天地之精，为群花之首。叶为阳，发生也；花为阴，成实也。 丹者赤色，火也。故能泻阴胞中之火。四物东加之，治妇人骨蒸。又曰︰牡丹皮入手厥阴、足少阴，故治无汗之骨蒸；地骨皮入足少阴、手少阳，故治有汗之骨蒸。神不足者手少阴，志不足者足少阴，故仲景肾气丸用之，治神志不足也。又能治肠胃积血，及吐血、衄血，必用之药，故犀角地黄汤用之。
@@ -4824,7 +4796,7 @@
 【主治】
 回阳救逆，补火助阳，散寒止痛
 【释名】
-其母名乌头。
+其母名乌头（《本经》）。
 时珍曰︰初种为乌头，象乌之头也。附乌头而生者为附子，如子附母也。乌头如芋魁，附子如芋子，盖一物也。别有草乌头、白附子，故俗呼此为黑附子，川乌头以别之。诸家不分乌头有川、草两种，皆混杂注解，今悉正之。
 【发明】
 宗奭曰︰补虚寒须用附子，风家即多用天雄，大略如此。其乌头、乌喙、附子，则量其材而用之。时珍曰︰按王氏《究原方》云︰附子性重滞，温脾逐寒。川乌头性轻疏，温脾去风。若是寒疾即用附子；风疾即用川乌头。一云︰凡人中风，不可先用风药及乌附。 若先用气药，后用乌附乃宜也。又凡用乌、附药，并宜冷服者，热因寒用也。盖阴寒在下，虚阳上浮。治之以寒，则阴气益甚而病增；治之以热，则拒格而不纳。热药冷冻饮料，下嗌之后，冷体既消，热性便发，而病气随愈。不违其情，而致大益，此反治之妙也。昔张仲景治寒疝 内结，用蜜煎乌头。《近效方》治喉痹，用蜜炙附子，含之咽汁。朱丹溪治疝气，用乌头、栀子。并热因寒用也。李东垣治冯翰林侄阴盛格阳伤寒，面赤目赤，烦渴引饮，脉来七、八至，但按之则散。用姜附东加人参，投半斤服之，得汗而愈。此则神圣之妙也。 吴绶曰︰附子乃阴证要药。凡伤寒传变三阴，及中寒夹阴，虽身大热而脉沉者，必用之。或厥冷腹痛，脉沉细，甚则唇青囊缩者，急须用之，有退阴回阳之力，起死回生之功。近 世阴证伤寒，往往疑似，不敢用附子，直待阴极阳竭而用之，已迟矣。且夹阴伤寒，内外皆阴，阳气顿衰。必须急用人参，健脉以益其原；佐以附子，温经散寒。舍此不用，将何以救 之？
@@ -4869,11 +4841,9 @@
 【主治】
 行气止痛，健脾消食
 【释名】
-蜜香（《别录》）、青木香（弘景）
-时珍曰︰木香，草类也。本名蜜香，因其香气如蜜也。缘沉香中有蜜香，遂讹此为木香尔。昔人谓之青木香。后人因呼马兜铃根为青木香，乃呼此为南木香、广木香以别之。今人又呼一种蔷薇为木香，愈乱真矣。
-《三洞珠囊》云︰五香者，即青木香也。一株五根，一茎五枝，一枝五叶，叶间五节，故名五香，烧之能上彻九天也。古方治痈疽有五香连翘汤，内用青木香。《古乐府》云︰氍毹 五木香，皆指此也。
-颂曰︰《修养书》云︰正月一日取五木煮汤以浴，令人至老须发黑。徐锴注云︰道家谓青木香为五香，亦云五木，多以为浴是矣。
-《金光明经》谓之矩琵佗香。
+蜜香（《别录》）、青木香（弘景）、五木香（《图经》）、南木香（《纲目》）。
+时珍曰︰木香，草类也。本名蜜香，因其香气如蜜也。缘沉香中有蜜香，遂讹此为木香尔。昔人谓之青木香。后人因呼马兜铃根为青木香，乃呼此为南木香、广木香以别之。今人又呼一种蔷薇为木香，愈乱真矣。《三洞珠囊》云︰五香者，即青木香也。一株五根，一茎五枝，一枝五叶，叶间五节，故名五香，烧之能上彻九天也。古方治痈疽有五香连翘汤，内用青木香。《古乐府》云︰氍毹 五木香，皆指此也。
+颂曰︰《修养书》云︰正月一日取五木煮汤以浴，令人至老须发黑。徐锴注云︰道家谓青木香为五香，亦云五木，多以为浴是矣。《金光明经》谓之矩琵佗香。
 【发明】
 弘景曰︰青木香，大秦国人以疗毒肿、消恶气有验。今惟制蛀虫丸用之。常以煮汁沐浴大佳。
 宗奭曰︰木香专泄决胸腹间滞塞冷气，他则次之。得橘皮、肉豆蔻、生姜相佐使绝佳，效尤速。
@@ -4927,7 +4897,7 @@
 【主治】
 滋阴养血，润燥息风，清心安神，养胃止渴
 【释名】
-烛夜
+烛夜（《古今志》）。
 时珍曰︰按徐铉云︰“鸡者稽也，能稽时也。”
 《广志》云︰“大曰蜀，小曰荆，雏曰𪇗 。
 《梵书》曰︰“鸡曰鸠七咤 。”
@@ -4951,7 +4921,7 @@
 【主治】
 补肾固精，养肝明目
 【释名】
-茨（《尔雅》）、旁通（《本经》）、屈人（《本经》）、止行（《本经》）、豺羽（《本经》）、升推。
+茨（《尔雅》）、旁通（《本经》）、屈人（《本经》）、止行（《本经》）、豺羽（《本经》）、升推（《本经》）。
 弘景曰︰多生道上及墙上，叶布地，子有刺，状如菱而小。长安最饶，人行多著木履。今军家乃铸铁作之，以布敌路，名铁蒺藜。
 《易》云︰据于蒺藜，言其凶伤；
 《诗》云︰墙有茨，不可扫也，以刺梗秽。方用甚稀。
@@ -4974,11 +4944,10 @@
 【主治】
 补肾固精，养肝明目
 【释名】
-鸡头（《本经》）、雁喙（同）、雁头（《古今注》）、鸿头（韩退之）、鸡雍（《庄子》）、卯菱（《管子》）、 子（音唯）、水流黄。
+鸡头（《本经》）、雁喙（同）、雁头（《古今注》）、鸿头（韩退之）、鸡雍（《庄子》）、卯菱（《管子》）、 子（音唯《弘景》）、水流黄（《谈圃》）。
 弘景曰︰此即今 子也。茎上花似鸡冠，故名鸡头。
 颂曰︰其苞形类鸡、雁头，故有诸名。
-时珍曰︰芡可济俭歉，故谓之芡。鸡雍见《庄子‧徐无鬼篇》。卯菱见《管子‧五行篇》。
-扬雄《方言》云︰南楚谓之鸡头，幽燕谓之雁头，徐、青、淮、泗谓之芡子。其茎谓之 ，亦曰 。郑樵《通志》以钩 为芡，误矣。钩 ，陆生草也，其茎可食。水流黄见下。
+时珍曰︰芡可济俭歉，故谓之芡。鸡雍见《庄子‧徐无鬼篇》。卯菱见《管子‧五行篇》。扬雄《方言》云︰南楚谓之鸡头，幽燕谓之雁头，徐、青、淮、泗谓之芡子。其茎谓之 ，亦曰 。郑樵《通志》以钩 为芡，误矣。钩 ，陆生草也，其茎可食。水流黄见下。
 【发明】
 弘景曰︰《仙方》取此合莲实饵之，甚益人。
 恭曰︰作粉食，益人胜于菱也。
@@ -5057,8 +5026,7 @@
 【释名】
 其根藕（《尔雅》），其实莲（《尔雅》），其茎叶荷（《说文》）。
 韩保升曰︰藕生水中，其叶名荷。按︰《尔雅》云︰荷，芙蕖。其茎茄，其叶蕸，其本蔤，其华菡萏，其实莲，其根藕，其中菂，菂中薏。邢昺注云︰芙蕖，总名也，别名芙蓉，江东人呼为荷。菡萏，莲花也。菂，莲实也。薏，菂中青心也。
-郭璞注云︰蔤，乃茎下白蒻在泥中者。莲，乃房也；菂，乃子也；薏，乃中心苦薏也。江东人呼荷花为芙蓉，北人以藕为荷，亦以莲为荷，蜀人以藕为茄，此皆习俗传误也。
-陆机《诗疏》云︰其茎为荷。其花未发为菡萏，已发为芙蕖。其实莲，莲之皮青里白。其子菂，菂为苦薏也。
+郭璞注云︰蔤，乃茎下白蒻在泥中者。莲，乃房也；菂，乃子也；薏，乃中心苦薏也。江东人呼荷花为芙蓉，北人以藕为荷，亦以莲为荷，蜀人以藕为茄，此皆习俗传误也。陆机《诗疏》云︰其茎为荷。其花未发为菡萏，已发为芙蕖。其实莲，莲之皮青里白。其子菂，菂为苦薏也。
 时珍曰︰《尔雅》以荷为根名，韩氏以荷为叶名，陆机以荷为茎名。按︰茎乃负叶者也，有负荷之义，当从陆说。蔤乃嫩蒻，如竹之行鞭者。节生二茎，一为叶，一为花，尽处乃生藕，为花、叶、根、实之本。显仁藏用，功成不居，可谓退藏于密矣，故谓之蔤。花叶常偶生，不偶不生，故根曰藕。或云藕善耕泥，故字从耦，耦者耕也。茄音加，加于蔤上也。蕸音遐，远于密也。菡萏，函合未发之意。芙蓉，敷布容艳之意。莲者连也，花实相连而出也。菂者的也，子在房中点点如的也。的乃凡物点注之名。薏，犹意也，含苦在内也。古诗云︰食子心无弃，苦心生意存是矣。
 【发明】
 时珍曰︰莲须本草不收，而《三因》诸方、固真丸、巨胜子丸各补益方中，往往用之。其功大抵与莲子同也。</t>
@@ -5129,7 +5097,7 @@
 【主治】
 补肾益精，养肝明目，止泻，安胎
 【释名】
-菟缕（《别录》）、菟蔂（《别录》）、菟芦（《本经》）、菟丘（《广雅》）、赤网（《别录》）、玉女（《尔雅》）、唐蒙（《尔雅》）、火焰草（《纲目》）、野狐丝（《纲目》）、金线草。
+菟缕（《别录》）、菟蔂（《别录》）、菟芦（《本经》）、菟丘（《广雅》）、赤网（《别录》）、玉女（《尔雅》）、唐蒙（《尔雅》）、火焰草（《纲目》）、野狐丝（《纲目》）、金线草（《纲目》）。
 禹锡曰︰按《吕氏春秋》云︰或谓菟丝无根也。其根不属地，茯苓是也。《抱朴子》云︰菟丝之草，下有伏菟之根。无此菟，则丝不得生于上，然实不属也。伏菟抽则菟丝死。又云︰菟丝初生之根，其形似兔握，故割其血以和丹服，立能变化。则菟丝之名因此也。
 弘景曰︰旧言下有茯苓，上有菟丝，不必尔也。
 颂曰︰《抱朴》所说今未见，岂别一类乎？孙炎释《尔雅》云︰唐也，蒙也，女萝也，菟丝也，一物四名，而本草唐蒙为一名。《诗》云︰茑与女萝。毛苌云︰女萝，菟丝也。而本草菟丝无女萝之名，惟松萝一名女萝。岂二物皆是寄生同名，而本草脱漏乎？
@@ -5335,7 +5303,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -5397,7 +5365,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5582,7 +5550,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -5873,13 +5841,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:E44"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="37.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.46484375" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.75" style="3" customWidth="1"/>
+    <col min="3" max="3" width="26.59765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.73046875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.4" customHeight="1">
@@ -6633,40 +6601,40 @@
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AC45"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="19" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.875" style="38" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="4.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="4.5" style="33" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="4.5" style="39" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.25" style="39" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.875" style="39" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.46484375" style="38" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.86328125" style="38" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="4.46484375" style="38" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="4.46484375" style="33" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="4.46484375" style="39" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.265625" style="39" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.86328125" style="39" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="4" style="40" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.875" style="40" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.25" style="40" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.86328125" style="40" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.265625" style="40" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="4" style="40" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.875" style="38" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="4.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.125" style="41" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.46484375" style="38" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.86328125" style="38" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="4.46484375" style="38" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.1328125" style="41" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="5" style="41" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.875" style="41" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.125" style="41" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.25" style="41" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.125" style="41" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.86328125" style="41" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.1328125" style="41" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.265625" style="41" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.1328125" style="41" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="5" style="41" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.25" style="41" bestFit="1" customWidth="1"/>
-    <col min="30" max="38" width="9" style="9" customWidth="1"/>
-    <col min="39" max="16384" width="9" style="9"/>
+    <col min="29" max="29" width="5.265625" style="41" bestFit="1" customWidth="1"/>
+    <col min="30" max="39" width="9" style="9" customWidth="1"/>
+    <col min="40" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="15.4" customHeight="1">
@@ -7158,17 +7126,23 @@
         <v>155</v>
       </c>
       <c r="B39" s="38">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="D39" s="38">
         <v>1.3</v>
       </c>
+      <c r="E39" s="38">
+        <v>0.7</v>
+      </c>
       <c r="F39" s="33">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="H39" s="33">
         <v>1.3</v>
       </c>
+      <c r="I39" s="33">
+        <v>0.7</v>
+      </c>
       <c r="N39" s="40">
         <v>1.5</v>
       </c>
@@ -7176,7 +7150,7 @@
         <v>1.5</v>
       </c>
       <c r="Q39" s="40">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="R39" s="38">
         <v>1.5</v>
@@ -7185,7 +7159,7 @@
         <v>1.5</v>
       </c>
       <c r="U39" s="38">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="40" spans="1:28" ht="18" customHeight="1">
@@ -7263,12 +7237,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:E45"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="25.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.75" style="3" customWidth="1"/>
+    <col min="1" max="1" width="25.46484375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.3984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.73046875" style="3" customWidth="1"/>
     <col min="5" max="5" width="13" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8033,14 +8007,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F306"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="14.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.125" style="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="9.25" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.46484375" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.1328125" style="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.86328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.1328125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="9.265625" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -14174,17 +14148,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:I123"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="16.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.3984375" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5" style="7" customWidth="1"/>
-    <col min="7" max="7" width="24.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.125" style="24" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.1328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.46484375" style="7" customWidth="1"/>
+    <col min="7" max="7" width="24.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.86328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.1328125" style="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -17390,21 +17364,21 @@
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="45.625" customWidth="1"/>
-    <col min="2" max="2" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.75" customWidth="1"/>
-    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="45.59765625" customWidth="1"/>
+    <col min="2" max="2" width="23.46484375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" customWidth="1"/>
+    <col min="5" max="5" width="10.46484375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1">

--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,16 +18,16 @@
     <sheet name="Theory" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="11">
     <font>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -91,13 +91,6 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="Microsoft YaHei"/>
-      <charset val="134"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
       <name val="Noto Sans JP"/>
       <charset val="134"/>
       <family val="3"/>
@@ -105,10 +98,10 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="游ゴシック"/>
-      <charset val="128"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <family val="3"/>
-      <sz val="6"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -195,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -286,20 +279,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -309,10 +295,13 @@
     <xf numFmtId="49" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="163">
     <dxf>
@@ -2286,12 +2275,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
-    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="10.625" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="8.25" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="4.625" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="7.3984375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="10.59765625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="8.265625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="4.59765625" bestFit="1" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -2310,7 +2299,7 @@
           <t>Gender</t>
         </is>
       </c>
-      <c r="D1" s="48" t="inlineStr">
+      <c r="D1" s="46" t="inlineStr">
         <is>
           <t>Age</t>
         </is>
@@ -2333,16 +2322,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="13" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="11.1328125" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="18" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="11.375" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.3984375" bestFit="1" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
           <t>TheoryID</t>
@@ -2353,7 +2342,7 @@
           <t>TheoryName</t>
         </is>
       </c>
-      <c r="C1" s="53" t="inlineStr">
+      <c r="C1" s="50" t="inlineStr">
         <is>
           <t>Experience</t>
         </is>
@@ -2555,79 +2544,79 @@
   <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col width="10.875" customWidth="1" style="46" min="1" max="1"/>
+    <col width="10.86328125" customWidth="1" style="45" min="1" max="1"/>
     <col width="20" customWidth="1" style="42" min="2" max="2"/>
-    <col width="14.375" bestFit="1" customWidth="1" style="42" min="3" max="3"/>
+    <col width="14.3984375" bestFit="1" customWidth="1" style="42" min="3" max="3"/>
     <col width="11" customWidth="1" style="42" min="4" max="4"/>
-    <col width="11.875" bestFit="1" customWidth="1" style="42" min="5" max="5"/>
-    <col width="15.375" customWidth="1" style="42" min="6" max="6"/>
-    <col width="10.25" bestFit="1" customWidth="1" style="42" min="7" max="7"/>
-    <col width="13.875" bestFit="1" customWidth="1" style="42" min="8" max="8"/>
+    <col width="11.86328125" bestFit="1" customWidth="1" style="42" min="5" max="5"/>
+    <col width="15.3984375" customWidth="1" style="42" min="6" max="6"/>
+    <col width="10.265625" bestFit="1" customWidth="1" style="42" min="7" max="7"/>
+    <col width="13.86328125" bestFit="1" customWidth="1" style="42" min="8" max="8"/>
     <col width="34" bestFit="1" customWidth="1" style="42" min="9" max="9"/>
     <col width="11" customWidth="1" style="42" min="10" max="10"/>
-    <col width="9" customWidth="1" style="42" min="11" max="17"/>
-    <col width="9" customWidth="1" style="42" min="18" max="16384"/>
+    <col width="9" customWidth="1" style="42" min="11" max="20"/>
+    <col width="9" customWidth="1" style="42" min="21" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="52" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>StoryID</t>
         </is>
       </c>
-      <c r="B1" s="50" t="inlineStr">
+      <c r="B1" s="47" t="inlineStr">
         <is>
           <t>StoryName</t>
         </is>
       </c>
-      <c r="C1" s="50" t="inlineStr">
+      <c r="C1" s="47" t="inlineStr">
         <is>
           <t>TriggerScene</t>
         </is>
       </c>
-      <c r="D1" s="49" t="inlineStr">
+      <c r="D1" s="29" t="inlineStr">
         <is>
           <t>TriggerDay</t>
         </is>
       </c>
-      <c r="E1" s="49" t="inlineStr">
+      <c r="E1" s="29" t="inlineStr">
         <is>
           <t>Reputation</t>
         </is>
       </c>
-      <c r="F1" s="49" t="inlineStr">
+      <c r="F1" s="29" t="inlineStr">
         <is>
           <t>EntryId</t>
         </is>
       </c>
-      <c r="G1" s="50" t="inlineStr">
+      <c r="G1" s="47" t="inlineStr">
         <is>
           <t>PlayOnce</t>
         </is>
       </c>
-      <c r="H1" s="50" t="inlineStr">
+      <c r="H1" s="47" t="inlineStr">
         <is>
           <t>ReturnScene</t>
         </is>
       </c>
-      <c r="I1" s="50" t="inlineStr">
+      <c r="I1" s="47" t="inlineStr">
         <is>
           <t>BackgroundPath</t>
         </is>
       </c>
-      <c r="J1" s="50" t="inlineStr">
+      <c r="J1" s="47" t="inlineStr">
         <is>
           <t>SortIndex</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="47" t="inlineStr">
+      <c r="A2" s="44" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="B2" s="44" t="inlineStr">
+      <c r="B2" s="43" t="inlineStr">
         <is>
           <t>落榜</t>
         </is>
@@ -2649,38 +2638,64 @@
       </c>
       <c r="H2" s="43" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>night</t>
         </is>
       </c>
       <c r="I2" s="43" t="n"/>
-      <c r="J2" s="43" t="n"/>
+      <c r="J2" s="43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="45" t="n"/>
-      <c r="B3" s="43" t="n"/>
-      <c r="C3" s="43" t="n"/>
-      <c r="D3" s="43" t="n"/>
-      <c r="E3" s="43" t="n"/>
+      <c r="A3" s="44" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="B3" s="43" t="inlineStr">
+        <is>
+          <t>初学医术</t>
+        </is>
+      </c>
+      <c r="C3" s="43" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="D3" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="43" t="n">
+        <v>0</v>
+      </c>
       <c r="F3" s="43" t="n"/>
-      <c r="G3" s="43" t="n"/>
-      <c r="H3" s="43" t="n"/>
+      <c r="G3" s="43" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" s="43" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
       <c r="I3" s="43" t="n"/>
-      <c r="J3" s="43" t="n"/>
+      <c r="J3" s="43" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="45" t="n"/>
+      <c r="A4" s="44" t="n"/>
       <c r="B4" s="43" t="n"/>
       <c r="C4" s="43" t="n"/>
       <c r="D4" s="43" t="n"/>
       <c r="E4" s="43" t="n"/>
-      <c r="F4" s="43" t="n"/>
+      <c r="F4" s="51" t="n"/>
       <c r="G4" s="43" t="n"/>
       <c r="H4" s="43" t="n"/>
       <c r="I4" s="43" t="n"/>
       <c r="J4" s="43" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="45" t="n"/>
+      <c r="A5" s="44" t="n"/>
       <c r="B5" s="43" t="n"/>
       <c r="C5" s="43" t="n"/>
       <c r="D5" s="43" t="n"/>
@@ -2692,7 +2707,7 @@
       <c r="J5" s="43" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="45" t="n"/>
+      <c r="A6" s="44" t="n"/>
       <c r="B6" s="43" t="n"/>
       <c r="C6" s="43" t="n"/>
       <c r="D6" s="43" t="n"/>
@@ -2704,7 +2719,7 @@
       <c r="J6" s="43" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="45" t="n"/>
+      <c r="A7" s="44" t="n"/>
       <c r="B7" s="43" t="n"/>
       <c r="C7" s="43" t="n"/>
       <c r="D7" s="43" t="n"/>
@@ -2716,7 +2731,7 @@
       <c r="J7" s="43" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="45" t="n"/>
+      <c r="A8" s="44" t="n"/>
       <c r="B8" s="43" t="n"/>
       <c r="C8" s="43" t="n"/>
       <c r="D8" s="43" t="n"/>
@@ -2728,7 +2743,7 @@
       <c r="J8" s="43" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="45" t="n"/>
+      <c r="A9" s="44" t="n"/>
       <c r="B9" s="43" t="n"/>
       <c r="C9" s="43" t="n"/>
       <c r="D9" s="43" t="n"/>
@@ -2740,7 +2755,7 @@
       <c r="J9" s="43" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="45" t="n"/>
+      <c r="A10" s="44" t="n"/>
       <c r="B10" s="43" t="n"/>
       <c r="C10" s="43" t="n"/>
       <c r="D10" s="43" t="n"/>
@@ -2752,7 +2767,7 @@
       <c r="J10" s="43" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="45" t="n"/>
+      <c r="A11" s="44" t="n"/>
       <c r="B11" s="43" t="n"/>
       <c r="C11" s="43" t="n"/>
       <c r="D11" s="43" t="n"/>
@@ -2764,7 +2779,7 @@
       <c r="J11" s="43" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="45" t="n"/>
+      <c r="A12" s="44" t="n"/>
       <c r="B12" s="43" t="n"/>
       <c r="C12" s="43" t="n"/>
       <c r="D12" s="43" t="n"/>
@@ -2776,7 +2791,7 @@
       <c r="J12" s="43" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="45" t="n"/>
+      <c r="A13" s="44" t="n"/>
       <c r="B13" s="43" t="n"/>
       <c r="C13" s="43" t="n"/>
       <c r="D13" s="43" t="n"/>
@@ -2788,7 +2803,7 @@
       <c r="J13" s="43" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="45" t="n"/>
+      <c r="A14" s="44" t="n"/>
       <c r="B14" s="43" t="n"/>
       <c r="C14" s="43" t="n"/>
       <c r="D14" s="43" t="n"/>
@@ -2800,7 +2815,7 @@
       <c r="J14" s="43" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="45" t="n"/>
+      <c r="A15" s="44" t="n"/>
       <c r="B15" s="43" t="n"/>
       <c r="C15" s="43" t="n"/>
       <c r="D15" s="43" t="n"/>
@@ -2812,7 +2827,7 @@
       <c r="J15" s="43" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="45" t="n"/>
+      <c r="A16" s="44" t="n"/>
       <c r="B16" s="43" t="n"/>
       <c r="C16" s="43" t="n"/>
       <c r="D16" s="43" t="n"/>
@@ -2824,7 +2839,7 @@
       <c r="J16" s="43" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="45" t="n"/>
+      <c r="A17" s="44" t="n"/>
       <c r="B17" s="43" t="n"/>
       <c r="C17" s="43" t="n"/>
       <c r="D17" s="43" t="n"/>
@@ -2836,7 +2851,7 @@
       <c r="J17" s="43" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="45" t="n"/>
+      <c r="A18" s="44" t="n"/>
       <c r="B18" s="43" t="n"/>
       <c r="C18" s="43" t="n"/>
       <c r="D18" s="43" t="n"/>
@@ -2848,7 +2863,7 @@
       <c r="J18" s="43" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="45" t="n"/>
+      <c r="A19" s="44" t="n"/>
       <c r="B19" s="43" t="n"/>
       <c r="C19" s="43" t="n"/>
       <c r="D19" s="43" t="n"/>
@@ -2860,7 +2875,7 @@
       <c r="J19" s="43" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="45" t="n"/>
+      <c r="A20" s="44" t="n"/>
       <c r="B20" s="43" t="n"/>
       <c r="C20" s="43" t="n"/>
       <c r="D20" s="43" t="n"/>
@@ -2882,58 +2897,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col width="8.75" bestFit="1" customWidth="1" style="35" min="1" max="1"/>
-    <col width="12.375" bestFit="1" customWidth="1" style="35" min="2" max="2"/>
-    <col width="11.25" bestFit="1" customWidth="1" style="35" min="3" max="3"/>
-    <col width="10.5" bestFit="1" customWidth="1" style="35" min="4" max="4"/>
-    <col width="9.5" bestFit="1" customWidth="1" style="35" min="5" max="5"/>
-    <col width="13.625" bestFit="1" customWidth="1" style="35" min="6" max="6"/>
-    <col width="31.625" bestFit="1" customWidth="1" style="35" min="7" max="7"/>
-    <col width="41.625" customWidth="1" style="35" min="8" max="8"/>
-    <col width="9" customWidth="1" style="42" min="9" max="14"/>
-    <col width="9" customWidth="1" style="42" min="15" max="16384"/>
+    <col width="8.73046875" bestFit="1" customWidth="1" style="35" min="1" max="1"/>
+    <col width="12.3984375" bestFit="1" customWidth="1" style="35" min="2" max="2"/>
+    <col width="11.265625" bestFit="1" customWidth="1" style="35" min="3" max="3"/>
+    <col width="10.46484375" bestFit="1" customWidth="1" style="35" min="4" max="4"/>
+    <col width="9.46484375" bestFit="1" customWidth="1" style="35" min="5" max="5"/>
+    <col width="13.59765625" bestFit="1" customWidth="1" style="35" min="6" max="6"/>
+    <col width="31.59765625" bestFit="1" customWidth="1" style="35" min="7" max="7"/>
+    <col width="41.59765625" customWidth="1" style="35" min="8" max="8"/>
+    <col width="9" customWidth="1" style="42" min="9" max="17"/>
+    <col width="9" customWidth="1" style="42" min="18" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="50" t="inlineStr">
+      <c r="A1" s="47" t="inlineStr">
         <is>
           <t>StoryID</t>
         </is>
       </c>
-      <c r="B1" s="50" t="inlineStr">
+      <c r="B1" s="47" t="inlineStr">
         <is>
           <t>StoryName</t>
         </is>
       </c>
-      <c r="C1" s="50" t="inlineStr">
+      <c r="C1" s="47" t="inlineStr">
         <is>
           <t>LineIndex</t>
         </is>
       </c>
-      <c r="D1" s="50" t="inlineStr">
+      <c r="D1" s="47" t="inlineStr">
         <is>
           <t>LineType</t>
         </is>
       </c>
-      <c r="E1" s="50" t="inlineStr">
+      <c r="E1" s="47" t="inlineStr">
         <is>
           <t>Speaker</t>
         </is>
       </c>
-      <c r="F1" s="51" t="inlineStr">
+      <c r="F1" s="48" t="inlineStr">
         <is>
           <t>PortraitSide</t>
         </is>
       </c>
-      <c r="G1" s="51" t="inlineStr">
+      <c r="G1" s="48" t="inlineStr">
         <is>
           <t>PortraitPath</t>
         </is>
       </c>
-      <c r="H1" s="50" t="inlineStr">
+      <c r="H1" s="47" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
@@ -3392,6 +3407,166 @@
       <c r="H13" t="inlineStr">
         <is>
           <t>李东壁十四岁考中秀才，可之后九年三次乡试落榜，本就无心科举的李东壁便下定决心开始随父亲学医。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>初学医术</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>res://Assets/Portrait/li_yan_wen.png</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>东壁啊，白天教你的都听明白了吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>初学医术</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>李东壁</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>res://Assets/Portrait/li_shi_zhen.png</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>平常日子里看您治病，其实已经窥探得些门道了。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>初学医术</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>李言闻</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>res://Assets/Portrait/li_yan_wen.png</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>学医最要紧的是积累，吃完晚饭去把这些天教你的内容再看一遍，明日一早你随我一起出诊。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>初学医术</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>dialogue</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>李东壁</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>res://Assets/Portrait/li_shi_zhen.png</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>哇，太好了！</t>
         </is>
       </c>
     </row>
@@ -3408,14 +3583,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F109"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="37" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="19.25" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="11.125" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
-    <col width="29.875" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
-    <col width="31.25" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
-    <col width="20.75" customWidth="1" style="3" min="6" max="6"/>
+    <col width="19.265625" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="11.1328125" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="29.86328125" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="31.265625" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
+    <col width="20.73046875" customWidth="1" style="3" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -3429,7 +3604,7 @@
           <t>DiseaseName</t>
         </is>
       </c>
-      <c r="C1" s="53" t="inlineStr">
+      <c r="C1" s="50" t="inlineStr">
         <is>
           <t>Experience</t>
         </is>
@@ -5172,13 +5347,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F109"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col width="25.5" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="15.125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="11.125" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
-    <col width="21.375" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
-    <col width="49.125" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
+    <col width="25.46484375" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
+    <col width="15.1328125" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="11.1328125" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="21.3984375" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="49.1328125" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
     <col width="13" bestFit="1" customWidth="1" style="3" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -5193,7 +5368,7 @@
           <t>FormulaName</t>
         </is>
       </c>
-      <c r="C1" s="53" t="inlineStr">
+      <c r="C1" s="50" t="inlineStr">
         <is>
           <t>Experience</t>
         </is>
@@ -7319,33 +7494,33 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AC45"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col width="19" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="35" min="2" max="2"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="35" min="3" max="3"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="35" min="4" max="5"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="30" min="6" max="9"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="36" min="10" max="11"/>
-    <col width="4.25" bestFit="1" customWidth="1" style="36" min="12" max="12"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="36" min="13" max="13"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="35" min="2" max="2"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="35" min="3" max="3"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="35" min="4" max="5"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="30" min="6" max="9"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="36" min="10" max="11"/>
+    <col width="4.265625" bestFit="1" customWidth="1" style="36" min="12" max="12"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="36" min="13" max="13"/>
     <col width="4" bestFit="1" customWidth="1" style="37" min="14" max="14"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="37" min="15" max="15"/>
-    <col width="4.25" bestFit="1" customWidth="1" style="37" min="16" max="16"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="37" min="15" max="15"/>
+    <col width="4.265625" bestFit="1" customWidth="1" style="37" min="16" max="16"/>
     <col width="4" bestFit="1" customWidth="1" style="37" min="17" max="17"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="35" min="18" max="18"/>
-    <col width="3.875" bestFit="1" customWidth="1" style="35" min="19" max="19"/>
-    <col width="4.5" bestFit="1" customWidth="1" style="35" min="20" max="21"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="38" min="22" max="22"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="35" min="18" max="18"/>
+    <col width="3.86328125" bestFit="1" customWidth="1" style="35" min="19" max="19"/>
+    <col width="4.46484375" bestFit="1" customWidth="1" style="35" min="20" max="21"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="38" min="22" max="22"/>
     <col width="5" bestFit="1" customWidth="1" style="38" min="23" max="23"/>
-    <col width="4.875" bestFit="1" customWidth="1" style="38" min="24" max="24"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="38" min="25" max="25"/>
-    <col width="5.25" bestFit="1" customWidth="1" style="38" min="26" max="26"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="38" min="27" max="27"/>
+    <col width="4.86328125" bestFit="1" customWidth="1" style="38" min="24" max="24"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="38" min="25" max="25"/>
+    <col width="5.265625" bestFit="1" customWidth="1" style="38" min="26" max="26"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="38" min="27" max="27"/>
     <col width="5" bestFit="1" customWidth="1" style="38" min="28" max="28"/>
-    <col width="5.25" bestFit="1" customWidth="1" style="38" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="48"/>
-    <col width="9" customWidth="1" style="9" min="49" max="16384"/>
+    <col width="5.265625" bestFit="1" customWidth="1" style="38" min="29" max="29"/>
+    <col width="9" customWidth="1" style="9" min="30" max="51"/>
+    <col width="9" customWidth="1" style="9" min="52" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -8094,14 +8269,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F306"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col width="14.375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="16.5" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
-    <col width="5.125" bestFit="1" customWidth="1" style="22" min="3" max="3"/>
-    <col width="7.875" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
-    <col width="9.125" customWidth="1" style="6" min="5" max="5"/>
-    <col width="9.25" bestFit="1" customWidth="1" style="10" min="6" max="6"/>
+    <col width="14.3984375" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
+    <col width="16.46484375" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
+    <col width="5.1328125" bestFit="1" customWidth="1" style="22" min="3" max="3"/>
+    <col width="7.86328125" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
+    <col width="9.1328125" customWidth="1" style="6" min="5" max="5"/>
+    <col width="9.265625" bestFit="1" customWidth="1" style="10" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16689,18 +16864,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J123"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col width="16.25" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
-    <col width="11.625" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
-    <col width="8.375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="16.265625" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
+    <col width="11.59765625" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
+    <col width="8.3984375" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
     <col width="8" bestFit="1" customWidth="1" style="7" min="4" max="4"/>
-    <col width="13.125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
-    <col width="10.5" customWidth="1" style="7" min="6" max="6"/>
-    <col width="11.125" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
-    <col width="24.25" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
-    <col width="12.875" bestFit="1" customWidth="1" style="3" min="9" max="9"/>
-    <col width="15.125" bestFit="1" customWidth="1" style="24" min="10" max="10"/>
+    <col width="13.1328125" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
+    <col width="10.46484375" customWidth="1" style="7" min="6" max="6"/>
+    <col width="11.1328125" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
+    <col width="24.265625" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
+    <col width="12.86328125" bestFit="1" customWidth="1" style="3" min="9" max="9"/>
+    <col width="15.1328125" bestFit="1" customWidth="1" style="24" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16734,7 +16909,7 @@
           <t>Toxicity</t>
         </is>
       </c>
-      <c r="G1" s="53" t="inlineStr">
+      <c r="G1" s="50" t="inlineStr">
         <is>
           <t>Experience</t>
         </is>
@@ -23789,17 +23964,17 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
-    <col width="45.625" customWidth="1" min="1" max="1"/>
-    <col width="23.5" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="10.75" customWidth="1" min="4" max="4"/>
-    <col width="10.5" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="11.375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="45.59765625" customWidth="1" min="1" max="1"/>
+    <col width="23.46484375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="11.59765625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="10.73046875" customWidth="1" min="4" max="4"/>
+    <col width="10.46484375" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="11.3984375" bestFit="1" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>BookID</t>

--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -226,7 +226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -355,9 +355,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2348,8 +2345,8 @@
     <col width="25.1328125" bestFit="1" customWidth="1" style="23" min="7" max="7"/>
     <col width="31.265625" bestFit="1" customWidth="1" style="23" min="8" max="8"/>
     <col width="33.3984375" bestFit="1" customWidth="1" style="23" min="9" max="9"/>
-    <col width="9.1328125" customWidth="1" style="23" min="10" max="30"/>
-    <col width="9.1328125" customWidth="1" style="23" min="31" max="16384"/>
+    <col width="9.1328125" customWidth="1" style="23" min="10" max="31"/>
+    <col width="9.1328125" customWidth="1" style="23" min="32" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1">
@@ -5210,7 +5207,7 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col width="8.46484375" bestFit="1" customWidth="1" style="38" min="1" max="1"/>
-    <col width="12.1328125" bestFit="1" customWidth="1" style="36" min="2" max="2"/>
+    <col width="15.1328125" customWidth="1" style="36" min="2" max="2"/>
     <col width="27.3984375" bestFit="1" customWidth="1" style="36" min="3" max="3"/>
     <col width="14.1328125" bestFit="1" customWidth="1" style="36" min="4" max="4"/>
     <col width="11.9296875" bestFit="1" customWidth="1" style="36" min="5" max="5"/>
@@ -5222,8 +5219,8 @@
     <col width="10.265625" bestFit="1" customWidth="1" style="36" min="11" max="11"/>
     <col width="13.86328125" bestFit="1" customWidth="1" style="36" min="12" max="12"/>
     <col width="11" customWidth="1" style="36" min="13" max="13"/>
-    <col width="9" customWidth="1" style="36" min="14" max="49"/>
-    <col width="9" customWidth="1" style="36" min="50" max="16384"/>
+    <col width="9" customWidth="1" style="36" min="14" max="50"/>
+    <col width="9" customWidth="1" style="36" min="51" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5247,27 +5244,27 @@
           <t>TriggerScene</t>
         </is>
       </c>
-      <c r="E1" s="62" t="inlineStr">
+      <c r="E1" s="61" t="inlineStr">
         <is>
           <t>TriggerDay</t>
         </is>
       </c>
-      <c r="F1" s="62" t="inlineStr">
+      <c r="F1" s="61" t="inlineStr">
         <is>
           <t>Reputation</t>
         </is>
       </c>
-      <c r="G1" s="62" t="inlineStr">
+      <c r="G1" s="61" t="inlineStr">
         <is>
           <t>EntryId</t>
         </is>
       </c>
-      <c r="H1" s="62" t="inlineStr">
+      <c r="H1" s="61" t="inlineStr">
         <is>
           <t>NpcID</t>
         </is>
       </c>
-      <c r="I1" s="63" t="inlineStr">
+      <c r="I1" s="62" t="inlineStr">
         <is>
           <t>TriggerNpcID</t>
         </is>
@@ -5443,7 +5440,7 @@
           <t>night</t>
         </is>
       </c>
-      <c r="E5" s="60" t="n">
+      <c r="E5" s="59" t="n">
         <v>2</v>
       </c>
       <c r="F5" s="37" t="n">
@@ -5461,11 +5458,11 @@
           <t>night</t>
         </is>
       </c>
-      <c r="M5" s="60" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="M5" s="59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="37" t="inlineStr">
         <is>
           <t>005_01</t>
@@ -5501,7 +5498,7 @@
       <c r="I6" s="37" t="inlineStr"/>
       <c r="J6" s="37" t="inlineStr">
         <is>
-          <t>res://Assets/Portrait/StoryNpc/shi_zi</t>
+          <t>res://Assets/Portrait/StoryNpc/shi_zi/shi_zi_before.png</t>
         </is>
       </c>
       <c r="K6" s="37" t="b">
@@ -5559,7 +5556,7 @@
           <t>night</t>
         </is>
       </c>
-      <c r="M7" s="60" t="n">
+      <c r="M7" s="59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5599,7 +5596,7 @@
       </c>
       <c r="J8" s="37" t="inlineStr">
         <is>
-          <t>res://Assets/Portrait/StoryNpc/shi_zi</t>
+          <t>res://Assets/Portrait/StoryNpc/shi_zi/shi_zi_before.png</t>
         </is>
       </c>
       <c r="K8" s="37" t="b">
@@ -5610,7 +5607,7 @@
           <t>night</t>
         </is>
       </c>
-      <c r="M8" s="60" t="n">
+      <c r="M8" s="59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5819,8 +5816,8 @@
     <col width="6.1328125" bestFit="1" customWidth="1" style="32" min="8" max="8"/>
     <col width="43.86328125" bestFit="1" customWidth="1" style="32" min="9" max="9"/>
     <col width="89.73046875" customWidth="1" style="32" min="10" max="10"/>
-    <col width="9" customWidth="1" style="36" min="11" max="45"/>
-    <col width="9" customWidth="1" style="36" min="46" max="16384"/>
+    <col width="9" customWidth="1" style="36" min="11" max="46"/>
+    <col width="9" customWidth="1" style="36" min="47" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6394,7 +6391,7 @@
           <t>dim</t>
         </is>
       </c>
-      <c r="I14" s="61" t="inlineStr">
+      <c r="I14" s="60" t="inlineStr">
         <is>
           <t>res://Assets/Background/002/002.png</t>
         </is>
@@ -6567,7 +6564,7 @@
         </is>
       </c>
       <c r="I18" s="51" t="inlineStr"/>
-      <c r="J18" s="58" t="inlineStr">
+      <c r="J18" s="57" t="inlineStr">
         <is>
           <t>都明白了，平常日子里看您治病，其实已经窥得些门道了。</t>
         </is>
@@ -7079,7 +7076,7 @@
         </is>
       </c>
       <c r="I30" s="32" t="inlineStr"/>
-      <c r="J30" s="59" t="inlineStr">
+      <c r="J30" s="58" t="inlineStr">
         <is>
           <t>人生在世不止考取科举一条路，你能找到一条适合自己的路，为师很欣慰。</t>
         </is>
@@ -7121,7 +7118,7 @@
         </is>
       </c>
       <c r="I31" s="32" t="inlineStr"/>
-      <c r="J31" s="59" t="inlineStr">
+      <c r="J31" s="58" t="inlineStr">
         <is>
           <t>承蒙老师教诲，学生愿精进医术一生治病救人。</t>
         </is>
@@ -7682,7 +7679,7 @@
           <t>right</t>
         </is>
       </c>
-      <c r="G45" s="59" t="inlineStr">
+      <c r="G45" s="58" t="inlineStr">
         <is>
           <t>before</t>
         </is>
@@ -7693,7 +7690,7 @@
         </is>
       </c>
       <c r="I45" s="32" t="inlineStr"/>
-      <c r="J45" s="59" t="inlineStr">
+      <c r="J45" s="58" t="inlineStr">
         <is>
           <t>咳咳咳，父王…</t>
         </is>
@@ -7735,7 +7732,7 @@
         </is>
       </c>
       <c r="I46" s="32" t="inlineStr"/>
-      <c r="J46" s="59" t="inlineStr">
+      <c r="J46" s="58" t="inlineStr">
         <is>
           <t>先生，小王就这么一个儿子，请您救救孩子吧。</t>
         </is>
@@ -10022,8 +10019,8 @@
     <col width="5.1328125" bestFit="1" customWidth="1" style="35" min="27" max="27"/>
     <col width="5" bestFit="1" customWidth="1" style="35" min="28" max="28"/>
     <col width="5.265625" bestFit="1" customWidth="1" style="35" min="29" max="29"/>
-    <col width="9" customWidth="1" style="9" min="30" max="77"/>
-    <col width="9" customWidth="1" style="9" min="78" max="16384"/>
+    <col width="9" customWidth="1" style="9" min="30" max="78"/>
+    <col width="9" customWidth="1" style="9" min="79" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.4" customHeight="1">
@@ -30076,8 +30073,8 @@
     <cfRule type="duplicateValues" priority="2366" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A77 A79:A100 A102:A106 A114:A1048576">
+    <cfRule type="duplicateValues" priority="2332" dxfId="0"/>
     <cfRule type="duplicateValues" priority="2331" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="2332" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A5">
     <cfRule type="duplicateValues" priority="162" dxfId="0"/>
@@ -30104,32 +30101,32 @@
     <cfRule type="duplicateValues" priority="126" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" priority="124" dxfId="0"/>
     <cfRule type="duplicateValues" priority="123" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="124" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
     <cfRule type="duplicateValues" priority="121" dxfId="0"/>
     <cfRule type="duplicateValues" priority="122" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
+    <cfRule type="duplicateValues" priority="120" dxfId="0"/>
     <cfRule type="duplicateValues" priority="119" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="120" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18">
+    <cfRule type="duplicateValues" priority="118" dxfId="0"/>
     <cfRule type="duplicateValues" priority="117" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="118" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:A20">
+    <cfRule type="duplicateValues" priority="116" dxfId="0"/>
     <cfRule type="duplicateValues" priority="115" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="116" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
     <cfRule type="duplicateValues" priority="112" dxfId="0"/>
     <cfRule type="duplicateValues" priority="113" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A26">
+    <cfRule type="duplicateValues" priority="111" dxfId="0"/>
     <cfRule type="duplicateValues" priority="110" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="111" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27">
     <cfRule type="duplicateValues" priority="140" dxfId="0"/>
@@ -30168,20 +30165,20 @@
     <cfRule type="duplicateValues" priority="632" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40">
+    <cfRule type="duplicateValues" priority="155" dxfId="0"/>
     <cfRule type="duplicateValues" priority="154" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="155" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41">
     <cfRule type="duplicateValues" priority="78" dxfId="0"/>
     <cfRule type="duplicateValues" priority="79" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43">
+    <cfRule type="duplicateValues" priority="77" dxfId="0"/>
     <cfRule type="duplicateValues" priority="76" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="77" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44">
+    <cfRule type="duplicateValues" priority="147" dxfId="0"/>
     <cfRule type="duplicateValues" priority="146" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="147" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45">
     <cfRule type="duplicateValues" priority="90" dxfId="0"/>
@@ -30192,8 +30189,8 @@
     <cfRule type="duplicateValues" priority="94" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:A48">
+    <cfRule type="duplicateValues" priority="55" dxfId="0"/>
     <cfRule type="duplicateValues" priority="54" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="55" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:A52">
     <cfRule type="duplicateValues" priority="106" dxfId="0"/>
@@ -30204,32 +30201,32 @@
     <cfRule type="duplicateValues" priority="45" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54">
+    <cfRule type="duplicateValues" priority="29" dxfId="0"/>
     <cfRule type="duplicateValues" priority="28" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="29" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55">
+    <cfRule type="duplicateValues" priority="134" dxfId="0"/>
     <cfRule type="duplicateValues" priority="133" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="134" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56">
+    <cfRule type="duplicateValues" priority="50" dxfId="0"/>
     <cfRule type="duplicateValues" priority="49" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="50" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57">
+    <cfRule type="duplicateValues" priority="149" dxfId="0"/>
     <cfRule type="duplicateValues" priority="148" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="149" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58">
     <cfRule type="duplicateValues" priority="152" dxfId="0"/>
     <cfRule type="duplicateValues" priority="153" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59">
+    <cfRule type="duplicateValues" priority="74" dxfId="0"/>
     <cfRule type="duplicateValues" priority="73" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="74" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A60">
+    <cfRule type="duplicateValues" priority="72" dxfId="0"/>
     <cfRule type="duplicateValues" priority="71" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="72" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61">
     <cfRule type="duplicateValues" priority="86" dxfId="0"/>
@@ -30240,8 +30237,8 @@
     <cfRule type="duplicateValues" priority="70" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63">
+    <cfRule type="duplicateValues" priority="66" dxfId="0"/>
     <cfRule type="duplicateValues" priority="65" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="66" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64">
     <cfRule type="duplicateValues" priority="60" dxfId="0"/>
@@ -30252,8 +30249,8 @@
     <cfRule type="duplicateValues" priority="59" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A66">
+    <cfRule type="duplicateValues" priority="57" dxfId="0"/>
     <cfRule type="duplicateValues" priority="56" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="57" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67">
     <cfRule type="duplicateValues" priority="150" dxfId="0"/>
@@ -30264,8 +30261,8 @@
     <cfRule type="duplicateValues" priority="866" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69">
+    <cfRule type="duplicateValues" priority="53" dxfId="0"/>
     <cfRule type="duplicateValues" priority="52" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="53" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70">
     <cfRule type="duplicateValues" priority="42" dxfId="0"/>
@@ -30276,36 +30273,36 @@
     <cfRule type="duplicateValues" priority="10" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72:A73">
+    <cfRule type="duplicateValues" priority="100" dxfId="0"/>
     <cfRule type="duplicateValues" priority="99" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="100" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A74">
     <cfRule type="duplicateValues" priority="95" dxfId="0"/>
     <cfRule type="duplicateValues" priority="96" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75:A77">
+    <cfRule type="duplicateValues" priority="39" dxfId="0"/>
     <cfRule type="duplicateValues" priority="38" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="39" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A78">
+    <cfRule type="duplicateValues" priority="2" dxfId="0"/>
     <cfRule type="duplicateValues" priority="1" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="2" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A79 A106">
     <cfRule type="duplicateValues" priority="1727" dxfId="0"/>
     <cfRule type="duplicateValues" priority="1728" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A80">
+    <cfRule type="duplicateValues" priority="63" dxfId="0"/>
     <cfRule type="duplicateValues" priority="62" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="63" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A82:A83">
     <cfRule type="duplicateValues" priority="982" dxfId="0"/>
     <cfRule type="duplicateValues" priority="983" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A84">
+    <cfRule type="duplicateValues" priority="136" dxfId="0"/>
     <cfRule type="duplicateValues" priority="135" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="136" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A85">
     <cfRule type="duplicateValues" priority="13" dxfId="0"/>
@@ -30336,12 +30333,12 @@
     <cfRule type="duplicateValues" priority="41" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A96">
+    <cfRule type="duplicateValues" priority="85" dxfId="0"/>
     <cfRule type="duplicateValues" priority="84" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="85" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A98">
+    <cfRule type="duplicateValues" priority="17" dxfId="0"/>
     <cfRule type="duplicateValues" priority="16" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="17" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99">
     <cfRule type="duplicateValues" priority="26" dxfId="0"/>
@@ -30356,12 +30353,12 @@
     <cfRule type="duplicateValues" priority="4" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A102">
+    <cfRule type="duplicateValues" priority="89" dxfId="0"/>
     <cfRule type="duplicateValues" priority="88" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="89" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A103">
+    <cfRule type="duplicateValues" priority="143" dxfId="0"/>
     <cfRule type="duplicateValues" priority="142" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="143" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A104:A105">
     <cfRule type="duplicateValues" priority="1709" dxfId="0"/>
@@ -30372,8 +30369,8 @@
     <cfRule type="duplicateValues" priority="1944" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114:A115">
+    <cfRule type="duplicateValues" priority="132" dxfId="0"/>
     <cfRule type="duplicateValues" priority="131" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="132" dxfId="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117:A1048576">
     <cfRule type="duplicateValues" priority="395" dxfId="0"/>

--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -5600,7 +5600,7 @@
         </is>
       </c>
       <c r="K8" s="37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="37" t="inlineStr">
         <is>

--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036BEF15-649D-4C6D-9C5D-129641F43518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4319E1-5ED5-476C-826B-8FA107147798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4406" uniqueCount="1231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4407" uniqueCount="1230">
   <si>
     <t>NpcID</t>
   </si>
@@ -1034,6 +1034,9 @@
     <t>大半夜的谁啊，谁在敲门啊？</t>
   </si>
   <si>
+    <t>hide</t>
+  </si>
+  <si>
     <t>res://Assets/Background/003/003_02.png</t>
   </si>
   <si>
@@ -1083,9 +1086,6 @@
   </si>
   <si>
     <t>咳咳咳，父王…</t>
-  </si>
-  <si>
-    <t>hide</t>
   </si>
   <si>
     <t>先生，小王就这么一个儿子，请您救救孩子吧。</t>
@@ -6008,16 +6008,12 @@
     <t>李东璧在行医过程中记录的心得笔记，白天行医时可翻阅笔记查找药材，方剂，疾病。
 在搜索栏输入药材，方剂，疾病的中文名或拼音，拼音首字母可快速查找。</t>
   </si>
-  <si>
-    <t>脾虚湿盛</t>
-    <phoneticPr fontId="15"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6132,6 +6128,13 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -6223,7 +6226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -6371,6 +6374,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -8285,8 +8289,8 @@
     <col min="8" max="8" width="25.125" style="23" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="31.25" style="23" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="33.375" style="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="35" width="9.125" style="23" customWidth="1"/>
-    <col min="36" max="16384" width="9.125" style="23"/>
+    <col min="11" max="36" width="9.125" style="23" customWidth="1"/>
+    <col min="37" max="16384" width="9.125" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.399999999999999" customHeight="1">
@@ -10309,8 +10313,8 @@
     <col min="11" max="11" width="10.25" style="36" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.875" style="36" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11" style="36" customWidth="1"/>
-    <col min="14" max="53" width="9" style="36" customWidth="1"/>
-    <col min="54" max="16384" width="9" style="36"/>
+    <col min="14" max="54" width="9" style="36" customWidth="1"/>
+    <col min="55" max="16384" width="9" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -10506,7 +10510,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>1230</v>
+        <v>35</v>
       </c>
       <c r="H6" s="37" t="s">
         <v>33</v>
@@ -10797,8 +10801,8 @@
     <col min="8" max="8" width="6.125" style="32" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="43.875" style="32" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="89.75" style="32" customWidth="1"/>
-    <col min="11" max="49" width="9" style="36" customWidth="1"/>
-    <col min="50" max="16384" width="9" style="36"/>
+    <col min="11" max="50" width="9" style="36" customWidth="1"/>
+    <col min="51" max="16384" width="9" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -11178,7 +11182,7 @@
       <c r="H14" s="53" t="s">
         <v>292</v>
       </c>
-      <c r="I14" s="64" t="s">
+      <c r="I14" s="65" t="s">
         <v>306</v>
       </c>
       <c r="J14" s="56" t="s">
@@ -11241,7 +11245,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" ht="18.75">
       <c r="A17" s="50" t="s">
         <v>264</v>
       </c>
@@ -11264,7 +11268,9 @@
       <c r="H17" s="53" t="s">
         <v>292</v>
       </c>
-      <c r="I17" s="51"/>
+      <c r="I17" s="65" t="s">
+        <v>306</v>
+      </c>
       <c r="J17" s="55" t="s">
         <v>310</v>
       </c>
@@ -11724,13 +11730,13 @@
       </c>
       <c r="G34" s="51"/>
       <c r="H34" s="53" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="I34" s="51" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J34" s="50" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -11758,7 +11764,7 @@
       </c>
       <c r="I35" s="51"/>
       <c r="J35" s="51" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -11784,7 +11790,7 @@
         <v>292</v>
       </c>
       <c r="J36" s="32" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -11812,7 +11818,7 @@
       </c>
       <c r="I37" s="51"/>
       <c r="J37" s="50" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -11835,10 +11841,10 @@
         <v>294</v>
       </c>
       <c r="H38" s="53" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="J38" s="32" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -11864,7 +11870,7 @@
         <v>292</v>
       </c>
       <c r="J39" s="32" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -11883,7 +11889,7 @@
       <c r="E40" s="50"/>
       <c r="F40" s="51"/>
       <c r="J40" s="32" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -11909,10 +11915,10 @@
         <v>292</v>
       </c>
       <c r="I41" s="51" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J41" s="32" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -11938,7 +11944,7 @@
         <v>292</v>
       </c>
       <c r="J42" s="32" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -11964,10 +11970,10 @@
         <v>292</v>
       </c>
       <c r="I43" s="51" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J43" s="32" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -11993,7 +11999,7 @@
         <v>292</v>
       </c>
       <c r="J44" s="32" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="18.75">
@@ -12016,14 +12022,14 @@
         <v>291</v>
       </c>
       <c r="G45" s="58" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H45" s="53" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I45" s="64"/>
       <c r="J45" s="58" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -12046,7 +12052,7 @@
         <v>296</v>
       </c>
       <c r="H46" s="53" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="J46" s="58" t="s">
         <v>347</v>
@@ -12078,7 +12084,7 @@
         <v>292</v>
       </c>
       <c r="I47" s="51" t="s">
-        <v>314</v>
+        <v>341</v>
       </c>
       <c r="J47" s="52" t="s">
         <v>349</v>
@@ -12160,13 +12166,13 @@
         <v>291</v>
       </c>
       <c r="G50" s="58" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H50" s="53" t="s">
         <v>292</v>
       </c>
       <c r="I50" s="51" t="s">
-        <v>314</v>
+        <v>341</v>
       </c>
       <c r="J50" s="52" t="s">
         <v>352</v>
@@ -13503,8 +13509,8 @@
     <col min="27" max="27" width="5.125" style="35" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="5" style="35" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="5.25" style="35" bestFit="1" customWidth="1"/>
-    <col min="30" max="81" width="9" style="9" customWidth="1"/>
-    <col min="82" max="16384" width="9" style="9"/>
+    <col min="30" max="82" width="9" style="9" customWidth="1"/>
+    <col min="83" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="15.4" customHeight="1">

--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B15F3A16-FE28-48A0-A15A-ACF708E3A2E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AF77CED-A9DF-430E-AE03-F4B2C9D776F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4642" yWindow="3188" windowWidth="21601" windowHeight="11422" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" r:id="rId1"/>
@@ -28,24 +28,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Npc!$A$1:$J$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4409" uniqueCount="1234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4411" uniqueCount="1236">
   <si>
     <t>NpcID</t>
   </si>
@@ -800,22 +787,22 @@
     <t>TriggerScene</t>
   </si>
   <si>
-    <t>Reputation</t>
-  </si>
-  <si>
-    <t>EntryId</t>
+    <t>ReturnScene</t>
+  </si>
+  <si>
+    <t>TriggerDay</t>
   </si>
   <si>
     <t>TriggerNpcID</t>
   </si>
   <si>
+    <t>TriggerCureCount</t>
+  </si>
+  <si>
     <t>ClinicNpcPortraitPath</t>
   </si>
   <si>
     <t>PlayOnce</t>
-  </si>
-  <si>
-    <t>ReturnScene</t>
   </si>
   <si>
     <t>SortIndex</t>
@@ -6012,16 +5999,24 @@
 在搜索栏输入药材，方剂，疾病的中文名或拼音，拼音首字母可快速查找。</t>
   </si>
   <si>
+    <t>Reputation</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>Experience</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
     <t>TriggerStoryID</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerDay</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerCureCount</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>TriggerReputation</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>TriggerEntryId</t>
+    <phoneticPr fontId="15"/>
   </si>
 </sst>
 </file>
@@ -6032,7 +6027,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -6130,17 +6125,17 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
+      <sz val="6"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -6381,7 +6376,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -6390,7 +6385,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="162">
     <dxf>
@@ -8290,20 +8285,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J71"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.625" style="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.75" style="23" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.25" style="23" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.625" style="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.875" style="23" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.125" style="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.125" style="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="31.25" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="33.375" style="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="38" width="9.125" style="23" customWidth="1"/>
-    <col min="39" max="16384" width="9.125" style="23"/>
+    <col min="2" max="2" width="10.59765625" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.73046875" style="23" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.265625" style="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.59765625" style="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.86328125" style="23" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.1328125" style="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.1328125" style="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.265625" style="23" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="33.3984375" style="23" bestFit="1" customWidth="1"/>
+    <col min="11" max="39" width="9.1328125" style="23" customWidth="1"/>
+    <col min="40" max="16384" width="9.1328125" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.399999999999999" customHeight="1">
@@ -10146,22 +10141,22 @@
       <sortCondition descending="1" ref="C1"/>
     </sortState>
   </autoFilter>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1">
@@ -10303,35 +10298,38 @@
       <c r="E14" s="7"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" style="38" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" style="38" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" style="36" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" style="36" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" style="36" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" style="36" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.5" style="36" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="36" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.25" style="36" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" style="36" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" style="36" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.625" style="36" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.75" style="36" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.75" style="36" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.875" style="36" bestFit="1" customWidth="1"/>
-    <col min="16" max="58" width="9" style="36" customWidth="1"/>
-    <col min="59" max="16384" width="9" style="36"/>
+    <col min="4" max="4" width="14.59765625" style="36" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" style="36" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" style="36" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" style="36" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="36" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" style="36" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.3984375" style="36" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.59765625" style="36" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.59765625" style="36" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.73046875" style="36" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.06640625" style="36" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12" style="36" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.73046875" style="36" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.86328125" style="36" bestFit="1" customWidth="1"/>
+    <col min="18" max="61" width="9" style="36" customWidth="1"/>
+    <col min="62" max="16384" width="9" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:17">
       <c r="A1" s="41" t="s">
         <v>247</v>
       </c>
@@ -10345,19 +10343,19 @@
         <v>250</v>
       </c>
       <c r="E1" s="39" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F1" s="60" t="s">
-        <v>1232</v>
+        <v>252</v>
       </c>
       <c r="G1" s="60" t="s">
-        <v>251</v>
+        <v>1234</v>
       </c>
       <c r="H1" s="60" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="I1" s="60" t="s">
-        <v>252</v>
+        <v>1235</v>
       </c>
       <c r="J1" s="61" t="s">
         <v>0</v>
@@ -10366,19 +10364,25 @@
         <v>253</v>
       </c>
       <c r="L1" s="61" t="s">
-        <v>1233</v>
+        <v>254</v>
       </c>
       <c r="M1" s="65" t="s">
-        <v>254</v>
-      </c>
-      <c r="N1" s="66" t="s">
         <v>255</v>
       </c>
-      <c r="O1" s="66" t="s">
+      <c r="N1" s="65" t="s">
+        <v>1231</v>
+      </c>
+      <c r="O1" s="65" t="s">
+        <v>1232</v>
+      </c>
+      <c r="P1" s="66" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q1" s="66" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:17">
       <c r="A2" s="37" t="s">
         <v>258</v>
       </c>
@@ -10406,14 +10410,16 @@
       <c r="K2" s="37"/>
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
-      <c r="N2" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="O2" s="37">
+      <c r="N2" s="37"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="37">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:17">
       <c r="A3" s="37" t="s">
         <v>263</v>
       </c>
@@ -10441,14 +10447,16 @@
       <c r="K3" s="37"/>
       <c r="L3" s="37"/>
       <c r="M3" s="37"/>
-      <c r="N3" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="O3" s="37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="37" t="s">
         <v>265</v>
       </c>
@@ -10476,14 +10484,16 @@
       <c r="K4" s="37"/>
       <c r="L4" s="37"/>
       <c r="M4" s="37"/>
-      <c r="N4" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="O4" s="37">
+      <c r="N4" s="37"/>
+      <c r="O4" s="37"/>
+      <c r="P4" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="37">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:17">
       <c r="A5" s="37" t="s">
         <v>267</v>
       </c>
@@ -10499,7 +10509,7 @@
       <c r="E5" s="37" t="s">
         <v>262</v>
       </c>
-      <c r="F5" s="59">
+      <c r="F5" s="37">
         <v>2</v>
       </c>
       <c r="G5" s="37">
@@ -10511,14 +10521,16 @@
       <c r="K5" s="37"/>
       <c r="L5" s="37"/>
       <c r="M5" s="37"/>
-      <c r="N5" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="O5" s="59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="36" customHeight="1">
+      <c r="N5" s="37"/>
+      <c r="O5" s="37"/>
+      <c r="P5" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="36" customHeight="1">
       <c r="A6" s="37" t="s">
         <v>269</v>
       </c>
@@ -10552,14 +10564,16 @@
       <c r="M6" s="37" t="s">
         <v>271</v>
       </c>
-      <c r="N6" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="O6" s="37">
+      <c r="N6" s="37"/>
+      <c r="O6" s="37"/>
+      <c r="P6" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="37">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="36" customHeight="1">
+    <row r="7" spans="1:17" ht="36" customHeight="1">
       <c r="A7" s="37" t="s">
         <v>272</v>
       </c>
@@ -10576,7 +10590,7 @@
         <v>262</v>
       </c>
       <c r="F7" s="37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" s="37">
         <v>0</v>
@@ -10589,14 +10603,16 @@
       </c>
       <c r="L7" s="37"/>
       <c r="M7" s="37"/>
-      <c r="N7" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" s="59">
+      <c r="N7" s="37"/>
+      <c r="O7" s="37"/>
+      <c r="P7" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="59">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="36" customHeight="1">
+    <row r="8" spans="1:17" ht="36" customHeight="1">
       <c r="A8" s="37" t="s">
         <v>275</v>
       </c>
@@ -10613,7 +10629,7 @@
         <v>262</v>
       </c>
       <c r="F8" s="37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="37">
         <v>0</v>
@@ -10626,14 +10642,16 @@
       </c>
       <c r="L8" s="37"/>
       <c r="M8" s="37"/>
-      <c r="N8" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8" s="59">
+      <c r="N8" s="37"/>
+      <c r="O8" s="37"/>
+      <c r="P8" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="59">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:17">
       <c r="A9" s="37"/>
       <c r="B9" s="37"/>
       <c r="C9" s="37"/>
@@ -10649,8 +10667,10 @@
       <c r="M9" s="37"/>
       <c r="N9" s="37"/>
       <c r="O9" s="37"/>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="P9" s="37"/>
+      <c r="Q9" s="37"/>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="37"/>
       <c r="B10" s="37"/>
       <c r="C10" s="37"/>
@@ -10666,8 +10686,10 @@
       <c r="M10" s="37"/>
       <c r="N10" s="37"/>
       <c r="O10" s="37"/>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="P10" s="37"/>
+      <c r="Q10" s="37"/>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="37"/>
       <c r="B11" s="37"/>
       <c r="C11" s="37"/>
@@ -10683,8 +10705,10 @@
       <c r="M11" s="37"/>
       <c r="N11" s="37"/>
       <c r="O11" s="37"/>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="P11" s="37"/>
+      <c r="Q11" s="37"/>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" s="37"/>
       <c r="B12" s="37"/>
       <c r="C12" s="37"/>
@@ -10700,8 +10724,10 @@
       <c r="M12" s="37"/>
       <c r="N12" s="37"/>
       <c r="O12" s="37"/>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="P12" s="37"/>
+      <c r="Q12" s="37"/>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="37"/>
       <c r="B13" s="37"/>
       <c r="C13" s="37"/>
@@ -10717,8 +10743,10 @@
       <c r="M13" s="37"/>
       <c r="N13" s="37"/>
       <c r="O13" s="37"/>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="P13" s="37"/>
+      <c r="Q13" s="37"/>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="37"/>
       <c r="B14" s="37"/>
       <c r="C14" s="37"/>
@@ -10734,8 +10762,10 @@
       <c r="M14" s="37"/>
       <c r="N14" s="37"/>
       <c r="O14" s="37"/>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="P14" s="37"/>
+      <c r="Q14" s="37"/>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="37"/>
       <c r="B15" s="37"/>
       <c r="C15" s="37"/>
@@ -10751,8 +10781,10 @@
       <c r="M15" s="37"/>
       <c r="N15" s="37"/>
       <c r="O15" s="37"/>
-    </row>
-    <row r="16" spans="1:15">
+      <c r="P15" s="37"/>
+      <c r="Q15" s="37"/>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="37"/>
       <c r="B16" s="37"/>
       <c r="C16" s="37"/>
@@ -10768,8 +10800,10 @@
       <c r="M16" s="37"/>
       <c r="N16" s="37"/>
       <c r="O16" s="37"/>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="P16" s="37"/>
+      <c r="Q16" s="37"/>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" s="37"/>
       <c r="B17" s="37"/>
       <c r="C17" s="37"/>
@@ -10785,8 +10819,10 @@
       <c r="M17" s="37"/>
       <c r="N17" s="37"/>
       <c r="O17" s="37"/>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="P17" s="37"/>
+      <c r="Q17" s="37"/>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" s="37"/>
       <c r="B18" s="37"/>
       <c r="C18" s="37"/>
@@ -10802,8 +10838,10 @@
       <c r="M18" s="37"/>
       <c r="N18" s="37"/>
       <c r="O18" s="37"/>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="P18" s="37"/>
+      <c r="Q18" s="37"/>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" s="37"/>
       <c r="B19" s="37"/>
       <c r="C19" s="37"/>
@@ -10819,8 +10857,10 @@
       <c r="M19" s="37"/>
       <c r="N19" s="37"/>
       <c r="O19" s="37"/>
-    </row>
-    <row r="20" spans="1:15">
+      <c r="P19" s="37"/>
+      <c r="Q19" s="37"/>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20" s="37"/>
       <c r="B20" s="37"/>
       <c r="C20" s="37"/>
@@ -10836,9 +10876,11 @@
       <c r="M20" s="37"/>
       <c r="N20" s="37"/>
       <c r="O20" s="37"/>
+      <c r="P20" s="37"/>
+      <c r="Q20" s="37"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -10847,19 +10889,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J54"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" style="32" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" style="32" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" style="32" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.25" style="32" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5" style="32" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5" style="32" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.625" style="32" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.875" style="32" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.125" style="32" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.265625" style="32" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.46484375" style="32" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.46484375" style="32" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.59765625" style="32" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.86328125" style="32" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.1328125" style="32" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="48" style="32" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="150.5" style="32" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.875" style="36"/>
+    <col min="10" max="10" width="150.46484375" style="32" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.86328125" style="36" customWidth="1"/>
+    <col min="12" max="16384" width="8.86328125" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -11170,7 +11213,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="30" customHeight="1">
+    <row r="12" spans="1:10" ht="33" customHeight="1">
       <c r="A12" s="50" t="s">
         <v>258</v>
       </c>
@@ -12059,7 +12102,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="18.75">
+    <row r="45" spans="1:10">
       <c r="A45" s="50" t="s">
         <v>269</v>
       </c>
@@ -12348,7 +12391,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -12358,14 +12401,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:F114"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="37" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.75" style="3" customWidth="1"/>
+    <col min="2" max="2" width="19.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.46484375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.86328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.73046875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1">
@@ -13532,7 +13575,7 @@
       <c r="C114" s="24"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -13541,33 +13584,33 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AC50"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="19" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.5" style="32" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.875" style="32" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="4.5" style="32" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="4.5" style="27" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="4.5" style="33" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.25" style="33" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.875" style="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.46484375" style="32" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.86328125" style="32" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="4.46484375" style="32" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="4.46484375" style="27" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="4.46484375" style="33" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.265625" style="33" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.86328125" style="33" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="4" style="34" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.875" style="34" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.25" style="34" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.86328125" style="34" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.265625" style="34" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="4" style="34" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.5" style="32" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.875" style="32" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="4.5" style="32" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.125" style="35" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.46484375" style="32" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.86328125" style="32" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="4.46484375" style="32" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.1328125" style="35" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="5" style="35" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.875" style="35" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.125" style="35" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.25" style="35" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.125" style="35" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.86328125" style="35" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.1328125" style="35" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.265625" style="35" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.1328125" style="35" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="5" style="35" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.25" style="35" bestFit="1" customWidth="1"/>
-    <col min="30" max="84" width="9" style="9" customWidth="1"/>
-    <col min="85" max="16384" width="9" style="9"/>
+    <col min="29" max="29" width="5.265625" style="35" bestFit="1" customWidth="1"/>
+    <col min="30" max="85" width="9" style="9" customWidth="1"/>
+    <col min="86" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="15.4" customHeight="1">
@@ -14215,7 +14258,7 @@
       <c r="A50" s="10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -14225,12 +14268,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:E114"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="25.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="49.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.46484375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.3984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="49.1328125" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -15137,7 +15180,7 @@
     <row r="112" ht="15" customHeight="1"/>
     <row r="114" ht="15" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -15146,15 +15189,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G357"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="14.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.125" style="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.125" style="6" customWidth="1"/>
-    <col min="7" max="7" width="9.25" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.46484375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.1328125" style="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.86328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.1328125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="9.265625" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -23350,7 +23393,7 @@
       <c r="F357" s="10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -23360,18 +23403,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:J129"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="16.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.3984375" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5" style="7" customWidth="1"/>
-    <col min="7" max="7" width="11.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="41.75" style="3" customWidth="1"/>
-    <col min="10" max="10" width="15.125" style="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.1328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.46484375" style="7" customWidth="1"/>
+    <col min="7" max="7" width="11.1328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="41.73046875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="15.1328125" style="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -27091,7 +27134,7 @@
       <c r="A129" s="10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="15"/>
   <conditionalFormatting sqref="A1:A8 A27 A30 A34 A40 A44 A57:A58 A67 A103 A116:A1048576">
     <cfRule type="duplicateValues" dxfId="161" priority="2013"/>
   </conditionalFormatting>
@@ -27132,8 +27175,8 @@
     <cfRule type="duplicateValues" dxfId="149" priority="2366"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A77 A79:A100 A102:A106 A114:A1048576">
-    <cfRule type="duplicateValues" dxfId="148" priority="2331"/>
-    <cfRule type="duplicateValues" dxfId="147" priority="2332"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="2332"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="2331"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A5">
     <cfRule type="duplicateValues" dxfId="146" priority="162"/>
@@ -27160,32 +27203,32 @@
     <cfRule type="duplicateValues" dxfId="137" priority="126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="136" priority="123"/>
-    <cfRule type="duplicateValues" dxfId="135" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
     <cfRule type="duplicateValues" dxfId="134" priority="121"/>
     <cfRule type="duplicateValues" dxfId="133" priority="122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
-    <cfRule type="duplicateValues" dxfId="132" priority="119"/>
-    <cfRule type="duplicateValues" dxfId="131" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18">
-    <cfRule type="duplicateValues" dxfId="130" priority="117"/>
-    <cfRule type="duplicateValues" dxfId="129" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:A20">
-    <cfRule type="duplicateValues" dxfId="128" priority="115"/>
-    <cfRule type="duplicateValues" dxfId="127" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
     <cfRule type="duplicateValues" dxfId="126" priority="112"/>
     <cfRule type="duplicateValues" dxfId="125" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A26">
-    <cfRule type="duplicateValues" dxfId="124" priority="110"/>
-    <cfRule type="duplicateValues" dxfId="123" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27">
     <cfRule type="duplicateValues" dxfId="122" priority="140"/>
@@ -27224,20 +27267,20 @@
     <cfRule type="duplicateValues" dxfId="105" priority="632"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40">
-    <cfRule type="duplicateValues" dxfId="104" priority="154"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="154"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41">
     <cfRule type="duplicateValues" dxfId="102" priority="78"/>
     <cfRule type="duplicateValues" dxfId="101" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43">
-    <cfRule type="duplicateValues" dxfId="100" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44">
-    <cfRule type="duplicateValues" dxfId="98" priority="146"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="146"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45">
     <cfRule type="duplicateValues" dxfId="96" priority="90"/>
@@ -27248,8 +27291,8 @@
     <cfRule type="duplicateValues" dxfId="93" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:A48">
-    <cfRule type="duplicateValues" dxfId="92" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:A52">
     <cfRule type="duplicateValues" dxfId="90" priority="106"/>
@@ -27260,32 +27303,32 @@
     <cfRule type="duplicateValues" dxfId="87" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54">
-    <cfRule type="duplicateValues" dxfId="86" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55">
-    <cfRule type="duplicateValues" dxfId="84" priority="133"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="133"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56">
-    <cfRule type="duplicateValues" dxfId="82" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57">
-    <cfRule type="duplicateValues" dxfId="80" priority="148"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="148"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58">
     <cfRule type="duplicateValues" dxfId="78" priority="152"/>
     <cfRule type="duplicateValues" dxfId="77" priority="153"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59">
-    <cfRule type="duplicateValues" dxfId="76" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A60">
-    <cfRule type="duplicateValues" dxfId="74" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61">
     <cfRule type="duplicateValues" dxfId="72" priority="86"/>
@@ -27296,8 +27339,8 @@
     <cfRule type="duplicateValues" dxfId="69" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63">
-    <cfRule type="duplicateValues" dxfId="68" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64">
     <cfRule type="duplicateValues" dxfId="66" priority="60"/>
@@ -27308,8 +27351,8 @@
     <cfRule type="duplicateValues" dxfId="63" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A66">
-    <cfRule type="duplicateValues" dxfId="62" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67">
     <cfRule type="duplicateValues" dxfId="60" priority="150"/>
@@ -27320,8 +27363,8 @@
     <cfRule type="duplicateValues" dxfId="57" priority="866"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69">
-    <cfRule type="duplicateValues" dxfId="56" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70">
     <cfRule type="duplicateValues" dxfId="54" priority="42"/>
@@ -27332,36 +27375,36 @@
     <cfRule type="duplicateValues" dxfId="51" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72:A73">
-    <cfRule type="duplicateValues" dxfId="50" priority="99"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="99"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A74">
     <cfRule type="duplicateValues" dxfId="48" priority="95"/>
     <cfRule type="duplicateValues" dxfId="47" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75:A77">
-    <cfRule type="duplicateValues" dxfId="46" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A78">
-    <cfRule type="duplicateValues" dxfId="44" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A79 A106">
     <cfRule type="duplicateValues" dxfId="42" priority="1727"/>
     <cfRule type="duplicateValues" dxfId="41" priority="1728"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A80">
-    <cfRule type="duplicateValues" dxfId="40" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A82:A83">
     <cfRule type="duplicateValues" dxfId="38" priority="982"/>
     <cfRule type="duplicateValues" dxfId="37" priority="983"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A84">
-    <cfRule type="duplicateValues" dxfId="36" priority="135"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A85">
     <cfRule type="duplicateValues" dxfId="34" priority="13"/>
@@ -27392,12 +27435,12 @@
     <cfRule type="duplicateValues" dxfId="21" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A96">
-    <cfRule type="duplicateValues" dxfId="20" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A98">
-    <cfRule type="duplicateValues" dxfId="18" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99">
     <cfRule type="duplicateValues" dxfId="16" priority="26"/>
@@ -27412,12 +27455,12 @@
     <cfRule type="duplicateValues" dxfId="11" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A102">
-    <cfRule type="duplicateValues" dxfId="10" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A103">
-    <cfRule type="duplicateValues" dxfId="8" priority="142"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="142"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A104:A105">
     <cfRule type="duplicateValues" dxfId="6" priority="1709"/>
@@ -27428,8 +27471,8 @@
     <cfRule type="duplicateValues" dxfId="3" priority="1944"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114:A115">
-    <cfRule type="duplicateValues" dxfId="2" priority="131"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="131"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="395"/>
@@ -27442,14 +27485,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="45.625" customWidth="1"/>
-    <col min="2" max="2" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.75" customWidth="1"/>
-    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="45.59765625" customWidth="1"/>
+    <col min="2" max="2" width="23.46484375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" customWidth="1"/>
+    <col min="5" max="5" width="10.46484375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1">
@@ -27869,7 +27912,7 @@
       <c r="F24" s="7"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -5511,7 +5511,7 @@
       </c>
       <c r="L5" s="37" t="inlineStr">
         <is>
-          <t>res://Assets/Portrait/StoryNpc/gu_wen/gu_wen_before.png</t>
+          <t>res://Assets/Portrait/StoryNpc/gu_wen/gu_wen.png</t>
         </is>
       </c>
       <c r="M5" s="37" t="inlineStr"/>

--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2472151D-0DA7-4DBD-B698-13D57606EB5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE191A9-5D83-4E13-A0CD-857706105EA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" r:id="rId1"/>
@@ -2059,9 +2059,6 @@
 【标准方】金锁固精丸</t>
   </si>
   <si>
-    <t>ren_shen</t>
-  </si>
-  <si>
     <t>妊娠</t>
   </si>
   <si>
@@ -3535,6 +3532,9 @@
   </si>
   <si>
     <t>ge_gen</t>
+  </si>
+  <si>
+    <t>ren_shen</t>
   </si>
   <si>
     <t>熟地黄</t>
@@ -6072,7 +6072,7 @@
 在搜索栏输入药材，方剂，疾病的中文名或拼音，拼音首字母可快速查找。</t>
   </si>
   <si>
-    <t>ren_shen_disease</t>
+    <t>ren_shen</t>
     <phoneticPr fontId="14"/>
   </si>
 </sst>
@@ -8361,8 +8361,8 @@
     <col min="7" max="7" width="25.125" style="23" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.25" style="23" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="33.375" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="42" width="9.125" style="23" customWidth="1"/>
-    <col min="43" max="16384" width="9.125" style="23"/>
+    <col min="10" max="43" width="9.125" style="23" customWidth="1"/>
+    <col min="44" max="16384" width="9.125" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.399999999999999" customHeight="1">
@@ -10313,8 +10313,8 @@
     <col min="14" max="14" width="12" style="36" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.75" style="36" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10.875" style="36" bestFit="1" customWidth="1"/>
-    <col min="17" max="65" width="9" style="36" customWidth="1"/>
-    <col min="66" max="16384" width="9" style="36"/>
+    <col min="17" max="66" width="9" style="36" customWidth="1"/>
+    <col min="67" max="16384" width="9" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -10905,8 +10905,8 @@
     <col min="8" max="8" width="8.125" style="32" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="48" style="32" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="150.5" style="32" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="8.875" style="36" customWidth="1"/>
-    <col min="17" max="16384" width="8.875" style="36"/>
+    <col min="11" max="17" width="8.875" style="36" customWidth="1"/>
+    <col min="18" max="16384" width="8.875" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -11286,7 +11286,7 @@
       <c r="H14" s="53" t="s">
         <v>304</v>
       </c>
-      <c r="I14" s="66" t="s">
+      <c r="I14" s="67" t="s">
         <v>318</v>
       </c>
       <c r="J14" s="56" t="s">
@@ -11372,7 +11372,7 @@
       <c r="H17" s="53" t="s">
         <v>304</v>
       </c>
-      <c r="I17" s="66" t="s">
+      <c r="I17" s="67" t="s">
         <v>322</v>
       </c>
       <c r="J17" s="55" t="s">
@@ -12210,7 +12210,7 @@
       <c r="H48" s="53" t="s">
         <v>362</v>
       </c>
-      <c r="I48" s="67"/>
+      <c r="I48" s="66"/>
       <c r="J48" s="58" t="s">
         <v>363</v>
       </c>
@@ -13669,59 +13669,59 @@
         <v>1251</v>
       </c>
       <c r="B47" s="47" t="s">
+        <v>591</v>
+      </c>
+      <c r="C47" s="25" t="s">
         <v>592</v>
       </c>
-      <c r="C47" s="25" t="s">
+      <c r="D47" s="10" t="s">
         <v>593</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>594</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>391</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="B48" s="10" t="s">
         <v>596</v>
       </c>
-      <c r="B48" s="10" t="s">
+      <c r="C48" s="25" t="s">
         <v>597</v>
       </c>
-      <c r="C48" s="25" t="s">
+      <c r="D48" s="10" t="s">
         <v>598</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>599</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>391</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="10" t="s">
+        <v>600</v>
+      </c>
+      <c r="B49" s="10" t="s">
         <v>601</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="C49" s="25" t="s">
         <v>602</v>
       </c>
-      <c r="C49" s="25" t="s">
+      <c r="D49" s="10" t="s">
         <v>603</v>
-      </c>
-      <c r="D49" s="10" t="s">
-        <v>604</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>391</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15" customHeight="1">
@@ -13942,8 +13942,8 @@
     <col min="27" max="27" width="5.125" style="35" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="5" style="35" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="5.25" style="35" bestFit="1" customWidth="1"/>
-    <col min="30" max="90" width="9" style="9" customWidth="1"/>
-    <col min="91" max="16384" width="9" style="9"/>
+    <col min="30" max="91" width="9" style="9" customWidth="1"/>
+    <col min="92" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="15.4" customHeight="1">
@@ -13951,88 +13951,88 @@
         <v>382</v>
       </c>
       <c r="B1" s="28" t="s">
+        <v>605</v>
+      </c>
+      <c r="C1" s="28" t="s">
         <v>606</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="D1" s="28" t="s">
         <v>607</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="E1" s="28" t="s">
         <v>608</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="F1" s="26" t="s">
         <v>609</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="G1" s="26" t="s">
         <v>610</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="H1" s="26" t="s">
         <v>611</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="I1" s="26" t="s">
         <v>612</v>
       </c>
-      <c r="I1" s="26" t="s">
+      <c r="J1" s="29" t="s">
         <v>613</v>
       </c>
-      <c r="J1" s="29" t="s">
+      <c r="K1" s="29" t="s">
         <v>614</v>
       </c>
-      <c r="K1" s="29" t="s">
+      <c r="L1" s="29" t="s">
         <v>615</v>
       </c>
-      <c r="L1" s="29" t="s">
+      <c r="M1" s="29" t="s">
         <v>616</v>
       </c>
-      <c r="M1" s="29" t="s">
+      <c r="N1" s="30" t="s">
         <v>617</v>
       </c>
-      <c r="N1" s="30" t="s">
+      <c r="O1" s="30" t="s">
         <v>618</v>
       </c>
-      <c r="O1" s="30" t="s">
+      <c r="P1" s="30" t="s">
         <v>619</v>
       </c>
-      <c r="P1" s="30" t="s">
+      <c r="Q1" s="30" t="s">
         <v>620</v>
       </c>
-      <c r="Q1" s="30" t="s">
+      <c r="R1" s="28" t="s">
         <v>621</v>
       </c>
-      <c r="R1" s="28" t="s">
+      <c r="S1" s="28" t="s">
         <v>622</v>
       </c>
-      <c r="S1" s="28" t="s">
+      <c r="T1" s="28" t="s">
         <v>623</v>
       </c>
-      <c r="T1" s="28" t="s">
+      <c r="U1" s="28" t="s">
         <v>624</v>
       </c>
-      <c r="U1" s="28" t="s">
+      <c r="V1" s="31" t="s">
         <v>625</v>
       </c>
-      <c r="V1" s="31" t="s">
+      <c r="W1" s="31" t="s">
         <v>626</v>
       </c>
-      <c r="W1" s="31" t="s">
+      <c r="X1" s="31" t="s">
         <v>627</v>
       </c>
-      <c r="X1" s="31" t="s">
+      <c r="Y1" s="31" t="s">
         <v>628</v>
       </c>
-      <c r="Y1" s="31" t="s">
+      <c r="Z1" s="31" t="s">
         <v>629</v>
       </c>
-      <c r="Z1" s="31" t="s">
+      <c r="AA1" s="31" t="s">
         <v>630</v>
       </c>
-      <c r="AA1" s="31" t="s">
+      <c r="AB1" s="31" t="s">
         <v>631</v>
       </c>
-      <c r="AB1" s="31" t="s">
+      <c r="AC1" s="31" t="s">
         <v>632</v>
-      </c>
-      <c r="AC1" s="31" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="18" customHeight="1">
@@ -14517,7 +14517,7 @@
     </row>
     <row r="47" spans="1:28" ht="18" customHeight="1">
       <c r="A47" s="10" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="Q47" s="34">
         <v>1.5</v>
@@ -14531,7 +14531,7 @@
     </row>
     <row r="48" spans="1:28" ht="18" customHeight="1">
       <c r="A48" s="10" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H48" s="27">
         <v>1.5</v>
@@ -14548,7 +14548,7 @@
     </row>
     <row r="49" spans="1:21" ht="18" customHeight="1">
       <c r="A49" s="10" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B49" s="32">
         <v>1.3</v>
@@ -14612,13 +14612,13 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>635</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>636</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>385</v>
@@ -14629,7 +14629,7 @@
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>390</v>
@@ -14638,15 +14638,15 @@
         <v>388</v>
       </c>
       <c r="D2" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>638</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1">
       <c r="A3" s="7" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>395</v>
@@ -14655,15 +14655,15 @@
         <v>394</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>399</v>
@@ -14672,15 +14672,15 @@
         <v>398</v>
       </c>
       <c r="D4" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>643</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>403</v>
@@ -14689,15 +14689,15 @@
         <v>402</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>407</v>
@@ -14706,15 +14706,15 @@
         <v>406</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>412</v>
@@ -14723,15 +14723,15 @@
         <v>410</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>650</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>417</v>
@@ -14740,15 +14740,15 @@
         <v>415</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>653</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>421</v>
@@ -14757,15 +14757,15 @@
         <v>420</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>425</v>
@@ -14774,15 +14774,15 @@
         <v>424</v>
       </c>
       <c r="D10" s="7" t="s">
+        <v>657</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>658</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>429</v>
@@ -14791,15 +14791,15 @@
         <v>428</v>
       </c>
       <c r="D11" s="7" t="s">
+        <v>660</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>661</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>433</v>
@@ -14808,15 +14808,15 @@
         <v>432</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1">
       <c r="A13" s="7" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>438</v>
@@ -14825,15 +14825,15 @@
         <v>436</v>
       </c>
       <c r="D13" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>666</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1">
       <c r="A14" s="7" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>443</v>
@@ -14842,15 +14842,15 @@
         <v>441</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1">
       <c r="A15" s="7" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>448</v>
@@ -14859,15 +14859,15 @@
         <v>446</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1">
       <c r="A16" s="7" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>453</v>
@@ -14876,15 +14876,15 @@
         <v>451</v>
       </c>
       <c r="D16" s="7" t="s">
+        <v>672</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>673</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1">
       <c r="A17" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>458</v>
@@ -14893,15 +14893,15 @@
         <v>456</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>462</v>
@@ -14910,15 +14910,15 @@
         <v>461</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1">
       <c r="A19" s="7" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>467</v>
@@ -14927,15 +14927,15 @@
         <v>465</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1">
       <c r="A20" s="7" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>471</v>
@@ -14944,15 +14944,15 @@
         <v>470</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1">
       <c r="A21" s="7" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>476</v>
@@ -14961,15 +14961,15 @@
         <v>474</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1">
       <c r="A22" s="7" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>479</v>
@@ -14978,15 +14978,15 @@
         <v>281</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="18" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>484</v>
@@ -14995,15 +14995,15 @@
         <v>482</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="18" customHeight="1">
       <c r="A24" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>489</v>
@@ -15012,15 +15012,15 @@
         <v>487</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="18" customHeight="1">
       <c r="A25" s="7" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>494</v>
@@ -15029,15 +15029,15 @@
         <v>492</v>
       </c>
       <c r="D25" s="7" t="s">
+        <v>691</v>
+      </c>
+      <c r="E25" s="7" t="s">
         <v>692</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="18" customHeight="1">
       <c r="A26" s="7" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>499</v>
@@ -15046,15 +15046,15 @@
         <v>497</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="18" customHeight="1">
       <c r="A27" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>503</v>
@@ -15063,15 +15063,15 @@
         <v>502</v>
       </c>
       <c r="D27" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="E27" s="7" t="s">
         <v>697</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="18" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>508</v>
@@ -15080,15 +15080,15 @@
         <v>506</v>
       </c>
       <c r="D28" s="11" t="s">
+        <v>699</v>
+      </c>
+      <c r="E28" s="7" t="s">
         <v>700</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="18" customHeight="1">
       <c r="A29" s="7" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>512</v>
@@ -15097,15 +15097,15 @@
         <v>511</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="18" customHeight="1">
       <c r="A30" s="7" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>515</v>
@@ -15114,15 +15114,15 @@
         <v>271</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="18" customHeight="1">
       <c r="A31" s="7" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>519</v>
@@ -15131,15 +15131,15 @@
         <v>518</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="18" customHeight="1">
       <c r="A32" s="7" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>524</v>
@@ -15148,15 +15148,15 @@
         <v>522</v>
       </c>
       <c r="D32" s="7" t="s">
+        <v>708</v>
+      </c>
+      <c r="E32" s="7" t="s">
         <v>709</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="18" customHeight="1">
       <c r="A33" s="7" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>529</v>
@@ -15165,15 +15165,15 @@
         <v>527</v>
       </c>
       <c r="D33" s="7" t="s">
+        <v>711</v>
+      </c>
+      <c r="E33" s="7" t="s">
         <v>712</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="18" customHeight="1">
       <c r="A34" s="7" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>534</v>
@@ -15182,15 +15182,15 @@
         <v>532</v>
       </c>
       <c r="D34" s="7" t="s">
+        <v>714</v>
+      </c>
+      <c r="E34" s="7" t="s">
         <v>715</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="18" customHeight="1">
       <c r="A35" s="7" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>539</v>
@@ -15199,15 +15199,15 @@
         <v>537</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="18" customHeight="1">
       <c r="A36" s="7" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>543</v>
@@ -15216,15 +15216,15 @@
         <v>542</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="18" customHeight="1">
       <c r="A37" s="11" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>548</v>
@@ -15233,15 +15233,15 @@
         <v>546</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="18" customHeight="1">
       <c r="A38" s="7" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>552</v>
@@ -15250,15 +15250,15 @@
         <v>551</v>
       </c>
       <c r="D38" s="7" t="s">
+        <v>723</v>
+      </c>
+      <c r="E38" s="7" t="s">
         <v>724</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="18" customHeight="1">
       <c r="A39" s="7" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>556</v>
@@ -15267,15 +15267,15 @@
         <v>555</v>
       </c>
       <c r="D39" s="7" t="s">
+        <v>726</v>
+      </c>
+      <c r="E39" s="7" t="s">
         <v>727</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="18" customHeight="1">
       <c r="A40" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>561</v>
@@ -15284,15 +15284,15 @@
         <v>559</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="18" customHeight="1">
       <c r="A41" s="7" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>566</v>
@@ -15301,15 +15301,15 @@
         <v>564</v>
       </c>
       <c r="D41" s="7" t="s">
+        <v>731</v>
+      </c>
+      <c r="E41" s="7" t="s">
         <v>732</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>733</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="18" customHeight="1">
       <c r="A42" s="7" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>571</v>
@@ -15318,15 +15318,15 @@
         <v>569</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="18" customHeight="1">
       <c r="A43" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>576</v>
@@ -15335,15 +15335,15 @@
         <v>574</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="18" customHeight="1">
       <c r="A44" s="7" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>581</v>
@@ -15352,15 +15352,15 @@
         <v>579</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="18" customHeight="1">
       <c r="A45" s="7" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>585</v>
@@ -15369,15 +15369,15 @@
         <v>584</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="18" customHeight="1">
       <c r="A46" s="7" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>589</v>
@@ -15386,61 +15386,61 @@
         <v>588</v>
       </c>
       <c r="D46" s="7" t="s">
+        <v>742</v>
+      </c>
+      <c r="E46" s="7" t="s">
         <v>743</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="18" customHeight="1">
       <c r="A47" s="11" t="s">
+        <v>744</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>593</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>591</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>714</v>
+      </c>
+      <c r="E47" s="7" t="s">
         <v>745</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>594</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>592</v>
-      </c>
-      <c r="D47" s="11" t="s">
-        <v>715</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="18" customHeight="1">
       <c r="A48" s="7" t="s">
+        <v>746</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>598</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>596</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="E48" s="7" t="s">
         <v>747</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>599</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>597</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>638</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="18" customHeight="1">
       <c r="A49" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="E49" s="7" t="s">
         <v>749</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>604</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>602</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>638</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="18" customHeight="1">
@@ -15535,25 +15535,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="12" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B1" s="63" t="s">
+        <v>750</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>751</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="D1" s="17" t="s">
         <v>752</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="E1" s="12" t="s">
         <v>753</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="F1" s="12" t="s">
         <v>754</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="G1" s="12" t="s">
         <v>755</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -15561,19 +15561,19 @@
         <v>390</v>
       </c>
       <c r="B2" s="10" t="s">
+        <v>756</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>757</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="D2" s="18" t="s">
         <v>758</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>759</v>
       </c>
       <c r="E2" s="10">
         <v>3</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G2" s="10" t="b">
         <v>1</v>
@@ -15584,19 +15584,19 @@
         <v>390</v>
       </c>
       <c r="B3" s="10" t="s">
+        <v>760</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>761</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="19" t="s">
         <v>762</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>763</v>
       </c>
       <c r="E3" s="10">
         <v>2</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G3" s="10" t="b">
         <v>1</v>
@@ -15607,19 +15607,19 @@
         <v>390</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>763</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>764</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="D4" s="20" t="s">
         <v>765</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>766</v>
       </c>
       <c r="E4" s="10">
         <v>2</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G4" s="10" t="b">
         <v>1</v>
@@ -15630,19 +15630,19 @@
         <v>390</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="D5" s="17" t="s">
         <v>768</v>
       </c>
-      <c r="D5" s="17" t="s">
-        <v>769</v>
-      </c>
       <c r="E5" s="10">
         <v>1</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G5" s="10" t="b">
         <v>1</v>
@@ -15653,19 +15653,19 @@
         <v>395</v>
       </c>
       <c r="B6" s="10" t="s">
+        <v>760</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>761</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>762</v>
-      </c>
       <c r="D6" s="18" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E6" s="10">
         <v>3</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G6" s="10" t="b">
         <v>1</v>
@@ -15676,19 +15676,19 @@
         <v>395</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>769</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>770</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>771</v>
-      </c>
       <c r="D7" s="19" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E7" s="10">
         <v>3</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G7" s="10" t="b">
         <v>1</v>
@@ -15699,19 +15699,19 @@
         <v>395</v>
       </c>
       <c r="B8" s="10" t="s">
+        <v>771</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>772</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>773</v>
-      </c>
       <c r="D8" s="20" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E8" s="10">
         <v>3</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G8" s="10" t="b">
         <v>1</v>
@@ -15722,19 +15722,19 @@
         <v>395</v>
       </c>
       <c r="B9" s="10" t="s">
+        <v>773</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>774</v>
       </c>
-      <c r="C9" s="10" t="s">
-        <v>775</v>
-      </c>
       <c r="D9" s="20" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E9" s="10">
         <v>2</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G9" s="10" t="b">
         <v>1</v>
@@ -15745,19 +15745,19 @@
         <v>395</v>
       </c>
       <c r="B10" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="D10" s="17" t="s">
         <v>768</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>769</v>
       </c>
       <c r="E10" s="10">
         <v>2</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G10" s="10" t="b">
         <v>1</v>
@@ -15768,19 +15768,19 @@
         <v>399</v>
       </c>
       <c r="B11" s="10" t="s">
+        <v>775</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>776</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="D11" s="18" t="s">
+        <v>758</v>
+      </c>
+      <c r="E11" s="10">
+        <v>1</v>
+      </c>
+      <c r="F11" s="10" t="s">
         <v>777</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>759</v>
-      </c>
-      <c r="E11" s="10">
-        <v>1</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>778</v>
       </c>
       <c r="G11" s="10" t="b">
         <v>1</v>
@@ -15791,19 +15791,19 @@
         <v>399</v>
       </c>
       <c r="B12" s="10" t="s">
+        <v>778</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>779</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>780</v>
-      </c>
       <c r="D12" s="18" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E12" s="10">
         <v>1</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G12" s="10" t="b">
         <v>1</v>
@@ -15814,19 +15814,19 @@
         <v>399</v>
       </c>
       <c r="B13" s="10" t="s">
+        <v>780</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>781</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>782</v>
-      </c>
       <c r="D13" s="19" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E13" s="10">
         <v>6</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G13" s="10" t="b">
         <v>1</v>
@@ -15837,19 +15837,19 @@
         <v>399</v>
       </c>
       <c r="B14" s="10" t="s">
+        <v>782</v>
+      </c>
+      <c r="C14" s="10" t="s">
         <v>783</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>784</v>
-      </c>
       <c r="D14" s="19" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E14" s="10">
         <v>4</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G14" s="10" t="b">
         <v>1</v>
@@ -15860,19 +15860,19 @@
         <v>399</v>
       </c>
       <c r="B15" s="10" t="s">
+        <v>784</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>785</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>786</v>
-      </c>
       <c r="D15" s="19" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E15" s="10">
         <v>6</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G15" s="10" t="b">
         <v>1</v>
@@ -15883,19 +15883,19 @@
         <v>399</v>
       </c>
       <c r="B16" s="10" t="s">
+        <v>786</v>
+      </c>
+      <c r="C16" s="10" t="s">
         <v>787</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>788</v>
-      </c>
       <c r="D16" s="19" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E16" s="10">
         <v>5</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G16" s="10" t="b">
         <v>1</v>
@@ -15906,19 +15906,19 @@
         <v>399</v>
       </c>
       <c r="B17" s="10" t="s">
+        <v>788</v>
+      </c>
+      <c r="C17" s="10" t="s">
         <v>789</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>790</v>
-      </c>
       <c r="D17" s="20" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E17" s="10">
         <v>6</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G17" s="10" t="b">
         <v>1</v>
@@ -15929,19 +15929,19 @@
         <v>399</v>
       </c>
       <c r="B18" s="10" t="s">
+        <v>790</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>791</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>792</v>
-      </c>
       <c r="D18" s="20" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E18" s="10">
         <v>4</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G18" s="10" t="b">
         <v>1</v>
@@ -15952,19 +15952,19 @@
         <v>399</v>
       </c>
       <c r="B19" s="10" t="s">
+        <v>792</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>793</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>794</v>
-      </c>
       <c r="D19" s="20" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E19" s="10">
         <v>4</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G19" s="10" t="b">
         <v>1</v>
@@ -15975,19 +15975,19 @@
         <v>399</v>
       </c>
       <c r="B20" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C20" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="D20" s="17" t="s">
         <v>768</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>769</v>
       </c>
       <c r="E20" s="10">
         <v>5</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G20" s="10" t="b">
         <v>1</v>
@@ -15998,19 +15998,19 @@
         <v>403</v>
       </c>
       <c r="B21" s="10" t="s">
+        <v>794</v>
+      </c>
+      <c r="C21" s="10" t="s">
         <v>795</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>796</v>
-      </c>
       <c r="D21" s="18" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E21" s="10">
         <v>1.5</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G21" s="10" t="b">
         <v>1</v>
@@ -16021,19 +16021,19 @@
         <v>403</v>
       </c>
       <c r="B22" s="10" t="s">
+        <v>763</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>764</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>765</v>
-      </c>
       <c r="D22" s="18" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E22" s="10">
         <v>2</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G22" s="10" t="b">
         <v>1</v>
@@ -16044,19 +16044,19 @@
         <v>403</v>
       </c>
       <c r="B23" s="10" t="s">
+        <v>796</v>
+      </c>
+      <c r="C23" s="10" t="s">
         <v>797</v>
       </c>
-      <c r="C23" s="10" t="s">
-        <v>798</v>
-      </c>
       <c r="D23" s="19" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E23" s="10">
         <v>1</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G23" s="10" t="b">
         <v>1</v>
@@ -16067,19 +16067,19 @@
         <v>403</v>
       </c>
       <c r="B24" s="10" t="s">
+        <v>798</v>
+      </c>
+      <c r="C24" s="10" t="s">
         <v>799</v>
       </c>
-      <c r="C24" s="10" t="s">
-        <v>800</v>
-      </c>
       <c r="D24" s="20" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E24" s="10">
         <v>1</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G24" s="10" t="b">
         <v>1</v>
@@ -16090,19 +16090,19 @@
         <v>403</v>
       </c>
       <c r="B25" s="10" t="s">
+        <v>786</v>
+      </c>
+      <c r="C25" s="10" t="s">
         <v>787</v>
       </c>
-      <c r="C25" s="10" t="s">
-        <v>788</v>
-      </c>
       <c r="D25" s="20" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E25" s="10">
         <v>1</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G25" s="10" t="b">
         <v>1</v>
@@ -16113,19 +16113,19 @@
         <v>403</v>
       </c>
       <c r="B26" s="10" t="s">
+        <v>800</v>
+      </c>
+      <c r="C26" s="10" t="s">
         <v>801</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>802</v>
-      </c>
       <c r="D26" s="20" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E26" s="10">
         <v>1</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G26" s="10" t="b">
         <v>1</v>
@@ -16136,19 +16136,19 @@
         <v>403</v>
       </c>
       <c r="B27" s="10" t="s">
+        <v>802</v>
+      </c>
+      <c r="C27" s="10" t="s">
         <v>803</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>804</v>
-      </c>
       <c r="D27" s="20" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E27" s="10">
         <v>1</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G27" s="10" t="b">
         <v>1</v>
@@ -16159,19 +16159,19 @@
         <v>407</v>
       </c>
       <c r="B28" s="10" t="s">
+        <v>763</v>
+      </c>
+      <c r="C28" s="10" t="s">
         <v>764</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>765</v>
-      </c>
       <c r="D28" s="18" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E28" s="10">
         <v>3</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G28" s="10" t="b">
         <v>1</v>
@@ -16182,19 +16182,19 @@
         <v>407</v>
       </c>
       <c r="B29" s="10" t="s">
+        <v>804</v>
+      </c>
+      <c r="C29" s="10" t="s">
         <v>805</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>806</v>
-      </c>
       <c r="D29" s="18" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E29" s="10">
         <v>3</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G29" s="10" t="b">
         <v>1</v>
@@ -16205,19 +16205,19 @@
         <v>407</v>
       </c>
       <c r="B30" s="10" t="s">
+        <v>806</v>
+      </c>
+      <c r="C30" s="10" t="s">
         <v>807</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>808</v>
-      </c>
       <c r="D30" s="19" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E30" s="10">
         <v>3</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G30" s="10" t="b">
         <v>1</v>
@@ -16228,19 +16228,19 @@
         <v>407</v>
       </c>
       <c r="B31" s="10" t="s">
+        <v>808</v>
+      </c>
+      <c r="C31" s="10" t="s">
         <v>809</v>
       </c>
-      <c r="C31" s="10" t="s">
-        <v>810</v>
-      </c>
       <c r="D31" s="19" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E31" s="10">
         <v>3</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G31" s="10" t="b">
         <v>1</v>
@@ -16257,13 +16257,13 @@
         <v>15</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E32" s="10">
         <v>3</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G32" s="10" t="b">
         <v>1</v>
@@ -16274,19 +16274,19 @@
         <v>407</v>
       </c>
       <c r="B33" s="10" t="s">
+        <v>810</v>
+      </c>
+      <c r="C33" s="10" t="s">
         <v>811</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>812</v>
-      </c>
       <c r="D33" s="20" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E33" s="10">
         <v>2</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G33" s="10" t="b">
         <v>1</v>
@@ -16297,19 +16297,19 @@
         <v>407</v>
       </c>
       <c r="B34" s="10" t="s">
+        <v>788</v>
+      </c>
+      <c r="C34" s="10" t="s">
         <v>789</v>
       </c>
-      <c r="C34" s="10" t="s">
-        <v>790</v>
-      </c>
       <c r="D34" s="20" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E34" s="10">
         <v>2</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G34" s="10" t="b">
         <v>1</v>
@@ -16320,19 +16320,19 @@
         <v>407</v>
       </c>
       <c r="B35" s="10" t="s">
+        <v>812</v>
+      </c>
+      <c r="C35" s="10" t="s">
         <v>813</v>
       </c>
-      <c r="C35" s="10" t="s">
-        <v>814</v>
-      </c>
       <c r="D35" s="20" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E35" s="10">
         <v>2</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G35" s="10" t="b">
         <v>1</v>
@@ -16343,19 +16343,19 @@
         <v>407</v>
       </c>
       <c r="B36" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C36" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="D36" s="17" t="s">
         <v>768</v>
       </c>
-      <c r="D36" s="17" t="s">
-        <v>769</v>
-      </c>
       <c r="E36" s="10">
         <v>1</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G36" s="10" t="b">
         <v>1</v>
@@ -16366,19 +16366,19 @@
         <v>412</v>
       </c>
       <c r="B37" s="10" t="s">
+        <v>814</v>
+      </c>
+      <c r="C37" s="10" t="s">
         <v>815</v>
       </c>
-      <c r="C37" s="10" t="s">
-        <v>816</v>
-      </c>
       <c r="D37" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E37" s="10">
         <v>1</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G37" s="10" t="b">
         <v>1</v>
@@ -16389,19 +16389,19 @@
         <v>412</v>
       </c>
       <c r="B38" s="10" t="s">
+        <v>816</v>
+      </c>
+      <c r="C38" s="10" t="s">
         <v>817</v>
       </c>
-      <c r="C38" s="10" t="s">
-        <v>818</v>
-      </c>
       <c r="D38" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E38" s="10">
         <v>1</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G38" s="10" t="b">
         <v>1</v>
@@ -16412,19 +16412,19 @@
         <v>412</v>
       </c>
       <c r="B39" s="10" t="s">
+        <v>818</v>
+      </c>
+      <c r="C39" s="10" t="s">
         <v>819</v>
       </c>
-      <c r="C39" s="10" t="s">
-        <v>820</v>
-      </c>
       <c r="D39" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E39" s="10">
         <v>5</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G39" s="10" t="b">
         <v>1</v>
@@ -16435,19 +16435,19 @@
         <v>417</v>
       </c>
       <c r="B40" s="10" t="s">
+        <v>820</v>
+      </c>
+      <c r="C40" s="10" t="s">
         <v>821</v>
       </c>
-      <c r="C40" s="10" t="s">
-        <v>822</v>
-      </c>
       <c r="D40" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E40" s="10">
         <v>2</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G40" s="10" t="b">
         <v>1</v>
@@ -16458,19 +16458,19 @@
         <v>417</v>
       </c>
       <c r="B41" s="10" t="s">
+        <v>756</v>
+      </c>
+      <c r="C41" s="10" t="s">
         <v>757</v>
       </c>
-      <c r="C41" s="10" t="s">
-        <v>758</v>
-      </c>
       <c r="D41" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E41" s="10">
         <v>3</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G41" s="10" t="b">
         <v>1</v>
@@ -16481,19 +16481,19 @@
         <v>417</v>
       </c>
       <c r="B42" s="10" t="s">
+        <v>769</v>
+      </c>
+      <c r="C42" s="10" t="s">
         <v>770</v>
       </c>
-      <c r="C42" s="10" t="s">
-        <v>771</v>
-      </c>
       <c r="D42" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E42" s="10">
         <v>3</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G42" s="10" t="b">
         <v>1</v>
@@ -16504,19 +16504,19 @@
         <v>417</v>
       </c>
       <c r="B43" s="10" t="s">
+        <v>814</v>
+      </c>
+      <c r="C43" s="10" t="s">
         <v>815</v>
       </c>
-      <c r="C43" s="10" t="s">
-        <v>816</v>
-      </c>
       <c r="D43" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E43" s="10">
         <v>3</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G43" s="10" t="b">
         <v>1</v>
@@ -16527,19 +16527,19 @@
         <v>417</v>
       </c>
       <c r="B44" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C44" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="D44" s="16" t="s">
         <v>768</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>769</v>
       </c>
       <c r="E44" s="10">
         <v>3</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G44" s="10" t="b">
         <v>1</v>
@@ -16550,19 +16550,19 @@
         <v>417</v>
       </c>
       <c r="B45" s="10" t="s">
+        <v>822</v>
+      </c>
+      <c r="C45" s="10" t="s">
         <v>823</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="D45" s="16" t="s">
+        <v>768</v>
+      </c>
+      <c r="E45" s="10">
+        <v>1</v>
+      </c>
+      <c r="F45" s="10" t="s">
         <v>824</v>
-      </c>
-      <c r="D45" s="16" t="s">
-        <v>769</v>
-      </c>
-      <c r="E45" s="10">
-        <v>1</v>
-      </c>
-      <c r="F45" s="10" t="s">
-        <v>825</v>
       </c>
       <c r="G45" s="10" t="b">
         <v>1</v>
@@ -16573,19 +16573,19 @@
         <v>421</v>
       </c>
       <c r="B46" s="10" t="s">
+        <v>825</v>
+      </c>
+      <c r="C46" s="10" t="s">
         <v>826</v>
       </c>
-      <c r="C46" s="10" t="s">
-        <v>827</v>
-      </c>
       <c r="D46" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E46" s="10">
         <v>2</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G46" s="10" t="b">
         <v>1</v>
@@ -16596,19 +16596,19 @@
         <v>421</v>
       </c>
       <c r="B47" s="10" t="s">
+        <v>827</v>
+      </c>
+      <c r="C47" s="10" t="s">
         <v>828</v>
       </c>
-      <c r="C47" s="10" t="s">
-        <v>829</v>
-      </c>
       <c r="D47" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E47" s="10">
         <v>6</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G47" s="10" t="b">
         <v>1</v>
@@ -16619,19 +16619,19 @@
         <v>421</v>
       </c>
       <c r="B48" s="10" t="s">
+        <v>760</v>
+      </c>
+      <c r="C48" s="10" t="s">
         <v>761</v>
       </c>
-      <c r="C48" s="10" t="s">
-        <v>762</v>
-      </c>
       <c r="D48" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E48" s="10">
         <v>3</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G48" s="10" t="b">
         <v>1</v>
@@ -16642,19 +16642,19 @@
         <v>421</v>
       </c>
       <c r="B49" s="10" t="s">
+        <v>829</v>
+      </c>
+      <c r="C49" s="10" t="s">
         <v>830</v>
       </c>
-      <c r="C49" s="10" t="s">
-        <v>831</v>
-      </c>
       <c r="D49" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E49" s="10">
         <v>5</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G49" s="10" t="b">
         <v>1</v>
@@ -16665,19 +16665,19 @@
         <v>421</v>
       </c>
       <c r="B50" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C50" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C50" s="10" t="s">
+      <c r="D50" s="16" t="s">
         <v>768</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>769</v>
       </c>
       <c r="E50" s="10">
         <v>3</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G50" s="10" t="b">
         <v>1</v>
@@ -16688,19 +16688,19 @@
         <v>425</v>
       </c>
       <c r="B51" s="10" t="s">
+        <v>831</v>
+      </c>
+      <c r="C51" s="10" t="s">
         <v>832</v>
       </c>
-      <c r="C51" s="10" t="s">
-        <v>833</v>
-      </c>
       <c r="D51" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E51" s="10">
         <v>1</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G51" s="10" t="b">
         <v>1</v>
@@ -16711,19 +16711,19 @@
         <v>425</v>
       </c>
       <c r="B52" s="10" t="s">
+        <v>833</v>
+      </c>
+      <c r="C52" s="10" t="s">
         <v>834</v>
       </c>
-      <c r="C52" s="10" t="s">
-        <v>835</v>
-      </c>
       <c r="D52" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E52" s="10">
         <v>3</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G52" s="10" t="b">
         <v>1</v>
@@ -16734,19 +16734,19 @@
         <v>425</v>
       </c>
       <c r="B53" s="10" t="s">
+        <v>835</v>
+      </c>
+      <c r="C53" s="10" t="s">
         <v>836</v>
       </c>
-      <c r="C53" s="10" t="s">
-        <v>837</v>
-      </c>
       <c r="D53" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E53" s="10">
         <v>3</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G53" s="10" t="b">
         <v>1</v>
@@ -16757,19 +16757,19 @@
         <v>425</v>
       </c>
       <c r="B54" s="10" t="s">
+        <v>756</v>
+      </c>
+      <c r="C54" s="10" t="s">
         <v>757</v>
       </c>
-      <c r="C54" s="10" t="s">
-        <v>758</v>
-      </c>
       <c r="D54" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E54" s="10">
         <v>3</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G54" s="10" t="b">
         <v>1</v>
@@ -16780,19 +16780,19 @@
         <v>425</v>
       </c>
       <c r="B55" s="10" t="s">
+        <v>760</v>
+      </c>
+      <c r="C55" s="10" t="s">
         <v>761</v>
       </c>
-      <c r="C55" s="10" t="s">
+      <c r="D55" s="14" t="s">
         <v>762</v>
-      </c>
-      <c r="D55" s="14" t="s">
-        <v>763</v>
       </c>
       <c r="E55" s="10">
         <v>3</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G55" s="10" t="b">
         <v>1</v>
@@ -16803,19 +16803,19 @@
         <v>425</v>
       </c>
       <c r="B56" s="10" t="s">
+        <v>837</v>
+      </c>
+      <c r="C56" s="10" t="s">
         <v>838</v>
       </c>
-      <c r="C56" s="10" t="s">
-        <v>839</v>
-      </c>
       <c r="D56" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E56" s="10">
         <v>2</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G56" s="10" t="b">
         <v>1</v>
@@ -16826,19 +16826,19 @@
         <v>425</v>
       </c>
       <c r="B57" s="10" t="s">
+        <v>839</v>
+      </c>
+      <c r="C57" s="10" t="s">
         <v>840</v>
       </c>
-      <c r="C57" s="10" t="s">
-        <v>841</v>
-      </c>
       <c r="D57" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E57" s="10">
         <v>2</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G57" s="10" t="b">
         <v>1</v>
@@ -16849,19 +16849,19 @@
         <v>425</v>
       </c>
       <c r="B58" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C58" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C58" s="10" t="s">
+      <c r="D58" s="16" t="s">
         <v>768</v>
-      </c>
-      <c r="D58" s="16" t="s">
-        <v>769</v>
       </c>
       <c r="E58" s="10">
         <v>3</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G58" s="10" t="b">
         <v>1</v>
@@ -16872,19 +16872,19 @@
         <v>429</v>
       </c>
       <c r="B59" s="10" t="s">
+        <v>818</v>
+      </c>
+      <c r="C59" s="10" t="s">
         <v>819</v>
       </c>
-      <c r="C59" s="10" t="s">
-        <v>820</v>
-      </c>
       <c r="D59" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E59" s="10">
         <v>5</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G59" s="10" t="b">
         <v>1</v>
@@ -16895,19 +16895,19 @@
         <v>429</v>
       </c>
       <c r="B60" s="10" t="s">
+        <v>760</v>
+      </c>
+      <c r="C60" s="10" t="s">
         <v>761</v>
       </c>
-      <c r="C60" s="10" t="s">
+      <c r="D60" s="14" t="s">
         <v>762</v>
-      </c>
-      <c r="D60" s="14" t="s">
-        <v>763</v>
       </c>
       <c r="E60" s="10">
         <v>3</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G60" s="10" t="b">
         <v>1</v>
@@ -16918,19 +16918,19 @@
         <v>429</v>
       </c>
       <c r="B61" s="10" t="s">
+        <v>841</v>
+      </c>
+      <c r="C61" s="10" t="s">
         <v>842</v>
       </c>
-      <c r="C61" s="10" t="s">
-        <v>843</v>
-      </c>
       <c r="D61" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E61" s="10">
         <v>3</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G61" s="10" t="b">
         <v>1</v>
@@ -16941,19 +16941,19 @@
         <v>429</v>
       </c>
       <c r="B62" s="10" t="s">
+        <v>837</v>
+      </c>
+      <c r="C62" s="10" t="s">
         <v>838</v>
       </c>
-      <c r="C62" s="10" t="s">
-        <v>839</v>
-      </c>
       <c r="D62" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E62" s="10">
         <v>2</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G62" s="10" t="b">
         <v>1</v>
@@ -16964,19 +16964,19 @@
         <v>429</v>
       </c>
       <c r="B63" s="10" t="s">
+        <v>839</v>
+      </c>
+      <c r="C63" s="10" t="s">
         <v>840</v>
       </c>
-      <c r="C63" s="10" t="s">
-        <v>841</v>
-      </c>
       <c r="D63" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E63" s="10">
         <v>2</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G63" s="10" t="b">
         <v>1</v>
@@ -16987,19 +16987,19 @@
         <v>429</v>
       </c>
       <c r="B64" s="10" t="s">
+        <v>843</v>
+      </c>
+      <c r="C64" s="10" t="s">
         <v>844</v>
       </c>
-      <c r="C64" s="10" t="s">
-        <v>845</v>
-      </c>
       <c r="D64" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E64" s="10">
         <v>3</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G64" s="10" t="b">
         <v>1</v>
@@ -17010,19 +17010,19 @@
         <v>429</v>
       </c>
       <c r="B65" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C65" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C65" s="10" t="s">
+      <c r="D65" s="16" t="s">
         <v>768</v>
       </c>
-      <c r="D65" s="16" t="s">
-        <v>769</v>
-      </c>
       <c r="E65" s="10">
         <v>1</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G65" s="10" t="b">
         <v>1</v>
@@ -17033,19 +17033,19 @@
         <v>433</v>
       </c>
       <c r="B66" s="10" t="s">
+        <v>756</v>
+      </c>
+      <c r="C66" s="10" t="s">
         <v>757</v>
       </c>
-      <c r="C66" s="10" t="s">
+      <c r="D66" s="13" t="s">
         <v>758</v>
-      </c>
-      <c r="D66" s="13" t="s">
-        <v>759</v>
       </c>
       <c r="E66" s="10">
         <v>3</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G66" s="10" t="b">
         <v>1</v>
@@ -17056,19 +17056,19 @@
         <v>433</v>
       </c>
       <c r="B67" s="10" t="s">
+        <v>825</v>
+      </c>
+      <c r="C67" s="10" t="s">
         <v>826</v>
       </c>
-      <c r="C67" s="10" t="s">
-        <v>827</v>
-      </c>
       <c r="D67" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E67" s="10">
         <v>8</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G67" s="10" t="b">
         <v>1</v>
@@ -17079,19 +17079,19 @@
         <v>433</v>
       </c>
       <c r="B68" s="10" t="s">
+        <v>763</v>
+      </c>
+      <c r="C68" s="10" t="s">
         <v>764</v>
       </c>
-      <c r="C68" s="10" t="s">
+      <c r="D68" s="15" t="s">
         <v>765</v>
-      </c>
-      <c r="D68" s="15" t="s">
-        <v>766</v>
       </c>
       <c r="E68" s="10">
         <v>3</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G68" s="10" t="b">
         <v>1</v>
@@ -17102,19 +17102,19 @@
         <v>433</v>
       </c>
       <c r="B69" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C69" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C69" s="10" t="s">
+      <c r="D69" s="16" t="s">
         <v>768</v>
-      </c>
-      <c r="D69" s="16" t="s">
-        <v>769</v>
       </c>
       <c r="E69" s="10">
         <v>2</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G69" s="10" t="b">
         <v>1</v>
@@ -17128,16 +17128,16 @@
         <v>290</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>591</v>
+        <v>845</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E70" s="10">
         <v>3</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G70" s="10" t="b">
         <v>1</v>
@@ -17148,19 +17148,19 @@
         <v>438</v>
       </c>
       <c r="B71" s="10" t="s">
+        <v>814</v>
+      </c>
+      <c r="C71" s="10" t="s">
         <v>815</v>
       </c>
-      <c r="C71" s="10" t="s">
-        <v>816</v>
-      </c>
       <c r="D71" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E71" s="10">
         <v>5</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G71" s="10" t="b">
         <v>1</v>
@@ -17177,13 +17177,13 @@
         <v>847</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E72" s="10">
         <v>5</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G72" s="10" t="b">
         <v>1</v>
@@ -17200,13 +17200,13 @@
         <v>849</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E73" s="10">
         <v>2</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G73" s="10" t="b">
         <v>1</v>
@@ -17223,13 +17223,13 @@
         <v>851</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E74" s="10">
         <v>3</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G74" s="10" t="b">
         <v>1</v>
@@ -17246,13 +17246,13 @@
         <v>853</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E75" s="10">
         <v>3</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G75" s="10" t="b">
         <v>1</v>
@@ -17263,19 +17263,19 @@
         <v>443</v>
       </c>
       <c r="B76" s="10" t="s">
+        <v>806</v>
+      </c>
+      <c r="C76" s="10" t="s">
         <v>807</v>
       </c>
-      <c r="C76" s="10" t="s">
-        <v>808</v>
-      </c>
       <c r="D76" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E76" s="10">
         <v>5</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G76" s="10" t="b">
         <v>1</v>
@@ -17292,13 +17292,13 @@
         <v>15</v>
       </c>
       <c r="D77" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E77" s="10">
         <v>5</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G77" s="10" t="b">
         <v>1</v>
@@ -17309,19 +17309,19 @@
         <v>443</v>
       </c>
       <c r="B78" s="10" t="s">
+        <v>810</v>
+      </c>
+      <c r="C78" s="10" t="s">
         <v>811</v>
       </c>
-      <c r="C78" s="10" t="s">
-        <v>812</v>
-      </c>
       <c r="D78" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E78" s="10">
         <v>3</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G78" s="10" t="b">
         <v>1</v>
@@ -17332,19 +17332,19 @@
         <v>443</v>
       </c>
       <c r="B79" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C79" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C79" s="10" t="s">
+      <c r="D79" s="16" t="s">
         <v>768</v>
-      </c>
-      <c r="D79" s="16" t="s">
-        <v>769</v>
       </c>
       <c r="E79" s="10">
         <v>1.5</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G79" s="10" t="b">
         <v>1</v>
@@ -17355,19 +17355,19 @@
         <v>448</v>
       </c>
       <c r="B80" s="10" t="s">
+        <v>796</v>
+      </c>
+      <c r="C80" s="10" t="s">
         <v>797</v>
       </c>
-      <c r="C80" s="10" t="s">
-        <v>798</v>
-      </c>
       <c r="D80" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E80" s="10">
         <v>3</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G80" s="10" t="b">
         <v>1</v>
@@ -17384,13 +17384,13 @@
         <v>855</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E81" s="10">
         <v>3</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G81" s="10" t="b">
         <v>1</v>
@@ -17407,13 +17407,13 @@
         <v>857</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E82" s="10">
         <v>2</v>
       </c>
       <c r="F82" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G82" s="10" t="b">
         <v>1</v>
@@ -17430,13 +17430,13 @@
         <v>859</v>
       </c>
       <c r="D83" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E83" s="10">
         <v>1.5</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G83" s="10" t="b">
         <v>1</v>
@@ -17453,13 +17453,13 @@
         <v>861</v>
       </c>
       <c r="D84" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E84" s="10">
         <v>1.5</v>
       </c>
       <c r="F84" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G84" s="10" t="b">
         <v>1</v>
@@ -17470,19 +17470,19 @@
         <v>448</v>
       </c>
       <c r="B85" s="10" t="s">
+        <v>794</v>
+      </c>
+      <c r="C85" s="10" t="s">
         <v>795</v>
       </c>
-      <c r="C85" s="10" t="s">
-        <v>796</v>
-      </c>
       <c r="D85" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E85" s="10">
         <v>1.5</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G85" s="10" t="b">
         <v>1</v>
@@ -17493,19 +17493,19 @@
         <v>448</v>
       </c>
       <c r="B86" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C86" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C86" s="10" t="s">
+      <c r="D86" s="16" t="s">
         <v>768</v>
       </c>
-      <c r="D86" s="16" t="s">
-        <v>769</v>
-      </c>
       <c r="E86" s="10">
         <v>1</v>
       </c>
       <c r="F86" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G86" s="10" t="b">
         <v>1</v>
@@ -17522,13 +17522,13 @@
         <v>863</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E87" s="10">
         <v>1.5</v>
       </c>
       <c r="F87" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G87" s="10" t="b">
         <v>1</v>
@@ -17539,19 +17539,19 @@
         <v>453</v>
       </c>
       <c r="B88" s="10" t="s">
+        <v>806</v>
+      </c>
+      <c r="C88" s="10" t="s">
         <v>807</v>
       </c>
-      <c r="C88" s="10" t="s">
-        <v>808</v>
-      </c>
       <c r="D88" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E88" s="10">
         <v>1.5</v>
       </c>
       <c r="F88" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G88" s="10" t="b">
         <v>1</v>
@@ -17568,13 +17568,13 @@
         <v>865</v>
       </c>
       <c r="D89" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E89" s="10">
         <v>1</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G89" s="10" t="b">
         <v>1</v>
@@ -17591,13 +17591,13 @@
         <v>867</v>
       </c>
       <c r="D90" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E90" s="10">
         <v>1</v>
       </c>
       <c r="F90" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G90" s="10" t="b">
         <v>1</v>
@@ -17608,19 +17608,19 @@
         <v>453</v>
       </c>
       <c r="B91" s="10" t="s">
+        <v>763</v>
+      </c>
+      <c r="C91" s="10" t="s">
         <v>764</v>
       </c>
-      <c r="C91" s="10" t="s">
+      <c r="D91" s="15" t="s">
         <v>765</v>
       </c>
-      <c r="D91" s="15" t="s">
-        <v>766</v>
-      </c>
       <c r="E91" s="10">
         <v>1</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G91" s="10" t="b">
         <v>1</v>
@@ -17637,13 +17637,13 @@
         <v>15</v>
       </c>
       <c r="D92" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E92" s="10">
         <v>1</v>
       </c>
       <c r="F92" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G92" s="10" t="b">
         <v>1</v>
@@ -17660,13 +17660,13 @@
         <v>869</v>
       </c>
       <c r="D93" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E93" s="10">
         <v>1</v>
       </c>
       <c r="F93" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G93" s="10" t="b">
         <v>1</v>
@@ -17677,19 +17677,19 @@
         <v>453</v>
       </c>
       <c r="B94" s="10" t="s">
+        <v>810</v>
+      </c>
+      <c r="C94" s="10" t="s">
         <v>811</v>
       </c>
-      <c r="C94" s="10" t="s">
-        <v>812</v>
-      </c>
       <c r="D94" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E94" s="10">
         <v>1</v>
       </c>
       <c r="F94" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G94" s="10" t="b">
         <v>1</v>
@@ -17700,19 +17700,19 @@
         <v>453</v>
       </c>
       <c r="B95" s="10" t="s">
+        <v>771</v>
+      </c>
+      <c r="C95" s="10" t="s">
         <v>772</v>
       </c>
-      <c r="C95" s="10" t="s">
-        <v>773</v>
-      </c>
       <c r="D95" s="16" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E95" s="10">
         <v>3</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G95" s="10" t="b">
         <v>1</v>
@@ -17723,19 +17723,19 @@
         <v>458</v>
       </c>
       <c r="B96" s="10" t="s">
+        <v>756</v>
+      </c>
+      <c r="C96" s="10" t="s">
         <v>757</v>
       </c>
-      <c r="C96" s="10" t="s">
+      <c r="D96" s="13" t="s">
         <v>758</v>
-      </c>
-      <c r="D96" s="13" t="s">
-        <v>759</v>
       </c>
       <c r="E96" s="10">
         <v>6</v>
       </c>
       <c r="F96" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G96" s="10" t="b">
         <v>1</v>
@@ -17746,19 +17746,19 @@
         <v>458</v>
       </c>
       <c r="B97" s="10" t="s">
+        <v>760</v>
+      </c>
+      <c r="C97" s="10" t="s">
         <v>761</v>
       </c>
-      <c r="C97" s="10" t="s">
+      <c r="D97" s="14" t="s">
         <v>762</v>
-      </c>
-      <c r="D97" s="14" t="s">
-        <v>763</v>
       </c>
       <c r="E97" s="10">
         <v>2</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G97" s="10" t="b">
         <v>1</v>
@@ -17769,19 +17769,19 @@
         <v>458</v>
       </c>
       <c r="B98" s="10" t="s">
+        <v>825</v>
+      </c>
+      <c r="C98" s="10" t="s">
         <v>826</v>
       </c>
-      <c r="C98" s="10" t="s">
-        <v>827</v>
-      </c>
       <c r="D98" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E98" s="10">
         <v>1</v>
       </c>
       <c r="F98" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G98" s="10" t="b">
         <v>1</v>
@@ -17792,19 +17792,19 @@
         <v>458</v>
       </c>
       <c r="B99" s="10" t="s">
+        <v>763</v>
+      </c>
+      <c r="C99" s="10" t="s">
         <v>764</v>
       </c>
-      <c r="C99" s="10" t="s">
+      <c r="D99" s="15" t="s">
         <v>765</v>
-      </c>
-      <c r="D99" s="15" t="s">
-        <v>766</v>
       </c>
       <c r="E99" s="10">
         <v>3</v>
       </c>
       <c r="F99" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G99" s="10" t="b">
         <v>1</v>
@@ -17815,19 +17815,19 @@
         <v>458</v>
       </c>
       <c r="B100" s="10" t="s">
+        <v>771</v>
+      </c>
+      <c r="C100" s="10" t="s">
         <v>772</v>
       </c>
-      <c r="C100" s="10" t="s">
-        <v>773</v>
-      </c>
       <c r="D100" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E100" s="10">
         <v>3</v>
       </c>
       <c r="F100" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G100" s="10" t="b">
         <v>1</v>
@@ -17838,19 +17838,19 @@
         <v>458</v>
       </c>
       <c r="B101" s="10" t="s">
+        <v>773</v>
+      </c>
+      <c r="C101" s="10" t="s">
         <v>774</v>
       </c>
-      <c r="C101" s="10" t="s">
-        <v>775</v>
-      </c>
       <c r="D101" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E101" s="10">
         <v>3</v>
       </c>
       <c r="F101" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G101" s="10" t="b">
         <v>1</v>
@@ -17861,19 +17861,19 @@
         <v>458</v>
       </c>
       <c r="B102" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C102" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C102" s="10" t="s">
+      <c r="D102" s="16" t="s">
         <v>768</v>
-      </c>
-      <c r="D102" s="16" t="s">
-        <v>769</v>
       </c>
       <c r="E102" s="10">
         <v>2</v>
       </c>
       <c r="F102" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G102" s="10" t="b">
         <v>1</v>
@@ -17884,19 +17884,19 @@
         <v>462</v>
       </c>
       <c r="B103" s="10" t="s">
+        <v>756</v>
+      </c>
+      <c r="C103" s="10" t="s">
         <v>757</v>
       </c>
-      <c r="C103" s="10" t="s">
+      <c r="D103" s="13" t="s">
         <v>758</v>
-      </c>
-      <c r="D103" s="13" t="s">
-        <v>759</v>
       </c>
       <c r="E103" s="10">
         <v>3</v>
       </c>
       <c r="F103" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G103" s="10" t="b">
         <v>1</v>
@@ -17907,19 +17907,19 @@
         <v>462</v>
       </c>
       <c r="B104" s="10" t="s">
+        <v>760</v>
+      </c>
+      <c r="C104" s="10" t="s">
         <v>761</v>
       </c>
-      <c r="C104" s="10" t="s">
-        <v>762</v>
-      </c>
       <c r="D104" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E104" s="10">
         <v>3</v>
       </c>
       <c r="F104" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G104" s="10" t="b">
         <v>1</v>
@@ -17936,13 +17936,13 @@
         <v>871</v>
       </c>
       <c r="D105" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E105" s="10">
         <v>2</v>
       </c>
       <c r="F105" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G105" s="10" t="b">
         <v>1</v>
@@ -17959,13 +17959,13 @@
         <v>873</v>
       </c>
       <c r="D106" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E106" s="10">
         <v>2</v>
       </c>
       <c r="F106" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G106" s="10" t="b">
         <v>1</v>
@@ -17976,19 +17976,19 @@
         <v>462</v>
       </c>
       <c r="B107" s="10" t="s">
+        <v>769</v>
+      </c>
+      <c r="C107" s="10" t="s">
         <v>770</v>
       </c>
-      <c r="C107" s="10" t="s">
-        <v>771</v>
-      </c>
       <c r="D107" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E107" s="10">
         <v>3</v>
       </c>
       <c r="F107" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G107" s="10" t="b">
         <v>1</v>
@@ -18005,13 +18005,13 @@
         <v>849</v>
       </c>
       <c r="D108" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E108" s="10">
         <v>2</v>
       </c>
       <c r="F108" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G108" s="10" t="b">
         <v>1</v>
@@ -18022,19 +18022,19 @@
         <v>462</v>
       </c>
       <c r="B109" s="10" t="s">
+        <v>806</v>
+      </c>
+      <c r="C109" s="10" t="s">
         <v>807</v>
       </c>
-      <c r="C109" s="10" t="s">
-        <v>808</v>
-      </c>
       <c r="D109" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E109" s="10">
         <v>3</v>
       </c>
       <c r="F109" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G109" s="10" t="b">
         <v>1</v>
@@ -18045,19 +18045,19 @@
         <v>462</v>
       </c>
       <c r="B110" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C110" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C110" s="10" t="s">
+      <c r="D110" s="16" t="s">
         <v>768</v>
-      </c>
-      <c r="D110" s="16" t="s">
-        <v>769</v>
       </c>
       <c r="E110" s="10">
         <v>2</v>
       </c>
       <c r="F110" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G110" s="10" t="b">
         <v>1</v>
@@ -18071,16 +18071,16 @@
         <v>290</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>591</v>
+        <v>845</v>
       </c>
       <c r="D111" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E111" s="10">
         <v>4</v>
       </c>
       <c r="F111" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G111" s="10" t="b">
         <v>1</v>
@@ -18091,19 +18091,19 @@
         <v>467</v>
       </c>
       <c r="B112" s="10" t="s">
+        <v>816</v>
+      </c>
+      <c r="C112" s="10" t="s">
         <v>817</v>
       </c>
-      <c r="C112" s="10" t="s">
-        <v>818</v>
-      </c>
       <c r="D112" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E112" s="10">
         <v>3</v>
       </c>
       <c r="F112" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G112" s="10" t="b">
         <v>1</v>
@@ -18114,19 +18114,19 @@
         <v>467</v>
       </c>
       <c r="B113" s="10" t="s">
+        <v>810</v>
+      </c>
+      <c r="C113" s="10" t="s">
         <v>811</v>
       </c>
-      <c r="C113" s="10" t="s">
-        <v>812</v>
-      </c>
       <c r="D113" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E113" s="10">
         <v>3</v>
       </c>
       <c r="F113" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G113" s="10" t="b">
         <v>1</v>
@@ -18137,19 +18137,19 @@
         <v>467</v>
       </c>
       <c r="B114" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C114" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C114" s="10" t="s">
+      <c r="D114" s="16" t="s">
         <v>768</v>
-      </c>
-      <c r="D114" s="16" t="s">
-        <v>769</v>
       </c>
       <c r="E114" s="10">
         <v>2</v>
       </c>
       <c r="F114" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G114" s="10" t="b">
         <v>1</v>
@@ -18166,13 +18166,13 @@
         <v>875</v>
       </c>
       <c r="D115" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E115" s="10">
         <v>3</v>
       </c>
       <c r="F115" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G115" s="10" t="b">
         <v>1</v>
@@ -18189,13 +18189,13 @@
         <v>877</v>
       </c>
       <c r="D116" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E116" s="10">
         <v>2</v>
       </c>
       <c r="F116" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G116" s="10" t="b">
         <v>1</v>
@@ -18212,13 +18212,13 @@
         <v>15</v>
       </c>
       <c r="D117" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E117" s="10">
         <v>2</v>
       </c>
       <c r="F117" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G117" s="10" t="b">
         <v>1</v>
@@ -18229,19 +18229,19 @@
         <v>471</v>
       </c>
       <c r="B118" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C118" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C118" s="10" t="s">
+      <c r="D118" s="16" t="s">
         <v>768</v>
       </c>
-      <c r="D118" s="16" t="s">
-        <v>769</v>
-      </c>
       <c r="E118" s="10">
         <v>1</v>
       </c>
       <c r="F118" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G118" s="10" t="b">
         <v>1</v>
@@ -18258,13 +18258,13 @@
         <v>871</v>
       </c>
       <c r="D119" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E119" s="10">
         <v>5</v>
       </c>
       <c r="F119" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G119" s="10" t="b">
         <v>1</v>
@@ -18278,16 +18278,16 @@
         <v>290</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>591</v>
+        <v>845</v>
       </c>
       <c r="D120" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E120" s="10">
         <v>5</v>
       </c>
       <c r="F120" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G120" s="10" t="b">
         <v>1</v>
@@ -18298,19 +18298,19 @@
         <v>476</v>
       </c>
       <c r="B121" s="10" t="s">
+        <v>816</v>
+      </c>
+      <c r="C121" s="10" t="s">
         <v>817</v>
       </c>
-      <c r="C121" s="10" t="s">
-        <v>818</v>
-      </c>
       <c r="D121" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E121" s="10">
         <v>5</v>
       </c>
       <c r="F121" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G121" s="10" t="b">
         <v>1</v>
@@ -18321,19 +18321,19 @@
         <v>476</v>
       </c>
       <c r="B122" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C122" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C122" s="10" t="s">
+      <c r="D122" s="16" t="s">
         <v>768</v>
-      </c>
-      <c r="D122" s="16" t="s">
-        <v>769</v>
       </c>
       <c r="E122" s="10">
         <v>5</v>
       </c>
       <c r="F122" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G122" s="10" t="b">
         <v>1</v>
@@ -18347,16 +18347,16 @@
         <v>290</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>591</v>
+        <v>845</v>
       </c>
       <c r="D123" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E123" s="10">
         <v>5</v>
       </c>
       <c r="F123" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G123" s="10" t="b">
         <v>1</v>
@@ -18367,19 +18367,19 @@
         <v>479</v>
       </c>
       <c r="B124" s="10" t="s">
+        <v>810</v>
+      </c>
+      <c r="C124" s="10" t="s">
         <v>811</v>
       </c>
-      <c r="C124" s="10" t="s">
-        <v>812</v>
-      </c>
       <c r="D124" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E124" s="10">
         <v>5</v>
       </c>
       <c r="F124" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G124" s="10" t="b">
         <v>1</v>
@@ -18390,19 +18390,19 @@
         <v>479</v>
       </c>
       <c r="B125" s="10" t="s">
+        <v>816</v>
+      </c>
+      <c r="C125" s="10" t="s">
         <v>817</v>
       </c>
-      <c r="C125" s="10" t="s">
-        <v>818</v>
-      </c>
       <c r="D125" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E125" s="10">
         <v>5</v>
       </c>
       <c r="F125" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G125" s="10" t="b">
         <v>1</v>
@@ -18419,13 +18419,13 @@
         <v>879</v>
       </c>
       <c r="D126" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E126" s="10">
         <v>5</v>
       </c>
       <c r="F126" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G126" s="10" t="b">
         <v>1</v>
@@ -18442,13 +18442,13 @@
         <v>881</v>
       </c>
       <c r="D127" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E127" s="10">
         <v>3</v>
       </c>
       <c r="F127" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G127" s="10" t="b">
         <v>1</v>
@@ -18465,13 +18465,13 @@
         <v>861</v>
       </c>
       <c r="D128" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E128" s="10">
         <v>3</v>
       </c>
       <c r="F128" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G128" s="10" t="b">
         <v>1</v>
@@ -18482,19 +18482,19 @@
         <v>479</v>
       </c>
       <c r="B129" s="10" t="s">
+        <v>831</v>
+      </c>
+      <c r="C129" s="10" t="s">
         <v>832</v>
       </c>
-      <c r="C129" s="10" t="s">
-        <v>833</v>
-      </c>
       <c r="D129" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E129" s="10">
         <v>7</v>
       </c>
       <c r="F129" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G129" s="10" t="b">
         <v>1</v>
@@ -18511,13 +18511,13 @@
         <v>883</v>
       </c>
       <c r="D130" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E130" s="10">
         <v>2</v>
       </c>
       <c r="F130" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G130" s="10" t="b">
         <v>1</v>
@@ -18528,19 +18528,19 @@
         <v>479</v>
       </c>
       <c r="B131" s="10" t="s">
+        <v>788</v>
+      </c>
+      <c r="C131" s="10" t="s">
         <v>789</v>
       </c>
-      <c r="C131" s="10" t="s">
-        <v>790</v>
-      </c>
       <c r="D131" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E131" s="10">
         <v>2</v>
       </c>
       <c r="F131" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G131" s="10" t="b">
         <v>1</v>
@@ -18551,19 +18551,19 @@
         <v>479</v>
       </c>
       <c r="B132" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C132" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C132" s="10" t="s">
+      <c r="D132" s="16" t="s">
         <v>768</v>
-      </c>
-      <c r="D132" s="16" t="s">
-        <v>769</v>
       </c>
       <c r="E132" s="10">
         <v>2</v>
       </c>
       <c r="F132" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G132" s="10" t="b">
         <v>1</v>
@@ -18580,13 +18580,13 @@
         <v>885</v>
       </c>
       <c r="D133" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E133" s="10">
         <v>5</v>
       </c>
       <c r="F133" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G133" s="10" t="b">
         <v>1</v>
@@ -18597,19 +18597,19 @@
         <v>484</v>
       </c>
       <c r="B134" s="10" t="s">
+        <v>804</v>
+      </c>
+      <c r="C134" s="10" t="s">
         <v>805</v>
       </c>
-      <c r="C134" s="10" t="s">
-        <v>806</v>
-      </c>
       <c r="D134" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E134" s="10">
         <v>3</v>
       </c>
       <c r="F134" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G134" s="10" t="b">
         <v>1</v>
@@ -18626,13 +18626,13 @@
         <v>887</v>
       </c>
       <c r="D135" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E135" s="10">
         <v>3</v>
       </c>
       <c r="F135" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G135" s="10" t="b">
         <v>1</v>
@@ -18643,19 +18643,19 @@
         <v>484</v>
       </c>
       <c r="B136" s="10" t="s">
+        <v>806</v>
+      </c>
+      <c r="C136" s="10" t="s">
         <v>807</v>
       </c>
-      <c r="C136" s="10" t="s">
-        <v>808</v>
-      </c>
       <c r="D136" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E136" s="10">
         <v>4</v>
       </c>
       <c r="F136" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G136" s="10" t="b">
         <v>1</v>
@@ -18672,13 +18672,13 @@
         <v>877</v>
       </c>
       <c r="D137" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E137" s="10">
         <v>4</v>
       </c>
       <c r="F137" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G137" s="10" t="b">
         <v>1</v>
@@ -18689,19 +18689,19 @@
         <v>484</v>
       </c>
       <c r="B138" s="10" t="s">
+        <v>816</v>
+      </c>
+      <c r="C138" s="10" t="s">
         <v>817</v>
       </c>
-      <c r="C138" s="10" t="s">
-        <v>818</v>
-      </c>
       <c r="D138" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E138" s="10">
         <v>4</v>
       </c>
       <c r="F138" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G138" s="10" t="b">
         <v>1</v>
@@ -18718,13 +18718,13 @@
         <v>875</v>
       </c>
       <c r="D139" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E139" s="10">
         <v>4</v>
       </c>
       <c r="F139" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G139" s="10" t="b">
         <v>1</v>
@@ -18741,13 +18741,13 @@
         <v>15</v>
       </c>
       <c r="D140" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E140" s="10">
         <v>3</v>
       </c>
       <c r="F140" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G140" s="10" t="b">
         <v>1</v>
@@ -18758,19 +18758,19 @@
         <v>484</v>
       </c>
       <c r="B141" s="10" t="s">
+        <v>810</v>
+      </c>
+      <c r="C141" s="10" t="s">
         <v>811</v>
       </c>
-      <c r="C141" s="10" t="s">
-        <v>812</v>
-      </c>
       <c r="D141" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E141" s="10">
         <v>5</v>
       </c>
       <c r="F141" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G141" s="10" t="b">
         <v>1</v>
@@ -18787,13 +18787,13 @@
         <v>889</v>
       </c>
       <c r="D142" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E142" s="10">
         <v>5</v>
       </c>
       <c r="F142" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G142" s="10" t="b">
         <v>1</v>
@@ -18804,19 +18804,19 @@
         <v>484</v>
       </c>
       <c r="B143" s="10" t="s">
+        <v>788</v>
+      </c>
+      <c r="C143" s="10" t="s">
         <v>789</v>
       </c>
-      <c r="C143" s="10" t="s">
-        <v>790</v>
-      </c>
       <c r="D143" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E143" s="10">
         <v>2</v>
       </c>
       <c r="F143" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G143" s="10" t="b">
         <v>1</v>
@@ -18827,19 +18827,19 @@
         <v>484</v>
       </c>
       <c r="B144" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C144" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C144" s="10" t="s">
+      <c r="D144" s="16" t="s">
         <v>768</v>
-      </c>
-      <c r="D144" s="16" t="s">
-        <v>769</v>
       </c>
       <c r="E144" s="10">
         <v>2</v>
       </c>
       <c r="F144" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G144" s="10" t="b">
         <v>1</v>
@@ -18850,19 +18850,19 @@
         <v>484</v>
       </c>
       <c r="B145" s="10" t="s">
+        <v>771</v>
+      </c>
+      <c r="C145" s="10" t="s">
         <v>772</v>
       </c>
-      <c r="C145" s="10" t="s">
-        <v>773</v>
-      </c>
       <c r="D145" s="16" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E145" s="10">
         <v>2</v>
       </c>
       <c r="F145" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G145" s="10" t="b">
         <v>1</v>
@@ -18873,19 +18873,19 @@
         <v>484</v>
       </c>
       <c r="B146" s="10" t="s">
+        <v>773</v>
+      </c>
+      <c r="C146" s="10" t="s">
         <v>774</v>
       </c>
-      <c r="C146" s="10" t="s">
-        <v>775</v>
-      </c>
       <c r="D146" s="16" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E146" s="10">
         <v>2</v>
       </c>
       <c r="F146" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G146" s="10" t="b">
         <v>1</v>
@@ -18896,19 +18896,19 @@
         <v>489</v>
       </c>
       <c r="B147" s="10" t="s">
+        <v>837</v>
+      </c>
+      <c r="C147" s="10" t="s">
         <v>838</v>
       </c>
-      <c r="C147" s="10" t="s">
-        <v>839</v>
-      </c>
       <c r="D147" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E147" s="10">
         <v>4</v>
       </c>
       <c r="F147" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G147" s="10" t="b">
         <v>1</v>
@@ -18919,19 +18919,19 @@
         <v>489</v>
       </c>
       <c r="B148" s="10" t="s">
+        <v>760</v>
+      </c>
+      <c r="C148" s="10" t="s">
         <v>761</v>
       </c>
-      <c r="C148" s="10" t="s">
+      <c r="D148" s="14" t="s">
         <v>762</v>
-      </c>
-      <c r="D148" s="14" t="s">
-        <v>763</v>
       </c>
       <c r="E148" s="10">
         <v>3</v>
       </c>
       <c r="F148" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G148" s="10" t="b">
         <v>1</v>
@@ -18942,19 +18942,19 @@
         <v>489</v>
       </c>
       <c r="B149" s="10" t="s">
+        <v>769</v>
+      </c>
+      <c r="C149" s="10" t="s">
         <v>770</v>
       </c>
-      <c r="C149" s="10" t="s">
-        <v>771</v>
-      </c>
       <c r="D149" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E149" s="10">
         <v>3</v>
       </c>
       <c r="F149" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G149" s="10" t="b">
         <v>1</v>
@@ -18971,13 +18971,13 @@
         <v>873</v>
       </c>
       <c r="D150" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E150" s="10">
         <v>1</v>
       </c>
       <c r="F150" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G150" s="10" t="b">
         <v>1</v>
@@ -18994,13 +18994,13 @@
         <v>891</v>
       </c>
       <c r="D151" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E151" s="10">
         <v>2</v>
       </c>
       <c r="F151" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G151" s="10" t="b">
         <v>1</v>
@@ -19011,19 +19011,19 @@
         <v>489</v>
       </c>
       <c r="B152" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C152" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C152" s="10" t="s">
+      <c r="D152" s="16" t="s">
         <v>768</v>
-      </c>
-      <c r="D152" s="16" t="s">
-        <v>769</v>
       </c>
       <c r="E152" s="10">
         <v>2</v>
       </c>
       <c r="F152" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G152" s="10" t="b">
         <v>1</v>
@@ -19034,19 +19034,19 @@
         <v>489</v>
       </c>
       <c r="B153" s="10" t="s">
+        <v>773</v>
+      </c>
+      <c r="C153" s="10" t="s">
         <v>774</v>
       </c>
-      <c r="C153" s="10" t="s">
-        <v>775</v>
-      </c>
       <c r="D153" s="16" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E153" s="10">
         <v>2</v>
       </c>
       <c r="F153" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G153" s="10" t="b">
         <v>1</v>
@@ -19063,13 +19063,13 @@
         <v>893</v>
       </c>
       <c r="D154" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E154" s="10">
         <v>2</v>
       </c>
       <c r="F154" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G154" s="10" t="b">
         <v>1</v>
@@ -19086,13 +19086,13 @@
         <v>891</v>
       </c>
       <c r="D155" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E155" s="10">
         <v>2</v>
       </c>
       <c r="F155" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G155" s="10" t="b">
         <v>1</v>
@@ -19103,19 +19103,19 @@
         <v>494</v>
       </c>
       <c r="B156" s="10" t="s">
+        <v>792</v>
+      </c>
+      <c r="C156" s="10" t="s">
         <v>793</v>
       </c>
-      <c r="C156" s="10" t="s">
-        <v>794</v>
-      </c>
       <c r="D156" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E156" s="10">
         <v>2</v>
       </c>
       <c r="F156" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G156" s="10" t="b">
         <v>1</v>
@@ -19126,19 +19126,19 @@
         <v>494</v>
       </c>
       <c r="B157" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C157" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C157" s="10" t="s">
-        <v>768</v>
-      </c>
       <c r="D157" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E157" s="10">
         <v>2</v>
       </c>
       <c r="F157" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G157" s="10" t="b">
         <v>1</v>
@@ -19149,19 +19149,19 @@
         <v>499</v>
       </c>
       <c r="B158" s="10" t="s">
+        <v>806</v>
+      </c>
+      <c r="C158" s="10" t="s">
         <v>807</v>
       </c>
-      <c r="C158" s="10" t="s">
-        <v>808</v>
-      </c>
       <c r="D158" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E158" s="10">
         <v>2.5</v>
       </c>
       <c r="F158" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G158" s="10" t="b">
         <v>1</v>
@@ -19178,13 +19178,13 @@
         <v>863</v>
       </c>
       <c r="D159" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E159" s="10">
         <v>2.5</v>
       </c>
       <c r="F159" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G159" s="10" t="b">
         <v>1</v>
@@ -19201,13 +19201,13 @@
         <v>869</v>
       </c>
       <c r="D160" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E160" s="10">
         <v>2</v>
       </c>
       <c r="F160" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G160" s="10" t="b">
         <v>1</v>
@@ -19224,13 +19224,13 @@
         <v>15</v>
       </c>
       <c r="D161" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E161" s="10">
         <v>1.5</v>
       </c>
       <c r="F161" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G161" s="10" t="b">
         <v>1</v>
@@ -19247,13 +19247,13 @@
         <v>895</v>
       </c>
       <c r="D162" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E162" s="10">
         <v>1</v>
       </c>
       <c r="F162" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G162" s="10" t="b">
         <v>1</v>
@@ -19264,19 +19264,19 @@
         <v>499</v>
       </c>
       <c r="B163" s="10" t="s">
+        <v>810</v>
+      </c>
+      <c r="C163" s="10" t="s">
         <v>811</v>
       </c>
-      <c r="C163" s="10" t="s">
-        <v>812</v>
-      </c>
       <c r="D163" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E163" s="10">
         <v>2</v>
       </c>
       <c r="F163" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G163" s="10" t="b">
         <v>1</v>
@@ -19293,13 +19293,13 @@
         <v>897</v>
       </c>
       <c r="D164" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E164" s="10">
         <v>1</v>
       </c>
       <c r="F164" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G164" s="10" t="b">
         <v>1</v>
@@ -19313,16 +19313,16 @@
         <v>290</v>
       </c>
       <c r="C165" s="10" t="s">
-        <v>591</v>
+        <v>845</v>
       </c>
       <c r="D165" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E165" s="10">
         <v>1</v>
       </c>
       <c r="F165" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G165" s="10" t="b">
         <v>1</v>
@@ -19333,19 +19333,19 @@
         <v>499</v>
       </c>
       <c r="B166" s="10" t="s">
+        <v>771</v>
+      </c>
+      <c r="C166" s="10" t="s">
         <v>772</v>
       </c>
-      <c r="C166" s="10" t="s">
-        <v>773</v>
-      </c>
       <c r="D166" s="16" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E166" s="10">
         <v>1</v>
       </c>
       <c r="F166" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G166" s="10" t="b">
         <v>1</v>
@@ -19356,19 +19356,19 @@
         <v>499</v>
       </c>
       <c r="B167" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C167" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C167" s="10" t="s">
+      <c r="D167" s="16" t="s">
         <v>768</v>
       </c>
-      <c r="D167" s="16" t="s">
-        <v>769</v>
-      </c>
       <c r="E167" s="10">
         <v>1</v>
       </c>
       <c r="F167" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G167" s="10" t="b">
         <v>1</v>
@@ -19379,19 +19379,19 @@
         <v>503</v>
       </c>
       <c r="B168" s="10" t="s">
+        <v>814</v>
+      </c>
+      <c r="C168" s="10" t="s">
         <v>815</v>
       </c>
-      <c r="C168" s="10" t="s">
-        <v>816</v>
-      </c>
       <c r="D168" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E168" s="10">
         <v>5</v>
       </c>
       <c r="F168" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G168" s="10" t="b">
         <v>1</v>
@@ -19405,16 +19405,16 @@
         <v>290</v>
       </c>
       <c r="C169" s="10" t="s">
-        <v>591</v>
+        <v>845</v>
       </c>
       <c r="D169" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E169" s="10">
         <v>3</v>
       </c>
       <c r="F169" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G169" s="10" t="b">
         <v>1</v>
@@ -19425,19 +19425,19 @@
         <v>503</v>
       </c>
       <c r="B170" s="10" t="s">
+        <v>837</v>
+      </c>
+      <c r="C170" s="10" t="s">
         <v>838</v>
       </c>
-      <c r="C170" s="10" t="s">
-        <v>839</v>
-      </c>
       <c r="D170" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E170" s="10">
         <v>5</v>
       </c>
       <c r="F170" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G170" s="10" t="b">
         <v>1</v>
@@ -19454,13 +19454,13 @@
         <v>899</v>
       </c>
       <c r="D171" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E171" s="10">
         <v>5</v>
       </c>
       <c r="F171" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G171" s="10" t="b">
         <v>1</v>
@@ -19471,19 +19471,19 @@
         <v>503</v>
       </c>
       <c r="B172" s="10" t="s">
+        <v>810</v>
+      </c>
+      <c r="C172" s="10" t="s">
         <v>811</v>
       </c>
-      <c r="C172" s="10" t="s">
-        <v>812</v>
-      </c>
       <c r="D172" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E172" s="10">
         <v>5</v>
       </c>
       <c r="F172" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G172" s="10" t="b">
         <v>1</v>
@@ -19500,13 +19500,13 @@
         <v>901</v>
       </c>
       <c r="D173" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E173" s="10">
         <v>3</v>
       </c>
       <c r="F173" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G173" s="10" t="b">
         <v>1</v>
@@ -19523,13 +19523,13 @@
         <v>903</v>
       </c>
       <c r="D174" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E174" s="10">
         <v>3</v>
       </c>
       <c r="F174" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G174" s="10" t="b">
         <v>1</v>
@@ -19546,13 +19546,13 @@
         <v>905</v>
       </c>
       <c r="D175" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E175" s="10">
         <v>3</v>
       </c>
       <c r="F175" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G175" s="10" t="b">
         <v>1</v>
@@ -19569,13 +19569,13 @@
         <v>849</v>
       </c>
       <c r="D176" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E176" s="10">
         <v>3</v>
       </c>
       <c r="F176" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G176" s="10" t="b">
         <v>1</v>
@@ -19586,19 +19586,19 @@
         <v>503</v>
       </c>
       <c r="B177" s="10" t="s">
+        <v>839</v>
+      </c>
+      <c r="C177" s="10" t="s">
         <v>840</v>
       </c>
-      <c r="C177" s="10" t="s">
-        <v>841</v>
-      </c>
       <c r="D177" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E177" s="10">
         <v>5</v>
       </c>
       <c r="F177" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G177" s="10" t="b">
         <v>1</v>
@@ -19609,19 +19609,19 @@
         <v>503</v>
       </c>
       <c r="B178" s="10" t="s">
+        <v>806</v>
+      </c>
+      <c r="C178" s="10" t="s">
         <v>807</v>
       </c>
-      <c r="C178" s="10" t="s">
-        <v>808</v>
-      </c>
       <c r="D178" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E178" s="10">
         <v>5</v>
       </c>
       <c r="F178" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G178" s="10" t="b">
         <v>1</v>
@@ -19638,13 +19638,13 @@
         <v>907</v>
       </c>
       <c r="D179" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E179" s="10">
         <v>3</v>
       </c>
       <c r="F179" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G179" s="10" t="b">
         <v>1</v>
@@ -19655,19 +19655,19 @@
         <v>503</v>
       </c>
       <c r="B180" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C180" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C180" s="10" t="s">
+      <c r="D180" s="16" t="s">
         <v>768</v>
-      </c>
-      <c r="D180" s="16" t="s">
-        <v>769</v>
       </c>
       <c r="E180" s="10">
         <v>4</v>
       </c>
       <c r="F180" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G180" s="10" t="b">
         <v>1</v>
@@ -19678,19 +19678,19 @@
         <v>503</v>
       </c>
       <c r="B181" s="10" t="s">
+        <v>771</v>
+      </c>
+      <c r="C181" s="10" t="s">
         <v>772</v>
       </c>
-      <c r="C181" s="10" t="s">
-        <v>773</v>
-      </c>
       <c r="D181" s="16" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E181" s="10">
         <v>1</v>
       </c>
       <c r="F181" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G181" s="10" t="b">
         <v>1</v>
@@ -19701,19 +19701,19 @@
         <v>503</v>
       </c>
       <c r="B182" s="10" t="s">
+        <v>773</v>
+      </c>
+      <c r="C182" s="10" t="s">
         <v>774</v>
       </c>
-      <c r="C182" s="10" t="s">
-        <v>775</v>
-      </c>
       <c r="D182" s="16" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E182" s="10">
         <v>1</v>
       </c>
       <c r="F182" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G182" s="10" t="b">
         <v>1</v>
@@ -19730,13 +19730,13 @@
         <v>909</v>
       </c>
       <c r="D183" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E183" s="10">
         <v>4</v>
       </c>
       <c r="F183" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G183" s="10" t="b">
         <v>1</v>
@@ -19753,13 +19753,13 @@
         <v>911</v>
       </c>
       <c r="D184" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E184" s="10">
         <v>3</v>
       </c>
       <c r="F184" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G184" s="10" t="b">
         <v>1</v>
@@ -19776,13 +19776,13 @@
         <v>913</v>
       </c>
       <c r="D185" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E185" s="10">
         <v>2</v>
       </c>
       <c r="F185" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G185" s="10" t="b">
         <v>1</v>
@@ -19793,19 +19793,19 @@
         <v>508</v>
       </c>
       <c r="B186" s="10" t="s">
+        <v>839</v>
+      </c>
+      <c r="C186" s="47" t="s">
         <v>840</v>
       </c>
-      <c r="C186" s="47" t="s">
-        <v>841</v>
-      </c>
       <c r="D186" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E186" s="10">
         <v>2</v>
       </c>
       <c r="F186" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G186" s="10" t="b">
         <v>1</v>
@@ -19822,13 +19822,13 @@
         <v>915</v>
       </c>
       <c r="D187" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E187" s="10">
         <v>3</v>
       </c>
       <c r="F187" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G187" s="10" t="b">
         <v>1</v>
@@ -19839,19 +19839,19 @@
         <v>508</v>
       </c>
       <c r="B188" s="10" t="s">
+        <v>837</v>
+      </c>
+      <c r="C188" s="47" t="s">
         <v>838</v>
       </c>
-      <c r="C188" s="47" t="s">
-        <v>839</v>
-      </c>
       <c r="D188" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E188" s="10">
         <v>3</v>
       </c>
       <c r="F188" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G188" s="10" t="b">
         <v>1</v>
@@ -19868,13 +19868,13 @@
         <v>893</v>
       </c>
       <c r="D189" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E189" s="10">
         <v>3</v>
       </c>
       <c r="F189" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G189" s="10" t="b">
         <v>1</v>
@@ -19885,19 +19885,19 @@
         <v>508</v>
       </c>
       <c r="B190" s="10" t="s">
+        <v>788</v>
+      </c>
+      <c r="C190" s="47" t="s">
         <v>789</v>
       </c>
-      <c r="C190" s="47" t="s">
-        <v>790</v>
-      </c>
       <c r="D190" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E190" s="10">
         <v>2</v>
       </c>
       <c r="F190" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G190" s="10" t="b">
         <v>1</v>
@@ -19908,19 +19908,19 @@
         <v>508</v>
       </c>
       <c r="B191" s="10" t="s">
+        <v>812</v>
+      </c>
+      <c r="C191" s="47" t="s">
         <v>813</v>
       </c>
-      <c r="C191" s="47" t="s">
-        <v>814</v>
-      </c>
       <c r="D191" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E191" s="10">
         <v>3</v>
       </c>
       <c r="F191" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G191" s="10" t="b">
         <v>1</v>
@@ -19937,13 +19937,13 @@
         <v>917</v>
       </c>
       <c r="D192" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E192" s="10">
         <v>1</v>
       </c>
       <c r="F192" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G192" s="10" t="b">
         <v>1</v>
@@ -19954,19 +19954,19 @@
         <v>508</v>
       </c>
       <c r="B193" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C193" s="47" t="s">
         <v>767</v>
       </c>
-      <c r="C193" s="47" t="s">
+      <c r="D193" s="16" t="s">
         <v>768</v>
-      </c>
-      <c r="D193" s="16" t="s">
-        <v>769</v>
       </c>
       <c r="E193" s="10">
         <v>2</v>
       </c>
       <c r="F193" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G193" s="10" t="b">
         <v>1</v>
@@ -19983,13 +19983,13 @@
         <v>893</v>
       </c>
       <c r="D194" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E194" s="10">
         <v>4</v>
       </c>
       <c r="F194" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G194" s="10" t="b">
         <v>1</v>
@@ -20006,13 +20006,13 @@
         <v>919</v>
       </c>
       <c r="D195" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E195" s="10">
         <v>1</v>
       </c>
       <c r="F195" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G195" s="10" t="b">
         <v>1</v>
@@ -20029,13 +20029,13 @@
         <v>855</v>
       </c>
       <c r="D196" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E196" s="10">
         <v>1</v>
       </c>
       <c r="F196" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G196" s="10" t="b">
         <v>1</v>
@@ -20052,13 +20052,13 @@
         <v>901</v>
       </c>
       <c r="D197" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E197" s="10">
         <v>1</v>
       </c>
       <c r="F197" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G197" s="10" t="b">
         <v>1</v>
@@ -20075,13 +20075,13 @@
         <v>903</v>
       </c>
       <c r="D198" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E198" s="10">
         <v>1</v>
       </c>
       <c r="F198" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G198" s="10" t="b">
         <v>1</v>
@@ -20092,19 +20092,19 @@
         <v>512</v>
       </c>
       <c r="B199" s="10" t="s">
+        <v>837</v>
+      </c>
+      <c r="C199" s="10" t="s">
         <v>838</v>
       </c>
-      <c r="C199" s="10" t="s">
-        <v>839</v>
-      </c>
       <c r="D199" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E199" s="10">
         <v>1</v>
       </c>
       <c r="F199" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G199" s="10" t="b">
         <v>1</v>
@@ -20118,16 +20118,16 @@
         <v>290</v>
       </c>
       <c r="C200" s="10" t="s">
-        <v>591</v>
+        <v>845</v>
       </c>
       <c r="D200" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E200" s="10">
         <v>5</v>
       </c>
       <c r="F200" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G200" s="10" t="b">
         <v>1</v>
@@ -20138,19 +20138,19 @@
         <v>512</v>
       </c>
       <c r="B201" s="10" t="s">
+        <v>810</v>
+      </c>
+      <c r="C201" s="10" t="s">
         <v>811</v>
       </c>
-      <c r="C201" s="10" t="s">
-        <v>812</v>
-      </c>
       <c r="D201" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E201" s="10">
         <v>5</v>
       </c>
       <c r="F201" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G201" s="10" t="b">
         <v>1</v>
@@ -20167,13 +20167,13 @@
         <v>921</v>
       </c>
       <c r="D202" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E202" s="10">
         <v>5</v>
       </c>
       <c r="F202" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G202" s="10" t="b">
         <v>1</v>
@@ -20190,13 +20190,13 @@
         <v>923</v>
       </c>
       <c r="D203" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E203" s="10">
         <v>5</v>
       </c>
       <c r="F203" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G203" s="10" t="b">
         <v>1</v>
@@ -20213,13 +20213,13 @@
         <v>905</v>
       </c>
       <c r="D204" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E204" s="10">
         <v>5</v>
       </c>
       <c r="F204" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G204" s="10" t="b">
         <v>1</v>
@@ -20236,13 +20236,13 @@
         <v>849</v>
       </c>
       <c r="D205" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E205" s="10">
         <v>5</v>
       </c>
       <c r="F205" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G205" s="10" t="b">
         <v>1</v>
@@ -20253,19 +20253,19 @@
         <v>512</v>
       </c>
       <c r="B206" s="10" t="s">
+        <v>788</v>
+      </c>
+      <c r="C206" s="10" t="s">
         <v>789</v>
       </c>
-      <c r="C206" s="10" t="s">
-        <v>790</v>
-      </c>
       <c r="D206" s="16" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E206" s="10">
         <v>5</v>
       </c>
       <c r="F206" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G206" s="10" t="b">
         <v>1</v>
@@ -20276,19 +20276,19 @@
         <v>515</v>
       </c>
       <c r="B207" s="10" t="s">
+        <v>760</v>
+      </c>
+      <c r="C207" s="10" t="s">
         <v>761</v>
       </c>
-      <c r="C207" s="10" t="s">
-        <v>762</v>
-      </c>
       <c r="D207" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E207" s="10">
         <v>4</v>
       </c>
       <c r="F207" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G207" s="10" t="b">
         <v>1</v>
@@ -20299,19 +20299,19 @@
         <v>515</v>
       </c>
       <c r="B208" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C208" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C208" s="10" t="s">
-        <v>768</v>
-      </c>
       <c r="D208" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E208" s="10">
         <v>2</v>
       </c>
       <c r="F208" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G208" s="10" t="b">
         <v>1</v>
@@ -20328,13 +20328,13 @@
         <v>925</v>
       </c>
       <c r="D209" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E209" s="10">
         <v>3</v>
       </c>
       <c r="F209" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G209" s="10" t="b">
         <v>1</v>
@@ -20345,19 +20345,19 @@
         <v>519</v>
       </c>
       <c r="B210" s="10" t="s">
+        <v>806</v>
+      </c>
+      <c r="C210" s="10" t="s">
         <v>807</v>
       </c>
-      <c r="C210" s="10" t="s">
-        <v>808</v>
-      </c>
       <c r="D210" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E210" s="10">
         <v>4</v>
       </c>
       <c r="F210" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G210" s="10" t="b">
         <v>1</v>
@@ -20374,13 +20374,13 @@
         <v>895</v>
       </c>
       <c r="D211" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E211" s="10">
         <v>5</v>
       </c>
       <c r="F211" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G211" s="10" t="b">
         <v>1</v>
@@ -20397,13 +20397,13 @@
         <v>15</v>
       </c>
       <c r="D212" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E212" s="10">
         <v>4</v>
       </c>
       <c r="F212" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G212" s="10" t="b">
         <v>1</v>
@@ -20420,13 +20420,13 @@
         <v>869</v>
       </c>
       <c r="D213" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E213" s="10">
         <v>4</v>
       </c>
       <c r="F213" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G213" s="10" t="b">
         <v>1</v>
@@ -20437,19 +20437,19 @@
         <v>519</v>
       </c>
       <c r="B214" s="10" t="s">
+        <v>810</v>
+      </c>
+      <c r="C214" s="10" t="s">
         <v>811</v>
       </c>
-      <c r="C214" s="10" t="s">
-        <v>812</v>
-      </c>
       <c r="D214" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E214" s="10">
         <v>4</v>
       </c>
       <c r="F214" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G214" s="10" t="b">
         <v>1</v>
@@ -20460,19 +20460,19 @@
         <v>519</v>
       </c>
       <c r="B215" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C215" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C215" s="10" t="s">
+      <c r="D215" s="16" t="s">
         <v>768</v>
-      </c>
-      <c r="D215" s="16" t="s">
-        <v>769</v>
       </c>
       <c r="E215" s="10">
         <v>2</v>
       </c>
       <c r="F215" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G215" s="10" t="b">
         <v>1</v>
@@ -20483,19 +20483,19 @@
         <v>519</v>
       </c>
       <c r="B216" s="10" t="s">
+        <v>771</v>
+      </c>
+      <c r="C216" s="10" t="s">
         <v>772</v>
       </c>
-      <c r="C216" s="10" t="s">
-        <v>773</v>
-      </c>
       <c r="D216" s="16" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E216" s="10">
         <v>1</v>
       </c>
       <c r="F216" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G216" s="10" t="b">
         <v>1</v>
@@ -20506,19 +20506,19 @@
         <v>519</v>
       </c>
       <c r="B217" s="10" t="s">
+        <v>773</v>
+      </c>
+      <c r="C217" s="10" t="s">
         <v>774</v>
       </c>
-      <c r="C217" s="10" t="s">
-        <v>775</v>
-      </c>
       <c r="D217" s="16" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E217" s="10">
         <v>1</v>
       </c>
       <c r="F217" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G217" s="10" t="b">
         <v>1</v>
@@ -20529,19 +20529,19 @@
         <v>524</v>
       </c>
       <c r="B218" s="10" t="s">
+        <v>814</v>
+      </c>
+      <c r="C218" s="10" t="s">
         <v>815</v>
       </c>
-      <c r="C218" s="10" t="s">
-        <v>816</v>
-      </c>
       <c r="D218" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E218" s="10">
         <v>1</v>
       </c>
       <c r="F218" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G218" s="10" t="b">
         <v>1</v>
@@ -20555,16 +20555,16 @@
         <v>290</v>
       </c>
       <c r="C219" s="10" t="s">
-        <v>591</v>
+        <v>845</v>
       </c>
       <c r="D219" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E219" s="10">
         <v>5</v>
       </c>
       <c r="F219" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G219" s="10" t="b">
         <v>1</v>
@@ -20581,13 +20581,13 @@
         <v>927</v>
       </c>
       <c r="D220" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E220" s="10">
         <v>5</v>
       </c>
       <c r="F220" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G220" s="10" t="b">
         <v>1</v>
@@ -20598,19 +20598,19 @@
         <v>524</v>
       </c>
       <c r="B221" s="10" t="s">
+        <v>816</v>
+      </c>
+      <c r="C221" s="10" t="s">
         <v>817</v>
       </c>
-      <c r="C221" s="10" t="s">
-        <v>818</v>
-      </c>
       <c r="D221" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E221" s="10">
         <v>5</v>
       </c>
       <c r="F221" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G221" s="10" t="b">
         <v>1</v>
@@ -20621,19 +20621,19 @@
         <v>524</v>
       </c>
       <c r="B222" s="10" t="s">
+        <v>837</v>
+      </c>
+      <c r="C222" s="10" t="s">
         <v>838</v>
       </c>
-      <c r="C222" s="10" t="s">
-        <v>839</v>
-      </c>
       <c r="D222" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E222" s="10">
         <v>5</v>
       </c>
       <c r="F222" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G222" s="10" t="b">
         <v>1</v>
@@ -20650,13 +20650,13 @@
         <v>901</v>
       </c>
       <c r="D223" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E223" s="10">
         <v>6</v>
       </c>
       <c r="F223" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G223" s="10" t="b">
         <v>1</v>
@@ -20673,13 +20673,13 @@
         <v>899</v>
       </c>
       <c r="D224" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E224" s="10">
         <v>5</v>
       </c>
       <c r="F224" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G224" s="10" t="b">
         <v>1</v>
@@ -20696,13 +20696,13 @@
         <v>905</v>
       </c>
       <c r="D225" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E225" s="10">
         <v>3</v>
       </c>
       <c r="F225" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G225" s="10" t="b">
         <v>1</v>
@@ -20719,13 +20719,13 @@
         <v>929</v>
       </c>
       <c r="D226" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E226" s="10">
         <v>2</v>
       </c>
       <c r="F226" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G226" s="10" t="b">
         <v>1</v>
@@ -20736,19 +20736,19 @@
         <v>524</v>
       </c>
       <c r="B227" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C227" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C227" s="10" t="s">
+      <c r="D227" s="16" t="s">
         <v>768</v>
-      </c>
-      <c r="D227" s="16" t="s">
-        <v>769</v>
       </c>
       <c r="E227" s="10">
         <v>2</v>
       </c>
       <c r="F227" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G227" s="10" t="b">
         <v>1</v>
@@ -20759,19 +20759,19 @@
         <v>524</v>
       </c>
       <c r="B228" s="10" t="s">
+        <v>771</v>
+      </c>
+      <c r="C228" s="10" t="s">
         <v>772</v>
       </c>
-      <c r="C228" s="10" t="s">
-        <v>773</v>
-      </c>
       <c r="D228" s="16" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E228" s="10">
         <v>1</v>
       </c>
       <c r="F228" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G228" s="10" t="b">
         <v>1</v>
@@ -20782,19 +20782,19 @@
         <v>524</v>
       </c>
       <c r="B229" s="10" t="s">
+        <v>773</v>
+      </c>
+      <c r="C229" s="10" t="s">
         <v>774</v>
       </c>
-      <c r="C229" s="10" t="s">
-        <v>775</v>
-      </c>
       <c r="D229" s="16" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E229" s="10">
         <v>1</v>
       </c>
       <c r="F229" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G229" s="10" t="b">
         <v>1</v>
@@ -20811,13 +20811,13 @@
         <v>931</v>
       </c>
       <c r="D230" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E230" s="10">
         <v>2</v>
       </c>
       <c r="F230" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G230" s="10" t="b">
         <v>1</v>
@@ -20834,13 +20834,13 @@
         <v>867</v>
       </c>
       <c r="D231" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E231" s="10">
         <v>3</v>
       </c>
       <c r="F231" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G231" s="10" t="b">
         <v>1</v>
@@ -20851,19 +20851,19 @@
         <v>529</v>
       </c>
       <c r="B232" s="10" t="s">
+        <v>800</v>
+      </c>
+      <c r="C232" s="10" t="s">
         <v>801</v>
       </c>
-      <c r="C232" s="10" t="s">
-        <v>802</v>
-      </c>
       <c r="D232" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E232" s="10">
         <v>3</v>
       </c>
       <c r="F232" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G232" s="10" t="b">
         <v>1</v>
@@ -20880,13 +20880,13 @@
         <v>933</v>
       </c>
       <c r="D233" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E233" s="10">
         <v>4</v>
       </c>
       <c r="F233" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G233" s="10" t="b">
         <v>1</v>
@@ -20903,13 +20903,13 @@
         <v>891</v>
       </c>
       <c r="D234" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E234" s="10">
         <v>3</v>
       </c>
       <c r="F234" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G234" s="10" t="b">
         <v>1</v>
@@ -20926,13 +20926,13 @@
         <v>935</v>
       </c>
       <c r="D235" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E235" s="10">
         <v>3</v>
       </c>
       <c r="F235" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G235" s="10" t="b">
         <v>1</v>
@@ -20943,19 +20943,19 @@
         <v>529</v>
       </c>
       <c r="B236" s="10" t="s">
+        <v>837</v>
+      </c>
+      <c r="C236" s="10" t="s">
         <v>838</v>
       </c>
-      <c r="C236" s="10" t="s">
-        <v>839</v>
-      </c>
       <c r="D236" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E236" s="10">
         <v>3</v>
       </c>
       <c r="F236" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G236" s="10" t="b">
         <v>1</v>
@@ -20972,13 +20972,13 @@
         <v>893</v>
       </c>
       <c r="D237" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E237" s="10">
         <v>6</v>
       </c>
       <c r="F237" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G237" s="10" t="b">
         <v>1</v>
@@ -20995,13 +20995,13 @@
         <v>917</v>
       </c>
       <c r="D238" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E238" s="10">
         <v>3</v>
       </c>
       <c r="F238" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G238" s="10" t="b">
         <v>1</v>
@@ -21012,19 +21012,19 @@
         <v>529</v>
       </c>
       <c r="B239" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C239" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C239" s="10" t="s">
+      <c r="D239" s="16" t="s">
         <v>768</v>
-      </c>
-      <c r="D239" s="16" t="s">
-        <v>769</v>
       </c>
       <c r="E239" s="10">
         <v>2</v>
       </c>
       <c r="F239" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G239" s="10" t="b">
         <v>1</v>
@@ -21041,13 +21041,13 @@
         <v>907</v>
       </c>
       <c r="D240" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E240" s="10">
         <v>1</v>
       </c>
       <c r="F240" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G240" s="10" t="b">
         <v>1</v>
@@ -21064,13 +21064,13 @@
         <v>937</v>
       </c>
       <c r="D241" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E241" s="10">
         <v>2</v>
       </c>
       <c r="F241" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G241" s="10" t="b">
         <v>1</v>
@@ -21081,19 +21081,19 @@
         <v>534</v>
       </c>
       <c r="B242" s="10" t="s">
+        <v>837</v>
+      </c>
+      <c r="C242" s="10" t="s">
         <v>838</v>
       </c>
-      <c r="C242" s="10" t="s">
-        <v>839</v>
-      </c>
       <c r="D242" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E242" s="10">
         <v>2</v>
       </c>
       <c r="F242" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G242" s="10" t="b">
         <v>1</v>
@@ -21110,13 +21110,13 @@
         <v>939</v>
       </c>
       <c r="D243" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E243" s="10">
         <v>3</v>
       </c>
       <c r="F243" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G243" s="10" t="b">
         <v>1</v>
@@ -21133,13 +21133,13 @@
         <v>941</v>
       </c>
       <c r="D244" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E244" s="10">
         <v>2</v>
       </c>
       <c r="F244" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G244" s="10" t="b">
         <v>1</v>
@@ -21150,19 +21150,19 @@
         <v>534</v>
       </c>
       <c r="B245" s="10" t="s">
+        <v>810</v>
+      </c>
+      <c r="C245" s="10" t="s">
         <v>811</v>
       </c>
-      <c r="C245" s="10" t="s">
-        <v>812</v>
-      </c>
       <c r="D245" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E245" s="10">
         <v>2</v>
       </c>
       <c r="F245" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G245" s="10" t="b">
         <v>1</v>
@@ -21179,13 +21179,13 @@
         <v>943</v>
       </c>
       <c r="D246" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E246" s="10">
         <v>1</v>
       </c>
       <c r="F246" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G246" s="10" t="b">
         <v>1</v>
@@ -21196,19 +21196,19 @@
         <v>534</v>
       </c>
       <c r="B247" s="10" t="s">
+        <v>771</v>
+      </c>
+      <c r="C247" s="10" t="s">
         <v>772</v>
       </c>
-      <c r="C247" s="10" t="s">
-        <v>773</v>
-      </c>
       <c r="D247" s="16" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E247" s="10">
         <v>1</v>
       </c>
       <c r="F247" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G247" s="10" t="b">
         <v>1</v>
@@ -21225,13 +21225,13 @@
         <v>917</v>
       </c>
       <c r="D248" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E248" s="10">
         <v>2</v>
       </c>
       <c r="F248" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G248" s="10" t="b">
         <v>1</v>
@@ -21248,13 +21248,13 @@
         <v>945</v>
       </c>
       <c r="D249" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E249" s="10">
         <v>1.5</v>
       </c>
       <c r="F249" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G249" s="10" t="b">
         <v>1</v>
@@ -21265,19 +21265,19 @@
         <v>539</v>
       </c>
       <c r="B250" s="10" t="s">
+        <v>839</v>
+      </c>
+      <c r="C250" s="10" t="s">
         <v>840</v>
       </c>
-      <c r="C250" s="10" t="s">
-        <v>841</v>
-      </c>
       <c r="D250" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E250" s="10">
         <v>1.5</v>
       </c>
       <c r="F250" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G250" s="10" t="b">
         <v>1</v>
@@ -21294,13 +21294,13 @@
         <v>15</v>
       </c>
       <c r="D251" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E251" s="10">
         <v>2</v>
       </c>
       <c r="F251" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G251" s="10" t="b">
         <v>1</v>
@@ -21311,19 +21311,19 @@
         <v>539</v>
       </c>
       <c r="B252" s="10" t="s">
+        <v>812</v>
+      </c>
+      <c r="C252" s="10" t="s">
         <v>813</v>
       </c>
-      <c r="C252" s="10" t="s">
-        <v>814</v>
-      </c>
       <c r="D252" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E252" s="10">
         <v>1.5</v>
       </c>
       <c r="F252" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G252" s="10" t="b">
         <v>1</v>
@@ -21334,19 +21334,19 @@
         <v>539</v>
       </c>
       <c r="B253" s="10" t="s">
+        <v>769</v>
+      </c>
+      <c r="C253" s="10" t="s">
         <v>770</v>
       </c>
-      <c r="C253" s="10" t="s">
-        <v>771</v>
-      </c>
       <c r="D253" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E253" s="10">
         <v>1.5</v>
       </c>
       <c r="F253" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G253" s="10" t="b">
         <v>1</v>
@@ -21357,19 +21357,19 @@
         <v>539</v>
       </c>
       <c r="B254" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C254" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C254" s="10" t="s">
+      <c r="D254" s="16" t="s">
         <v>768</v>
-      </c>
-      <c r="D254" s="16" t="s">
-        <v>769</v>
       </c>
       <c r="E254" s="10">
         <v>0.5</v>
       </c>
       <c r="F254" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G254" s="10" t="b">
         <v>1</v>
@@ -21386,13 +21386,13 @@
         <v>847</v>
       </c>
       <c r="D255" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E255" s="10">
         <v>4</v>
       </c>
       <c r="F255" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G255" s="10" t="b">
         <v>1</v>
@@ -21403,19 +21403,19 @@
         <v>543</v>
       </c>
       <c r="B256" s="10" t="s">
+        <v>837</v>
+      </c>
+      <c r="C256" s="10" t="s">
         <v>838</v>
       </c>
-      <c r="C256" s="10" t="s">
-        <v>839</v>
-      </c>
       <c r="D256" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E256" s="10">
         <v>3</v>
       </c>
       <c r="F256" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G256" s="10" t="b">
         <v>1</v>
@@ -21426,19 +21426,19 @@
         <v>543</v>
       </c>
       <c r="B257" s="10" t="s">
+        <v>769</v>
+      </c>
+      <c r="C257" s="10" t="s">
         <v>770</v>
       </c>
-      <c r="C257" s="10" t="s">
-        <v>771</v>
-      </c>
       <c r="D257" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E257" s="10">
         <v>3</v>
       </c>
       <c r="F257" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G257" s="10" t="b">
         <v>1</v>
@@ -21449,19 +21449,19 @@
         <v>543</v>
       </c>
       <c r="B258" s="10" t="s">
+        <v>839</v>
+      </c>
+      <c r="C258" s="10" t="s">
         <v>840</v>
       </c>
-      <c r="C258" s="10" t="s">
-        <v>841</v>
-      </c>
       <c r="D258" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E258" s="10">
         <v>2</v>
       </c>
       <c r="F258" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G258" s="10" t="b">
         <v>1</v>
@@ -21472,19 +21472,19 @@
         <v>548</v>
       </c>
       <c r="B259" s="10" t="s">
+        <v>837</v>
+      </c>
+      <c r="C259" s="47" t="s">
         <v>838</v>
       </c>
-      <c r="C259" s="47" t="s">
-        <v>839</v>
-      </c>
       <c r="D259" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E259" s="10">
         <v>3</v>
       </c>
       <c r="F259" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G259" s="10" t="b">
         <v>1</v>
@@ -21495,19 +21495,19 @@
         <v>548</v>
       </c>
       <c r="B260" s="10" t="s">
+        <v>839</v>
+      </c>
+      <c r="C260" s="10" t="s">
         <v>840</v>
       </c>
-      <c r="C260" s="10" t="s">
-        <v>841</v>
-      </c>
       <c r="D260" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E260" s="10">
         <v>2</v>
       </c>
       <c r="F260" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G260" s="10" t="b">
         <v>1</v>
@@ -21524,13 +21524,13 @@
         <v>913</v>
       </c>
       <c r="D261" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E261" s="10">
         <v>2</v>
       </c>
       <c r="F261" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G261" s="10" t="b">
         <v>1</v>
@@ -21547,13 +21547,13 @@
         <v>909</v>
       </c>
       <c r="D262" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E262" s="10">
         <v>3</v>
       </c>
       <c r="F262" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G262" s="10" t="b">
         <v>1</v>
@@ -21570,13 +21570,13 @@
         <v>911</v>
       </c>
       <c r="D263" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E263" s="10">
         <v>3</v>
       </c>
       <c r="F263" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G263" s="10" t="b">
         <v>1</v>
@@ -21593,13 +21593,13 @@
         <v>947</v>
       </c>
       <c r="D264" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E264" s="10">
         <v>2</v>
       </c>
       <c r="F264" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G264" s="10" t="b">
         <v>1</v>
@@ -21616,13 +21616,13 @@
         <v>949</v>
       </c>
       <c r="D265" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E265" s="10">
         <v>2</v>
       </c>
       <c r="F265" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G265" s="10" t="b">
         <v>1</v>
@@ -21639,13 +21639,13 @@
         <v>945</v>
       </c>
       <c r="D266" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E266" s="10">
         <v>1</v>
       </c>
       <c r="F266" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G266" s="10" t="b">
         <v>1</v>
@@ -21662,13 +21662,13 @@
         <v>941</v>
       </c>
       <c r="D267" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E267" s="10">
         <v>2</v>
       </c>
       <c r="F267" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G267" s="10" t="b">
         <v>1</v>
@@ -21679,19 +21679,19 @@
         <v>548</v>
       </c>
       <c r="B268" s="10" t="s">
+        <v>812</v>
+      </c>
+      <c r="C268" s="47" t="s">
         <v>813</v>
       </c>
-      <c r="C268" s="47" t="s">
-        <v>814</v>
-      </c>
       <c r="D268" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E268" s="10">
         <v>1</v>
       </c>
       <c r="F268" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G268" s="10" t="b">
         <v>1</v>
@@ -21708,13 +21708,13 @@
         <v>951</v>
       </c>
       <c r="D269" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E269" s="10">
         <v>1</v>
       </c>
       <c r="F269" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G269" s="10" t="b">
         <v>1</v>
@@ -21725,19 +21725,19 @@
         <v>548</v>
       </c>
       <c r="B270" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C270" s="47" t="s">
         <v>767</v>
       </c>
-      <c r="C270" s="47" t="s">
+      <c r="D270" s="16" t="s">
         <v>768</v>
-      </c>
-      <c r="D270" s="16" t="s">
-        <v>769</v>
       </c>
       <c r="E270" s="10">
         <v>3</v>
       </c>
       <c r="F270" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G270" s="10" t="b">
         <v>1</v>
@@ -21754,13 +21754,13 @@
         <v>893</v>
       </c>
       <c r="D271" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E271" s="10">
         <v>1</v>
       </c>
       <c r="F271" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G271" s="10" t="b">
         <v>1</v>
@@ -21777,13 +21777,13 @@
         <v>939</v>
       </c>
       <c r="D272" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E272" s="10">
         <v>6</v>
       </c>
       <c r="F272" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G272" s="10" t="b">
         <v>1</v>
@@ -21794,19 +21794,19 @@
         <v>552</v>
       </c>
       <c r="B273" s="10" t="s">
+        <v>796</v>
+      </c>
+      <c r="C273" s="10" t="s">
         <v>797</v>
       </c>
-      <c r="C273" s="10" t="s">
-        <v>798</v>
-      </c>
       <c r="D273" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E273" s="10">
         <v>3</v>
       </c>
       <c r="F273" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G273" s="10" t="b">
         <v>1</v>
@@ -21823,13 +21823,13 @@
         <v>855</v>
       </c>
       <c r="D274" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E274" s="10">
         <v>3</v>
       </c>
       <c r="F274" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G274" s="10" t="b">
         <v>1</v>
@@ -21840,19 +21840,19 @@
         <v>552</v>
       </c>
       <c r="B275" s="10" t="s">
+        <v>837</v>
+      </c>
+      <c r="C275" s="10" t="s">
         <v>838</v>
       </c>
-      <c r="C275" s="10" t="s">
-        <v>839</v>
-      </c>
       <c r="D275" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E275" s="10">
         <v>3</v>
       </c>
       <c r="F275" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G275" s="10" t="b">
         <v>1</v>
@@ -21869,13 +21869,13 @@
         <v>953</v>
       </c>
       <c r="D276" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E276" s="10">
         <v>1.5</v>
       </c>
       <c r="F276" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G276" s="10" t="b">
         <v>1</v>
@@ -21892,13 +21892,13 @@
         <v>955</v>
       </c>
       <c r="D277" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E277" s="10">
         <v>3</v>
       </c>
       <c r="F277" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G277" s="10" t="b">
         <v>1</v>
@@ -21915,13 +21915,13 @@
         <v>957</v>
       </c>
       <c r="D278" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E278" s="10">
         <v>3</v>
       </c>
       <c r="F278" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G278" s="10" t="b">
         <v>1</v>
@@ -21932,19 +21932,19 @@
         <v>556</v>
       </c>
       <c r="B279" s="10" t="s">
+        <v>818</v>
+      </c>
+      <c r="C279" s="10" t="s">
         <v>819</v>
       </c>
-      <c r="C279" s="10" t="s">
-        <v>820</v>
-      </c>
       <c r="D279" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E279" s="10">
         <v>3</v>
       </c>
       <c r="F279" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G279" s="10" t="b">
         <v>1</v>
@@ -21955,19 +21955,19 @@
         <v>556</v>
       </c>
       <c r="B280" s="10" t="s">
+        <v>825</v>
+      </c>
+      <c r="C280" s="10" t="s">
         <v>826</v>
       </c>
-      <c r="C280" s="10" t="s">
-        <v>827</v>
-      </c>
       <c r="D280" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E280" s="10">
         <v>3</v>
       </c>
       <c r="F280" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G280" s="10" t="b">
         <v>1</v>
@@ -21978,19 +21978,19 @@
         <v>556</v>
       </c>
       <c r="B281" s="10" t="s">
+        <v>810</v>
+      </c>
+      <c r="C281" s="10" t="s">
         <v>811</v>
       </c>
-      <c r="C281" s="10" t="s">
-        <v>812</v>
-      </c>
       <c r="D281" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E281" s="10">
         <v>3</v>
       </c>
       <c r="F281" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G281" s="10" t="b">
         <v>1</v>
@@ -22001,19 +22001,19 @@
         <v>556</v>
       </c>
       <c r="B282" s="10" t="s">
+        <v>806</v>
+      </c>
+      <c r="C282" s="10" t="s">
         <v>807</v>
       </c>
-      <c r="C282" s="10" t="s">
-        <v>808</v>
-      </c>
       <c r="D282" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E282" s="10">
         <v>3</v>
       </c>
       <c r="F282" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G282" s="10" t="b">
         <v>1</v>
@@ -22030,13 +22030,13 @@
         <v>15</v>
       </c>
       <c r="D283" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E283" s="10">
         <v>3</v>
       </c>
       <c r="F283" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G283" s="10" t="b">
         <v>1</v>
@@ -22050,16 +22050,16 @@
         <v>290</v>
       </c>
       <c r="C284" s="10" t="s">
-        <v>591</v>
+        <v>845</v>
       </c>
       <c r="D284" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E284" s="10">
         <v>3</v>
       </c>
       <c r="F284" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G284" s="10" t="b">
         <v>1</v>
@@ -22070,19 +22070,19 @@
         <v>556</v>
       </c>
       <c r="B285" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C285" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C285" s="10" t="s">
+      <c r="D285" s="16" t="s">
         <v>768</v>
-      </c>
-      <c r="D285" s="16" t="s">
-        <v>769</v>
       </c>
       <c r="E285" s="10">
         <v>3</v>
       </c>
       <c r="F285" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G285" s="10" t="b">
         <v>1</v>
@@ -22093,19 +22093,19 @@
         <v>556</v>
       </c>
       <c r="B286" s="10" t="s">
+        <v>771</v>
+      </c>
+      <c r="C286" s="10" t="s">
         <v>772</v>
       </c>
-      <c r="C286" s="10" t="s">
-        <v>773</v>
-      </c>
       <c r="D286" s="16" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E286" s="10">
         <v>2</v>
       </c>
       <c r="F286" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G286" s="10" t="b">
         <v>1</v>
@@ -22122,13 +22122,13 @@
         <v>917</v>
       </c>
       <c r="D287" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E287" s="10">
         <v>3</v>
       </c>
       <c r="F287" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G287" s="10" t="b">
         <v>1</v>
@@ -22139,19 +22139,19 @@
         <v>561</v>
       </c>
       <c r="B288" s="10" t="s">
+        <v>837</v>
+      </c>
+      <c r="C288" s="10" t="s">
         <v>838</v>
       </c>
-      <c r="C288" s="10" t="s">
-        <v>839</v>
-      </c>
       <c r="D288" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E288" s="10">
         <v>3</v>
       </c>
       <c r="F288" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G288" s="10" t="b">
         <v>1</v>
@@ -22162,19 +22162,19 @@
         <v>561</v>
       </c>
       <c r="B289" s="10" t="s">
+        <v>769</v>
+      </c>
+      <c r="C289" s="10" t="s">
         <v>770</v>
       </c>
-      <c r="C289" s="10" t="s">
-        <v>771</v>
-      </c>
       <c r="D289" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E289" s="10">
         <v>3</v>
       </c>
       <c r="F289" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G289" s="10" t="b">
         <v>1</v>
@@ -22185,19 +22185,19 @@
         <v>561</v>
       </c>
       <c r="B290" s="10" t="s">
+        <v>816</v>
+      </c>
+      <c r="C290" s="10" t="s">
         <v>817</v>
       </c>
-      <c r="C290" s="10" t="s">
-        <v>818</v>
-      </c>
       <c r="D290" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E290" s="10">
         <v>3</v>
       </c>
       <c r="F290" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G290" s="10" t="b">
         <v>1</v>
@@ -22208,19 +22208,19 @@
         <v>561</v>
       </c>
       <c r="B291" s="10" t="s">
+        <v>810</v>
+      </c>
+      <c r="C291" s="10" t="s">
         <v>811</v>
       </c>
-      <c r="C291" s="10" t="s">
-        <v>812</v>
-      </c>
       <c r="D291" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E291" s="10">
         <v>3</v>
       </c>
       <c r="F291" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G291" s="10" t="b">
         <v>1</v>
@@ -22231,19 +22231,19 @@
         <v>561</v>
       </c>
       <c r="B292" s="10" t="s">
+        <v>771</v>
+      </c>
+      <c r="C292" s="10" t="s">
         <v>772</v>
       </c>
-      <c r="C292" s="10" t="s">
-        <v>773</v>
-      </c>
       <c r="D292" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E292" s="10">
         <v>1</v>
       </c>
       <c r="F292" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G292" s="10" t="b">
         <v>1</v>
@@ -22254,19 +22254,19 @@
         <v>561</v>
       </c>
       <c r="B293" s="10" t="s">
+        <v>784</v>
+      </c>
+      <c r="C293" s="10" t="s">
         <v>785</v>
       </c>
-      <c r="C293" s="10" t="s">
-        <v>786</v>
-      </c>
       <c r="D293" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E293" s="10">
         <v>1</v>
       </c>
       <c r="F293" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G293" s="10" t="b">
         <v>1</v>
@@ -22277,19 +22277,19 @@
         <v>561</v>
       </c>
       <c r="B294" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C294" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C294" s="10" t="s">
+      <c r="D294" s="16" t="s">
         <v>768</v>
       </c>
-      <c r="D294" s="16" t="s">
-        <v>769</v>
-      </c>
       <c r="E294" s="10">
         <v>1</v>
       </c>
       <c r="F294" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G294" s="10" t="b">
         <v>1</v>
@@ -22306,13 +22306,13 @@
         <v>959</v>
       </c>
       <c r="D295" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E295" s="10">
         <v>5</v>
       </c>
       <c r="F295" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G295" s="10" t="b">
         <v>1</v>
@@ -22326,16 +22326,16 @@
         <v>290</v>
       </c>
       <c r="C296" s="10" t="s">
-        <v>591</v>
+        <v>845</v>
       </c>
       <c r="D296" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E296" s="10">
         <v>4</v>
       </c>
       <c r="F296" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G296" s="10" t="b">
         <v>1</v>
@@ -22346,19 +22346,19 @@
         <v>566</v>
       </c>
       <c r="B297" s="10" t="s">
+        <v>827</v>
+      </c>
+      <c r="C297" s="10" t="s">
         <v>828</v>
       </c>
-      <c r="C297" s="10" t="s">
-        <v>829</v>
-      </c>
       <c r="D297" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E297" s="10">
         <v>3</v>
       </c>
       <c r="F297" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G297" s="10" t="b">
         <v>1</v>
@@ -22369,19 +22369,19 @@
         <v>566</v>
       </c>
       <c r="B298" s="10" t="s">
+        <v>798</v>
+      </c>
+      <c r="C298" s="10" t="s">
         <v>799</v>
       </c>
-      <c r="C298" s="10" t="s">
-        <v>800</v>
-      </c>
       <c r="D298" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E298" s="10">
         <v>3</v>
       </c>
       <c r="F298" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G298" s="10" t="b">
         <v>1</v>
@@ -22398,13 +22398,13 @@
         <v>853</v>
       </c>
       <c r="D299" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E299" s="10">
         <v>3</v>
       </c>
       <c r="F299" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G299" s="10" t="b">
         <v>1</v>
@@ -22415,19 +22415,19 @@
         <v>566</v>
       </c>
       <c r="B300" s="10" t="s">
+        <v>810</v>
+      </c>
+      <c r="C300" s="10" t="s">
         <v>811</v>
       </c>
-      <c r="C300" s="10" t="s">
-        <v>812</v>
-      </c>
       <c r="D300" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E300" s="10">
         <v>4</v>
       </c>
       <c r="F300" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G300" s="10" t="b">
         <v>1</v>
@@ -22438,19 +22438,19 @@
         <v>566</v>
       </c>
       <c r="B301" s="10" t="s">
+        <v>763</v>
+      </c>
+      <c r="C301" s="10" t="s">
         <v>764</v>
       </c>
-      <c r="C301" s="10" t="s">
+      <c r="D301" s="15" t="s">
         <v>765</v>
-      </c>
-      <c r="D301" s="15" t="s">
-        <v>766</v>
       </c>
       <c r="E301" s="10">
         <v>4</v>
       </c>
       <c r="F301" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G301" s="10" t="b">
         <v>1</v>
@@ -22461,19 +22461,19 @@
         <v>566</v>
       </c>
       <c r="B302" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C302" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C302" s="10" t="s">
+      <c r="D302" s="16" t="s">
         <v>768</v>
-      </c>
-      <c r="D302" s="16" t="s">
-        <v>769</v>
       </c>
       <c r="E302" s="10">
         <v>3</v>
       </c>
       <c r="F302" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G302" s="10" t="b">
         <v>1</v>
@@ -22490,13 +22490,13 @@
         <v>847</v>
       </c>
       <c r="D303" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E303" s="10">
         <v>8</v>
       </c>
       <c r="F303" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G303" s="10" t="b">
         <v>1</v>
@@ -22513,13 +22513,13 @@
         <v>961</v>
       </c>
       <c r="D304" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E304" s="10">
         <v>4</v>
       </c>
       <c r="F304" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G304" s="10" t="b">
         <v>1</v>
@@ -22536,13 +22536,13 @@
         <v>879</v>
       </c>
       <c r="D305" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E305" s="10">
         <v>4</v>
       </c>
       <c r="F305" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G305" s="10" t="b">
         <v>1</v>
@@ -22559,13 +22559,13 @@
         <v>933</v>
       </c>
       <c r="D306" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E306" s="10">
         <v>3</v>
       </c>
       <c r="F306" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G306" s="10" t="b">
         <v>1</v>
@@ -22576,19 +22576,19 @@
         <v>571</v>
       </c>
       <c r="B307" s="10" t="s">
+        <v>810</v>
+      </c>
+      <c r="C307" s="10" t="s">
         <v>811</v>
       </c>
-      <c r="C307" s="10" t="s">
-        <v>812</v>
-      </c>
       <c r="D307" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E307" s="10">
         <v>3</v>
       </c>
       <c r="F307" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G307" s="10" t="b">
         <v>1</v>
@@ -22605,13 +22605,13 @@
         <v>949</v>
       </c>
       <c r="D308" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E308" s="10">
         <v>3</v>
       </c>
       <c r="F308" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G308" s="10" t="b">
         <v>1</v>
@@ -22628,13 +22628,13 @@
         <v>963</v>
       </c>
       <c r="D309" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E309" s="10">
         <v>2</v>
       </c>
       <c r="F309" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G309" s="10" t="b">
         <v>1</v>
@@ -22645,19 +22645,19 @@
         <v>576</v>
       </c>
       <c r="B310" s="10" t="s">
+        <v>760</v>
+      </c>
+      <c r="C310" s="10" t="s">
         <v>761</v>
       </c>
-      <c r="C310" s="10" t="s">
-        <v>762</v>
-      </c>
       <c r="D310" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E310" s="10">
         <v>3</v>
       </c>
       <c r="F310" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G310" s="10" t="b">
         <v>1</v>
@@ -22674,13 +22674,13 @@
         <v>847</v>
       </c>
       <c r="D311" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E311" s="10">
         <v>1</v>
       </c>
       <c r="F311" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G311" s="10" t="b">
         <v>1</v>
@@ -22697,13 +22697,13 @@
         <v>961</v>
       </c>
       <c r="D312" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E312" s="10">
         <v>4</v>
       </c>
       <c r="F312" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G312" s="10" t="b">
         <v>1</v>
@@ -22720,13 +22720,13 @@
         <v>879</v>
       </c>
       <c r="D313" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E313" s="10">
         <v>5</v>
       </c>
       <c r="F313" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G313" s="10" t="b">
         <v>1</v>
@@ -22743,13 +22743,13 @@
         <v>933</v>
       </c>
       <c r="D314" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E314" s="10">
         <v>3</v>
       </c>
       <c r="F314" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G314" s="10" t="b">
         <v>1</v>
@@ -22760,19 +22760,19 @@
         <v>576</v>
       </c>
       <c r="B315" s="10" t="s">
+        <v>810</v>
+      </c>
+      <c r="C315" s="10" t="s">
         <v>811</v>
       </c>
-      <c r="C315" s="10" t="s">
-        <v>812</v>
-      </c>
       <c r="D315" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E315" s="10">
         <v>3</v>
       </c>
       <c r="F315" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G315" s="10" t="b">
         <v>1</v>
@@ -22789,13 +22789,13 @@
         <v>949</v>
       </c>
       <c r="D316" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E316" s="10">
         <v>3</v>
       </c>
       <c r="F316" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G316" s="10" t="b">
         <v>1</v>
@@ -22812,13 +22812,13 @@
         <v>963</v>
       </c>
       <c r="D317" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E317" s="10">
         <v>3</v>
       </c>
       <c r="F317" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G317" s="10" t="b">
         <v>1</v>
@@ -22829,19 +22829,19 @@
         <v>581</v>
       </c>
       <c r="B318" s="10" t="s">
+        <v>810</v>
+      </c>
+      <c r="C318" s="10" t="s">
         <v>811</v>
       </c>
-      <c r="C318" s="10" t="s">
-        <v>812</v>
-      </c>
       <c r="D318" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E318" s="10">
         <v>3</v>
       </c>
       <c r="F318" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G318" s="10" t="b">
         <v>1</v>
@@ -22852,19 +22852,19 @@
         <v>581</v>
       </c>
       <c r="B319" s="10" t="s">
+        <v>816</v>
+      </c>
+      <c r="C319" s="10" t="s">
         <v>817</v>
       </c>
-      <c r="C319" s="10" t="s">
-        <v>818</v>
-      </c>
       <c r="D319" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E319" s="10">
         <v>3</v>
       </c>
       <c r="F319" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G319" s="10" t="b">
         <v>1</v>
@@ -22875,19 +22875,19 @@
         <v>581</v>
       </c>
       <c r="B320" s="10" t="s">
+        <v>771</v>
+      </c>
+      <c r="C320" s="10" t="s">
         <v>772</v>
       </c>
-      <c r="C320" s="10" t="s">
-        <v>773</v>
-      </c>
       <c r="D320" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E320" s="10">
         <v>2</v>
       </c>
       <c r="F320" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G320" s="10" t="b">
         <v>1</v>
@@ -22898,19 +22898,19 @@
         <v>581</v>
       </c>
       <c r="B321" s="10" t="s">
+        <v>769</v>
+      </c>
+      <c r="C321" s="10" t="s">
         <v>770</v>
       </c>
-      <c r="C321" s="10" t="s">
-        <v>771</v>
-      </c>
       <c r="D321" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E321" s="10">
         <v>3</v>
       </c>
       <c r="F321" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G321" s="10" t="b">
         <v>1</v>
@@ -22927,13 +22927,13 @@
         <v>847</v>
       </c>
       <c r="D322" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E322" s="10">
         <v>8</v>
       </c>
       <c r="F322" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G322" s="10" t="b">
         <v>1</v>
@@ -22950,13 +22950,13 @@
         <v>965</v>
       </c>
       <c r="D323" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E323" s="10">
         <v>4</v>
       </c>
       <c r="F323" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G323" s="10" t="b">
         <v>1</v>
@@ -22973,13 +22973,13 @@
         <v>967</v>
       </c>
       <c r="D324" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E324" s="10">
         <v>4</v>
       </c>
       <c r="F324" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G324" s="10" t="b">
         <v>1</v>
@@ -22996,13 +22996,13 @@
         <v>939</v>
       </c>
       <c r="D325" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E325" s="10">
         <v>4</v>
       </c>
       <c r="F325" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G325" s="10" t="b">
         <v>1</v>
@@ -23019,13 +23019,13 @@
         <v>969</v>
       </c>
       <c r="D326" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E326" s="10">
         <v>4</v>
       </c>
       <c r="F326" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G326" s="10" t="b">
         <v>1</v>
@@ -23042,13 +23042,13 @@
         <v>961</v>
       </c>
       <c r="D327" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E327" s="10">
         <v>4</v>
       </c>
       <c r="F327" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G327" s="10" t="b">
         <v>1</v>
@@ -23065,13 +23065,13 @@
         <v>879</v>
       </c>
       <c r="D328" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E328" s="10">
         <v>4</v>
       </c>
       <c r="F328" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G328" s="10" t="b">
         <v>1</v>
@@ -23088,13 +23088,13 @@
         <v>915</v>
       </c>
       <c r="D329" s="16" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E329" s="10">
         <v>3</v>
       </c>
       <c r="F329" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G329" s="10" t="b">
         <v>1</v>
@@ -23111,13 +23111,13 @@
         <v>971</v>
       </c>
       <c r="D330" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E330" s="10">
         <v>5</v>
       </c>
       <c r="F330" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G330" s="10" t="b">
         <v>1</v>
@@ -23134,13 +23134,13 @@
         <v>973</v>
       </c>
       <c r="D331" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E331" s="10">
         <v>5</v>
       </c>
       <c r="F331" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G331" s="10" t="b">
         <v>1</v>
@@ -23157,13 +23157,13 @@
         <v>975</v>
       </c>
       <c r="D332" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E332" s="10">
         <v>5</v>
       </c>
       <c r="F332" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G332" s="10" t="b">
         <v>1</v>
@@ -23180,13 +23180,13 @@
         <v>977</v>
       </c>
       <c r="D333" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E333" s="10">
         <v>5</v>
       </c>
       <c r="F333" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G333" s="10" t="b">
         <v>1</v>
@@ -23203,13 +23203,13 @@
         <v>979</v>
       </c>
       <c r="D334" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E334" s="10">
         <v>3</v>
       </c>
       <c r="F334" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G334" s="10" t="b">
         <v>1</v>
@@ -23226,13 +23226,13 @@
         <v>881</v>
       </c>
       <c r="D335" s="16" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E335" s="10">
         <v>3</v>
       </c>
       <c r="F335" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G335" s="10" t="b">
         <v>1</v>
@@ -23240,22 +23240,22 @@
     </row>
     <row r="336" spans="1:7">
       <c r="A336" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B336" s="10" t="s">
+        <v>816</v>
+      </c>
+      <c r="C336" s="47" t="s">
         <v>817</v>
       </c>
-      <c r="C336" s="47" t="s">
-        <v>818</v>
-      </c>
       <c r="D336" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E336" s="10">
         <v>2</v>
       </c>
       <c r="F336" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G336" s="10" t="b">
         <v>1</v>
@@ -23263,22 +23263,22 @@
     </row>
     <row r="337" spans="1:7">
       <c r="A337" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B337" s="10" t="s">
         <v>290</v>
       </c>
       <c r="C337" s="47" t="s">
-        <v>591</v>
+        <v>845</v>
       </c>
       <c r="D337" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E337" s="10">
         <v>1</v>
       </c>
       <c r="F337" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G337" s="10" t="b">
         <v>1</v>
@@ -23286,22 +23286,22 @@
     </row>
     <row r="338" spans="1:7">
       <c r="A338" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B338" s="10" t="s">
+        <v>814</v>
+      </c>
+      <c r="C338" s="47" t="s">
         <v>815</v>
       </c>
-      <c r="C338" s="47" t="s">
-        <v>816</v>
-      </c>
       <c r="D338" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E338" s="10">
         <v>1</v>
       </c>
       <c r="F338" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G338" s="10" t="b">
         <v>1</v>
@@ -23309,7 +23309,7 @@
     </row>
     <row r="339" spans="1:7">
       <c r="A339" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B339" s="10" t="s">
         <v>980</v>
@@ -23318,13 +23318,13 @@
         <v>981</v>
       </c>
       <c r="D339" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E339" s="10">
         <v>1</v>
       </c>
       <c r="F339" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G339" s="10" t="b">
         <v>1</v>
@@ -23332,7 +23332,7 @@
     </row>
     <row r="340" spans="1:7">
       <c r="A340" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B340" s="10" t="s">
         <v>846</v>
@@ -23341,13 +23341,13 @@
         <v>847</v>
       </c>
       <c r="D340" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E340" s="10">
         <v>1</v>
       </c>
       <c r="F340" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G340" s="10" t="b">
         <v>1</v>
@@ -23355,22 +23355,22 @@
     </row>
     <row r="341" spans="1:7">
       <c r="A341" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B341" s="10" t="s">
+        <v>837</v>
+      </c>
+      <c r="C341" s="47" t="s">
         <v>838</v>
       </c>
-      <c r="C341" s="47" t="s">
-        <v>839</v>
-      </c>
       <c r="D341" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E341" s="10">
         <v>1</v>
       </c>
       <c r="F341" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G341" s="10" t="b">
         <v>1</v>
@@ -23378,16 +23378,16 @@
     </row>
     <row r="342" spans="1:7">
       <c r="A342" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B342" s="10" t="s">
+        <v>769</v>
+      </c>
+      <c r="C342" s="47" t="s">
         <v>770</v>
       </c>
-      <c r="C342" s="47" t="s">
-        <v>771</v>
-      </c>
       <c r="D342" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E342" s="10">
         <v>8</v>
@@ -23401,16 +23401,16 @@
     </row>
     <row r="343" spans="1:7">
       <c r="A343" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B343" s="10" t="s">
+        <v>839</v>
+      </c>
+      <c r="C343" s="47" t="s">
         <v>840</v>
       </c>
-      <c r="C343" s="47" t="s">
-        <v>841</v>
-      </c>
       <c r="D343" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E343" s="10">
         <v>8</v>
@@ -23424,7 +23424,7 @@
     </row>
     <row r="344" spans="1:7">
       <c r="A344" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B344" s="10" t="s">
         <v>866</v>
@@ -23433,13 +23433,13 @@
         <v>867</v>
       </c>
       <c r="D344" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E344" s="10">
         <v>1</v>
       </c>
       <c r="F344" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G344" s="10" t="b">
         <v>1</v>
@@ -23447,7 +23447,7 @@
     </row>
     <row r="345" spans="1:7">
       <c r="A345" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B345" s="10" t="s">
         <v>882</v>
@@ -23456,7 +23456,7 @@
         <v>883</v>
       </c>
       <c r="D345" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E345" s="10">
         <v>5</v>
@@ -23470,16 +23470,16 @@
     </row>
     <row r="346" spans="1:7">
       <c r="A346" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B346" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C346" s="47" t="s">
         <v>767</v>
       </c>
-      <c r="C346" s="47" t="s">
+      <c r="D346" s="16" t="s">
         <v>768</v>
-      </c>
-      <c r="D346" s="16" t="s">
-        <v>769</v>
       </c>
       <c r="E346" s="10">
         <v>5</v>
@@ -23493,7 +23493,7 @@
     </row>
     <row r="347" spans="1:7">
       <c r="A347" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B347" s="10" t="s">
         <v>983</v>
@@ -23502,7 +23502,7 @@
         <v>984</v>
       </c>
       <c r="D347" s="16" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E347" s="10">
         <v>5</v>
@@ -23516,7 +23516,7 @@
     </row>
     <row r="348" spans="1:7">
       <c r="A348" s="10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B348" s="10" t="s">
         <v>924</v>
@@ -23525,13 +23525,13 @@
         <v>925</v>
       </c>
       <c r="D348" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E348" s="10">
         <v>4</v>
       </c>
       <c r="F348" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G348" s="10" t="b">
         <v>1</v>
@@ -23539,7 +23539,7 @@
     </row>
     <row r="349" spans="1:7">
       <c r="A349" s="10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B349" s="10" t="s">
         <v>866</v>
@@ -23548,13 +23548,13 @@
         <v>867</v>
       </c>
       <c r="D349" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E349" s="10">
         <v>3</v>
       </c>
       <c r="F349" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G349" s="10" t="b">
         <v>1</v>
@@ -23562,22 +23562,22 @@
     </row>
     <row r="350" spans="1:7">
       <c r="A350" s="10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B350" s="10" t="s">
+        <v>769</v>
+      </c>
+      <c r="C350" s="10" t="s">
         <v>770</v>
       </c>
-      <c r="C350" s="10" t="s">
-        <v>771</v>
-      </c>
       <c r="D350" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E350" s="10">
         <v>3</v>
       </c>
       <c r="F350" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G350" s="10" t="b">
         <v>1</v>
@@ -23585,7 +23585,7 @@
     </row>
     <row r="351" spans="1:7">
       <c r="A351" s="10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B351" s="10" t="s">
         <v>985</v>
@@ -23594,13 +23594,13 @@
         <v>986</v>
       </c>
       <c r="D351" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E351" s="10">
         <v>3</v>
       </c>
       <c r="F351" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G351" s="10" t="b">
         <v>1</v>
@@ -23608,7 +23608,7 @@
     </row>
     <row r="352" spans="1:7">
       <c r="A352" s="10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B352" s="10" t="s">
         <v>987</v>
@@ -23617,13 +23617,13 @@
         <v>988</v>
       </c>
       <c r="D352" s="16" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E352" s="10">
         <v>1</v>
       </c>
       <c r="F352" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G352" s="10" t="b">
         <v>1</v>
@@ -23631,22 +23631,22 @@
     </row>
     <row r="353" spans="1:7">
       <c r="A353" s="10" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B353" s="10" t="s">
+        <v>825</v>
+      </c>
+      <c r="C353" s="10" t="s">
         <v>826</v>
       </c>
-      <c r="C353" s="10" t="s">
-        <v>827</v>
-      </c>
       <c r="D353" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E353" s="10">
         <v>2</v>
       </c>
       <c r="F353" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G353" s="10" t="b">
         <v>1</v>
@@ -23654,22 +23654,22 @@
     </row>
     <row r="354" spans="1:7">
       <c r="A354" s="10" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B354" s="10" t="s">
+        <v>827</v>
+      </c>
+      <c r="C354" s="10" t="s">
         <v>828</v>
       </c>
-      <c r="C354" s="10" t="s">
-        <v>829</v>
-      </c>
       <c r="D354" s="14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E354" s="10">
         <v>6</v>
       </c>
       <c r="F354" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G354" s="10" t="b">
         <v>1</v>
@@ -23677,22 +23677,22 @@
     </row>
     <row r="355" spans="1:7">
       <c r="A355" s="10" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B355" s="10" t="s">
+        <v>829</v>
+      </c>
+      <c r="C355" s="10" t="s">
         <v>830</v>
       </c>
-      <c r="C355" s="10" t="s">
-        <v>831</v>
-      </c>
       <c r="D355" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E355" s="10">
         <v>3</v>
       </c>
       <c r="F355" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G355" s="10" t="b">
         <v>1</v>
@@ -23700,22 +23700,22 @@
     </row>
     <row r="356" spans="1:7">
       <c r="A356" s="10" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B356" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="C356" s="10" t="s">
         <v>767</v>
       </c>
-      <c r="C356" s="10" t="s">
+      <c r="D356" s="16" t="s">
         <v>768</v>
-      </c>
-      <c r="D356" s="16" t="s">
-        <v>769</v>
       </c>
       <c r="E356" s="10">
         <v>2</v>
       </c>
       <c r="F356" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G356" s="10" t="b">
         <v>1</v>
@@ -23752,10 +23752,10 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>989</v>
@@ -23781,10 +23781,10 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="7" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>993</v>
@@ -23813,10 +23813,10 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="7" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>993</v>
@@ -23845,10 +23845,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="7" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>993</v>
@@ -23877,10 +23877,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="7" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>1009</v>
@@ -23909,10 +23909,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="7" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>1014</v>
@@ -23941,10 +23941,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="7" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>993</v>
@@ -23973,10 +23973,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="7" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>993</v>
@@ -24005,10 +24005,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="7" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>1014</v>
@@ -24037,10 +24037,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="7" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>1014</v>
@@ -24069,10 +24069,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="7" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>1014</v>
@@ -24101,10 +24101,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="7" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>993</v>
@@ -24133,10 +24133,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="7" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>1030</v>
@@ -24165,10 +24165,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="7" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>1030</v>
@@ -24197,10 +24197,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="7" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>1009</v>
@@ -24229,10 +24229,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="7" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>1014</v>
@@ -24261,10 +24261,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="7" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>1014</v>
@@ -24293,10 +24293,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="7" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>1014</v>
@@ -24325,10 +24325,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="7" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>1014</v>
@@ -24357,10 +24357,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="7" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>1014</v>
@@ -24389,10 +24389,10 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="7" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>1014</v>
@@ -24421,10 +24421,10 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="7" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>1030</v>
@@ -24453,10 +24453,10 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="7" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>993</v>
@@ -24485,10 +24485,10 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="7" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>993</v>
@@ -24517,10 +24517,10 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="7" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>1014</v>
@@ -24581,10 +24581,10 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="7" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>1009</v>
@@ -24613,10 +24613,10 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="7" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>1014</v>
@@ -24645,10 +24645,10 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>993</v>
@@ -24677,10 +24677,10 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="10" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>993</v>
@@ -24709,10 +24709,10 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="7" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>993</v>
@@ -24741,10 +24741,10 @@
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="7" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>1069</v>
@@ -24773,10 +24773,10 @@
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="7" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>1009</v>
@@ -24805,10 +24805,10 @@
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="10" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>1014</v>
@@ -24837,10 +24837,10 @@
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="10" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>1014</v>
@@ -24869,10 +24869,10 @@
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="10" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>1009</v>
@@ -24901,10 +24901,10 @@
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="7" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>1030</v>
@@ -24933,10 +24933,10 @@
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="7" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>993</v>
@@ -24965,10 +24965,10 @@
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="7" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>993</v>
@@ -24997,10 +24997,10 @@
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="7" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>993</v>
@@ -25029,10 +25029,10 @@
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="7" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>993</v>
@@ -25061,10 +25061,10 @@
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="7" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>1009</v>
@@ -25093,10 +25093,10 @@
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="7" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>1030</v>
@@ -25125,7 +25125,7 @@
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="10" t="s">
-        <v>591</v>
+        <v>845</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>290</v>
@@ -27918,7 +27918,7 @@
     </row>
     <row r="6" spans="1:6" ht="18" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>1208</v>
@@ -27936,7 +27936,7 @@
     </row>
     <row r="7" spans="1:6" ht="18" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>1211</v>
@@ -27954,7 +27954,7 @@
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>1213</v>
@@ -27972,7 +27972,7 @@
     </row>
     <row r="9" spans="1:6" ht="18" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>1214</v>
@@ -27988,7 +27988,7 @@
     </row>
     <row r="10" spans="1:6" ht="18" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>1215</v>
@@ -28006,7 +28006,7 @@
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>1217</v>
@@ -28022,7 +28022,7 @@
     </row>
     <row r="12" spans="1:6" ht="18" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>1218</v>
@@ -28040,7 +28040,7 @@
     </row>
     <row r="13" spans="1:6" ht="18" customHeight="1">
       <c r="A13" s="7" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>1220</v>
@@ -28058,7 +28058,7 @@
     </row>
     <row r="14" spans="1:6" ht="18" customHeight="1">
       <c r="A14" s="7" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>1222</v>
@@ -28076,7 +28076,7 @@
     </row>
     <row r="15" spans="1:6" ht="18" customHeight="1">
       <c r="A15" s="7" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>1224</v>
@@ -28094,7 +28094,7 @@
     </row>
     <row r="16" spans="1:6" ht="18" customHeight="1">
       <c r="A16" s="7" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>1226</v>
@@ -28112,7 +28112,7 @@
     </row>
     <row r="17" spans="1:6" ht="18" customHeight="1">
       <c r="A17" s="7" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>1228</v>
@@ -28130,7 +28130,7 @@
     </row>
     <row r="18" spans="1:6" ht="18" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>1230</v>
@@ -28148,7 +28148,7 @@
     </row>
     <row r="19" spans="1:6" ht="18" customHeight="1">
       <c r="A19" s="7" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>1232</v>
@@ -28166,7 +28166,7 @@
     </row>
     <row r="20" spans="1:6" ht="18" customHeight="1">
       <c r="A20" s="7" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>1234</v>
@@ -28184,7 +28184,7 @@
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1">
       <c r="A21" s="7" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>1236</v>
@@ -28202,7 +28202,7 @@
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1">
       <c r="A22" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>1238</v>
@@ -28220,7 +28220,7 @@
     </row>
     <row r="23" spans="1:6" ht="18" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>1240</v>

--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE191A9-5D83-4E13-A0CD-857706105EA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB483EED-A360-4E4C-B162-42AA24905A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2059,6 +2059,9 @@
 【标准方】金锁固精丸</t>
   </si>
   <si>
+    <t>ren_shen</t>
+  </si>
+  <si>
     <t>妊娠</t>
   </si>
   <si>
@@ -3532,9 +3535,6 @@
   </si>
   <si>
     <t>ge_gen</t>
-  </si>
-  <si>
-    <t>ren_shen</t>
   </si>
   <si>
     <t>熟地黄</t>
@@ -6072,7 +6072,7 @@
 在搜索栏输入药材，方剂，疾病的中文名或拼音，拼音首字母可快速查找。</t>
   </si>
   <si>
-    <t>ren_shen</t>
+    <t>ren_shen_disease</t>
     <phoneticPr fontId="14"/>
   </si>
 </sst>
@@ -8361,8 +8361,8 @@
     <col min="7" max="7" width="25.125" style="23" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.25" style="23" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="33.375" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="43" width="9.125" style="23" customWidth="1"/>
-    <col min="44" max="16384" width="9.125" style="23"/>
+    <col min="10" max="44" width="9.125" style="23" customWidth="1"/>
+    <col min="45" max="16384" width="9.125" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.399999999999999" customHeight="1">
@@ -10313,8 +10313,8 @@
     <col min="14" max="14" width="12" style="36" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.75" style="36" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10.875" style="36" bestFit="1" customWidth="1"/>
-    <col min="17" max="66" width="9" style="36" customWidth="1"/>
-    <col min="67" max="16384" width="9" style="36"/>
+    <col min="17" max="67" width="9" style="36" customWidth="1"/>
+    <col min="68" max="16384" width="9" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -10905,8 +10905,8 @@
     <col min="8" max="8" width="8.125" style="32" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="48" style="32" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="150.5" style="32" bestFit="1" customWidth="1"/>
-    <col min="11" max="17" width="8.875" style="36" customWidth="1"/>
-    <col min="18" max="16384" width="8.875" style="36"/>
+    <col min="11" max="18" width="8.875" style="36" customWidth="1"/>
+    <col min="19" max="16384" width="8.875" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -13669,59 +13669,59 @@
         <v>1251</v>
       </c>
       <c r="B47" s="47" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C47" s="25" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>391</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="10" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C48" s="25" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>391</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="10" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C49" s="25" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>391</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15" customHeight="1">
@@ -13942,8 +13942,8 @@
     <col min="27" max="27" width="5.125" style="35" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="5" style="35" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="5.25" style="35" bestFit="1" customWidth="1"/>
-    <col min="30" max="91" width="9" style="9" customWidth="1"/>
-    <col min="92" max="16384" width="9" style="9"/>
+    <col min="30" max="92" width="9" style="9" customWidth="1"/>
+    <col min="93" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="15.4" customHeight="1">
@@ -13951,88 +13951,88 @@
         <v>382</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F1" s="26" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="G1" s="26" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1" s="26" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="I1" s="26" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="J1" s="29" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="K1" s="29" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L1" s="29" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M1" s="29" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N1" s="30" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="O1" s="30" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="P1" s="30" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="Q1" s="30" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="R1" s="28" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="S1" s="28" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="T1" s="28" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="U1" s="28" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="V1" s="31" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="W1" s="31" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="X1" s="31" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="Y1" s="31" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="Z1" s="31" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AA1" s="31" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AB1" s="31" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AC1" s="31" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="18" customHeight="1">
@@ -14517,7 +14517,7 @@
     </row>
     <row r="47" spans="1:28" ht="18" customHeight="1">
       <c r="A47" s="10" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="Q47" s="34">
         <v>1.5</v>
@@ -14531,7 +14531,7 @@
     </row>
     <row r="48" spans="1:28" ht="18" customHeight="1">
       <c r="A48" s="10" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H48" s="27">
         <v>1.5</v>
@@ -14548,7 +14548,7 @@
     </row>
     <row r="49" spans="1:21" ht="18" customHeight="1">
       <c r="A49" s="10" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B49" s="32">
         <v>1.3</v>
@@ -14612,13 +14612,13 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>385</v>
@@ -14629,7 +14629,7 @@
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>390</v>
@@ -14638,15 +14638,15 @@
         <v>388</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1">
       <c r="A3" s="7" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>395</v>
@@ -14655,15 +14655,15 @@
         <v>394</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>399</v>
@@ -14672,15 +14672,15 @@
         <v>398</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>403</v>
@@ -14689,15 +14689,15 @@
         <v>402</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>407</v>
@@ -14706,15 +14706,15 @@
         <v>406</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>412</v>
@@ -14723,15 +14723,15 @@
         <v>410</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>417</v>
@@ -14740,15 +14740,15 @@
         <v>415</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>421</v>
@@ -14757,15 +14757,15 @@
         <v>420</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>425</v>
@@ -14774,15 +14774,15 @@
         <v>424</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>429</v>
@@ -14791,15 +14791,15 @@
         <v>428</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>433</v>
@@ -14808,15 +14808,15 @@
         <v>432</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1">
       <c r="A13" s="7" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>438</v>
@@ -14825,15 +14825,15 @@
         <v>436</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1">
       <c r="A14" s="7" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>443</v>
@@ -14842,15 +14842,15 @@
         <v>441</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1">
       <c r="A15" s="7" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>448</v>
@@ -14859,15 +14859,15 @@
         <v>446</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1">
       <c r="A16" s="7" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>453</v>
@@ -14876,15 +14876,15 @@
         <v>451</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1">
       <c r="A17" s="7" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>458</v>
@@ -14893,15 +14893,15 @@
         <v>456</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>462</v>
@@ -14910,15 +14910,15 @@
         <v>461</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1">
       <c r="A19" s="7" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>467</v>
@@ -14927,15 +14927,15 @@
         <v>465</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1">
       <c r="A20" s="7" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>471</v>
@@ -14944,15 +14944,15 @@
         <v>470</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1">
       <c r="A21" s="7" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>476</v>
@@ -14961,15 +14961,15 @@
         <v>474</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1">
       <c r="A22" s="7" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>479</v>
@@ -14978,15 +14978,15 @@
         <v>281</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="18" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>484</v>
@@ -14995,15 +14995,15 @@
         <v>482</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="18" customHeight="1">
       <c r="A24" s="7" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>489</v>
@@ -15012,15 +15012,15 @@
         <v>487</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="18" customHeight="1">
       <c r="A25" s="7" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>494</v>
@@ -15029,15 +15029,15 @@
         <v>492</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="18" customHeight="1">
       <c r="A26" s="7" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>499</v>
@@ -15046,15 +15046,15 @@
         <v>497</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="18" customHeight="1">
       <c r="A27" s="7" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>503</v>
@@ -15063,15 +15063,15 @@
         <v>502</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="18" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>508</v>
@@ -15080,15 +15080,15 @@
         <v>506</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="18" customHeight="1">
       <c r="A29" s="7" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>512</v>
@@ -15097,15 +15097,15 @@
         <v>511</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="18" customHeight="1">
       <c r="A30" s="7" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>515</v>
@@ -15114,15 +15114,15 @@
         <v>271</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="18" customHeight="1">
       <c r="A31" s="7" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>519</v>
@@ -15131,15 +15131,15 @@
         <v>518</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="18" customHeight="1">
       <c r="A32" s="7" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>524</v>
@@ -15148,15 +15148,15 @@
         <v>522</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="18" customHeight="1">
       <c r="A33" s="7" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>529</v>
@@ -15165,15 +15165,15 @@
         <v>527</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="18" customHeight="1">
       <c r="A34" s="7" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>534</v>
@@ -15182,15 +15182,15 @@
         <v>532</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="18" customHeight="1">
       <c r="A35" s="7" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>539</v>
@@ -15199,15 +15199,15 @@
         <v>537</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="18" customHeight="1">
       <c r="A36" s="7" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>543</v>
@@ -15216,15 +15216,15 @@
         <v>542</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="18" customHeight="1">
       <c r="A37" s="11" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>548</v>
@@ -15233,15 +15233,15 @@
         <v>546</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="18" customHeight="1">
       <c r="A38" s="7" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>552</v>
@@ -15250,15 +15250,15 @@
         <v>551</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="18" customHeight="1">
       <c r="A39" s="7" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>556</v>
@@ -15267,15 +15267,15 @@
         <v>555</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="18" customHeight="1">
       <c r="A40" s="7" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>561</v>
@@ -15284,15 +15284,15 @@
         <v>559</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="18" customHeight="1">
       <c r="A41" s="7" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>566</v>
@@ -15301,15 +15301,15 @@
         <v>564</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="18" customHeight="1">
       <c r="A42" s="7" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>571</v>
@@ -15318,15 +15318,15 @@
         <v>569</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="18" customHeight="1">
       <c r="A43" s="7" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>576</v>
@@ -15335,15 +15335,15 @@
         <v>574</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="18" customHeight="1">
       <c r="A44" s="7" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>581</v>
@@ -15352,15 +15352,15 @@
         <v>579</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="18" customHeight="1">
       <c r="A45" s="7" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>585</v>
@@ -15369,15 +15369,15 @@
         <v>584</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="18" customHeight="1">
       <c r="A46" s="7" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>589</v>
@@ -15386,61 +15386,61 @@
         <v>588</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="18" customHeight="1">
       <c r="A47" s="11" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="18" customHeight="1">
       <c r="A48" s="7" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="18" customHeight="1">
       <c r="A49" s="7" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="18" customHeight="1">
@@ -15535,25 +15535,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="12" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B1" s="63" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -15561,19 +15561,19 @@
         <v>390</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E2" s="10">
         <v>3</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G2" s="10" t="b">
         <v>1</v>
@@ -15584,19 +15584,19 @@
         <v>390</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E3" s="10">
         <v>2</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G3" s="10" t="b">
         <v>1</v>
@@ -15607,19 +15607,19 @@
         <v>390</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E4" s="10">
         <v>2</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G4" s="10" t="b">
         <v>1</v>
@@ -15630,19 +15630,19 @@
         <v>390</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E5" s="10">
         <v>1</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G5" s="10" t="b">
         <v>1</v>
@@ -15653,19 +15653,19 @@
         <v>395</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E6" s="10">
         <v>3</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G6" s="10" t="b">
         <v>1</v>
@@ -15676,19 +15676,19 @@
         <v>395</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E7" s="10">
         <v>3</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G7" s="10" t="b">
         <v>1</v>
@@ -15699,19 +15699,19 @@
         <v>395</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E8" s="10">
         <v>3</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G8" s="10" t="b">
         <v>1</v>
@@ -15722,19 +15722,19 @@
         <v>395</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E9" s="10">
         <v>2</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G9" s="10" t="b">
         <v>1</v>
@@ -15745,19 +15745,19 @@
         <v>395</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E10" s="10">
         <v>2</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G10" s="10" t="b">
         <v>1</v>
@@ -15768,19 +15768,19 @@
         <v>399</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E11" s="10">
         <v>1</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G11" s="10" t="b">
         <v>1</v>
@@ -15791,19 +15791,19 @@
         <v>399</v>
       </c>
       <c r="B12" s="10" t="s">
+        <v>779</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>780</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>759</v>
+      </c>
+      <c r="E12" s="10">
+        <v>1</v>
+      </c>
+      <c r="F12" s="10" t="s">
         <v>778</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>779</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>758</v>
-      </c>
-      <c r="E12" s="10">
-        <v>1</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>777</v>
       </c>
       <c r="G12" s="10" t="b">
         <v>1</v>
@@ -15814,19 +15814,19 @@
         <v>399</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E13" s="10">
         <v>6</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G13" s="10" t="b">
         <v>1</v>
@@ -15837,19 +15837,19 @@
         <v>399</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E14" s="10">
         <v>4</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G14" s="10" t="b">
         <v>1</v>
@@ -15860,19 +15860,19 @@
         <v>399</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E15" s="10">
         <v>6</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G15" s="10" t="b">
         <v>1</v>
@@ -15883,19 +15883,19 @@
         <v>399</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E16" s="10">
         <v>5</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G16" s="10" t="b">
         <v>1</v>
@@ -15906,19 +15906,19 @@
         <v>399</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E17" s="10">
         <v>6</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G17" s="10" t="b">
         <v>1</v>
@@ -15929,19 +15929,19 @@
         <v>399</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E18" s="10">
         <v>4</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G18" s="10" t="b">
         <v>1</v>
@@ -15952,19 +15952,19 @@
         <v>399</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E19" s="10">
         <v>4</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G19" s="10" t="b">
         <v>1</v>
@@ -15975,19 +15975,19 @@
         <v>399</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E20" s="10">
         <v>5</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G20" s="10" t="b">
         <v>1</v>
@@ -15998,19 +15998,19 @@
         <v>403</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E21" s="10">
         <v>1.5</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G21" s="10" t="b">
         <v>1</v>
@@ -16021,19 +16021,19 @@
         <v>403</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E22" s="10">
         <v>2</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G22" s="10" t="b">
         <v>1</v>
@@ -16044,19 +16044,19 @@
         <v>403</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E23" s="10">
         <v>1</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G23" s="10" t="b">
         <v>1</v>
@@ -16067,19 +16067,19 @@
         <v>403</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E24" s="10">
         <v>1</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G24" s="10" t="b">
         <v>1</v>
@@ -16090,19 +16090,19 @@
         <v>403</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E25" s="10">
         <v>1</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G25" s="10" t="b">
         <v>1</v>
@@ -16113,19 +16113,19 @@
         <v>403</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E26" s="10">
         <v>1</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G26" s="10" t="b">
         <v>1</v>
@@ -16136,19 +16136,19 @@
         <v>403</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E27" s="10">
         <v>1</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G27" s="10" t="b">
         <v>1</v>
@@ -16159,19 +16159,19 @@
         <v>407</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E28" s="10">
         <v>3</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G28" s="10" t="b">
         <v>1</v>
@@ -16182,19 +16182,19 @@
         <v>407</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E29" s="10">
         <v>3</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G29" s="10" t="b">
         <v>1</v>
@@ -16205,19 +16205,19 @@
         <v>407</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E30" s="10">
         <v>3</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G30" s="10" t="b">
         <v>1</v>
@@ -16228,19 +16228,19 @@
         <v>407</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E31" s="10">
         <v>3</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G31" s="10" t="b">
         <v>1</v>
@@ -16257,13 +16257,13 @@
         <v>15</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E32" s="10">
         <v>3</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G32" s="10" t="b">
         <v>1</v>
@@ -16274,19 +16274,19 @@
         <v>407</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D33" s="20" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E33" s="10">
         <v>2</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G33" s="10" t="b">
         <v>1</v>
@@ -16297,19 +16297,19 @@
         <v>407</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D34" s="20" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E34" s="10">
         <v>2</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G34" s="10" t="b">
         <v>1</v>
@@ -16320,19 +16320,19 @@
         <v>407</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D35" s="20" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E35" s="10">
         <v>2</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G35" s="10" t="b">
         <v>1</v>
@@ -16343,19 +16343,19 @@
         <v>407</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E36" s="10">
         <v>1</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G36" s="10" t="b">
         <v>1</v>
@@ -16366,19 +16366,19 @@
         <v>412</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E37" s="10">
         <v>1</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G37" s="10" t="b">
         <v>1</v>
@@ -16389,19 +16389,19 @@
         <v>412</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E38" s="10">
         <v>1</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G38" s="10" t="b">
         <v>1</v>
@@ -16412,19 +16412,19 @@
         <v>412</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E39" s="10">
         <v>5</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G39" s="10" t="b">
         <v>1</v>
@@ -16435,19 +16435,19 @@
         <v>417</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E40" s="10">
         <v>2</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G40" s="10" t="b">
         <v>1</v>
@@ -16458,19 +16458,19 @@
         <v>417</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E41" s="10">
         <v>3</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G41" s="10" t="b">
         <v>1</v>
@@ -16481,19 +16481,19 @@
         <v>417</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E42" s="10">
         <v>3</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G42" s="10" t="b">
         <v>1</v>
@@ -16504,19 +16504,19 @@
         <v>417</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E43" s="10">
         <v>3</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G43" s="10" t="b">
         <v>1</v>
@@ -16527,19 +16527,19 @@
         <v>417</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E44" s="10">
         <v>3</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G44" s="10" t="b">
         <v>1</v>
@@ -16550,19 +16550,19 @@
         <v>417</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E45" s="10">
         <v>1</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="G45" s="10" t="b">
         <v>1</v>
@@ -16573,19 +16573,19 @@
         <v>421</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E46" s="10">
         <v>2</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G46" s="10" t="b">
         <v>1</v>
@@ -16596,19 +16596,19 @@
         <v>421</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E47" s="10">
         <v>6</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G47" s="10" t="b">
         <v>1</v>
@@ -16619,19 +16619,19 @@
         <v>421</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E48" s="10">
         <v>3</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G48" s="10" t="b">
         <v>1</v>
@@ -16642,19 +16642,19 @@
         <v>421</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E49" s="10">
         <v>5</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G49" s="10" t="b">
         <v>1</v>
@@ -16665,19 +16665,19 @@
         <v>421</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E50" s="10">
         <v>3</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G50" s="10" t="b">
         <v>1</v>
@@ -16688,19 +16688,19 @@
         <v>425</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E51" s="10">
         <v>1</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G51" s="10" t="b">
         <v>1</v>
@@ -16711,19 +16711,19 @@
         <v>425</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E52" s="10">
         <v>3</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G52" s="10" t="b">
         <v>1</v>
@@ -16734,19 +16734,19 @@
         <v>425</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E53" s="10">
         <v>3</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G53" s="10" t="b">
         <v>1</v>
@@ -16757,19 +16757,19 @@
         <v>425</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E54" s="10">
         <v>3</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G54" s="10" t="b">
         <v>1</v>
@@ -16780,19 +16780,19 @@
         <v>425</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E55" s="10">
         <v>3</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G55" s="10" t="b">
         <v>1</v>
@@ -16803,19 +16803,19 @@
         <v>425</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E56" s="10">
         <v>2</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G56" s="10" t="b">
         <v>1</v>
@@ -16826,19 +16826,19 @@
         <v>425</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E57" s="10">
         <v>2</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G57" s="10" t="b">
         <v>1</v>
@@ -16849,19 +16849,19 @@
         <v>425</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E58" s="10">
         <v>3</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G58" s="10" t="b">
         <v>1</v>
@@ -16872,19 +16872,19 @@
         <v>429</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E59" s="10">
         <v>5</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G59" s="10" t="b">
         <v>1</v>
@@ -16895,19 +16895,19 @@
         <v>429</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E60" s="10">
         <v>3</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G60" s="10" t="b">
         <v>1</v>
@@ -16918,19 +16918,19 @@
         <v>429</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E61" s="10">
         <v>3</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G61" s="10" t="b">
         <v>1</v>
@@ -16941,19 +16941,19 @@
         <v>429</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E62" s="10">
         <v>2</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G62" s="10" t="b">
         <v>1</v>
@@ -16964,19 +16964,19 @@
         <v>429</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E63" s="10">
         <v>2</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G63" s="10" t="b">
         <v>1</v>
@@ -16987,19 +16987,19 @@
         <v>429</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E64" s="10">
         <v>3</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G64" s="10" t="b">
         <v>1</v>
@@ -17010,19 +17010,19 @@
         <v>429</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E65" s="10">
         <v>1</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G65" s="10" t="b">
         <v>1</v>
@@ -17033,19 +17033,19 @@
         <v>433</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E66" s="10">
         <v>3</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G66" s="10" t="b">
         <v>1</v>
@@ -17056,19 +17056,19 @@
         <v>433</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E67" s="10">
         <v>8</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G67" s="10" t="b">
         <v>1</v>
@@ -17079,19 +17079,19 @@
         <v>433</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E68" s="10">
         <v>3</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G68" s="10" t="b">
         <v>1</v>
@@ -17102,19 +17102,19 @@
         <v>433</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D69" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E69" s="10">
         <v>2</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G69" s="10" t="b">
         <v>1</v>
@@ -17128,16 +17128,16 @@
         <v>290</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>845</v>
+        <v>591</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E70" s="10">
         <v>3</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G70" s="10" t="b">
         <v>1</v>
@@ -17148,19 +17148,19 @@
         <v>438</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E71" s="10">
         <v>5</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G71" s="10" t="b">
         <v>1</v>
@@ -17177,13 +17177,13 @@
         <v>847</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E72" s="10">
         <v>5</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G72" s="10" t="b">
         <v>1</v>
@@ -17200,13 +17200,13 @@
         <v>849</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E73" s="10">
         <v>2</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G73" s="10" t="b">
         <v>1</v>
@@ -17223,13 +17223,13 @@
         <v>851</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E74" s="10">
         <v>3</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G74" s="10" t="b">
         <v>1</v>
@@ -17246,13 +17246,13 @@
         <v>853</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E75" s="10">
         <v>3</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G75" s="10" t="b">
         <v>1</v>
@@ -17263,19 +17263,19 @@
         <v>443</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E76" s="10">
         <v>5</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G76" s="10" t="b">
         <v>1</v>
@@ -17292,13 +17292,13 @@
         <v>15</v>
       </c>
       <c r="D77" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E77" s="10">
         <v>5</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G77" s="10" t="b">
         <v>1</v>
@@ -17309,19 +17309,19 @@
         <v>443</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D78" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E78" s="10">
         <v>3</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G78" s="10" t="b">
         <v>1</v>
@@ -17332,19 +17332,19 @@
         <v>443</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D79" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E79" s="10">
         <v>1.5</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G79" s="10" t="b">
         <v>1</v>
@@ -17355,19 +17355,19 @@
         <v>448</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E80" s="10">
         <v>3</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G80" s="10" t="b">
         <v>1</v>
@@ -17384,13 +17384,13 @@
         <v>855</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E81" s="10">
         <v>3</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G81" s="10" t="b">
         <v>1</v>
@@ -17407,13 +17407,13 @@
         <v>857</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E82" s="10">
         <v>2</v>
       </c>
       <c r="F82" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G82" s="10" t="b">
         <v>1</v>
@@ -17430,13 +17430,13 @@
         <v>859</v>
       </c>
       <c r="D83" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E83" s="10">
         <v>1.5</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G83" s="10" t="b">
         <v>1</v>
@@ -17453,13 +17453,13 @@
         <v>861</v>
       </c>
       <c r="D84" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E84" s="10">
         <v>1.5</v>
       </c>
       <c r="F84" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G84" s="10" t="b">
         <v>1</v>
@@ -17470,19 +17470,19 @@
         <v>448</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E85" s="10">
         <v>1.5</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G85" s="10" t="b">
         <v>1</v>
@@ -17493,19 +17493,19 @@
         <v>448</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D86" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E86" s="10">
         <v>1</v>
       </c>
       <c r="F86" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G86" s="10" t="b">
         <v>1</v>
@@ -17522,13 +17522,13 @@
         <v>863</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E87" s="10">
         <v>1.5</v>
       </c>
       <c r="F87" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G87" s="10" t="b">
         <v>1</v>
@@ -17539,19 +17539,19 @@
         <v>453</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D88" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E88" s="10">
         <v>1.5</v>
       </c>
       <c r="F88" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G88" s="10" t="b">
         <v>1</v>
@@ -17568,13 +17568,13 @@
         <v>865</v>
       </c>
       <c r="D89" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E89" s="10">
         <v>1</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G89" s="10" t="b">
         <v>1</v>
@@ -17591,13 +17591,13 @@
         <v>867</v>
       </c>
       <c r="D90" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E90" s="10">
         <v>1</v>
       </c>
       <c r="F90" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G90" s="10" t="b">
         <v>1</v>
@@ -17608,19 +17608,19 @@
         <v>453</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D91" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E91" s="10">
         <v>1</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G91" s="10" t="b">
         <v>1</v>
@@ -17637,13 +17637,13 @@
         <v>15</v>
       </c>
       <c r="D92" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E92" s="10">
         <v>1</v>
       </c>
       <c r="F92" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G92" s="10" t="b">
         <v>1</v>
@@ -17660,13 +17660,13 @@
         <v>869</v>
       </c>
       <c r="D93" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E93" s="10">
         <v>1</v>
       </c>
       <c r="F93" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G93" s="10" t="b">
         <v>1</v>
@@ -17677,19 +17677,19 @@
         <v>453</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D94" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E94" s="10">
         <v>1</v>
       </c>
       <c r="F94" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G94" s="10" t="b">
         <v>1</v>
@@ -17700,19 +17700,19 @@
         <v>453</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D95" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E95" s="10">
         <v>3</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G95" s="10" t="b">
         <v>1</v>
@@ -17723,19 +17723,19 @@
         <v>458</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D96" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E96" s="10">
         <v>6</v>
       </c>
       <c r="F96" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G96" s="10" t="b">
         <v>1</v>
@@ -17746,19 +17746,19 @@
         <v>458</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D97" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E97" s="10">
         <v>2</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G97" s="10" t="b">
         <v>1</v>
@@ -17769,19 +17769,19 @@
         <v>458</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D98" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E98" s="10">
         <v>1</v>
       </c>
       <c r="F98" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G98" s="10" t="b">
         <v>1</v>
@@ -17792,19 +17792,19 @@
         <v>458</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D99" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E99" s="10">
         <v>3</v>
       </c>
       <c r="F99" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G99" s="10" t="b">
         <v>1</v>
@@ -17815,19 +17815,19 @@
         <v>458</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D100" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E100" s="10">
         <v>3</v>
       </c>
       <c r="F100" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G100" s="10" t="b">
         <v>1</v>
@@ -17838,19 +17838,19 @@
         <v>458</v>
       </c>
       <c r="B101" s="10" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D101" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E101" s="10">
         <v>3</v>
       </c>
       <c r="F101" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G101" s="10" t="b">
         <v>1</v>
@@ -17861,19 +17861,19 @@
         <v>458</v>
       </c>
       <c r="B102" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D102" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E102" s="10">
         <v>2</v>
       </c>
       <c r="F102" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G102" s="10" t="b">
         <v>1</v>
@@ -17884,19 +17884,19 @@
         <v>462</v>
       </c>
       <c r="B103" s="10" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D103" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E103" s="10">
         <v>3</v>
       </c>
       <c r="F103" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G103" s="10" t="b">
         <v>1</v>
@@ -17907,19 +17907,19 @@
         <v>462</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D104" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E104" s="10">
         <v>3</v>
       </c>
       <c r="F104" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G104" s="10" t="b">
         <v>1</v>
@@ -17936,13 +17936,13 @@
         <v>871</v>
       </c>
       <c r="D105" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E105" s="10">
         <v>2</v>
       </c>
       <c r="F105" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G105" s="10" t="b">
         <v>1</v>
@@ -17959,13 +17959,13 @@
         <v>873</v>
       </c>
       <c r="D106" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E106" s="10">
         <v>2</v>
       </c>
       <c r="F106" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G106" s="10" t="b">
         <v>1</v>
@@ -17976,19 +17976,19 @@
         <v>462</v>
       </c>
       <c r="B107" s="10" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D107" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E107" s="10">
         <v>3</v>
       </c>
       <c r="F107" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G107" s="10" t="b">
         <v>1</v>
@@ -18005,13 +18005,13 @@
         <v>849</v>
       </c>
       <c r="D108" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E108" s="10">
         <v>2</v>
       </c>
       <c r="F108" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G108" s="10" t="b">
         <v>1</v>
@@ -18022,19 +18022,19 @@
         <v>462</v>
       </c>
       <c r="B109" s="10" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D109" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E109" s="10">
         <v>3</v>
       </c>
       <c r="F109" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G109" s="10" t="b">
         <v>1</v>
@@ -18045,19 +18045,19 @@
         <v>462</v>
       </c>
       <c r="B110" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D110" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E110" s="10">
         <v>2</v>
       </c>
       <c r="F110" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G110" s="10" t="b">
         <v>1</v>
@@ -18071,16 +18071,16 @@
         <v>290</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>845</v>
+        <v>591</v>
       </c>
       <c r="D111" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E111" s="10">
         <v>4</v>
       </c>
       <c r="F111" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G111" s="10" t="b">
         <v>1</v>
@@ -18091,19 +18091,19 @@
         <v>467</v>
       </c>
       <c r="B112" s="10" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D112" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E112" s="10">
         <v>3</v>
       </c>
       <c r="F112" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G112" s="10" t="b">
         <v>1</v>
@@ -18114,19 +18114,19 @@
         <v>467</v>
       </c>
       <c r="B113" s="10" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D113" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E113" s="10">
         <v>3</v>
       </c>
       <c r="F113" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G113" s="10" t="b">
         <v>1</v>
@@ -18137,19 +18137,19 @@
         <v>467</v>
       </c>
       <c r="B114" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D114" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E114" s="10">
         <v>2</v>
       </c>
       <c r="F114" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G114" s="10" t="b">
         <v>1</v>
@@ -18166,13 +18166,13 @@
         <v>875</v>
       </c>
       <c r="D115" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E115" s="10">
         <v>3</v>
       </c>
       <c r="F115" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G115" s="10" t="b">
         <v>1</v>
@@ -18189,13 +18189,13 @@
         <v>877</v>
       </c>
       <c r="D116" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E116" s="10">
         <v>2</v>
       </c>
       <c r="F116" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G116" s="10" t="b">
         <v>1</v>
@@ -18212,13 +18212,13 @@
         <v>15</v>
       </c>
       <c r="D117" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E117" s="10">
         <v>2</v>
       </c>
       <c r="F117" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G117" s="10" t="b">
         <v>1</v>
@@ -18229,19 +18229,19 @@
         <v>471</v>
       </c>
       <c r="B118" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D118" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E118" s="10">
         <v>1</v>
       </c>
       <c r="F118" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G118" s="10" t="b">
         <v>1</v>
@@ -18258,13 +18258,13 @@
         <v>871</v>
       </c>
       <c r="D119" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E119" s="10">
         <v>5</v>
       </c>
       <c r="F119" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G119" s="10" t="b">
         <v>1</v>
@@ -18278,16 +18278,16 @@
         <v>290</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>845</v>
+        <v>591</v>
       </c>
       <c r="D120" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E120" s="10">
         <v>5</v>
       </c>
       <c r="F120" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G120" s="10" t="b">
         <v>1</v>
@@ -18298,19 +18298,19 @@
         <v>476</v>
       </c>
       <c r="B121" s="10" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D121" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E121" s="10">
         <v>5</v>
       </c>
       <c r="F121" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G121" s="10" t="b">
         <v>1</v>
@@ -18321,19 +18321,19 @@
         <v>476</v>
       </c>
       <c r="B122" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D122" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E122" s="10">
         <v>5</v>
       </c>
       <c r="F122" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G122" s="10" t="b">
         <v>1</v>
@@ -18347,16 +18347,16 @@
         <v>290</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>845</v>
+        <v>591</v>
       </c>
       <c r="D123" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E123" s="10">
         <v>5</v>
       </c>
       <c r="F123" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G123" s="10" t="b">
         <v>1</v>
@@ -18367,19 +18367,19 @@
         <v>479</v>
       </c>
       <c r="B124" s="10" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D124" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E124" s="10">
         <v>5</v>
       </c>
       <c r="F124" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G124" s="10" t="b">
         <v>1</v>
@@ -18390,19 +18390,19 @@
         <v>479</v>
       </c>
       <c r="B125" s="10" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D125" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E125" s="10">
         <v>5</v>
       </c>
       <c r="F125" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G125" s="10" t="b">
         <v>1</v>
@@ -18419,13 +18419,13 @@
         <v>879</v>
       </c>
       <c r="D126" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E126" s="10">
         <v>5</v>
       </c>
       <c r="F126" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G126" s="10" t="b">
         <v>1</v>
@@ -18442,13 +18442,13 @@
         <v>881</v>
       </c>
       <c r="D127" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E127" s="10">
         <v>3</v>
       </c>
       <c r="F127" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G127" s="10" t="b">
         <v>1</v>
@@ -18465,13 +18465,13 @@
         <v>861</v>
       </c>
       <c r="D128" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E128" s="10">
         <v>3</v>
       </c>
       <c r="F128" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G128" s="10" t="b">
         <v>1</v>
@@ -18482,19 +18482,19 @@
         <v>479</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D129" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E129" s="10">
         <v>7</v>
       </c>
       <c r="F129" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G129" s="10" t="b">
         <v>1</v>
@@ -18511,13 +18511,13 @@
         <v>883</v>
       </c>
       <c r="D130" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E130" s="10">
         <v>2</v>
       </c>
       <c r="F130" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G130" s="10" t="b">
         <v>1</v>
@@ -18528,19 +18528,19 @@
         <v>479</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D131" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E131" s="10">
         <v>2</v>
       </c>
       <c r="F131" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G131" s="10" t="b">
         <v>1</v>
@@ -18551,19 +18551,19 @@
         <v>479</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C132" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D132" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E132" s="10">
         <v>2</v>
       </c>
       <c r="F132" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G132" s="10" t="b">
         <v>1</v>
@@ -18580,13 +18580,13 @@
         <v>885</v>
       </c>
       <c r="D133" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E133" s="10">
         <v>5</v>
       </c>
       <c r="F133" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G133" s="10" t="b">
         <v>1</v>
@@ -18597,19 +18597,19 @@
         <v>484</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C134" s="10" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D134" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E134" s="10">
         <v>3</v>
       </c>
       <c r="F134" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G134" s="10" t="b">
         <v>1</v>
@@ -18626,13 +18626,13 @@
         <v>887</v>
       </c>
       <c r="D135" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E135" s="10">
         <v>3</v>
       </c>
       <c r="F135" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G135" s="10" t="b">
         <v>1</v>
@@ -18643,19 +18643,19 @@
         <v>484</v>
       </c>
       <c r="B136" s="10" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D136" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E136" s="10">
         <v>4</v>
       </c>
       <c r="F136" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G136" s="10" t="b">
         <v>1</v>
@@ -18672,13 +18672,13 @@
         <v>877</v>
       </c>
       <c r="D137" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E137" s="10">
         <v>4</v>
       </c>
       <c r="F137" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G137" s="10" t="b">
         <v>1</v>
@@ -18689,19 +18689,19 @@
         <v>484</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C138" s="10" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D138" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E138" s="10">
         <v>4</v>
       </c>
       <c r="F138" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G138" s="10" t="b">
         <v>1</v>
@@ -18718,13 +18718,13 @@
         <v>875</v>
       </c>
       <c r="D139" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E139" s="10">
         <v>4</v>
       </c>
       <c r="F139" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G139" s="10" t="b">
         <v>1</v>
@@ -18741,13 +18741,13 @@
         <v>15</v>
       </c>
       <c r="D140" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E140" s="10">
         <v>3</v>
       </c>
       <c r="F140" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G140" s="10" t="b">
         <v>1</v>
@@ -18758,19 +18758,19 @@
         <v>484</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D141" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E141" s="10">
         <v>5</v>
       </c>
       <c r="F141" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G141" s="10" t="b">
         <v>1</v>
@@ -18787,13 +18787,13 @@
         <v>889</v>
       </c>
       <c r="D142" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E142" s="10">
         <v>5</v>
       </c>
       <c r="F142" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G142" s="10" t="b">
         <v>1</v>
@@ -18804,19 +18804,19 @@
         <v>484</v>
       </c>
       <c r="B143" s="10" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C143" s="10" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D143" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E143" s="10">
         <v>2</v>
       </c>
       <c r="F143" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G143" s="10" t="b">
         <v>1</v>
@@ -18827,19 +18827,19 @@
         <v>484</v>
       </c>
       <c r="B144" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C144" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D144" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E144" s="10">
         <v>2</v>
       </c>
       <c r="F144" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G144" s="10" t="b">
         <v>1</v>
@@ -18850,19 +18850,19 @@
         <v>484</v>
       </c>
       <c r="B145" s="10" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C145" s="10" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D145" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E145" s="10">
         <v>2</v>
       </c>
       <c r="F145" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G145" s="10" t="b">
         <v>1</v>
@@ -18873,19 +18873,19 @@
         <v>484</v>
       </c>
       <c r="B146" s="10" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C146" s="10" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D146" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E146" s="10">
         <v>2</v>
       </c>
       <c r="F146" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G146" s="10" t="b">
         <v>1</v>
@@ -18896,19 +18896,19 @@
         <v>489</v>
       </c>
       <c r="B147" s="10" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C147" s="10" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D147" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E147" s="10">
         <v>4</v>
       </c>
       <c r="F147" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G147" s="10" t="b">
         <v>1</v>
@@ -18919,19 +18919,19 @@
         <v>489</v>
       </c>
       <c r="B148" s="10" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C148" s="10" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D148" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E148" s="10">
         <v>3</v>
       </c>
       <c r="F148" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G148" s="10" t="b">
         <v>1</v>
@@ -18942,19 +18942,19 @@
         <v>489</v>
       </c>
       <c r="B149" s="10" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C149" s="10" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D149" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E149" s="10">
         <v>3</v>
       </c>
       <c r="F149" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G149" s="10" t="b">
         <v>1</v>
@@ -18971,13 +18971,13 @@
         <v>873</v>
       </c>
       <c r="D150" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E150" s="10">
         <v>1</v>
       </c>
       <c r="F150" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G150" s="10" t="b">
         <v>1</v>
@@ -18994,13 +18994,13 @@
         <v>891</v>
       </c>
       <c r="D151" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E151" s="10">
         <v>2</v>
       </c>
       <c r="F151" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G151" s="10" t="b">
         <v>1</v>
@@ -19011,19 +19011,19 @@
         <v>489</v>
       </c>
       <c r="B152" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C152" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D152" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E152" s="10">
         <v>2</v>
       </c>
       <c r="F152" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G152" s="10" t="b">
         <v>1</v>
@@ -19034,19 +19034,19 @@
         <v>489</v>
       </c>
       <c r="B153" s="10" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C153" s="10" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D153" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E153" s="10">
         <v>2</v>
       </c>
       <c r="F153" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G153" s="10" t="b">
         <v>1</v>
@@ -19063,13 +19063,13 @@
         <v>893</v>
       </c>
       <c r="D154" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E154" s="10">
         <v>2</v>
       </c>
       <c r="F154" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G154" s="10" t="b">
         <v>1</v>
@@ -19086,13 +19086,13 @@
         <v>891</v>
       </c>
       <c r="D155" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E155" s="10">
         <v>2</v>
       </c>
       <c r="F155" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G155" s="10" t="b">
         <v>1</v>
@@ -19103,19 +19103,19 @@
         <v>494</v>
       </c>
       <c r="B156" s="10" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C156" s="10" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D156" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E156" s="10">
         <v>2</v>
       </c>
       <c r="F156" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G156" s="10" t="b">
         <v>1</v>
@@ -19126,19 +19126,19 @@
         <v>494</v>
       </c>
       <c r="B157" s="10" t="s">
+        <v>767</v>
+      </c>
+      <c r="C157" s="10" t="s">
+        <v>768</v>
+      </c>
+      <c r="D157" s="15" t="s">
         <v>766</v>
-      </c>
-      <c r="C157" s="10" t="s">
-        <v>767</v>
-      </c>
-      <c r="D157" s="15" t="s">
-        <v>765</v>
       </c>
       <c r="E157" s="10">
         <v>2</v>
       </c>
       <c r="F157" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G157" s="10" t="b">
         <v>1</v>
@@ -19149,19 +19149,19 @@
         <v>499</v>
       </c>
       <c r="B158" s="10" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D158" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E158" s="10">
         <v>2.5</v>
       </c>
       <c r="F158" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G158" s="10" t="b">
         <v>1</v>
@@ -19178,13 +19178,13 @@
         <v>863</v>
       </c>
       <c r="D159" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E159" s="10">
         <v>2.5</v>
       </c>
       <c r="F159" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G159" s="10" t="b">
         <v>1</v>
@@ -19201,13 +19201,13 @@
         <v>869</v>
       </c>
       <c r="D160" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E160" s="10">
         <v>2</v>
       </c>
       <c r="F160" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G160" s="10" t="b">
         <v>1</v>
@@ -19224,13 +19224,13 @@
         <v>15</v>
       </c>
       <c r="D161" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E161" s="10">
         <v>1.5</v>
       </c>
       <c r="F161" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G161" s="10" t="b">
         <v>1</v>
@@ -19247,13 +19247,13 @@
         <v>895</v>
       </c>
       <c r="D162" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E162" s="10">
         <v>1</v>
       </c>
       <c r="F162" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G162" s="10" t="b">
         <v>1</v>
@@ -19264,19 +19264,19 @@
         <v>499</v>
       </c>
       <c r="B163" s="10" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C163" s="10" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D163" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E163" s="10">
         <v>2</v>
       </c>
       <c r="F163" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G163" s="10" t="b">
         <v>1</v>
@@ -19293,13 +19293,13 @@
         <v>897</v>
       </c>
       <c r="D164" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E164" s="10">
         <v>1</v>
       </c>
       <c r="F164" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G164" s="10" t="b">
         <v>1</v>
@@ -19313,16 +19313,16 @@
         <v>290</v>
       </c>
       <c r="C165" s="10" t="s">
-        <v>845</v>
+        <v>591</v>
       </c>
       <c r="D165" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E165" s="10">
         <v>1</v>
       </c>
       <c r="F165" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G165" s="10" t="b">
         <v>1</v>
@@ -19333,19 +19333,19 @@
         <v>499</v>
       </c>
       <c r="B166" s="10" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C166" s="10" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D166" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E166" s="10">
         <v>1</v>
       </c>
       <c r="F166" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G166" s="10" t="b">
         <v>1</v>
@@ -19356,19 +19356,19 @@
         <v>499</v>
       </c>
       <c r="B167" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C167" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D167" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E167" s="10">
         <v>1</v>
       </c>
       <c r="F167" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G167" s="10" t="b">
         <v>1</v>
@@ -19379,19 +19379,19 @@
         <v>503</v>
       </c>
       <c r="B168" s="10" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C168" s="10" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D168" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E168" s="10">
         <v>5</v>
       </c>
       <c r="F168" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G168" s="10" t="b">
         <v>1</v>
@@ -19405,16 +19405,16 @@
         <v>290</v>
       </c>
       <c r="C169" s="10" t="s">
-        <v>845</v>
+        <v>591</v>
       </c>
       <c r="D169" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E169" s="10">
         <v>3</v>
       </c>
       <c r="F169" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G169" s="10" t="b">
         <v>1</v>
@@ -19425,19 +19425,19 @@
         <v>503</v>
       </c>
       <c r="B170" s="10" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C170" s="10" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D170" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E170" s="10">
         <v>5</v>
       </c>
       <c r="F170" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G170" s="10" t="b">
         <v>1</v>
@@ -19454,13 +19454,13 @@
         <v>899</v>
       </c>
       <c r="D171" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E171" s="10">
         <v>5</v>
       </c>
       <c r="F171" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G171" s="10" t="b">
         <v>1</v>
@@ -19471,19 +19471,19 @@
         <v>503</v>
       </c>
       <c r="B172" s="10" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C172" s="10" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D172" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E172" s="10">
         <v>5</v>
       </c>
       <c r="F172" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G172" s="10" t="b">
         <v>1</v>
@@ -19500,13 +19500,13 @@
         <v>901</v>
       </c>
       <c r="D173" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E173" s="10">
         <v>3</v>
       </c>
       <c r="F173" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G173" s="10" t="b">
         <v>1</v>
@@ -19523,13 +19523,13 @@
         <v>903</v>
       </c>
       <c r="D174" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E174" s="10">
         <v>3</v>
       </c>
       <c r="F174" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G174" s="10" t="b">
         <v>1</v>
@@ -19546,13 +19546,13 @@
         <v>905</v>
       </c>
       <c r="D175" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E175" s="10">
         <v>3</v>
       </c>
       <c r="F175" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G175" s="10" t="b">
         <v>1</v>
@@ -19569,13 +19569,13 @@
         <v>849</v>
       </c>
       <c r="D176" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E176" s="10">
         <v>3</v>
       </c>
       <c r="F176" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G176" s="10" t="b">
         <v>1</v>
@@ -19586,19 +19586,19 @@
         <v>503</v>
       </c>
       <c r="B177" s="10" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C177" s="10" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D177" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E177" s="10">
         <v>5</v>
       </c>
       <c r="F177" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G177" s="10" t="b">
         <v>1</v>
@@ -19609,19 +19609,19 @@
         <v>503</v>
       </c>
       <c r="B178" s="10" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C178" s="10" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D178" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E178" s="10">
         <v>5</v>
       </c>
       <c r="F178" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G178" s="10" t="b">
         <v>1</v>
@@ -19638,13 +19638,13 @@
         <v>907</v>
       </c>
       <c r="D179" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E179" s="10">
         <v>3</v>
       </c>
       <c r="F179" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G179" s="10" t="b">
         <v>1</v>
@@ -19655,19 +19655,19 @@
         <v>503</v>
       </c>
       <c r="B180" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C180" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D180" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E180" s="10">
         <v>4</v>
       </c>
       <c r="F180" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G180" s="10" t="b">
         <v>1</v>
@@ -19678,19 +19678,19 @@
         <v>503</v>
       </c>
       <c r="B181" s="10" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C181" s="10" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D181" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E181" s="10">
         <v>1</v>
       </c>
       <c r="F181" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G181" s="10" t="b">
         <v>1</v>
@@ -19701,19 +19701,19 @@
         <v>503</v>
       </c>
       <c r="B182" s="10" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C182" s="10" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D182" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E182" s="10">
         <v>1</v>
       </c>
       <c r="F182" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G182" s="10" t="b">
         <v>1</v>
@@ -19730,13 +19730,13 @@
         <v>909</v>
       </c>
       <c r="D183" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E183" s="10">
         <v>4</v>
       </c>
       <c r="F183" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G183" s="10" t="b">
         <v>1</v>
@@ -19753,13 +19753,13 @@
         <v>911</v>
       </c>
       <c r="D184" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E184" s="10">
         <v>3</v>
       </c>
       <c r="F184" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G184" s="10" t="b">
         <v>1</v>
@@ -19776,13 +19776,13 @@
         <v>913</v>
       </c>
       <c r="D185" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E185" s="10">
         <v>2</v>
       </c>
       <c r="F185" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G185" s="10" t="b">
         <v>1</v>
@@ -19793,19 +19793,19 @@
         <v>508</v>
       </c>
       <c r="B186" s="10" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C186" s="47" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D186" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E186" s="10">
         <v>2</v>
       </c>
       <c r="F186" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G186" s="10" t="b">
         <v>1</v>
@@ -19822,13 +19822,13 @@
         <v>915</v>
       </c>
       <c r="D187" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E187" s="10">
         <v>3</v>
       </c>
       <c r="F187" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G187" s="10" t="b">
         <v>1</v>
@@ -19839,19 +19839,19 @@
         <v>508</v>
       </c>
       <c r="B188" s="10" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C188" s="47" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D188" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E188" s="10">
         <v>3</v>
       </c>
       <c r="F188" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G188" s="10" t="b">
         <v>1</v>
@@ -19868,13 +19868,13 @@
         <v>893</v>
       </c>
       <c r="D189" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E189" s="10">
         <v>3</v>
       </c>
       <c r="F189" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G189" s="10" t="b">
         <v>1</v>
@@ -19885,19 +19885,19 @@
         <v>508</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C190" s="47" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D190" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E190" s="10">
         <v>2</v>
       </c>
       <c r="F190" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G190" s="10" t="b">
         <v>1</v>
@@ -19908,19 +19908,19 @@
         <v>508</v>
       </c>
       <c r="B191" s="10" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C191" s="47" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D191" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E191" s="10">
         <v>3</v>
       </c>
       <c r="F191" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G191" s="10" t="b">
         <v>1</v>
@@ -19937,13 +19937,13 @@
         <v>917</v>
       </c>
       <c r="D192" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E192" s="10">
         <v>1</v>
       </c>
       <c r="F192" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G192" s="10" t="b">
         <v>1</v>
@@ -19954,19 +19954,19 @@
         <v>508</v>
       </c>
       <c r="B193" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C193" s="47" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D193" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E193" s="10">
         <v>2</v>
       </c>
       <c r="F193" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G193" s="10" t="b">
         <v>1</v>
@@ -19983,13 +19983,13 @@
         <v>893</v>
       </c>
       <c r="D194" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E194" s="10">
         <v>4</v>
       </c>
       <c r="F194" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G194" s="10" t="b">
         <v>1</v>
@@ -20006,13 +20006,13 @@
         <v>919</v>
       </c>
       <c r="D195" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E195" s="10">
         <v>1</v>
       </c>
       <c r="F195" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G195" s="10" t="b">
         <v>1</v>
@@ -20029,13 +20029,13 @@
         <v>855</v>
       </c>
       <c r="D196" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E196" s="10">
         <v>1</v>
       </c>
       <c r="F196" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G196" s="10" t="b">
         <v>1</v>
@@ -20052,13 +20052,13 @@
         <v>901</v>
       </c>
       <c r="D197" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E197" s="10">
         <v>1</v>
       </c>
       <c r="F197" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G197" s="10" t="b">
         <v>1</v>
@@ -20075,13 +20075,13 @@
         <v>903</v>
       </c>
       <c r="D198" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E198" s="10">
         <v>1</v>
       </c>
       <c r="F198" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G198" s="10" t="b">
         <v>1</v>
@@ -20092,19 +20092,19 @@
         <v>512</v>
       </c>
       <c r="B199" s="10" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C199" s="10" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D199" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E199" s="10">
         <v>1</v>
       </c>
       <c r="F199" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G199" s="10" t="b">
         <v>1</v>
@@ -20118,16 +20118,16 @@
         <v>290</v>
       </c>
       <c r="C200" s="10" t="s">
-        <v>845</v>
+        <v>591</v>
       </c>
       <c r="D200" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E200" s="10">
         <v>5</v>
       </c>
       <c r="F200" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G200" s="10" t="b">
         <v>1</v>
@@ -20138,19 +20138,19 @@
         <v>512</v>
       </c>
       <c r="B201" s="10" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C201" s="10" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D201" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E201" s="10">
         <v>5</v>
       </c>
       <c r="F201" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G201" s="10" t="b">
         <v>1</v>
@@ -20167,13 +20167,13 @@
         <v>921</v>
       </c>
       <c r="D202" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E202" s="10">
         <v>5</v>
       </c>
       <c r="F202" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G202" s="10" t="b">
         <v>1</v>
@@ -20190,13 +20190,13 @@
         <v>923</v>
       </c>
       <c r="D203" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E203" s="10">
         <v>5</v>
       </c>
       <c r="F203" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G203" s="10" t="b">
         <v>1</v>
@@ -20213,13 +20213,13 @@
         <v>905</v>
       </c>
       <c r="D204" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E204" s="10">
         <v>5</v>
       </c>
       <c r="F204" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G204" s="10" t="b">
         <v>1</v>
@@ -20236,13 +20236,13 @@
         <v>849</v>
       </c>
       <c r="D205" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E205" s="10">
         <v>5</v>
       </c>
       <c r="F205" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G205" s="10" t="b">
         <v>1</v>
@@ -20253,19 +20253,19 @@
         <v>512</v>
       </c>
       <c r="B206" s="10" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C206" s="10" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D206" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E206" s="10">
         <v>5</v>
       </c>
       <c r="F206" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G206" s="10" t="b">
         <v>1</v>
@@ -20276,19 +20276,19 @@
         <v>515</v>
       </c>
       <c r="B207" s="10" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C207" s="10" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D207" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E207" s="10">
         <v>4</v>
       </c>
       <c r="F207" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G207" s="10" t="b">
         <v>1</v>
@@ -20299,19 +20299,19 @@
         <v>515</v>
       </c>
       <c r="B208" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C208" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D208" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E208" s="10">
         <v>2</v>
       </c>
       <c r="F208" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G208" s="10" t="b">
         <v>1</v>
@@ -20328,13 +20328,13 @@
         <v>925</v>
       </c>
       <c r="D209" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E209" s="10">
         <v>3</v>
       </c>
       <c r="F209" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G209" s="10" t="b">
         <v>1</v>
@@ -20345,19 +20345,19 @@
         <v>519</v>
       </c>
       <c r="B210" s="10" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C210" s="10" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D210" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E210" s="10">
         <v>4</v>
       </c>
       <c r="F210" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G210" s="10" t="b">
         <v>1</v>
@@ -20374,13 +20374,13 @@
         <v>895</v>
       </c>
       <c r="D211" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E211" s="10">
         <v>5</v>
       </c>
       <c r="F211" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G211" s="10" t="b">
         <v>1</v>
@@ -20397,13 +20397,13 @@
         <v>15</v>
       </c>
       <c r="D212" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E212" s="10">
         <v>4</v>
       </c>
       <c r="F212" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G212" s="10" t="b">
         <v>1</v>
@@ -20420,13 +20420,13 @@
         <v>869</v>
       </c>
       <c r="D213" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E213" s="10">
         <v>4</v>
       </c>
       <c r="F213" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G213" s="10" t="b">
         <v>1</v>
@@ -20437,19 +20437,19 @@
         <v>519</v>
       </c>
       <c r="B214" s="10" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C214" s="10" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D214" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E214" s="10">
         <v>4</v>
       </c>
       <c r="F214" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G214" s="10" t="b">
         <v>1</v>
@@ -20460,19 +20460,19 @@
         <v>519</v>
       </c>
       <c r="B215" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C215" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D215" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E215" s="10">
         <v>2</v>
       </c>
       <c r="F215" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G215" s="10" t="b">
         <v>1</v>
@@ -20483,19 +20483,19 @@
         <v>519</v>
       </c>
       <c r="B216" s="10" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C216" s="10" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D216" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E216" s="10">
         <v>1</v>
       </c>
       <c r="F216" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G216" s="10" t="b">
         <v>1</v>
@@ -20506,19 +20506,19 @@
         <v>519</v>
       </c>
       <c r="B217" s="10" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C217" s="10" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D217" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E217" s="10">
         <v>1</v>
       </c>
       <c r="F217" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G217" s="10" t="b">
         <v>1</v>
@@ -20529,19 +20529,19 @@
         <v>524</v>
       </c>
       <c r="B218" s="10" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C218" s="10" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D218" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E218" s="10">
         <v>1</v>
       </c>
       <c r="F218" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G218" s="10" t="b">
         <v>1</v>
@@ -20555,16 +20555,16 @@
         <v>290</v>
       </c>
       <c r="C219" s="10" t="s">
-        <v>845</v>
+        <v>591</v>
       </c>
       <c r="D219" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E219" s="10">
         <v>5</v>
       </c>
       <c r="F219" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G219" s="10" t="b">
         <v>1</v>
@@ -20581,13 +20581,13 @@
         <v>927</v>
       </c>
       <c r="D220" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E220" s="10">
         <v>5</v>
       </c>
       <c r="F220" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G220" s="10" t="b">
         <v>1</v>
@@ -20598,19 +20598,19 @@
         <v>524</v>
       </c>
       <c r="B221" s="10" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C221" s="10" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D221" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E221" s="10">
         <v>5</v>
       </c>
       <c r="F221" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G221" s="10" t="b">
         <v>1</v>
@@ -20621,19 +20621,19 @@
         <v>524</v>
       </c>
       <c r="B222" s="10" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C222" s="10" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D222" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E222" s="10">
         <v>5</v>
       </c>
       <c r="F222" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G222" s="10" t="b">
         <v>1</v>
@@ -20650,13 +20650,13 @@
         <v>901</v>
       </c>
       <c r="D223" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E223" s="10">
         <v>6</v>
       </c>
       <c r="F223" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G223" s="10" t="b">
         <v>1</v>
@@ -20673,13 +20673,13 @@
         <v>899</v>
       </c>
       <c r="D224" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E224" s="10">
         <v>5</v>
       </c>
       <c r="F224" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G224" s="10" t="b">
         <v>1</v>
@@ -20696,13 +20696,13 @@
         <v>905</v>
       </c>
       <c r="D225" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E225" s="10">
         <v>3</v>
       </c>
       <c r="F225" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G225" s="10" t="b">
         <v>1</v>
@@ -20719,13 +20719,13 @@
         <v>929</v>
       </c>
       <c r="D226" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E226" s="10">
         <v>2</v>
       </c>
       <c r="F226" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G226" s="10" t="b">
         <v>1</v>
@@ -20736,19 +20736,19 @@
         <v>524</v>
       </c>
       <c r="B227" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C227" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D227" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E227" s="10">
         <v>2</v>
       </c>
       <c r="F227" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G227" s="10" t="b">
         <v>1</v>
@@ -20759,19 +20759,19 @@
         <v>524</v>
       </c>
       <c r="B228" s="10" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C228" s="10" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D228" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E228" s="10">
         <v>1</v>
       </c>
       <c r="F228" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G228" s="10" t="b">
         <v>1</v>
@@ -20782,19 +20782,19 @@
         <v>524</v>
       </c>
       <c r="B229" s="10" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C229" s="10" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D229" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E229" s="10">
         <v>1</v>
       </c>
       <c r="F229" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G229" s="10" t="b">
         <v>1</v>
@@ -20811,13 +20811,13 @@
         <v>931</v>
       </c>
       <c r="D230" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E230" s="10">
         <v>2</v>
       </c>
       <c r="F230" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G230" s="10" t="b">
         <v>1</v>
@@ -20834,13 +20834,13 @@
         <v>867</v>
       </c>
       <c r="D231" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E231" s="10">
         <v>3</v>
       </c>
       <c r="F231" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G231" s="10" t="b">
         <v>1</v>
@@ -20851,19 +20851,19 @@
         <v>529</v>
       </c>
       <c r="B232" s="10" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C232" s="10" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D232" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E232" s="10">
         <v>3</v>
       </c>
       <c r="F232" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G232" s="10" t="b">
         <v>1</v>
@@ -20880,13 +20880,13 @@
         <v>933</v>
       </c>
       <c r="D233" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E233" s="10">
         <v>4</v>
       </c>
       <c r="F233" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G233" s="10" t="b">
         <v>1</v>
@@ -20903,13 +20903,13 @@
         <v>891</v>
       </c>
       <c r="D234" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E234" s="10">
         <v>3</v>
       </c>
       <c r="F234" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G234" s="10" t="b">
         <v>1</v>
@@ -20926,13 +20926,13 @@
         <v>935</v>
       </c>
       <c r="D235" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E235" s="10">
         <v>3</v>
       </c>
       <c r="F235" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G235" s="10" t="b">
         <v>1</v>
@@ -20943,19 +20943,19 @@
         <v>529</v>
       </c>
       <c r="B236" s="10" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C236" s="10" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D236" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E236" s="10">
         <v>3</v>
       </c>
       <c r="F236" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G236" s="10" t="b">
         <v>1</v>
@@ -20972,13 +20972,13 @@
         <v>893</v>
       </c>
       <c r="D237" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E237" s="10">
         <v>6</v>
       </c>
       <c r="F237" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G237" s="10" t="b">
         <v>1</v>
@@ -20995,13 +20995,13 @@
         <v>917</v>
       </c>
       <c r="D238" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E238" s="10">
         <v>3</v>
       </c>
       <c r="F238" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G238" s="10" t="b">
         <v>1</v>
@@ -21012,19 +21012,19 @@
         <v>529</v>
       </c>
       <c r="B239" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C239" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D239" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E239" s="10">
         <v>2</v>
       </c>
       <c r="F239" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G239" s="10" t="b">
         <v>1</v>
@@ -21041,13 +21041,13 @@
         <v>907</v>
       </c>
       <c r="D240" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E240" s="10">
         <v>1</v>
       </c>
       <c r="F240" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G240" s="10" t="b">
         <v>1</v>
@@ -21064,13 +21064,13 @@
         <v>937</v>
       </c>
       <c r="D241" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E241" s="10">
         <v>2</v>
       </c>
       <c r="F241" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G241" s="10" t="b">
         <v>1</v>
@@ -21081,19 +21081,19 @@
         <v>534</v>
       </c>
       <c r="B242" s="10" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C242" s="10" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D242" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E242" s="10">
         <v>2</v>
       </c>
       <c r="F242" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G242" s="10" t="b">
         <v>1</v>
@@ -21110,13 +21110,13 @@
         <v>939</v>
       </c>
       <c r="D243" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E243" s="10">
         <v>3</v>
       </c>
       <c r="F243" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G243" s="10" t="b">
         <v>1</v>
@@ -21133,13 +21133,13 @@
         <v>941</v>
       </c>
       <c r="D244" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E244" s="10">
         <v>2</v>
       </c>
       <c r="F244" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G244" s="10" t="b">
         <v>1</v>
@@ -21150,19 +21150,19 @@
         <v>534</v>
       </c>
       <c r="B245" s="10" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C245" s="10" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D245" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E245" s="10">
         <v>2</v>
       </c>
       <c r="F245" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G245" s="10" t="b">
         <v>1</v>
@@ -21179,13 +21179,13 @@
         <v>943</v>
       </c>
       <c r="D246" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E246" s="10">
         <v>1</v>
       </c>
       <c r="F246" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G246" s="10" t="b">
         <v>1</v>
@@ -21196,19 +21196,19 @@
         <v>534</v>
       </c>
       <c r="B247" s="10" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C247" s="10" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D247" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E247" s="10">
         <v>1</v>
       </c>
       <c r="F247" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G247" s="10" t="b">
         <v>1</v>
@@ -21225,13 +21225,13 @@
         <v>917</v>
       </c>
       <c r="D248" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E248" s="10">
         <v>2</v>
       </c>
       <c r="F248" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G248" s="10" t="b">
         <v>1</v>
@@ -21248,13 +21248,13 @@
         <v>945</v>
       </c>
       <c r="D249" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E249" s="10">
         <v>1.5</v>
       </c>
       <c r="F249" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G249" s="10" t="b">
         <v>1</v>
@@ -21265,19 +21265,19 @@
         <v>539</v>
       </c>
       <c r="B250" s="10" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C250" s="10" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D250" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E250" s="10">
         <v>1.5</v>
       </c>
       <c r="F250" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G250" s="10" t="b">
         <v>1</v>
@@ -21294,13 +21294,13 @@
         <v>15</v>
       </c>
       <c r="D251" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E251" s="10">
         <v>2</v>
       </c>
       <c r="F251" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G251" s="10" t="b">
         <v>1</v>
@@ -21311,19 +21311,19 @@
         <v>539</v>
       </c>
       <c r="B252" s="10" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C252" s="10" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D252" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E252" s="10">
         <v>1.5</v>
       </c>
       <c r="F252" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G252" s="10" t="b">
         <v>1</v>
@@ -21334,19 +21334,19 @@
         <v>539</v>
       </c>
       <c r="B253" s="10" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C253" s="10" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D253" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E253" s="10">
         <v>1.5</v>
       </c>
       <c r="F253" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G253" s="10" t="b">
         <v>1</v>
@@ -21357,19 +21357,19 @@
         <v>539</v>
       </c>
       <c r="B254" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C254" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D254" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E254" s="10">
         <v>0.5</v>
       </c>
       <c r="F254" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G254" s="10" t="b">
         <v>1</v>
@@ -21386,13 +21386,13 @@
         <v>847</v>
       </c>
       <c r="D255" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E255" s="10">
         <v>4</v>
       </c>
       <c r="F255" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G255" s="10" t="b">
         <v>1</v>
@@ -21403,19 +21403,19 @@
         <v>543</v>
       </c>
       <c r="B256" s="10" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C256" s="10" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D256" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E256" s="10">
         <v>3</v>
       </c>
       <c r="F256" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G256" s="10" t="b">
         <v>1</v>
@@ -21426,19 +21426,19 @@
         <v>543</v>
       </c>
       <c r="B257" s="10" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C257" s="10" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D257" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E257" s="10">
         <v>3</v>
       </c>
       <c r="F257" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G257" s="10" t="b">
         <v>1</v>
@@ -21449,19 +21449,19 @@
         <v>543</v>
       </c>
       <c r="B258" s="10" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C258" s="10" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D258" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E258" s="10">
         <v>2</v>
       </c>
       <c r="F258" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G258" s="10" t="b">
         <v>1</v>
@@ -21472,19 +21472,19 @@
         <v>548</v>
       </c>
       <c r="B259" s="10" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C259" s="47" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D259" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E259" s="10">
         <v>3</v>
       </c>
       <c r="F259" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G259" s="10" t="b">
         <v>1</v>
@@ -21495,19 +21495,19 @@
         <v>548</v>
       </c>
       <c r="B260" s="10" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C260" s="10" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D260" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E260" s="10">
         <v>2</v>
       </c>
       <c r="F260" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G260" s="10" t="b">
         <v>1</v>
@@ -21524,13 +21524,13 @@
         <v>913</v>
       </c>
       <c r="D261" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E261" s="10">
         <v>2</v>
       </c>
       <c r="F261" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G261" s="10" t="b">
         <v>1</v>
@@ -21547,13 +21547,13 @@
         <v>909</v>
       </c>
       <c r="D262" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E262" s="10">
         <v>3</v>
       </c>
       <c r="F262" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G262" s="10" t="b">
         <v>1</v>
@@ -21570,13 +21570,13 @@
         <v>911</v>
       </c>
       <c r="D263" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E263" s="10">
         <v>3</v>
       </c>
       <c r="F263" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G263" s="10" t="b">
         <v>1</v>
@@ -21593,13 +21593,13 @@
         <v>947</v>
       </c>
       <c r="D264" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E264" s="10">
         <v>2</v>
       </c>
       <c r="F264" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G264" s="10" t="b">
         <v>1</v>
@@ -21616,13 +21616,13 @@
         <v>949</v>
       </c>
       <c r="D265" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E265" s="10">
         <v>2</v>
       </c>
       <c r="F265" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G265" s="10" t="b">
         <v>1</v>
@@ -21639,13 +21639,13 @@
         <v>945</v>
       </c>
       <c r="D266" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E266" s="10">
         <v>1</v>
       </c>
       <c r="F266" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G266" s="10" t="b">
         <v>1</v>
@@ -21662,13 +21662,13 @@
         <v>941</v>
       </c>
       <c r="D267" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E267" s="10">
         <v>2</v>
       </c>
       <c r="F267" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G267" s="10" t="b">
         <v>1</v>
@@ -21679,19 +21679,19 @@
         <v>548</v>
       </c>
       <c r="B268" s="10" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C268" s="47" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D268" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E268" s="10">
         <v>1</v>
       </c>
       <c r="F268" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G268" s="10" t="b">
         <v>1</v>
@@ -21708,13 +21708,13 @@
         <v>951</v>
       </c>
       <c r="D269" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E269" s="10">
         <v>1</v>
       </c>
       <c r="F269" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G269" s="10" t="b">
         <v>1</v>
@@ -21725,19 +21725,19 @@
         <v>548</v>
       </c>
       <c r="B270" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C270" s="47" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D270" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E270" s="10">
         <v>3</v>
       </c>
       <c r="F270" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G270" s="10" t="b">
         <v>1</v>
@@ -21754,13 +21754,13 @@
         <v>893</v>
       </c>
       <c r="D271" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E271" s="10">
         <v>1</v>
       </c>
       <c r="F271" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G271" s="10" t="b">
         <v>1</v>
@@ -21777,13 +21777,13 @@
         <v>939</v>
       </c>
       <c r="D272" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E272" s="10">
         <v>6</v>
       </c>
       <c r="F272" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G272" s="10" t="b">
         <v>1</v>
@@ -21794,19 +21794,19 @@
         <v>552</v>
       </c>
       <c r="B273" s="10" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C273" s="10" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D273" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E273" s="10">
         <v>3</v>
       </c>
       <c r="F273" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G273" s="10" t="b">
         <v>1</v>
@@ -21823,13 +21823,13 @@
         <v>855</v>
       </c>
       <c r="D274" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E274" s="10">
         <v>3</v>
       </c>
       <c r="F274" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G274" s="10" t="b">
         <v>1</v>
@@ -21840,19 +21840,19 @@
         <v>552</v>
       </c>
       <c r="B275" s="10" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C275" s="10" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D275" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E275" s="10">
         <v>3</v>
       </c>
       <c r="F275" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G275" s="10" t="b">
         <v>1</v>
@@ -21869,13 +21869,13 @@
         <v>953</v>
       </c>
       <c r="D276" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E276" s="10">
         <v>1.5</v>
       </c>
       <c r="F276" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G276" s="10" t="b">
         <v>1</v>
@@ -21892,13 +21892,13 @@
         <v>955</v>
       </c>
       <c r="D277" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E277" s="10">
         <v>3</v>
       </c>
       <c r="F277" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G277" s="10" t="b">
         <v>1</v>
@@ -21915,13 +21915,13 @@
         <v>957</v>
       </c>
       <c r="D278" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E278" s="10">
         <v>3</v>
       </c>
       <c r="F278" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G278" s="10" t="b">
         <v>1</v>
@@ -21932,19 +21932,19 @@
         <v>556</v>
       </c>
       <c r="B279" s="10" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C279" s="10" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D279" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E279" s="10">
         <v>3</v>
       </c>
       <c r="F279" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G279" s="10" t="b">
         <v>1</v>
@@ -21955,19 +21955,19 @@
         <v>556</v>
       </c>
       <c r="B280" s="10" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C280" s="10" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D280" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E280" s="10">
         <v>3</v>
       </c>
       <c r="F280" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G280" s="10" t="b">
         <v>1</v>
@@ -21978,19 +21978,19 @@
         <v>556</v>
       </c>
       <c r="B281" s="10" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C281" s="10" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D281" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E281" s="10">
         <v>3</v>
       </c>
       <c r="F281" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G281" s="10" t="b">
         <v>1</v>
@@ -22001,19 +22001,19 @@
         <v>556</v>
       </c>
       <c r="B282" s="10" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C282" s="10" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D282" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E282" s="10">
         <v>3</v>
       </c>
       <c r="F282" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G282" s="10" t="b">
         <v>1</v>
@@ -22030,13 +22030,13 @@
         <v>15</v>
       </c>
       <c r="D283" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E283" s="10">
         <v>3</v>
       </c>
       <c r="F283" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G283" s="10" t="b">
         <v>1</v>
@@ -22050,16 +22050,16 @@
         <v>290</v>
       </c>
       <c r="C284" s="10" t="s">
-        <v>845</v>
+        <v>591</v>
       </c>
       <c r="D284" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E284" s="10">
         <v>3</v>
       </c>
       <c r="F284" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G284" s="10" t="b">
         <v>1</v>
@@ -22070,19 +22070,19 @@
         <v>556</v>
       </c>
       <c r="B285" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C285" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D285" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E285" s="10">
         <v>3</v>
       </c>
       <c r="F285" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G285" s="10" t="b">
         <v>1</v>
@@ -22093,19 +22093,19 @@
         <v>556</v>
       </c>
       <c r="B286" s="10" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C286" s="10" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D286" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E286" s="10">
         <v>2</v>
       </c>
       <c r="F286" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G286" s="10" t="b">
         <v>1</v>
@@ -22122,13 +22122,13 @@
         <v>917</v>
       </c>
       <c r="D287" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E287" s="10">
         <v>3</v>
       </c>
       <c r="F287" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G287" s="10" t="b">
         <v>1</v>
@@ -22139,19 +22139,19 @@
         <v>561</v>
       </c>
       <c r="B288" s="10" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C288" s="10" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D288" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E288" s="10">
         <v>3</v>
       </c>
       <c r="F288" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G288" s="10" t="b">
         <v>1</v>
@@ -22162,19 +22162,19 @@
         <v>561</v>
       </c>
       <c r="B289" s="10" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C289" s="10" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D289" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E289" s="10">
         <v>3</v>
       </c>
       <c r="F289" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G289" s="10" t="b">
         <v>1</v>
@@ -22185,19 +22185,19 @@
         <v>561</v>
       </c>
       <c r="B290" s="10" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C290" s="10" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D290" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E290" s="10">
         <v>3</v>
       </c>
       <c r="F290" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G290" s="10" t="b">
         <v>1</v>
@@ -22208,19 +22208,19 @@
         <v>561</v>
       </c>
       <c r="B291" s="10" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C291" s="10" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D291" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E291" s="10">
         <v>3</v>
       </c>
       <c r="F291" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G291" s="10" t="b">
         <v>1</v>
@@ -22231,19 +22231,19 @@
         <v>561</v>
       </c>
       <c r="B292" s="10" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C292" s="10" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D292" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E292" s="10">
         <v>1</v>
       </c>
       <c r="F292" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G292" s="10" t="b">
         <v>1</v>
@@ -22254,19 +22254,19 @@
         <v>561</v>
       </c>
       <c r="B293" s="10" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C293" s="10" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D293" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E293" s="10">
         <v>1</v>
       </c>
       <c r="F293" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G293" s="10" t="b">
         <v>1</v>
@@ -22277,19 +22277,19 @@
         <v>561</v>
       </c>
       <c r="B294" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C294" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D294" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E294" s="10">
         <v>1</v>
       </c>
       <c r="F294" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G294" s="10" t="b">
         <v>1</v>
@@ -22306,13 +22306,13 @@
         <v>959</v>
       </c>
       <c r="D295" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E295" s="10">
         <v>5</v>
       </c>
       <c r="F295" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G295" s="10" t="b">
         <v>1</v>
@@ -22326,16 +22326,16 @@
         <v>290</v>
       </c>
       <c r="C296" s="10" t="s">
-        <v>845</v>
+        <v>591</v>
       </c>
       <c r="D296" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E296" s="10">
         <v>4</v>
       </c>
       <c r="F296" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G296" s="10" t="b">
         <v>1</v>
@@ -22346,19 +22346,19 @@
         <v>566</v>
       </c>
       <c r="B297" s="10" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C297" s="10" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="D297" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E297" s="10">
         <v>3</v>
       </c>
       <c r="F297" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G297" s="10" t="b">
         <v>1</v>
@@ -22369,19 +22369,19 @@
         <v>566</v>
       </c>
       <c r="B298" s="10" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C298" s="10" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D298" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E298" s="10">
         <v>3</v>
       </c>
       <c r="F298" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G298" s="10" t="b">
         <v>1</v>
@@ -22398,13 +22398,13 @@
         <v>853</v>
       </c>
       <c r="D299" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E299" s="10">
         <v>3</v>
       </c>
       <c r="F299" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G299" s="10" t="b">
         <v>1</v>
@@ -22415,19 +22415,19 @@
         <v>566</v>
       </c>
       <c r="B300" s="10" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C300" s="10" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D300" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E300" s="10">
         <v>4</v>
       </c>
       <c r="F300" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G300" s="10" t="b">
         <v>1</v>
@@ -22438,19 +22438,19 @@
         <v>566</v>
       </c>
       <c r="B301" s="10" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C301" s="10" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D301" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E301" s="10">
         <v>4</v>
       </c>
       <c r="F301" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G301" s="10" t="b">
         <v>1</v>
@@ -22461,19 +22461,19 @@
         <v>566</v>
       </c>
       <c r="B302" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C302" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D302" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E302" s="10">
         <v>3</v>
       </c>
       <c r="F302" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G302" s="10" t="b">
         <v>1</v>
@@ -22490,13 +22490,13 @@
         <v>847</v>
       </c>
       <c r="D303" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E303" s="10">
         <v>8</v>
       </c>
       <c r="F303" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G303" s="10" t="b">
         <v>1</v>
@@ -22513,13 +22513,13 @@
         <v>961</v>
       </c>
       <c r="D304" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E304" s="10">
         <v>4</v>
       </c>
       <c r="F304" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G304" s="10" t="b">
         <v>1</v>
@@ -22536,13 +22536,13 @@
         <v>879</v>
       </c>
       <c r="D305" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E305" s="10">
         <v>4</v>
       </c>
       <c r="F305" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G305" s="10" t="b">
         <v>1</v>
@@ -22559,13 +22559,13 @@
         <v>933</v>
       </c>
       <c r="D306" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E306" s="10">
         <v>3</v>
       </c>
       <c r="F306" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G306" s="10" t="b">
         <v>1</v>
@@ -22576,19 +22576,19 @@
         <v>571</v>
       </c>
       <c r="B307" s="10" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C307" s="10" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D307" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E307" s="10">
         <v>3</v>
       </c>
       <c r="F307" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G307" s="10" t="b">
         <v>1</v>
@@ -22605,13 +22605,13 @@
         <v>949</v>
       </c>
       <c r="D308" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E308" s="10">
         <v>3</v>
       </c>
       <c r="F308" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G308" s="10" t="b">
         <v>1</v>
@@ -22628,13 +22628,13 @@
         <v>963</v>
       </c>
       <c r="D309" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E309" s="10">
         <v>2</v>
       </c>
       <c r="F309" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G309" s="10" t="b">
         <v>1</v>
@@ -22645,19 +22645,19 @@
         <v>576</v>
       </c>
       <c r="B310" s="10" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C310" s="10" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D310" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E310" s="10">
         <v>3</v>
       </c>
       <c r="F310" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G310" s="10" t="b">
         <v>1</v>
@@ -22674,13 +22674,13 @@
         <v>847</v>
       </c>
       <c r="D311" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E311" s="10">
         <v>1</v>
       </c>
       <c r="F311" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G311" s="10" t="b">
         <v>1</v>
@@ -22697,13 +22697,13 @@
         <v>961</v>
       </c>
       <c r="D312" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E312" s="10">
         <v>4</v>
       </c>
       <c r="F312" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G312" s="10" t="b">
         <v>1</v>
@@ -22720,13 +22720,13 @@
         <v>879</v>
       </c>
       <c r="D313" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E313" s="10">
         <v>5</v>
       </c>
       <c r="F313" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G313" s="10" t="b">
         <v>1</v>
@@ -22743,13 +22743,13 @@
         <v>933</v>
       </c>
       <c r="D314" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E314" s="10">
         <v>3</v>
       </c>
       <c r="F314" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G314" s="10" t="b">
         <v>1</v>
@@ -22760,19 +22760,19 @@
         <v>576</v>
       </c>
       <c r="B315" s="10" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C315" s="10" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D315" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E315" s="10">
         <v>3</v>
       </c>
       <c r="F315" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G315" s="10" t="b">
         <v>1</v>
@@ -22789,13 +22789,13 @@
         <v>949</v>
       </c>
       <c r="D316" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E316" s="10">
         <v>3</v>
       </c>
       <c r="F316" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G316" s="10" t="b">
         <v>1</v>
@@ -22812,13 +22812,13 @@
         <v>963</v>
       </c>
       <c r="D317" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E317" s="10">
         <v>3</v>
       </c>
       <c r="F317" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G317" s="10" t="b">
         <v>1</v>
@@ -22829,19 +22829,19 @@
         <v>581</v>
       </c>
       <c r="B318" s="10" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C318" s="10" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D318" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E318" s="10">
         <v>3</v>
       </c>
       <c r="F318" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G318" s="10" t="b">
         <v>1</v>
@@ -22852,19 +22852,19 @@
         <v>581</v>
       </c>
       <c r="B319" s="10" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C319" s="10" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D319" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E319" s="10">
         <v>3</v>
       </c>
       <c r="F319" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G319" s="10" t="b">
         <v>1</v>
@@ -22875,19 +22875,19 @@
         <v>581</v>
       </c>
       <c r="B320" s="10" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C320" s="10" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D320" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E320" s="10">
         <v>2</v>
       </c>
       <c r="F320" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G320" s="10" t="b">
         <v>1</v>
@@ -22898,19 +22898,19 @@
         <v>581</v>
       </c>
       <c r="B321" s="10" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C321" s="10" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D321" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E321" s="10">
         <v>3</v>
       </c>
       <c r="F321" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G321" s="10" t="b">
         <v>1</v>
@@ -22927,13 +22927,13 @@
         <v>847</v>
       </c>
       <c r="D322" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E322" s="10">
         <v>8</v>
       </c>
       <c r="F322" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G322" s="10" t="b">
         <v>1</v>
@@ -22950,13 +22950,13 @@
         <v>965</v>
       </c>
       <c r="D323" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E323" s="10">
         <v>4</v>
       </c>
       <c r="F323" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G323" s="10" t="b">
         <v>1</v>
@@ -22973,13 +22973,13 @@
         <v>967</v>
       </c>
       <c r="D324" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E324" s="10">
         <v>4</v>
       </c>
       <c r="F324" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G324" s="10" t="b">
         <v>1</v>
@@ -22996,13 +22996,13 @@
         <v>939</v>
       </c>
       <c r="D325" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E325" s="10">
         <v>4</v>
       </c>
       <c r="F325" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G325" s="10" t="b">
         <v>1</v>
@@ -23019,13 +23019,13 @@
         <v>969</v>
       </c>
       <c r="D326" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E326" s="10">
         <v>4</v>
       </c>
       <c r="F326" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G326" s="10" t="b">
         <v>1</v>
@@ -23042,13 +23042,13 @@
         <v>961</v>
       </c>
       <c r="D327" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E327" s="10">
         <v>4</v>
       </c>
       <c r="F327" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G327" s="10" t="b">
         <v>1</v>
@@ -23065,13 +23065,13 @@
         <v>879</v>
       </c>
       <c r="D328" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E328" s="10">
         <v>4</v>
       </c>
       <c r="F328" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G328" s="10" t="b">
         <v>1</v>
@@ -23088,13 +23088,13 @@
         <v>915</v>
       </c>
       <c r="D329" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E329" s="10">
         <v>3</v>
       </c>
       <c r="F329" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G329" s="10" t="b">
         <v>1</v>
@@ -23111,13 +23111,13 @@
         <v>971</v>
       </c>
       <c r="D330" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E330" s="10">
         <v>5</v>
       </c>
       <c r="F330" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G330" s="10" t="b">
         <v>1</v>
@@ -23134,13 +23134,13 @@
         <v>973</v>
       </c>
       <c r="D331" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E331" s="10">
         <v>5</v>
       </c>
       <c r="F331" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G331" s="10" t="b">
         <v>1</v>
@@ -23157,13 +23157,13 @@
         <v>975</v>
       </c>
       <c r="D332" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E332" s="10">
         <v>5</v>
       </c>
       <c r="F332" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G332" s="10" t="b">
         <v>1</v>
@@ -23180,13 +23180,13 @@
         <v>977</v>
       </c>
       <c r="D333" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E333" s="10">
         <v>5</v>
       </c>
       <c r="F333" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G333" s="10" t="b">
         <v>1</v>
@@ -23203,13 +23203,13 @@
         <v>979</v>
       </c>
       <c r="D334" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E334" s="10">
         <v>3</v>
       </c>
       <c r="F334" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G334" s="10" t="b">
         <v>1</v>
@@ -23226,13 +23226,13 @@
         <v>881</v>
       </c>
       <c r="D335" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E335" s="10">
         <v>3</v>
       </c>
       <c r="F335" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G335" s="10" t="b">
         <v>1</v>
@@ -23240,22 +23240,22 @@
     </row>
     <row r="336" spans="1:7">
       <c r="A336" s="10" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B336" s="10" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C336" s="47" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D336" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E336" s="10">
         <v>2</v>
       </c>
       <c r="F336" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G336" s="10" t="b">
         <v>1</v>
@@ -23263,22 +23263,22 @@
     </row>
     <row r="337" spans="1:7">
       <c r="A337" s="10" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B337" s="10" t="s">
         <v>290</v>
       </c>
       <c r="C337" s="47" t="s">
-        <v>845</v>
+        <v>591</v>
       </c>
       <c r="D337" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E337" s="10">
         <v>1</v>
       </c>
       <c r="F337" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G337" s="10" t="b">
         <v>1</v>
@@ -23286,22 +23286,22 @@
     </row>
     <row r="338" spans="1:7">
       <c r="A338" s="10" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B338" s="10" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C338" s="47" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D338" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E338" s="10">
         <v>1</v>
       </c>
       <c r="F338" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G338" s="10" t="b">
         <v>1</v>
@@ -23309,7 +23309,7 @@
     </row>
     <row r="339" spans="1:7">
       <c r="A339" s="10" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B339" s="10" t="s">
         <v>980</v>
@@ -23318,13 +23318,13 @@
         <v>981</v>
       </c>
       <c r="D339" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E339" s="10">
         <v>1</v>
       </c>
       <c r="F339" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G339" s="10" t="b">
         <v>1</v>
@@ -23332,7 +23332,7 @@
     </row>
     <row r="340" spans="1:7">
       <c r="A340" s="10" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B340" s="10" t="s">
         <v>846</v>
@@ -23341,13 +23341,13 @@
         <v>847</v>
       </c>
       <c r="D340" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E340" s="10">
         <v>1</v>
       </c>
       <c r="F340" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G340" s="10" t="b">
         <v>1</v>
@@ -23355,22 +23355,22 @@
     </row>
     <row r="341" spans="1:7">
       <c r="A341" s="10" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B341" s="10" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C341" s="47" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D341" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E341" s="10">
         <v>1</v>
       </c>
       <c r="F341" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G341" s="10" t="b">
         <v>1</v>
@@ -23378,16 +23378,16 @@
     </row>
     <row r="342" spans="1:7">
       <c r="A342" s="10" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B342" s="10" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C342" s="47" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D342" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E342" s="10">
         <v>8</v>
@@ -23401,16 +23401,16 @@
     </row>
     <row r="343" spans="1:7">
       <c r="A343" s="10" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B343" s="10" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C343" s="47" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D343" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E343" s="10">
         <v>8</v>
@@ -23424,7 +23424,7 @@
     </row>
     <row r="344" spans="1:7">
       <c r="A344" s="10" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B344" s="10" t="s">
         <v>866</v>
@@ -23433,13 +23433,13 @@
         <v>867</v>
       </c>
       <c r="D344" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E344" s="10">
         <v>1</v>
       </c>
       <c r="F344" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G344" s="10" t="b">
         <v>1</v>
@@ -23447,7 +23447,7 @@
     </row>
     <row r="345" spans="1:7">
       <c r="A345" s="10" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B345" s="10" t="s">
         <v>882</v>
@@ -23456,7 +23456,7 @@
         <v>883</v>
       </c>
       <c r="D345" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E345" s="10">
         <v>5</v>
@@ -23470,16 +23470,16 @@
     </row>
     <row r="346" spans="1:7">
       <c r="A346" s="10" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B346" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C346" s="47" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D346" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E346" s="10">
         <v>5</v>
@@ -23493,7 +23493,7 @@
     </row>
     <row r="347" spans="1:7">
       <c r="A347" s="10" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B347" s="10" t="s">
         <v>983</v>
@@ -23502,7 +23502,7 @@
         <v>984</v>
       </c>
       <c r="D347" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E347" s="10">
         <v>5</v>
@@ -23516,7 +23516,7 @@
     </row>
     <row r="348" spans="1:7">
       <c r="A348" s="10" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B348" s="10" t="s">
         <v>924</v>
@@ -23525,13 +23525,13 @@
         <v>925</v>
       </c>
       <c r="D348" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E348" s="10">
         <v>4</v>
       </c>
       <c r="F348" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G348" s="10" t="b">
         <v>1</v>
@@ -23539,7 +23539,7 @@
     </row>
     <row r="349" spans="1:7">
       <c r="A349" s="10" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B349" s="10" t="s">
         <v>866</v>
@@ -23548,13 +23548,13 @@
         <v>867</v>
       </c>
       <c r="D349" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E349" s="10">
         <v>3</v>
       </c>
       <c r="F349" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G349" s="10" t="b">
         <v>1</v>
@@ -23562,22 +23562,22 @@
     </row>
     <row r="350" spans="1:7">
       <c r="A350" s="10" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B350" s="10" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C350" s="10" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D350" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E350" s="10">
         <v>3</v>
       </c>
       <c r="F350" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G350" s="10" t="b">
         <v>1</v>
@@ -23585,7 +23585,7 @@
     </row>
     <row r="351" spans="1:7">
       <c r="A351" s="10" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B351" s="10" t="s">
         <v>985</v>
@@ -23594,13 +23594,13 @@
         <v>986</v>
       </c>
       <c r="D351" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E351" s="10">
         <v>3</v>
       </c>
       <c r="F351" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G351" s="10" t="b">
         <v>1</v>
@@ -23608,7 +23608,7 @@
     </row>
     <row r="352" spans="1:7">
       <c r="A352" s="10" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B352" s="10" t="s">
         <v>987</v>
@@ -23617,13 +23617,13 @@
         <v>988</v>
       </c>
       <c r="D352" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E352" s="10">
         <v>1</v>
       </c>
       <c r="F352" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G352" s="10" t="b">
         <v>1</v>
@@ -23631,22 +23631,22 @@
     </row>
     <row r="353" spans="1:7">
       <c r="A353" s="10" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B353" s="10" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C353" s="10" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D353" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E353" s="10">
         <v>2</v>
       </c>
       <c r="F353" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G353" s="10" t="b">
         <v>1</v>
@@ -23654,22 +23654,22 @@
     </row>
     <row r="354" spans="1:7">
       <c r="A354" s="10" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B354" s="10" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C354" s="10" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="D354" s="14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E354" s="10">
         <v>6</v>
       </c>
       <c r="F354" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G354" s="10" t="b">
         <v>1</v>
@@ -23677,22 +23677,22 @@
     </row>
     <row r="355" spans="1:7">
       <c r="A355" s="10" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B355" s="10" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C355" s="10" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="D355" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E355" s="10">
         <v>3</v>
       </c>
       <c r="F355" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G355" s="10" t="b">
         <v>1</v>
@@ -23700,22 +23700,22 @@
     </row>
     <row r="356" spans="1:7">
       <c r="A356" s="10" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B356" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C356" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D356" s="16" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E356" s="10">
         <v>2</v>
       </c>
       <c r="F356" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G356" s="10" t="b">
         <v>1</v>
@@ -23752,10 +23752,10 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>751</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>750</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>989</v>
@@ -23781,10 +23781,10 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="7" t="s">
+        <v>758</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>757</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>756</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>993</v>
@@ -23813,10 +23813,10 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="7" t="s">
+        <v>762</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>761</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>760</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>993</v>
@@ -23845,10 +23845,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="7" t="s">
+        <v>765</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>764</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>763</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>993</v>
@@ -23877,10 +23877,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="7" t="s">
+        <v>768</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>767</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>766</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>1009</v>
@@ -23909,10 +23909,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="7" t="s">
+        <v>771</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>770</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>769</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>1014</v>
@@ -23941,10 +23941,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="7" t="s">
+        <v>773</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>772</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>771</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>993</v>
@@ -23973,10 +23973,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="7" t="s">
+        <v>775</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>774</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>773</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>993</v>
@@ -24005,10 +24005,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="7" t="s">
+        <v>777</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>776</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>775</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>1014</v>
@@ -24037,10 +24037,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="7" t="s">
+        <v>780</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>779</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>778</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>1014</v>
@@ -24069,10 +24069,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="7" t="s">
+        <v>782</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>781</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>780</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>1014</v>
@@ -24101,10 +24101,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="7" t="s">
+        <v>784</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>783</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>782</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>993</v>
@@ -24133,10 +24133,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="7" t="s">
+        <v>786</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>785</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>784</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>1030</v>
@@ -24165,10 +24165,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="7" t="s">
+        <v>788</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>787</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>786</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>1030</v>
@@ -24197,10 +24197,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="7" t="s">
+        <v>790</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>789</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>788</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>1009</v>
@@ -24229,10 +24229,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="7" t="s">
+        <v>792</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>791</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>790</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>1014</v>
@@ -24261,10 +24261,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="7" t="s">
+        <v>794</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>793</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>792</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>1014</v>
@@ -24293,10 +24293,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="7" t="s">
+        <v>796</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>795</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>794</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>1014</v>
@@ -24325,10 +24325,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="7" t="s">
+        <v>798</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>797</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>796</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>1014</v>
@@ -24357,10 +24357,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="7" t="s">
+        <v>800</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>799</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>798</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>1014</v>
@@ -24389,10 +24389,10 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="7" t="s">
+        <v>802</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>801</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>800</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>1014</v>
@@ -24421,10 +24421,10 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="7" t="s">
+        <v>804</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>803</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>802</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>1030</v>
@@ -24453,10 +24453,10 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="7" t="s">
+        <v>806</v>
+      </c>
+      <c r="B23" s="7" t="s">
         <v>805</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>804</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>993</v>
@@ -24485,10 +24485,10 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="7" t="s">
+        <v>808</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>807</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>806</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>993</v>
@@ -24517,10 +24517,10 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="7" t="s">
+        <v>810</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>809</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>808</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>1014</v>
@@ -24581,10 +24581,10 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="B27" s="7" t="s">
         <v>811</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>810</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>1009</v>
@@ -24613,10 +24613,10 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="7" t="s">
+        <v>814</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>813</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>812</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>1014</v>
@@ -24645,10 +24645,10 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="7" t="s">
+        <v>816</v>
+      </c>
+      <c r="B29" s="7" t="s">
         <v>815</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>814</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>993</v>
@@ -24677,10 +24677,10 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="10" t="s">
+        <v>818</v>
+      </c>
+      <c r="B30" s="7" t="s">
         <v>817</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>816</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>993</v>
@@ -24709,10 +24709,10 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="7" t="s">
+        <v>820</v>
+      </c>
+      <c r="B31" s="7" t="s">
         <v>819</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>818</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>993</v>
@@ -24741,10 +24741,10 @@
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="7" t="s">
+        <v>822</v>
+      </c>
+      <c r="B32" s="11" t="s">
         <v>821</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>820</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>1069</v>
@@ -24773,10 +24773,10 @@
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="7" t="s">
+        <v>824</v>
+      </c>
+      <c r="B33" s="7" t="s">
         <v>823</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>822</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>1009</v>
@@ -24805,10 +24805,10 @@
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="10" t="s">
+        <v>827</v>
+      </c>
+      <c r="B34" s="7" t="s">
         <v>826</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>825</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>1014</v>
@@ -24837,10 +24837,10 @@
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="10" t="s">
+        <v>829</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>828</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>827</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>1014</v>
@@ -24869,10 +24869,10 @@
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="10" t="s">
+        <v>831</v>
+      </c>
+      <c r="B36" s="7" t="s">
         <v>830</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>829</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>1009</v>
@@ -24901,10 +24901,10 @@
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="7" t="s">
+        <v>833</v>
+      </c>
+      <c r="B37" s="7" t="s">
         <v>832</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>831</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>1030</v>
@@ -24933,10 +24933,10 @@
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="B38" s="7" t="s">
         <v>834</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>833</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>993</v>
@@ -24965,10 +24965,10 @@
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="B39" s="7" t="s">
         <v>836</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>835</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>993</v>
@@ -24997,10 +24997,10 @@
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="7" t="s">
+        <v>839</v>
+      </c>
+      <c r="B40" s="7" t="s">
         <v>838</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>837</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>993</v>
@@ -25029,10 +25029,10 @@
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="7" t="s">
+        <v>841</v>
+      </c>
+      <c r="B41" s="7" t="s">
         <v>840</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>839</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>993</v>
@@ -25061,10 +25061,10 @@
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="7" t="s">
+        <v>843</v>
+      </c>
+      <c r="B42" s="7" t="s">
         <v>842</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>841</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>1009</v>
@@ -25093,10 +25093,10 @@
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="7" t="s">
+        <v>845</v>
+      </c>
+      <c r="B43" s="7" t="s">
         <v>844</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>843</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>1030</v>
@@ -25125,7 +25125,7 @@
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="10" t="s">
-        <v>845</v>
+        <v>591</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>290</v>
@@ -27918,7 +27918,7 @@
     </row>
     <row r="6" spans="1:6" ht="18" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>1208</v>
@@ -27936,7 +27936,7 @@
     </row>
     <row r="7" spans="1:6" ht="18" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>1211</v>
@@ -27954,7 +27954,7 @@
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>1213</v>
@@ -27972,7 +27972,7 @@
     </row>
     <row r="9" spans="1:6" ht="18" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>1214</v>
@@ -27988,7 +27988,7 @@
     </row>
     <row r="10" spans="1:6" ht="18" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>1215</v>
@@ -28006,7 +28006,7 @@
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>1217</v>
@@ -28022,7 +28022,7 @@
     </row>
     <row r="12" spans="1:6" ht="18" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>1218</v>
@@ -28040,7 +28040,7 @@
     </row>
     <row r="13" spans="1:6" ht="18" customHeight="1">
       <c r="A13" s="7" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>1220</v>
@@ -28058,7 +28058,7 @@
     </row>
     <row r="14" spans="1:6" ht="18" customHeight="1">
       <c r="A14" s="7" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>1222</v>
@@ -28076,7 +28076,7 @@
     </row>
     <row r="15" spans="1:6" ht="18" customHeight="1">
       <c r="A15" s="7" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>1224</v>
@@ -28094,7 +28094,7 @@
     </row>
     <row r="16" spans="1:6" ht="18" customHeight="1">
       <c r="A16" s="7" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>1226</v>
@@ -28112,7 +28112,7 @@
     </row>
     <row r="17" spans="1:6" ht="18" customHeight="1">
       <c r="A17" s="7" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>1228</v>
@@ -28130,7 +28130,7 @@
     </row>
     <row r="18" spans="1:6" ht="18" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>1230</v>
@@ -28148,7 +28148,7 @@
     </row>
     <row r="19" spans="1:6" ht="18" customHeight="1">
       <c r="A19" s="7" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>1232</v>
@@ -28166,7 +28166,7 @@
     </row>
     <row r="20" spans="1:6" ht="18" customHeight="1">
       <c r="A20" s="7" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>1234</v>
@@ -28184,7 +28184,7 @@
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1">
       <c r="A21" s="7" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>1236</v>
@@ -28202,7 +28202,7 @@
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1">
       <c r="A22" s="7" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>1238</v>
@@ -28220,7 +28220,7 @@
     </row>
     <row r="23" spans="1:6" ht="18" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>1240</v>

--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB483EED-A360-4E4C-B162-42AA24905A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4252CB20-BB0D-454A-9E85-A6165691AF7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4503" uniqueCount="1252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4503" uniqueCount="1253">
   <si>
     <t>NpcID</t>
   </si>
@@ -2059,7 +2059,7 @@
 【标准方】金锁固精丸</t>
   </si>
   <si>
-    <t>ren_shen</t>
+    <t>ren_shen_disease</t>
   </si>
   <si>
     <t>妊娠</t>
@@ -3535,6 +3535,9 @@
   </si>
   <si>
     <t>ge_gen</t>
+  </si>
+  <si>
+    <t>ren_shen</t>
   </si>
   <si>
     <t>熟地黄</t>
@@ -6072,7 +6075,19 @@
 在搜索栏输入药材，方剂，疾病的中文名或拼音，拼音首字母可快速查找。</t>
   </si>
   <si>
-    <t>ren_shen_disease</t>
+    <r>
+      <t>要上来</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>访</t>
+    </r>
     <phoneticPr fontId="14"/>
   </si>
 </sst>
@@ -8361,8 +8376,8 @@
     <col min="7" max="7" width="25.125" style="23" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.25" style="23" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="33.375" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="44" width="9.125" style="23" customWidth="1"/>
-    <col min="45" max="16384" width="9.125" style="23"/>
+    <col min="10" max="45" width="9.125" style="23" customWidth="1"/>
+    <col min="46" max="16384" width="9.125" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.399999999999999" customHeight="1">
@@ -10150,10 +10165,10 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="C1" s="42" t="s">
         <v>257</v>
@@ -10167,53 +10182,53 @@
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="C2" s="7">
         <v>0</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1">
       <c r="A3" s="7" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="C3" s="7">
         <v>0</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="C4" s="7">
         <v>0</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1">
@@ -10313,8 +10328,8 @@
     <col min="14" max="14" width="12" style="36" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.75" style="36" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10.875" style="36" bestFit="1" customWidth="1"/>
-    <col min="17" max="67" width="9" style="36" customWidth="1"/>
-    <col min="68" max="16384" width="9" style="36"/>
+    <col min="17" max="68" width="9" style="36" customWidth="1"/>
+    <col min="69" max="16384" width="9" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -10708,7 +10723,7 @@
         <v>288</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>289</v>
+        <v>1252</v>
       </c>
       <c r="C11" s="37" t="s">
         <v>262</v>
@@ -10905,8 +10920,8 @@
     <col min="8" max="8" width="8.125" style="32" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="48" style="32" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="150.5" style="32" bestFit="1" customWidth="1"/>
-    <col min="11" max="18" width="8.875" style="36" customWidth="1"/>
-    <col min="19" max="16384" width="8.875" style="36"/>
+    <col min="11" max="19" width="8.875" style="36" customWidth="1"/>
+    <col min="20" max="16384" width="8.875" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -13666,7 +13681,7 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="47" t="s">
-        <v>1251</v>
+        <v>591</v>
       </c>
       <c r="B47" s="47" t="s">
         <v>592</v>
@@ -13942,8 +13957,8 @@
     <col min="27" max="27" width="5.125" style="35" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="5" style="35" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="5.25" style="35" bestFit="1" customWidth="1"/>
-    <col min="30" max="92" width="9" style="9" customWidth="1"/>
-    <col min="93" max="16384" width="9" style="9"/>
+    <col min="30" max="93" width="9" style="9" customWidth="1"/>
+    <col min="94" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="15.4" customHeight="1">
@@ -17128,7 +17143,7 @@
         <v>290</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>591</v>
+        <v>846</v>
       </c>
       <c r="D70" s="13" t="s">
         <v>759</v>
@@ -17171,10 +17186,10 @@
         <v>438</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D72" s="14" t="s">
         <v>763</v>
@@ -17194,10 +17209,10 @@
         <v>438</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D73" s="15" t="s">
         <v>766</v>
@@ -17217,10 +17232,10 @@
         <v>438</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D74" s="15" t="s">
         <v>766</v>
@@ -17240,10 +17255,10 @@
         <v>438</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D75" s="15" t="s">
         <v>766</v>
@@ -17378,10 +17393,10 @@
         <v>448</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D81" s="13" t="s">
         <v>759</v>
@@ -17401,10 +17416,10 @@
         <v>448</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D82" s="14" t="s">
         <v>763</v>
@@ -17424,10 +17439,10 @@
         <v>448</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D83" s="14" t="s">
         <v>763</v>
@@ -17447,10 +17462,10 @@
         <v>448</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="D84" s="15" t="s">
         <v>766</v>
@@ -17516,10 +17531,10 @@
         <v>453</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D87" s="13" t="s">
         <v>759</v>
@@ -17562,10 +17577,10 @@
         <v>453</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D89" s="14" t="s">
         <v>763</v>
@@ -17585,10 +17600,10 @@
         <v>453</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="D90" s="14" t="s">
         <v>763</v>
@@ -17654,10 +17669,10 @@
         <v>453</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D93" s="15" t="s">
         <v>766</v>
@@ -17930,10 +17945,10 @@
         <v>462</v>
       </c>
       <c r="B105" s="10" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="D105" s="14" t="s">
         <v>763</v>
@@ -17953,10 +17968,10 @@
         <v>462</v>
       </c>
       <c r="B106" s="10" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D106" s="14" t="s">
         <v>763</v>
@@ -17999,10 +18014,10 @@
         <v>462</v>
       </c>
       <c r="B108" s="10" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D108" s="15" t="s">
         <v>766</v>
@@ -18071,7 +18086,7 @@
         <v>290</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>591</v>
+        <v>846</v>
       </c>
       <c r="D111" s="13" t="s">
         <v>759</v>
@@ -18160,10 +18175,10 @@
         <v>471</v>
       </c>
       <c r="B115" s="10" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D115" s="13" t="s">
         <v>759</v>
@@ -18183,10 +18198,10 @@
         <v>471</v>
       </c>
       <c r="B116" s="10" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="D116" s="14" t="s">
         <v>763</v>
@@ -18252,10 +18267,10 @@
         <v>476</v>
       </c>
       <c r="B119" s="10" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="D119" s="13" t="s">
         <v>759</v>
@@ -18278,7 +18293,7 @@
         <v>290</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>591</v>
+        <v>846</v>
       </c>
       <c r="D120" s="14" t="s">
         <v>763</v>
@@ -18347,7 +18362,7 @@
         <v>290</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>591</v>
+        <v>846</v>
       </c>
       <c r="D123" s="13" t="s">
         <v>759</v>
@@ -18413,10 +18428,10 @@
         <v>479</v>
       </c>
       <c r="B126" s="10" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D126" s="14" t="s">
         <v>763</v>
@@ -18436,10 +18451,10 @@
         <v>479</v>
       </c>
       <c r="B127" s="10" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="D127" s="14" t="s">
         <v>763</v>
@@ -18459,10 +18474,10 @@
         <v>479</v>
       </c>
       <c r="B128" s="10" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C128" s="10" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="D128" s="14" t="s">
         <v>763</v>
@@ -18505,10 +18520,10 @@
         <v>479</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="D130" s="15" t="s">
         <v>766</v>
@@ -18574,10 +18589,10 @@
         <v>484</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="D133" s="13" t="s">
         <v>759</v>
@@ -18620,10 +18635,10 @@
         <v>484</v>
       </c>
       <c r="B135" s="10" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C135" s="10" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D135" s="14" t="s">
         <v>763</v>
@@ -18666,10 +18681,10 @@
         <v>484</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="D137" s="14" t="s">
         <v>763</v>
@@ -18712,10 +18727,10 @@
         <v>484</v>
       </c>
       <c r="B139" s="10" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C139" s="10" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D139" s="15" t="s">
         <v>766</v>
@@ -18781,10 +18796,10 @@
         <v>484</v>
       </c>
       <c r="B142" s="10" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D142" s="15" t="s">
         <v>766</v>
@@ -18965,10 +18980,10 @@
         <v>489</v>
       </c>
       <c r="B150" s="10" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C150" s="10" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D150" s="15" t="s">
         <v>766</v>
@@ -18988,10 +19003,10 @@
         <v>489</v>
       </c>
       <c r="B151" s="10" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C151" s="10" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D151" s="15" t="s">
         <v>766</v>
@@ -19057,10 +19072,10 @@
         <v>494</v>
       </c>
       <c r="B154" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C154" s="10" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D154" s="13" t="s">
         <v>759</v>
@@ -19080,10 +19095,10 @@
         <v>494</v>
       </c>
       <c r="B155" s="10" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D155" s="13" t="s">
         <v>759</v>
@@ -19172,10 +19187,10 @@
         <v>499</v>
       </c>
       <c r="B159" s="10" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C159" s="10" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D159" s="13" t="s">
         <v>759</v>
@@ -19195,10 +19210,10 @@
         <v>499</v>
       </c>
       <c r="B160" s="10" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C160" s="10" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D160" s="14" t="s">
         <v>763</v>
@@ -19241,10 +19256,10 @@
         <v>499</v>
       </c>
       <c r="B162" s="10" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C162" s="10" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D162" s="15" t="s">
         <v>766</v>
@@ -19287,10 +19302,10 @@
         <v>499</v>
       </c>
       <c r="B164" s="10" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C164" s="10" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="D164" s="15" t="s">
         <v>766</v>
@@ -19313,7 +19328,7 @@
         <v>290</v>
       </c>
       <c r="C165" s="10" t="s">
-        <v>591</v>
+        <v>846</v>
       </c>
       <c r="D165" s="15" t="s">
         <v>766</v>
@@ -19405,7 +19420,7 @@
         <v>290</v>
       </c>
       <c r="C169" s="10" t="s">
-        <v>591</v>
+        <v>846</v>
       </c>
       <c r="D169" s="13" t="s">
         <v>759</v>
@@ -19448,10 +19463,10 @@
         <v>503</v>
       </c>
       <c r="B171" s="10" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C171" s="10" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="D171" s="14" t="s">
         <v>763</v>
@@ -19494,10 +19509,10 @@
         <v>503</v>
       </c>
       <c r="B173" s="10" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C173" s="10" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D173" s="15" t="s">
         <v>766</v>
@@ -19517,10 +19532,10 @@
         <v>503</v>
       </c>
       <c r="B174" s="10" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C174" s="10" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D174" s="15" t="s">
         <v>766</v>
@@ -19540,10 +19555,10 @@
         <v>503</v>
       </c>
       <c r="B175" s="10" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C175" s="10" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D175" s="15" t="s">
         <v>766</v>
@@ -19563,10 +19578,10 @@
         <v>503</v>
       </c>
       <c r="B176" s="10" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C176" s="10" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D176" s="15" t="s">
         <v>766</v>
@@ -19632,10 +19647,10 @@
         <v>503</v>
       </c>
       <c r="B179" s="10" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C179" s="10" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="D179" s="15" t="s">
         <v>766</v>
@@ -19724,10 +19739,10 @@
         <v>508</v>
       </c>
       <c r="B183" s="10" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C183" s="47" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D183" s="13" t="s">
         <v>759</v>
@@ -19747,10 +19762,10 @@
         <v>508</v>
       </c>
       <c r="B184" s="10" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C184" s="47" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="D184" s="13" t="s">
         <v>759</v>
@@ -19770,10 +19785,10 @@
         <v>508</v>
       </c>
       <c r="B185" s="10" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C185" s="47" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D185" s="14" t="s">
         <v>763</v>
@@ -19816,10 +19831,10 @@
         <v>508</v>
       </c>
       <c r="B187" s="10" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C187" s="47" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D187" s="14" t="s">
         <v>763</v>
@@ -19862,10 +19877,10 @@
         <v>508</v>
       </c>
       <c r="B189" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C189" s="47" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D189" s="15" t="s">
         <v>766</v>
@@ -19931,10 +19946,10 @@
         <v>508</v>
       </c>
       <c r="B192" s="10" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C192" s="47" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="D192" s="15" t="s">
         <v>766</v>
@@ -19977,10 +19992,10 @@
         <v>512</v>
       </c>
       <c r="B194" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C194" s="10" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D194" s="13" t="s">
         <v>759</v>
@@ -20000,10 +20015,10 @@
         <v>512</v>
       </c>
       <c r="B195" s="10" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C195" s="10" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="D195" s="14" t="s">
         <v>763</v>
@@ -20023,10 +20038,10 @@
         <v>512</v>
       </c>
       <c r="B196" s="10" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C196" s="10" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D196" s="14" t="s">
         <v>763</v>
@@ -20046,10 +20061,10 @@
         <v>512</v>
       </c>
       <c r="B197" s="10" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C197" s="10" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D197" s="14" t="s">
         <v>763</v>
@@ -20069,10 +20084,10 @@
         <v>512</v>
       </c>
       <c r="B198" s="10" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C198" s="10" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D198" s="14" t="s">
         <v>763</v>
@@ -20118,7 +20133,7 @@
         <v>290</v>
       </c>
       <c r="C200" s="10" t="s">
-        <v>591</v>
+        <v>846</v>
       </c>
       <c r="D200" s="15" t="s">
         <v>766</v>
@@ -20161,10 +20176,10 @@
         <v>512</v>
       </c>
       <c r="B202" s="10" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C202" s="10" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D202" s="15" t="s">
         <v>766</v>
@@ -20184,10 +20199,10 @@
         <v>512</v>
       </c>
       <c r="B203" s="10" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C203" s="10" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D203" s="15" t="s">
         <v>766</v>
@@ -20207,10 +20222,10 @@
         <v>512</v>
       </c>
       <c r="B204" s="10" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C204" s="10" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D204" s="15" t="s">
         <v>766</v>
@@ -20230,10 +20245,10 @@
         <v>512</v>
       </c>
       <c r="B205" s="10" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C205" s="10" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D205" s="15" t="s">
         <v>766</v>
@@ -20322,10 +20337,10 @@
         <v>519</v>
       </c>
       <c r="B209" s="10" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C209" s="10" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="D209" s="13" t="s">
         <v>759</v>
@@ -20368,10 +20383,10 @@
         <v>519</v>
       </c>
       <c r="B211" s="10" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C211" s="10" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D211" s="14" t="s">
         <v>763</v>
@@ -20414,10 +20429,10 @@
         <v>519</v>
       </c>
       <c r="B213" s="10" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C213" s="10" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D213" s="15" t="s">
         <v>766</v>
@@ -20555,7 +20570,7 @@
         <v>290</v>
       </c>
       <c r="C219" s="10" t="s">
-        <v>591</v>
+        <v>846</v>
       </c>
       <c r="D219" s="13" t="s">
         <v>759</v>
@@ -20575,10 +20590,10 @@
         <v>524</v>
       </c>
       <c r="B220" s="10" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="C220" s="10" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D220" s="14" t="s">
         <v>763</v>
@@ -20644,10 +20659,10 @@
         <v>524</v>
       </c>
       <c r="B223" s="10" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C223" s="10" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D223" s="14" t="s">
         <v>763</v>
@@ -20667,10 +20682,10 @@
         <v>524</v>
       </c>
       <c r="B224" s="10" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C224" s="10" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="D224" s="15" t="s">
         <v>766</v>
@@ -20690,10 +20705,10 @@
         <v>524</v>
       </c>
       <c r="B225" s="10" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C225" s="10" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D225" s="15" t="s">
         <v>766</v>
@@ -20713,10 +20728,10 @@
         <v>524</v>
       </c>
       <c r="B226" s="10" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C226" s="10" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D226" s="15" t="s">
         <v>766</v>
@@ -20805,10 +20820,10 @@
         <v>529</v>
       </c>
       <c r="B230" s="10" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C230" s="10" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D230" s="13" t="s">
         <v>759</v>
@@ -20828,10 +20843,10 @@
         <v>529</v>
       </c>
       <c r="B231" s="10" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C231" s="10" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="D231" s="14" t="s">
         <v>763</v>
@@ -20874,10 +20889,10 @@
         <v>529</v>
       </c>
       <c r="B233" s="10" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C233" s="10" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D233" s="15" t="s">
         <v>766</v>
@@ -20897,10 +20912,10 @@
         <v>529</v>
       </c>
       <c r="B234" s="10" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C234" s="10" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D234" s="15" t="s">
         <v>766</v>
@@ -20920,10 +20935,10 @@
         <v>529</v>
       </c>
       <c r="B235" s="10" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="C235" s="10" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="D235" s="15" t="s">
         <v>766</v>
@@ -20966,10 +20981,10 @@
         <v>529</v>
       </c>
       <c r="B237" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C237" s="10" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D237" s="15" t="s">
         <v>766</v>
@@ -20989,10 +21004,10 @@
         <v>529</v>
       </c>
       <c r="B238" s="10" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C238" s="10" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="D238" s="15" t="s">
         <v>766</v>
@@ -21035,10 +21050,10 @@
         <v>534</v>
       </c>
       <c r="B240" s="10" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C240" s="10" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="D240" s="13" t="s">
         <v>759</v>
@@ -21058,10 +21073,10 @@
         <v>534</v>
       </c>
       <c r="B241" s="10" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C241" s="10" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="D241" s="13" t="s">
         <v>759</v>
@@ -21104,10 +21119,10 @@
         <v>534</v>
       </c>
       <c r="B243" s="10" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C243" s="10" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D243" s="14" t="s">
         <v>763</v>
@@ -21127,10 +21142,10 @@
         <v>534</v>
       </c>
       <c r="B244" s="10" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C244" s="10" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="D244" s="15" t="s">
         <v>766</v>
@@ -21173,10 +21188,10 @@
         <v>534</v>
       </c>
       <c r="B246" s="10" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C246" s="10" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="D246" s="15" t="s">
         <v>766</v>
@@ -21219,10 +21234,10 @@
         <v>539</v>
       </c>
       <c r="B248" s="10" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C248" s="10" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="D248" s="13" t="s">
         <v>759</v>
@@ -21242,10 +21257,10 @@
         <v>539</v>
       </c>
       <c r="B249" s="10" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C249" s="10" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="D249" s="14" t="s">
         <v>763</v>
@@ -21380,10 +21395,10 @@
         <v>543</v>
       </c>
       <c r="B255" s="10" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C255" s="10" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D255" s="13" t="s">
         <v>759</v>
@@ -21518,10 +21533,10 @@
         <v>548</v>
       </c>
       <c r="B261" s="10" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C261" s="47" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D261" s="13" t="s">
         <v>759</v>
@@ -21541,10 +21556,10 @@
         <v>548</v>
       </c>
       <c r="B262" s="10" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C262" s="47" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D262" s="14" t="s">
         <v>763</v>
@@ -21564,10 +21579,10 @@
         <v>548</v>
       </c>
       <c r="B263" s="10" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C263" s="47" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="D263" s="14" t="s">
         <v>763</v>
@@ -21587,10 +21602,10 @@
         <v>548</v>
       </c>
       <c r="B264" s="10" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="C264" s="47" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="D264" s="14" t="s">
         <v>763</v>
@@ -21610,10 +21625,10 @@
         <v>548</v>
       </c>
       <c r="B265" s="10" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C265" s="47" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="D265" s="14" t="s">
         <v>763</v>
@@ -21633,10 +21648,10 @@
         <v>548</v>
       </c>
       <c r="B266" s="10" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C266" s="47" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="D266" s="15" t="s">
         <v>766</v>
@@ -21656,10 +21671,10 @@
         <v>548</v>
       </c>
       <c r="B267" s="10" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C267" s="47" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="D267" s="15" t="s">
         <v>766</v>
@@ -21702,10 +21717,10 @@
         <v>548</v>
       </c>
       <c r="B269" s="10" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C269" s="47" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="D269" s="15" t="s">
         <v>766</v>
@@ -21748,10 +21763,10 @@
         <v>552</v>
       </c>
       <c r="B271" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C271" s="10" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D271" s="13" t="s">
         <v>759</v>
@@ -21771,10 +21786,10 @@
         <v>552</v>
       </c>
       <c r="B272" s="10" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C272" s="10" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D272" s="14" t="s">
         <v>763</v>
@@ -21817,10 +21832,10 @@
         <v>552</v>
       </c>
       <c r="B274" s="10" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C274" s="10" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D274" s="14" t="s">
         <v>763</v>
@@ -21863,10 +21878,10 @@
         <v>552</v>
       </c>
       <c r="B276" s="10" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C276" s="10" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="D276" s="15" t="s">
         <v>766</v>
@@ -21886,10 +21901,10 @@
         <v>556</v>
       </c>
       <c r="B277" s="10" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C277" s="10" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="D277" s="13" t="s">
         <v>759</v>
@@ -21909,10 +21924,10 @@
         <v>556</v>
       </c>
       <c r="B278" s="10" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C278" s="10" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="D278" s="13" t="s">
         <v>759</v>
@@ -22050,7 +22065,7 @@
         <v>290</v>
       </c>
       <c r="C284" s="10" t="s">
-        <v>591</v>
+        <v>846</v>
       </c>
       <c r="D284" s="15" t="s">
         <v>766</v>
@@ -22116,10 +22131,10 @@
         <v>561</v>
       </c>
       <c r="B287" s="10" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C287" s="10" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="D287" s="13" t="s">
         <v>759</v>
@@ -22300,10 +22315,10 @@
         <v>566</v>
       </c>
       <c r="B295" s="10" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C295" s="10" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="D295" s="13" t="s">
         <v>759</v>
@@ -22326,7 +22341,7 @@
         <v>290</v>
       </c>
       <c r="C296" s="10" t="s">
-        <v>591</v>
+        <v>846</v>
       </c>
       <c r="D296" s="13" t="s">
         <v>759</v>
@@ -22392,10 +22407,10 @@
         <v>566</v>
       </c>
       <c r="B299" s="10" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C299" s="10" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D299" s="14" t="s">
         <v>763</v>
@@ -22484,10 +22499,10 @@
         <v>571</v>
       </c>
       <c r="B303" s="10" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C303" s="10" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D303" s="13" t="s">
         <v>759</v>
@@ -22507,10 +22522,10 @@
         <v>571</v>
       </c>
       <c r="B304" s="10" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C304" s="10" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="D304" s="14" t="s">
         <v>763</v>
@@ -22530,10 +22545,10 @@
         <v>571</v>
       </c>
       <c r="B305" s="10" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C305" s="10" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D305" s="14" t="s">
         <v>763</v>
@@ -22553,10 +22568,10 @@
         <v>571</v>
       </c>
       <c r="B306" s="10" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C306" s="10" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D306" s="15" t="s">
         <v>766</v>
@@ -22599,10 +22614,10 @@
         <v>571</v>
       </c>
       <c r="B308" s="10" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C308" s="10" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="D308" s="15" t="s">
         <v>766</v>
@@ -22622,10 +22637,10 @@
         <v>576</v>
       </c>
       <c r="B309" s="10" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C309" s="10" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="D309" s="13" t="s">
         <v>759</v>
@@ -22668,10 +22683,10 @@
         <v>576</v>
       </c>
       <c r="B311" s="10" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C311" s="10" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D311" s="14" t="s">
         <v>763</v>
@@ -22691,10 +22706,10 @@
         <v>576</v>
       </c>
       <c r="B312" s="10" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C312" s="10" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="D312" s="14" t="s">
         <v>763</v>
@@ -22714,10 +22729,10 @@
         <v>576</v>
       </c>
       <c r="B313" s="10" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C313" s="10" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D313" s="14" t="s">
         <v>763</v>
@@ -22737,10 +22752,10 @@
         <v>576</v>
       </c>
       <c r="B314" s="10" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C314" s="10" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D314" s="15" t="s">
         <v>766</v>
@@ -22783,10 +22798,10 @@
         <v>576</v>
       </c>
       <c r="B316" s="10" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C316" s="10" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="D316" s="15" t="s">
         <v>766</v>
@@ -22806,10 +22821,10 @@
         <v>581</v>
       </c>
       <c r="B317" s="10" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C317" s="10" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="D317" s="13" t="s">
         <v>759</v>
@@ -22921,10 +22936,10 @@
         <v>585</v>
       </c>
       <c r="B322" s="10" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C322" s="10" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D322" s="13" t="s">
         <v>759</v>
@@ -22944,10 +22959,10 @@
         <v>585</v>
       </c>
       <c r="B323" s="10" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="C323" s="10" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D323" s="14" t="s">
         <v>763</v>
@@ -22967,10 +22982,10 @@
         <v>585</v>
       </c>
       <c r="B324" s="10" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C324" s="10" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="D324" s="14" t="s">
         <v>763</v>
@@ -22990,10 +23005,10 @@
         <v>585</v>
       </c>
       <c r="B325" s="10" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C325" s="10" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D325" s="14" t="s">
         <v>763</v>
@@ -23013,10 +23028,10 @@
         <v>585</v>
       </c>
       <c r="B326" s="10" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C326" s="10" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D326" s="14" t="s">
         <v>763</v>
@@ -23036,10 +23051,10 @@
         <v>585</v>
       </c>
       <c r="B327" s="10" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C327" s="10" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="D327" s="15" t="s">
         <v>766</v>
@@ -23059,10 +23074,10 @@
         <v>585</v>
       </c>
       <c r="B328" s="10" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C328" s="10" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D328" s="15" t="s">
         <v>766</v>
@@ -23082,10 +23097,10 @@
         <v>585</v>
       </c>
       <c r="B329" s="10" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C329" s="10" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D329" s="16" t="s">
         <v>769</v>
@@ -23105,10 +23120,10 @@
         <v>589</v>
       </c>
       <c r="B330" s="10" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="C330" s="10" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="D330" s="13" t="s">
         <v>759</v>
@@ -23128,10 +23143,10 @@
         <v>589</v>
       </c>
       <c r="B331" s="10" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C331" s="10" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="D331" s="14" t="s">
         <v>763</v>
@@ -23151,10 +23166,10 @@
         <v>589</v>
       </c>
       <c r="B332" s="10" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C332" s="10" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="D332" s="15" t="s">
         <v>766</v>
@@ -23174,10 +23189,10 @@
         <v>589</v>
       </c>
       <c r="B333" s="10" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="C333" s="10" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="D333" s="15" t="s">
         <v>766</v>
@@ -23197,10 +23212,10 @@
         <v>589</v>
       </c>
       <c r="B334" s="10" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C334" s="10" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="D334" s="15" t="s">
         <v>766</v>
@@ -23220,10 +23235,10 @@
         <v>589</v>
       </c>
       <c r="B335" s="10" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C335" s="10" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="D335" s="16" t="s">
         <v>769</v>
@@ -23269,7 +23284,7 @@
         <v>290</v>
       </c>
       <c r="C337" s="47" t="s">
-        <v>591</v>
+        <v>846</v>
       </c>
       <c r="D337" s="14" t="s">
         <v>763</v>
@@ -23312,10 +23327,10 @@
         <v>594</v>
       </c>
       <c r="B339" s="10" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C339" s="47" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="D339" s="14" t="s">
         <v>763</v>
@@ -23335,10 +23350,10 @@
         <v>594</v>
       </c>
       <c r="B340" s="10" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C340" s="47" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D340" s="14" t="s">
         <v>763</v>
@@ -23393,7 +23408,7 @@
         <v>8</v>
       </c>
       <c r="F342" s="47" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="G342" s="10" t="b">
         <v>1</v>
@@ -23416,7 +23431,7 @@
         <v>8</v>
       </c>
       <c r="F343" s="47" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="G343" s="10" t="b">
         <v>1</v>
@@ -23427,10 +23442,10 @@
         <v>594</v>
       </c>
       <c r="B344" s="10" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C344" s="47" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="D344" s="15" t="s">
         <v>766</v>
@@ -23450,10 +23465,10 @@
         <v>594</v>
       </c>
       <c r="B345" s="10" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C345" s="47" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="D345" s="15" t="s">
         <v>766</v>
@@ -23462,7 +23477,7 @@
         <v>5</v>
       </c>
       <c r="F345" s="47" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="G345" s="10" t="b">
         <v>1</v>
@@ -23485,7 +23500,7 @@
         <v>5</v>
       </c>
       <c r="F346" s="47" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="G346" s="10" t="b">
         <v>1</v>
@@ -23496,10 +23511,10 @@
         <v>594</v>
       </c>
       <c r="B347" s="10" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="C347" s="47" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="D347" s="16" t="s">
         <v>769</v>
@@ -23508,7 +23523,7 @@
         <v>5</v>
       </c>
       <c r="F347" s="47" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="G347" s="10" t="b">
         <v>1</v>
@@ -23519,10 +23534,10 @@
         <v>599</v>
       </c>
       <c r="B348" s="10" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C348" s="10" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="D348" s="13" t="s">
         <v>759</v>
@@ -23542,10 +23557,10 @@
         <v>599</v>
       </c>
       <c r="B349" s="10" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C349" s="10" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="D349" s="14" t="s">
         <v>763</v>
@@ -23588,10 +23603,10 @@
         <v>599</v>
       </c>
       <c r="B351" s="10" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="C351" s="10" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="D351" s="15" t="s">
         <v>766</v>
@@ -23611,10 +23626,10 @@
         <v>599</v>
       </c>
       <c r="B352" s="10" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="C352" s="10" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="D352" s="16" t="s">
         <v>769</v>
@@ -23758,16 +23773,16 @@
         <v>751</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="F1" s="22" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="G1" s="42" t="s">
         <v>257</v>
@@ -23787,28 +23802,28 @@
         <v>757</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G2" s="25">
         <v>0</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="J2" s="23" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -23819,28 +23834,28 @@
         <v>761</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G3" s="25">
         <v>0</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="J3" s="23" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -23851,28 +23866,28 @@
         <v>764</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="G4" s="25">
         <v>0</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="J4" s="23" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -23883,28 +23898,28 @@
         <v>767</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G5" s="25">
         <v>0</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="J5" s="23" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -23915,28 +23930,28 @@
         <v>770</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G6" s="25">
         <v>0</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="J6" s="23" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -23947,28 +23962,28 @@
         <v>772</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G7" s="25">
         <v>0</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="J7" s="23" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -23979,28 +23994,28 @@
         <v>774</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G8" s="25">
         <v>0</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="J8" s="23" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -24011,28 +24026,28 @@
         <v>776</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G9" s="25">
         <v>1</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="J9" s="23" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -24043,28 +24058,28 @@
         <v>779</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G10" s="25">
         <v>2</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="J10" s="23" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -24075,28 +24090,28 @@
         <v>781</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G11" s="25">
         <v>3</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="J11" s="23" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -24107,28 +24122,28 @@
         <v>783</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G12" s="25">
         <v>4</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="J12" s="23" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -24139,28 +24154,28 @@
         <v>785</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G13" s="25">
         <v>5</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="J13" s="23" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -24171,28 +24186,28 @@
         <v>787</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G14" s="25">
         <v>6</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="J14" s="23" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -24203,28 +24218,28 @@
         <v>789</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="G15" s="25">
         <v>7</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="J15" s="23" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -24235,28 +24250,28 @@
         <v>791</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G16" s="25">
         <v>8</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="J16" s="23" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -24267,28 +24282,28 @@
         <v>793</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G17" s="25">
         <v>9</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="J17" s="23" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -24299,28 +24314,28 @@
         <v>795</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G18" s="25">
         <v>10</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="J18" s="23" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -24331,28 +24346,28 @@
         <v>797</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G19" s="25">
         <v>11</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="J19" s="23" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -24363,28 +24378,28 @@
         <v>799</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G20" s="25">
         <v>12</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="J20" s="23" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -24395,28 +24410,28 @@
         <v>801</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G21" s="25">
         <v>13</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="J21" s="23" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -24427,28 +24442,28 @@
         <v>803</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G22" s="25">
         <v>14</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="J22" s="23" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -24459,28 +24474,28 @@
         <v>805</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G23" s="25">
         <v>15</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="J23" s="23" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -24491,28 +24506,28 @@
         <v>807</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="G24" s="25">
         <v>16</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="J24" s="23" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -24523,28 +24538,28 @@
         <v>809</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G25" s="25">
         <v>17</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="J25" s="23" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -24555,28 +24570,28 @@
         <v>16</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G26" s="25">
         <v>18</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="J26" s="23" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -24587,28 +24602,28 @@
         <v>811</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G27" s="25">
         <v>19</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="J27" s="23" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -24619,28 +24634,28 @@
         <v>813</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G28" s="25">
         <v>20</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="J28" s="23" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -24651,28 +24666,28 @@
         <v>815</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G29" s="25">
         <v>21</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="J29" s="23" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -24683,28 +24698,28 @@
         <v>817</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G30" s="25">
         <v>22</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="J30" s="23" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -24715,28 +24730,28 @@
         <v>819</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="F31" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G31" s="25">
         <v>23</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="J31" s="23" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -24747,28 +24762,28 @@
         <v>821</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="G32" s="25">
         <v>24</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="J32" s="23" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -24779,28 +24794,28 @@
         <v>823</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F33" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G33" s="25">
         <v>25</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="J33" s="23" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -24811,28 +24826,28 @@
         <v>826</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F34" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G34" s="25">
         <v>26</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="J34" s="23" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -24843,28 +24858,28 @@
         <v>828</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G35" s="25">
         <v>27</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="J35" s="23" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -24875,28 +24890,28 @@
         <v>830</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F36" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G36" s="25">
         <v>28</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="J36" s="23" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -24907,28 +24922,28 @@
         <v>832</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F37" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G37" s="25">
         <v>29</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="J37" s="23" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -24939,28 +24954,28 @@
         <v>834</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G38" s="25">
         <v>30</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="J38" s="23" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -24971,28 +24986,28 @@
         <v>836</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="F39" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G39" s="25">
         <v>31</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="J39" s="23" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -25003,28 +25018,28 @@
         <v>838</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="F40" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G40" s="25">
         <v>32</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="J40" s="23" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -25035,28 +25050,28 @@
         <v>840</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="F41" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G41" s="25">
         <v>33</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="J41" s="23" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -25067,28 +25082,28 @@
         <v>842</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="F42" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G42" s="25">
         <v>34</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="J42" s="23" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -25099,2332 +25114,2332 @@
         <v>844</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F43" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G43" s="25">
         <v>35</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J43" s="23" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="10" t="s">
-        <v>591</v>
+        <v>846</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>290</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="F44" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G44" s="25">
         <v>36</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="J44" s="23" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="10" t="s">
+        <v>848</v>
+      </c>
+      <c r="B45" s="7" t="s">
         <v>847</v>
       </c>
-      <c r="B45" s="7" t="s">
-        <v>846</v>
-      </c>
       <c r="C45" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="F45" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G45" s="25">
         <v>37</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="J45" s="23" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="10" t="s">
+        <v>850</v>
+      </c>
+      <c r="B46" s="7" t="s">
         <v>849</v>
       </c>
-      <c r="B46" s="7" t="s">
-        <v>848</v>
-      </c>
       <c r="C46" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="F46" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G46" s="25">
         <v>38</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="J46" s="23" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="10" t="s">
+        <v>852</v>
+      </c>
+      <c r="B47" s="7" t="s">
         <v>851</v>
       </c>
-      <c r="B47" s="7" t="s">
-        <v>850</v>
-      </c>
       <c r="C47" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="F47" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G47" s="25">
         <v>39</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="J47" s="23" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="10" t="s">
+        <v>854</v>
+      </c>
+      <c r="B48" s="7" t="s">
         <v>853</v>
       </c>
-      <c r="B48" s="7" t="s">
-        <v>852</v>
-      </c>
       <c r="C48" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="F48" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G48" s="25">
         <v>40</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="J48" s="23" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="10" t="s">
+        <v>856</v>
+      </c>
+      <c r="B49" s="11" t="s">
         <v>855</v>
       </c>
-      <c r="B49" s="11" t="s">
-        <v>854</v>
-      </c>
       <c r="C49" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="F49" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G49" s="25">
         <v>41</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="J49" s="23" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="10" t="s">
+        <v>858</v>
+      </c>
+      <c r="B50" s="7" t="s">
         <v>857</v>
       </c>
-      <c r="B50" s="7" t="s">
-        <v>856</v>
-      </c>
       <c r="C50" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F50" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G50" s="25">
         <v>42</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="J50" s="23" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="10" t="s">
+        <v>860</v>
+      </c>
+      <c r="B51" s="7" t="s">
         <v>859</v>
       </c>
-      <c r="B51" s="7" t="s">
-        <v>858</v>
-      </c>
       <c r="C51" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F51" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G51" s="25">
         <v>43</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="J51" s="23" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="10" t="s">
+        <v>862</v>
+      </c>
+      <c r="B52" s="7" t="s">
         <v>861</v>
       </c>
-      <c r="B52" s="7" t="s">
-        <v>860</v>
-      </c>
       <c r="C52" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="F52" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G52" s="25">
         <v>44</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="J52" s="23" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="10" t="s">
+        <v>864</v>
+      </c>
+      <c r="B53" s="7" t="s">
         <v>863</v>
       </c>
-      <c r="B53" s="7" t="s">
-        <v>862</v>
-      </c>
       <c r="C53" s="7" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="G53" s="25">
         <v>45</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="J53" s="23" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="10" t="s">
+        <v>866</v>
+      </c>
+      <c r="B54" s="7" t="s">
         <v>865</v>
       </c>
-      <c r="B54" s="7" t="s">
-        <v>864</v>
-      </c>
       <c r="C54" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F54" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G54" s="25">
         <v>46</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I54" s="7" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="J54" s="23" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="10" t="s">
+        <v>868</v>
+      </c>
+      <c r="B55" s="7" t="s">
         <v>867</v>
       </c>
-      <c r="B55" s="7" t="s">
-        <v>866</v>
-      </c>
       <c r="C55" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="F55" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G55" s="25">
         <v>47</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="J55" s="23" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="10" t="s">
+        <v>870</v>
+      </c>
+      <c r="B56" s="7" t="s">
         <v>869</v>
       </c>
-      <c r="B56" s="7" t="s">
-        <v>868</v>
-      </c>
       <c r="C56" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F56" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G56" s="25">
         <v>48</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I56" s="7" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="J56" s="23" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="10" t="s">
+        <v>872</v>
+      </c>
+      <c r="B57" s="7" t="s">
         <v>871</v>
       </c>
-      <c r="B57" s="7" t="s">
-        <v>870</v>
-      </c>
       <c r="C57" s="7" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="F57" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G57" s="25">
         <v>49</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="J57" s="23" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="10" t="s">
+        <v>874</v>
+      </c>
+      <c r="B58" s="7" t="s">
         <v>873</v>
       </c>
-      <c r="B58" s="7" t="s">
-        <v>872</v>
-      </c>
       <c r="C58" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="G58" s="25">
         <v>50</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I58" s="7" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="J58" s="23" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="10" t="s">
+        <v>876</v>
+      </c>
+      <c r="B59" s="7" t="s">
         <v>875</v>
       </c>
-      <c r="B59" s="7" t="s">
-        <v>874</v>
-      </c>
       <c r="C59" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="F59" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G59" s="25">
         <v>51</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I59" s="7" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="J59" s="23" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="10" t="s">
+        <v>878</v>
+      </c>
+      <c r="B60" s="7" t="s">
         <v>877</v>
       </c>
-      <c r="B60" s="7" t="s">
-        <v>876</v>
-      </c>
       <c r="C60" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F60" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G60" s="25">
         <v>52</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I60" s="7" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="J60" s="23" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="10" t="s">
+        <v>880</v>
+      </c>
+      <c r="B61" s="7" t="s">
         <v>879</v>
       </c>
-      <c r="B61" s="7" t="s">
-        <v>878</v>
-      </c>
       <c r="C61" s="7" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F61" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G61" s="25">
         <v>53</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I61" s="7" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="J61" s="48" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="10" t="s">
+        <v>882</v>
+      </c>
+      <c r="B62" s="7" t="s">
         <v>881</v>
       </c>
-      <c r="B62" s="7" t="s">
-        <v>880</v>
-      </c>
       <c r="C62" s="7" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="F62" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G62" s="25">
         <v>54</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I62" s="7" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="J62" s="23" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="10" t="s">
+        <v>884</v>
+      </c>
+      <c r="B63" s="7" t="s">
         <v>883</v>
       </c>
-      <c r="B63" s="7" t="s">
-        <v>882</v>
-      </c>
       <c r="C63" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="F63" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G63" s="25">
         <v>55</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I63" s="7" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="J63" s="23" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="10" t="s">
+        <v>886</v>
+      </c>
+      <c r="B64" s="7" t="s">
         <v>885</v>
       </c>
-      <c r="B64" s="7" t="s">
-        <v>884</v>
-      </c>
       <c r="C64" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F64" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G64" s="25">
         <v>56</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I64" s="7" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="J64" s="23" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="10" t="s">
+        <v>888</v>
+      </c>
+      <c r="B65" s="7" t="s">
         <v>887</v>
       </c>
-      <c r="B65" s="7" t="s">
-        <v>886</v>
-      </c>
       <c r="C65" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F65" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G65" s="25">
         <v>57</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I65" s="7" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="J65" s="23" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="10" t="s">
+        <v>890</v>
+      </c>
+      <c r="B66" s="7" t="s">
         <v>889</v>
       </c>
-      <c r="B66" s="7" t="s">
-        <v>888</v>
-      </c>
       <c r="C66" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F66" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G66" s="25">
         <v>58</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I66" s="7" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="J66" s="23" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="10" t="s">
+        <v>892</v>
+      </c>
+      <c r="B67" s="7" t="s">
         <v>891</v>
       </c>
-      <c r="B67" s="7" t="s">
-        <v>890</v>
-      </c>
       <c r="C67" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="F67" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G67" s="25">
         <v>59</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I67" s="7" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="J67" s="23" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="10" t="s">
+        <v>894</v>
+      </c>
+      <c r="B68" s="7" t="s">
         <v>893</v>
       </c>
-      <c r="B68" s="7" t="s">
-        <v>892</v>
-      </c>
       <c r="C68" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="F68" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G68" s="25">
         <v>60</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I68" s="7" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="J68" s="23" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="10" t="s">
+        <v>896</v>
+      </c>
+      <c r="B69" s="7" t="s">
         <v>895</v>
       </c>
-      <c r="B69" s="7" t="s">
-        <v>894</v>
-      </c>
       <c r="C69" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="F69" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G69" s="25">
         <v>61</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I69" s="7" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="J69" s="23" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="10" t="s">
+        <v>898</v>
+      </c>
+      <c r="B70" s="7" t="s">
         <v>897</v>
       </c>
-      <c r="B70" s="7" t="s">
-        <v>896</v>
-      </c>
       <c r="C70" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F70" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G70" s="25">
         <v>62</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I70" s="7" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="J70" s="23" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="10" t="s">
+        <v>900</v>
+      </c>
+      <c r="B71" s="7" t="s">
         <v>899</v>
       </c>
-      <c r="B71" s="7" t="s">
-        <v>898</v>
-      </c>
       <c r="C71" s="7" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F71" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G71" s="25">
         <v>63</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I71" s="7" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="J71" s="23" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="10" t="s">
+        <v>902</v>
+      </c>
+      <c r="B72" s="7" t="s">
         <v>901</v>
       </c>
-      <c r="B72" s="7" t="s">
-        <v>900</v>
-      </c>
       <c r="C72" s="7" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="F72" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G72" s="25">
         <v>64</v>
       </c>
       <c r="H72" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I72" s="7" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="J72" s="23" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="10" t="s">
+        <v>904</v>
+      </c>
+      <c r="B73" s="7" t="s">
         <v>903</v>
       </c>
-      <c r="B73" s="7" t="s">
-        <v>902</v>
-      </c>
       <c r="C73" s="7" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="F73" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G73" s="25">
         <v>65</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I73" s="7" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="J73" s="23" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" s="10" t="s">
+        <v>906</v>
+      </c>
+      <c r="B74" s="7" t="s">
         <v>905</v>
       </c>
-      <c r="B74" s="7" t="s">
-        <v>904</v>
-      </c>
       <c r="C74" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="F74" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G74" s="25">
         <v>66</v>
       </c>
       <c r="H74" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I74" s="7" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="J74" s="23" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" s="10" t="s">
+        <v>908</v>
+      </c>
+      <c r="B75" s="7" t="s">
         <v>907</v>
       </c>
-      <c r="B75" s="7" t="s">
-        <v>906</v>
-      </c>
       <c r="C75" s="11" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="F75" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G75" s="25">
         <v>67</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I75" s="7" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="10" t="s">
+        <v>910</v>
+      </c>
+      <c r="B76" s="7" t="s">
         <v>909</v>
       </c>
-      <c r="B76" s="7" t="s">
-        <v>908</v>
-      </c>
       <c r="C76" s="11" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="F76" s="25" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="G76" s="25">
         <v>68</v>
       </c>
       <c r="H76" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I76" s="7" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="J76" s="48" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="10" t="s">
+        <v>912</v>
+      </c>
+      <c r="B77" s="11" t="s">
         <v>911</v>
       </c>
-      <c r="B77" s="11" t="s">
-        <v>910</v>
-      </c>
       <c r="C77" s="11" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="F77" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G77" s="25">
         <v>69</v>
       </c>
       <c r="H77" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I77" s="7" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="J77" s="48" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="7" t="s">
+        <v>914</v>
+      </c>
+      <c r="B78" s="7" t="s">
         <v>913</v>
       </c>
-      <c r="B78" s="7" t="s">
-        <v>912</v>
-      </c>
       <c r="C78" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="F78" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G78" s="25">
         <v>70</v>
       </c>
       <c r="H78" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I78" s="7" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="10" t="s">
+        <v>916</v>
+      </c>
+      <c r="B79" s="7" t="s">
         <v>915</v>
       </c>
-      <c r="B79" s="7" t="s">
-        <v>914</v>
-      </c>
       <c r="C79" s="7" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="F79" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G79" s="25">
         <v>71</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I79" s="7" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="10" t="s">
+        <v>918</v>
+      </c>
+      <c r="B80" s="7" t="s">
         <v>917</v>
       </c>
-      <c r="B80" s="7" t="s">
-        <v>916</v>
-      </c>
       <c r="C80" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="F80" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G80" s="25">
         <v>72</v>
       </c>
       <c r="H80" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I80" s="7" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="10" t="s">
+        <v>920</v>
+      </c>
+      <c r="B81" s="11" t="s">
         <v>919</v>
       </c>
-      <c r="B81" s="11" t="s">
-        <v>918</v>
-      </c>
       <c r="C81" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="F81" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G81" s="25">
         <v>73</v>
       </c>
       <c r="H81" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I81" s="7" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="10" t="s">
+        <v>922</v>
+      </c>
+      <c r="B82" s="7" t="s">
         <v>921</v>
       </c>
-      <c r="B82" s="7" t="s">
-        <v>920</v>
-      </c>
       <c r="C82" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F82" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G82" s="25">
         <v>74</v>
       </c>
       <c r="H82" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I82" s="7" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="10" t="s">
+        <v>924</v>
+      </c>
+      <c r="B83" s="7" t="s">
         <v>923</v>
       </c>
-      <c r="B83" s="7" t="s">
-        <v>922</v>
-      </c>
       <c r="C83" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="F83" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G83" s="25">
         <v>75</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I83" s="7" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="J83" s="23" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="10" t="s">
+        <v>926</v>
+      </c>
+      <c r="B84" s="7" t="s">
         <v>925</v>
       </c>
-      <c r="B84" s="7" t="s">
-        <v>924</v>
-      </c>
       <c r="C84" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="F84" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G84" s="25">
         <v>76</v>
       </c>
       <c r="H84" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I84" s="7" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="J84" s="23" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="10" t="s">
+        <v>928</v>
+      </c>
+      <c r="B85" s="7" t="s">
         <v>927</v>
       </c>
-      <c r="B85" s="7" t="s">
-        <v>926</v>
-      </c>
       <c r="C85" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F85" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G85" s="25">
         <v>77</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I85" s="7" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="J85" s="23" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="B86" s="7" t="s">
         <v>929</v>
       </c>
-      <c r="B86" s="7" t="s">
-        <v>928</v>
-      </c>
       <c r="C86" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="F86" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G86" s="25">
         <v>78</v>
       </c>
       <c r="H86" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I86" s="7" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="J86" s="23" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="10" t="s">
+        <v>932</v>
+      </c>
+      <c r="B87" s="7" t="s">
         <v>931</v>
       </c>
-      <c r="B87" s="7" t="s">
-        <v>930</v>
-      </c>
       <c r="C87" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="F87" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G87" s="25">
         <v>79</v>
       </c>
       <c r="H87" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I87" s="7" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="J87" s="23" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="B88" s="7" t="s">
         <v>933</v>
       </c>
-      <c r="B88" s="7" t="s">
-        <v>932</v>
-      </c>
       <c r="C88" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="F88" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G88" s="25">
         <v>80</v>
       </c>
       <c r="H88" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I88" s="7" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="J88" s="23" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="10" t="s">
+        <v>936</v>
+      </c>
+      <c r="B89" s="7" t="s">
         <v>935</v>
       </c>
-      <c r="B89" s="7" t="s">
-        <v>934</v>
-      </c>
       <c r="C89" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="F89" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G89" s="25">
         <v>81</v>
       </c>
       <c r="H89" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I89" s="7" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="J89" s="48" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="10" t="s">
+        <v>938</v>
+      </c>
+      <c r="B90" s="7" t="s">
         <v>937</v>
       </c>
-      <c r="B90" s="7" t="s">
-        <v>936</v>
-      </c>
       <c r="C90" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="F90" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G90" s="25">
         <v>82</v>
       </c>
       <c r="H90" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I90" s="7" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="J90" s="23" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="10" t="s">
+        <v>940</v>
+      </c>
+      <c r="B91" s="7" t="s">
         <v>939</v>
       </c>
-      <c r="B91" s="7" t="s">
-        <v>938</v>
-      </c>
       <c r="C91" s="7" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="F91" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G91" s="25">
         <v>83</v>
       </c>
       <c r="H91" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I91" s="7" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="J91" s="23" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="10" t="s">
+        <v>942</v>
+      </c>
+      <c r="B92" s="7" t="s">
         <v>941</v>
       </c>
-      <c r="B92" s="7" t="s">
-        <v>940</v>
-      </c>
       <c r="C92" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F92" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G92" s="25">
         <v>84</v>
       </c>
       <c r="H92" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I92" s="7" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="J92" s="23" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="10" t="s">
+        <v>944</v>
+      </c>
+      <c r="B93" s="7" t="s">
         <v>943</v>
       </c>
-      <c r="B93" s="7" t="s">
-        <v>942</v>
-      </c>
       <c r="C93" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="F93" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G93" s="25">
         <v>85</v>
       </c>
       <c r="H93" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I93" s="7" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="J93" s="23" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" s="10" t="s">
+        <v>946</v>
+      </c>
+      <c r="B94" s="7" t="s">
         <v>945</v>
       </c>
-      <c r="B94" s="7" t="s">
-        <v>944</v>
-      </c>
       <c r="C94" s="7" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="F94" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G94" s="25">
         <v>86</v>
       </c>
       <c r="H94" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I94" s="7" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="J94" s="23" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="10" t="s">
+        <v>948</v>
+      </c>
+      <c r="B95" s="11" t="s">
         <v>947</v>
       </c>
-      <c r="B95" s="11" t="s">
-        <v>946</v>
-      </c>
       <c r="C95" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="F95" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G95" s="25">
         <v>87</v>
       </c>
       <c r="H95" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I95" s="7" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="J95" s="48" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="10" t="s">
+        <v>950</v>
+      </c>
+      <c r="B96" s="7" t="s">
         <v>949</v>
       </c>
-      <c r="B96" s="7" t="s">
-        <v>948</v>
-      </c>
       <c r="C96" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="F96" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G96" s="25">
         <v>88</v>
       </c>
       <c r="H96" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I96" s="7" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="J96" s="23" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="97" spans="1:10">
       <c r="A97" s="10" t="s">
+        <v>952</v>
+      </c>
+      <c r="B97" s="11" t="s">
         <v>951</v>
       </c>
-      <c r="B97" s="11" t="s">
-        <v>950</v>
-      </c>
       <c r="C97" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="F97" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G97" s="25">
         <v>89</v>
       </c>
       <c r="H97" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I97" s="7" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="J97" s="23" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="98" spans="1:10">
       <c r="A98" s="10" t="s">
+        <v>954</v>
+      </c>
+      <c r="B98" s="7" t="s">
         <v>953</v>
       </c>
-      <c r="B98" s="7" t="s">
-        <v>952</v>
-      </c>
       <c r="C98" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="G98" s="25">
         <v>90</v>
       </c>
       <c r="H98" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I98" s="7" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="J98" s="23" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="99" spans="1:10">
       <c r="A99" s="10" t="s">
+        <v>956</v>
+      </c>
+      <c r="B99" s="7" t="s">
         <v>955</v>
       </c>
-      <c r="B99" s="7" t="s">
-        <v>954</v>
-      </c>
       <c r="C99" s="7" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="F99" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G99" s="25">
         <v>91</v>
       </c>
       <c r="H99" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I99" s="7" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="J99" s="23" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="100" spans="1:10">
       <c r="A100" s="7" t="s">
+        <v>958</v>
+      </c>
+      <c r="B100" s="7" t="s">
         <v>957</v>
       </c>
-      <c r="B100" s="7" t="s">
-        <v>956</v>
-      </c>
       <c r="C100" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="F100" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G100" s="25">
         <v>92</v>
       </c>
       <c r="H100" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I100" s="7" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="J100" s="23" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="101" spans="1:10">
       <c r="A101" s="10" t="s">
+        <v>960</v>
+      </c>
+      <c r="B101" s="7" t="s">
         <v>959</v>
       </c>
-      <c r="B101" s="7" t="s">
-        <v>958</v>
-      </c>
       <c r="C101" s="7" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="G101" s="25">
         <v>93</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I101" s="7" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="J101" s="49" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="102" spans="1:10">
       <c r="A102" s="10" t="s">
+        <v>962</v>
+      </c>
+      <c r="B102" s="7" t="s">
         <v>961</v>
       </c>
-      <c r="B102" s="7" t="s">
-        <v>960</v>
-      </c>
       <c r="C102" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="F102" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G102" s="25">
         <v>94</v>
       </c>
       <c r="H102" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I102" s="7" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="J102" s="23" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="103" spans="1:10">
       <c r="A103" s="10" t="s">
+        <v>964</v>
+      </c>
+      <c r="B103" s="7" t="s">
         <v>963</v>
       </c>
-      <c r="B103" s="7" t="s">
-        <v>962</v>
-      </c>
       <c r="C103" s="11" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="F103" s="25" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="G103" s="25">
         <v>95</v>
       </c>
       <c r="H103" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I103" s="7" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="J103" s="23" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="104" spans="1:10">
       <c r="A104" s="10" t="s">
+        <v>966</v>
+      </c>
+      <c r="B104" s="7" t="s">
         <v>965</v>
       </c>
-      <c r="B104" s="7" t="s">
-        <v>964</v>
-      </c>
       <c r="C104" s="7" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="F104" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G104" s="25">
         <v>96</v>
       </c>
       <c r="H104" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I104" s="7" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="J104" s="23" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="105" spans="1:10">
       <c r="A105" s="10" t="s">
+        <v>968</v>
+      </c>
+      <c r="B105" s="7" t="s">
         <v>967</v>
       </c>
-      <c r="B105" s="7" t="s">
-        <v>966</v>
-      </c>
       <c r="C105" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="F105" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G105" s="25">
         <v>97</v>
       </c>
       <c r="H105" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I105" s="7" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="J105" s="23" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="106" spans="1:10">
       <c r="A106" s="10" t="s">
+        <v>970</v>
+      </c>
+      <c r="B106" s="7" t="s">
         <v>969</v>
       </c>
-      <c r="B106" s="7" t="s">
-        <v>968</v>
-      </c>
       <c r="C106" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="F106" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G106" s="25">
         <v>98</v>
       </c>
       <c r="H106" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I106" s="7" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="J106" s="23" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="107" spans="1:10">
       <c r="A107" s="10" t="s">
+        <v>972</v>
+      </c>
+      <c r="B107" s="7" t="s">
         <v>971</v>
       </c>
-      <c r="B107" s="7" t="s">
-        <v>970</v>
-      </c>
       <c r="C107" s="7" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="F107" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G107" s="25">
         <v>99</v>
       </c>
       <c r="H107" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I107" s="7" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="J107" s="23" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="108" spans="1:10">
       <c r="A108" s="10" t="s">
+        <v>974</v>
+      </c>
+      <c r="B108" s="7" t="s">
         <v>973</v>
       </c>
-      <c r="B108" s="7" t="s">
-        <v>972</v>
-      </c>
       <c r="C108" s="7" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="F108" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G108" s="25">
         <v>100</v>
       </c>
       <c r="H108" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I108" s="7" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="J108" s="23" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="109" spans="1:10">
       <c r="A109" s="10" t="s">
+        <v>976</v>
+      </c>
+      <c r="B109" s="7" t="s">
         <v>975</v>
       </c>
-      <c r="B109" s="7" t="s">
-        <v>974</v>
-      </c>
       <c r="C109" s="7" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="F109" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G109" s="25">
         <v>101</v>
       </c>
       <c r="H109" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I109" s="7" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="J109" s="49" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="110" spans="1:10">
       <c r="A110" s="10" t="s">
+        <v>978</v>
+      </c>
+      <c r="B110" s="7" t="s">
         <v>977</v>
       </c>
-      <c r="B110" s="7" t="s">
-        <v>976</v>
-      </c>
       <c r="C110" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="F110" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G110" s="25">
         <v>102</v>
       </c>
       <c r="H110" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I110" s="7" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="J110" s="23" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="111" spans="1:10">
       <c r="A111" s="10" t="s">
+        <v>980</v>
+      </c>
+      <c r="B111" s="7" t="s">
         <v>979</v>
       </c>
-      <c r="B111" s="7" t="s">
-        <v>978</v>
-      </c>
       <c r="C111" s="7" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="F111" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G111" s="25">
         <v>103</v>
       </c>
       <c r="H111" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I111" s="7" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="J111" s="23" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="112" spans="1:10">
       <c r="A112" s="10" t="s">
+        <v>982</v>
+      </c>
+      <c r="B112" s="11" t="s">
         <v>981</v>
       </c>
-      <c r="B112" s="11" t="s">
-        <v>980</v>
-      </c>
       <c r="C112" s="11" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="F112" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G112" s="25">
         <v>104</v>
       </c>
       <c r="H112" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I112" s="7" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="J112" s="48" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="113" spans="1:10">
       <c r="A113" s="10" t="s">
+        <v>985</v>
+      </c>
+      <c r="B113" s="7" t="s">
         <v>984</v>
       </c>
-      <c r="B113" s="7" t="s">
-        <v>983</v>
-      </c>
       <c r="C113" s="11" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F113" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G113" s="25">
         <v>105</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I113" s="7" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="J113" s="48" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="114" spans="1:10">
       <c r="A114" s="10" t="s">
+        <v>987</v>
+      </c>
+      <c r="B114" s="7" t="s">
         <v>986</v>
       </c>
-      <c r="B114" s="7" t="s">
-        <v>985</v>
-      </c>
       <c r="C114" s="7" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="F114" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G114" s="25">
         <v>106</v>
       </c>
       <c r="H114" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I114" s="7" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="J114" s="23" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="115" spans="1:10">
       <c r="A115" s="10" t="s">
+        <v>989</v>
+      </c>
+      <c r="B115" s="7" t="s">
         <v>988</v>
       </c>
-      <c r="B115" s="7" t="s">
-        <v>987</v>
-      </c>
       <c r="C115" s="7" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="F115" s="25" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G115" s="25">
         <v>107</v>
       </c>
       <c r="H115" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I115" s="7" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="J115" s="23" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="117" spans="1:10">
@@ -27833,13 +27848,13 @@
         <v>385</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>259</v>
@@ -27850,13 +27865,13 @@
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>37</v>
@@ -27868,13 +27883,13 @@
     </row>
     <row r="3" spans="1:6" ht="18" customHeight="1">
       <c r="A3" s="7" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7">
@@ -27884,13 +27899,13 @@
     </row>
     <row r="4" spans="1:6" ht="18" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="7">
@@ -27903,13 +27918,13 @@
         <v>391</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>254</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="E5" s="7">
         <v>3</v>
@@ -27921,13 +27936,13 @@
         <v>638</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="E6" s="7">
         <v>4</v>
@@ -27939,13 +27954,13 @@
         <v>643</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="E7" s="7">
         <v>5</v>
@@ -27957,13 +27972,13 @@
         <v>653</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="E8" s="7">
         <v>6</v>
@@ -27975,10 +27990,10 @@
         <v>661</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="7">
@@ -27991,13 +28006,13 @@
         <v>666</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="E10" s="7">
         <v>8</v>
@@ -28009,10 +28024,10 @@
         <v>658</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7">
@@ -28025,13 +28040,13 @@
         <v>715</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="E12" s="7">
         <v>10</v>
@@ -28043,13 +28058,13 @@
         <v>692</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="E13" s="7">
         <v>12</v>
@@ -28061,13 +28076,13 @@
         <v>673</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="E14" s="7">
         <v>11</v>
@@ -28079,13 +28094,13 @@
         <v>727</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="E15" s="7">
         <v>13</v>
@@ -28097,13 +28112,13 @@
         <v>712</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="E16" s="7">
         <v>14</v>
@@ -28115,13 +28130,13 @@
         <v>724</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="E17" s="7">
         <v>15</v>
@@ -28133,13 +28148,13 @@
         <v>709</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="E18" s="7">
         <v>16</v>
@@ -28151,13 +28166,13 @@
         <v>697</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="E19" s="7">
         <v>17</v>
@@ -28169,13 +28184,13 @@
         <v>650</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="E20" s="7">
         <v>18</v>
@@ -28187,13 +28202,13 @@
         <v>743</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="E21" s="7">
         <v>19</v>
@@ -28205,13 +28220,13 @@
         <v>732</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="E22" s="7">
         <v>20</v>
@@ -28223,13 +28238,13 @@
         <v>700</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="E23" s="7">
         <v>21</v>

--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84624A44-AB60-44D7-A338-64264C76A711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F98B36A1-64C4-4D55-8AB0-0871A9B003EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5303" uniqueCount="1405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5303" uniqueCount="1404">
   <si>
     <t>NpcID</t>
   </si>
@@ -161,6 +161,18 @@
     <t>陆忠</t>
   </si>
   <si>
+    <t>wu_shi_liang</t>
+  </si>
+  <si>
+    <t>吴世良</t>
+  </si>
+  <si>
+    <t>ya_yi</t>
+  </si>
+  <si>
+    <t>衙役</t>
+  </si>
+  <si>
     <t>xing_kong</t>
   </si>
   <si>
@@ -179,12 +191,6 @@
     <t>杨素娘</t>
   </si>
   <si>
-    <t>wu_shi_liang</t>
-  </si>
-  <si>
-    <t>吴世良</t>
-  </si>
-  <si>
     <t>cao_wang</t>
   </si>
   <si>
@@ -1490,9 +1496,6 @@
     <t>别乱说，快去吧他吐的收拾收拾，还有病患要看病呢。</t>
   </si>
   <si>
-    <t>衙役</t>
-  </si>
-  <si>
     <t>李大夫，知州大人请您去州衙有事商议。</t>
   </si>
   <si>
@@ -1656,9 +1659,6 @@
   </si>
   <si>
     <t>是在下唐突了。</t>
-  </si>
-  <si>
-    <t>无妨，您和令尊医术高明</t>
   </si>
   <si>
     <t>DiseaseID</t>
@@ -6528,11 +6528,7 @@
 在搜索栏输入药材，方剂，疾病的中文名或拼音，拼音首字母可快速查找。</t>
   </si>
   <si>
-    <t>衙役</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>ya_yi</t>
+    <t>无妨，您和令尊医术高明，赈灾药材用的是什么方子想必心里有数。</t>
     <phoneticPr fontId="14"/>
   </si>
 </sst>
@@ -6913,10 +6909,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -8830,8 +8826,8 @@
     <col min="7" max="7" width="25.125" style="23" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.25" style="23" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="33.375" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="54" width="9.125" style="23" customWidth="1"/>
-    <col min="55" max="16384" width="9.125" style="23"/>
+    <col min="10" max="55" width="9.125" style="23" customWidth="1"/>
+    <col min="56" max="16384" width="9.125" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.399999999999999" customHeight="1">
@@ -9138,10 +9134,10 @@
     </row>
     <row r="15" spans="1:9" ht="18" customHeight="1">
       <c r="A15" s="7" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>11</v>
@@ -9159,10 +9155,10 @@
     </row>
     <row r="16" spans="1:9" ht="18" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>1404</v>
+        <v>40</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>1403</v>
+        <v>41</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>11</v>
@@ -9180,10 +9176,10 @@
     </row>
     <row r="17" spans="1:9" ht="18" customHeight="1">
       <c r="A17" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>11</v>
@@ -9201,10 +9197,10 @@
     </row>
     <row r="18" spans="1:9" ht="18" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>11</v>
@@ -9222,10 +9218,10 @@
     </row>
     <row r="19" spans="1:9" ht="18" customHeight="1">
       <c r="A19" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>11</v>
@@ -9243,10 +9239,10 @@
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1">
       <c r="A20" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>11</v>
@@ -9264,13 +9260,13 @@
     </row>
     <row r="21" spans="1:9" ht="18" customHeight="1">
       <c r="A21" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>12</v>
@@ -9279,27 +9275,27 @@
         <v>44</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G21" s="43" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="18" customHeight="1">
       <c r="A22" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>21</v>
@@ -9308,27 +9304,27 @@
         <v>46</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G22" s="43" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="18" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>12</v>
@@ -9337,27 +9333,27 @@
         <v>62</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G23" s="43" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="18" customHeight="1">
       <c r="A24" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>21</v>
@@ -9366,27 +9362,27 @@
         <v>76</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G24" s="43" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="18" customHeight="1">
       <c r="A25" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>12</v>
@@ -9395,27 +9391,27 @@
         <v>24</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G25" s="43" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="18" customHeight="1">
       <c r="A26" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>21</v>
@@ -9424,27 +9420,27 @@
         <v>18</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G26" s="43" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="18" customHeight="1">
       <c r="A27" s="7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>12</v>
@@ -9453,27 +9449,27 @@
         <v>41</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G27" s="43" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="18" customHeight="1">
       <c r="A28" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>12</v>
@@ -9482,27 +9478,27 @@
         <v>43</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G28" s="43" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="18" customHeight="1">
       <c r="A29" s="7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>12</v>
@@ -9511,27 +9507,27 @@
         <v>34</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G29" s="43" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="18" customHeight="1">
       <c r="A30" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>21</v>
@@ -9540,27 +9536,27 @@
         <v>32</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G30" s="43" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="18" customHeight="1">
       <c r="A31" s="7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>12</v>
@@ -9569,27 +9565,27 @@
         <v>31</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G31" s="43" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="18" customHeight="1">
       <c r="A32" s="7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>12</v>
@@ -9598,27 +9594,27 @@
         <v>25</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G32" s="43" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="18" customHeight="1">
       <c r="A33" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>12</v>
@@ -9627,27 +9623,27 @@
         <v>48</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G33" s="43" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="18" customHeight="1">
       <c r="A34" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>12</v>
@@ -9656,27 +9652,27 @@
         <v>16</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G34" s="43" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="18" customHeight="1">
       <c r="A35" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>12</v>
@@ -9685,27 +9681,27 @@
         <v>30</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G35" s="43" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="18" customHeight="1">
       <c r="A36" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>21</v>
@@ -9714,27 +9710,27 @@
         <v>39</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G36" s="43" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="18" customHeight="1">
       <c r="A37" s="7" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>12</v>
@@ -9743,27 +9739,27 @@
         <v>68</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G37" s="43" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="18" customHeight="1">
       <c r="A38" s="7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>21</v>
@@ -9772,27 +9768,27 @@
         <v>61</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G38" s="43" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="18" customHeight="1">
       <c r="A39" s="7" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>12</v>
@@ -9801,27 +9797,27 @@
         <v>36</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G39" s="43" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="18" customHeight="1">
       <c r="A40" s="7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>12</v>
@@ -9830,27 +9826,27 @@
         <v>33</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G40" s="43" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="18" customHeight="1">
       <c r="A41" s="7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>12</v>
@@ -9859,27 +9855,27 @@
         <v>82</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G41" s="43" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="18" customHeight="1">
       <c r="A42" s="7" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>12</v>
@@ -9888,27 +9884,27 @@
         <v>40</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G42" s="43" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="18" customHeight="1">
       <c r="A43" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>21</v>
@@ -9917,27 +9913,27 @@
         <v>49</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G43" s="43" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="18" customHeight="1">
       <c r="A44" s="7" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D44" s="7" t="s">
         <v>12</v>
@@ -9946,27 +9942,27 @@
         <v>26</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G44" s="43" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="18" customHeight="1">
       <c r="A45" s="7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>21</v>
@@ -9975,27 +9971,27 @@
         <v>22</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G45" s="43" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="18" customHeight="1">
       <c r="A46" s="7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>21</v>
@@ -10004,27 +10000,27 @@
         <v>80</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G46" s="43" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="18" customHeight="1">
       <c r="A47" s="7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>12</v>
@@ -10033,27 +10029,27 @@
         <v>41</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G47" s="43" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="18" customHeight="1">
       <c r="A48" s="7" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>12</v>
@@ -10062,27 +10058,27 @@
         <v>42</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G48" s="43" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="18" customHeight="1">
       <c r="A49" s="7" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>21</v>
@@ -10091,27 +10087,27 @@
         <v>14</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G49" s="43" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="18" customHeight="1">
       <c r="A50" s="7" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>12</v>
@@ -10120,27 +10116,27 @@
         <v>38</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G50" s="43" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="18" customHeight="1">
       <c r="A51" s="7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>12</v>
@@ -10149,27 +10145,27 @@
         <v>43</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G51" s="43" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="18" customHeight="1">
       <c r="A52" s="7" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>21</v>
@@ -10178,27 +10174,27 @@
         <v>44</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G52" s="43" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="18" customHeight="1">
       <c r="A53" s="7" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>12</v>
@@ -10207,27 +10203,27 @@
         <v>27</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G53" s="43" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="18" customHeight="1">
       <c r="A54" s="7" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B54" s="46" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>21</v>
@@ -10236,27 +10232,27 @@
         <v>18</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G54" s="43" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I54" s="7" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="18" customHeight="1">
       <c r="A55" s="7" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>21</v>
@@ -10265,27 +10261,27 @@
         <v>22</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G55" s="43" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="18" customHeight="1">
       <c r="A56" s="7" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D56" s="7" t="s">
         <v>21</v>
@@ -10294,27 +10290,27 @@
         <v>23</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G56" s="43" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I56" s="7" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="18" customHeight="1">
       <c r="A57" s="7" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>21</v>
@@ -10323,27 +10319,27 @@
         <v>45</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G57" s="43" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="18" customHeight="1">
       <c r="A58" s="7" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D58" s="7" t="s">
         <v>12</v>
@@ -10352,27 +10348,27 @@
         <v>18</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G58" s="43" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I58" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="18" customHeight="1">
       <c r="A59" s="7" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D59" s="7" t="s">
         <v>21</v>
@@ -10381,27 +10377,27 @@
         <v>28</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G59" s="43" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I59" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="18" customHeight="1">
       <c r="A60" s="7" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D60" s="7" t="s">
         <v>12</v>
@@ -10410,27 +10406,27 @@
         <v>51</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G60" s="43" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I60" s="7" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="18" customHeight="1">
       <c r="A61" s="7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B61" s="46" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D61" s="7" t="s">
         <v>12</v>
@@ -10439,27 +10435,27 @@
         <v>47</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G61" s="43" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I61" s="7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="18" customHeight="1">
       <c r="A62" s="7" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D62" s="7" t="s">
         <v>12</v>
@@ -10468,27 +10464,27 @@
         <v>21</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G62" s="43" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I62" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="18" customHeight="1">
       <c r="A63" s="7" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D63" s="7" t="s">
         <v>21</v>
@@ -10497,27 +10493,27 @@
         <v>52</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="G63" s="43" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I63" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="18" customHeight="1">
       <c r="A64" s="7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D64" s="7" t="s">
         <v>12</v>
@@ -10526,27 +10522,27 @@
         <v>53</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G64" s="43" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I64" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="18" customHeight="1">
       <c r="A65" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D65" s="7" t="s">
         <v>12</v>
@@ -10555,16 +10551,16 @@
         <v>49</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G65" s="43" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I65" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="18" customHeight="1">
@@ -10709,7 +10705,7 @@
         <v>1395</v>
       </c>
       <c r="C1" s="42" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>542</v>
@@ -10866,75 +10862,75 @@
     <col min="14" max="14" width="12" style="36" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.75" style="36" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10.875" style="36" bestFit="1" customWidth="1"/>
-    <col min="17" max="77" width="9" style="36" customWidth="1"/>
-    <col min="78" max="16384" width="9" style="36"/>
+    <col min="17" max="78" width="9" style="36" customWidth="1"/>
+    <col min="79" max="16384" width="9" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="41" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B1" s="39" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C1" s="39" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D1" s="39" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E1" s="39" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F1" s="60" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="G1" s="60" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H1" s="60" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I1" s="60" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J1" s="61" t="s">
         <v>0</v>
       </c>
       <c r="K1" s="61" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L1" s="64" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="M1" s="64" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="N1" s="64" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="O1" s="65" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="P1" s="65" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="37" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D2" s="37" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="37" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F2" s="37">
         <v>1</v>
@@ -10956,19 +10952,19 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="37" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B3" s="37" t="s">
+        <v>274</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>270</v>
+      </c>
+      <c r="D3" s="37" t="s">
         <v>272</v>
       </c>
-      <c r="C3" s="37" t="s">
-        <v>268</v>
-      </c>
-      <c r="D3" s="37" t="s">
-        <v>270</v>
-      </c>
       <c r="E3" s="37" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F3" s="37">
         <v>1</v>
@@ -10990,19 +10986,19 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="37" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D4" s="37" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E4" s="37" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F4" s="37">
         <v>2</v>
@@ -11024,19 +11020,19 @@
     </row>
     <row r="5" spans="1:16" ht="36" customHeight="1">
       <c r="A5" s="37" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E5" s="37" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F5" s="37">
         <v>3</v>
@@ -11048,10 +11044,10 @@
         <v>26</v>
       </c>
       <c r="K5" s="37" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L5" s="37" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M5" s="37"/>
       <c r="N5" s="37"/>
@@ -11064,24 +11060,24 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="37" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F6" s="37"/>
       <c r="G6" s="37"/>
       <c r="H6" s="37" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I6" s="37"/>
       <c r="J6" s="37"/>
@@ -11100,24 +11096,24 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="37" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E7" s="37" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F7" s="37"/>
       <c r="G7" s="37"/>
       <c r="H7" s="37" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I7" s="37"/>
       <c r="J7" s="37"/>
@@ -11134,34 +11130,34 @@
     </row>
     <row r="8" spans="1:16" ht="36" customHeight="1">
       <c r="A8" s="37" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D8" s="37" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E8" s="37" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F8" s="37"/>
       <c r="G8" s="37"/>
       <c r="H8" s="37"/>
       <c r="I8" s="37" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="J8" s="37" t="s">
         <v>30</v>
       </c>
       <c r="K8" s="37" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L8" s="37" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M8" s="37"/>
       <c r="N8" s="37"/>
@@ -11174,24 +11170,24 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="37" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D9" s="37" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E9" s="37" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F9" s="37"/>
       <c r="G9" s="37"/>
       <c r="H9" s="37" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="I9" s="37"/>
       <c r="J9" s="37"/>
@@ -11212,24 +11208,24 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="37" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B10" s="37" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F10" s="37"/>
       <c r="G10" s="37"/>
       <c r="H10" s="37" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="I10" s="37"/>
       <c r="J10" s="37"/>
@@ -11246,25 +11242,25 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="37" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C11" s="37" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D11" s="37" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E11" s="37" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F11" s="37"/>
       <c r="G11" s="37"/>
       <c r="H11" s="37"/>
       <c r="I11" s="37" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="J11" s="37"/>
       <c r="K11" s="37"/>
@@ -11280,34 +11276,34 @@
     </row>
     <row r="12" spans="1:16" ht="36" customHeight="1">
       <c r="A12" s="37" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F12" s="37"/>
       <c r="G12" s="37"/>
       <c r="H12" s="37"/>
       <c r="I12" s="37" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="J12" s="37" t="s">
         <v>13</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="L12" s="37" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M12" s="37"/>
       <c r="N12" s="37"/>
@@ -11320,24 +11316,24 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="37" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B13" s="37" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D13" s="37" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E13" s="37" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F13" s="37"/>
       <c r="G13" s="37"/>
       <c r="H13" s="37" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I13" s="37"/>
       <c r="J13" s="37"/>
@@ -11354,24 +11350,24 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="37" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F14" s="37"/>
       <c r="G14" s="37"/>
       <c r="H14" s="37" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I14" s="37"/>
       <c r="J14" s="37"/>
@@ -11388,34 +11384,34 @@
     </row>
     <row r="15" spans="1:16" ht="36" customHeight="1">
       <c r="A15" s="37" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F15" s="37"/>
       <c r="G15" s="37"/>
       <c r="H15" s="37"/>
       <c r="I15" s="37" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J15" s="37" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K15" s="37" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L15" s="37" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="M15" s="37"/>
       <c r="N15" s="37"/>
@@ -11428,24 +11424,24 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="37" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C16" s="37" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F16" s="37"/>
       <c r="G16" s="37"/>
       <c r="H16" s="37" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I16" s="37"/>
       <c r="J16" s="37"/>
@@ -11462,24 +11458,24 @@
     </row>
     <row r="17" spans="1:16">
       <c r="A17" s="37" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E17" s="37" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F17" s="37"/>
       <c r="G17" s="37"/>
       <c r="H17" s="37" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I17" s="37"/>
       <c r="J17" s="37"/>
@@ -11496,34 +11492,34 @@
     </row>
     <row r="18" spans="1:16" ht="36" customHeight="1">
       <c r="A18" s="37" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C18" s="37" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F18" s="37"/>
       <c r="G18" s="37"/>
       <c r="H18" s="37"/>
       <c r="I18" s="37" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J18" s="37" t="s">
         <v>34</v>
       </c>
       <c r="K18" s="37" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L18" s="37" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M18" s="37"/>
       <c r="N18" s="37"/>
@@ -11536,24 +11532,24 @@
     </row>
     <row r="19" spans="1:16">
       <c r="A19" s="37" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C19" s="37" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D19" s="37" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E19" s="37" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F19" s="37"/>
       <c r="G19" s="37"/>
       <c r="H19" s="37" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I19" s="37"/>
       <c r="J19" s="37"/>
@@ -11570,24 +11566,24 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="37" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C20" s="37" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D20" s="37" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F20" s="37"/>
       <c r="G20" s="37"/>
       <c r="H20" s="37" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I20" s="37"/>
       <c r="J20" s="37"/>
@@ -11604,26 +11600,26 @@
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="37" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C21" s="37" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D21" s="37" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E21" s="37" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F21" s="37">
         <v>5</v>
       </c>
       <c r="G21" s="37"/>
       <c r="H21" s="37" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I21" s="37"/>
       <c r="J21" s="37"/>
@@ -11640,26 +11636,26 @@
     </row>
     <row r="22" spans="1:16">
       <c r="A22" s="37" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B22" s="37" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F22" s="37">
         <v>1</v>
       </c>
       <c r="G22" s="37"/>
       <c r="H22" s="37" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="I22" s="37"/>
       <c r="J22" s="37"/>
@@ -11676,26 +11672,26 @@
     </row>
     <row r="23" spans="1:16">
       <c r="A23" s="37" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C23" s="37" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D23" s="37" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E23" s="37" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F23" s="37">
         <v>1</v>
       </c>
       <c r="G23" s="37"/>
       <c r="H23" s="37" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="I23" s="37"/>
       <c r="J23" s="37"/>
@@ -11712,26 +11708,26 @@
     </row>
     <row r="24" spans="1:16">
       <c r="A24" s="37" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F24" s="37">
         <v>1</v>
       </c>
       <c r="G24" s="37"/>
       <c r="H24" s="37" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I24" s="37"/>
       <c r="J24" s="37"/>
@@ -11748,26 +11744,26 @@
     </row>
     <row r="25" spans="1:16">
       <c r="A25" s="37" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C25" s="37" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D25" s="37" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E25" s="37" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F25" s="37">
         <v>1</v>
       </c>
       <c r="G25" s="37"/>
       <c r="H25" s="37" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I25" s="37"/>
       <c r="J25" s="37"/>
@@ -11782,40 +11778,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="36">
+    <row r="26" spans="1:16" ht="36" customHeight="1">
       <c r="A26" s="37" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E26" s="37" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F26" s="37">
         <v>1</v>
       </c>
       <c r="G26" s="37"/>
       <c r="H26" s="37" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J26" s="37" t="s">
         <v>9</v>
       </c>
       <c r="K26" s="37" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L26" s="37" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M26" s="37"/>
       <c r="N26" s="37"/>
@@ -11828,24 +11824,24 @@
     </row>
     <row r="27" spans="1:16">
       <c r="A27" s="37" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B27" s="37" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C27" s="37" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D27" s="37" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E27" s="37" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F27" s="37"/>
       <c r="G27" s="37"/>
       <c r="H27" s="37" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I27" s="37"/>
       <c r="J27" s="37"/>
@@ -12350,4525 +12346,4525 @@
     <col min="8" max="8" width="8.125" style="32" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="48" style="32" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="150.5" style="32" bestFit="1" customWidth="1"/>
-    <col min="11" max="28" width="8.875" style="36" customWidth="1"/>
-    <col min="29" max="16384" width="8.875" style="36"/>
+    <col min="11" max="29" width="8.875" style="36" customWidth="1"/>
+    <col min="30" max="16384" width="8.875" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="39" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B1" s="39" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C1" s="39" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D1" s="39" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E1" s="39" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F1" s="40" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G1" s="40" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="H1" s="40" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I1" s="39" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="J1" s="40" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="50" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B2" s="50" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C2" s="50">
         <v>1</v>
       </c>
       <c r="D2" s="50" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E2" s="50"/>
       <c r="F2" s="51"/>
       <c r="G2" s="51"/>
       <c r="H2" s="51"/>
       <c r="I2" s="51" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J2" s="50" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="50" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C3" s="50">
         <v>2</v>
       </c>
       <c r="D3" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E3" s="52" t="s">
         <v>23</v>
       </c>
       <c r="F3" s="53" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G3" s="51"/>
       <c r="H3" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I3" s="51"/>
       <c r="J3" s="54" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="50" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B4" s="50" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C4" s="50">
         <v>3</v>
       </c>
       <c r="D4" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E4" s="50" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G4" s="51"/>
       <c r="H4" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I4" s="51"/>
       <c r="J4" s="50" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="50" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C5" s="50">
         <v>4</v>
       </c>
       <c r="D5" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E5" s="50" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="51" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G5" s="51"/>
       <c r="H5" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I5" s="51"/>
       <c r="J5" s="55" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="50" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B6" s="50" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C6" s="50">
         <v>5</v>
       </c>
       <c r="D6" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E6" s="52" t="s">
         <v>23</v>
       </c>
       <c r="F6" s="53" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G6" s="51"/>
       <c r="H6" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I6" s="51"/>
       <c r="J6" s="56" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="50" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B7" s="50" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C7" s="50">
         <v>6</v>
       </c>
       <c r="D7" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E7" s="50" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G7" s="51"/>
       <c r="H7" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I7" s="51"/>
       <c r="J7" s="55" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="50" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B8" s="50" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C8" s="50">
         <v>7</v>
       </c>
       <c r="D8" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E8" s="50" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="51" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G8" s="51"/>
       <c r="H8" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I8" s="51"/>
       <c r="J8" s="55" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="50" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B9" s="50" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C9" s="50">
         <v>8</v>
       </c>
       <c r="D9" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E9" s="50" t="s">
         <v>16</v>
       </c>
       <c r="F9" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G9" s="51"/>
       <c r="H9" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I9" s="51"/>
       <c r="J9" s="55" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="50" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B10" s="50" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C10" s="50">
         <v>9</v>
       </c>
       <c r="D10" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E10" s="50" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="51" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G10" s="51"/>
       <c r="H10" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I10" s="51"/>
       <c r="J10" s="55" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="50" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B11" s="50" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C11" s="50">
         <v>10</v>
       </c>
       <c r="D11" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E11" s="50" t="s">
         <v>16</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G11" s="51"/>
       <c r="H11" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I11" s="51"/>
       <c r="J11" s="55" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="30" customHeight="1">
       <c r="A12" s="50" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B12" s="50" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C12" s="50">
         <v>11</v>
       </c>
       <c r="D12" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E12" s="50" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="51" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G12" s="51"/>
       <c r="H12" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I12" s="51"/>
       <c r="J12" s="56" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="32" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C13" s="32">
         <v>12</v>
       </c>
       <c r="D13" s="50" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F13" s="51"/>
       <c r="J13" s="55" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="18.75">
       <c r="A14" s="50" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B14" s="50" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C14" s="50">
         <v>1</v>
       </c>
       <c r="D14" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E14" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F14" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G14" s="51"/>
       <c r="H14" s="53" t="s">
-        <v>350</v>
-      </c>
-      <c r="I14" s="69" t="s">
-        <v>364</v>
+        <v>352</v>
+      </c>
+      <c r="I14" s="70" t="s">
+        <v>366</v>
       </c>
       <c r="J14" s="56" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="50" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B15" s="50" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C15" s="50">
         <v>2</v>
       </c>
       <c r="D15" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E15" s="52" t="s">
         <v>20</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G15" s="51"/>
       <c r="H15" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I15" s="51"/>
       <c r="J15" s="56" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="50" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B16" s="50" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C16" s="50">
         <v>3</v>
       </c>
       <c r="D16" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E16" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F16" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G16" s="51"/>
       <c r="H16" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I16" s="51"/>
       <c r="J16" s="52" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="18.75">
       <c r="A17" s="50" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B17" s="50" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C17" s="50">
         <v>4</v>
       </c>
       <c r="D17" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E17" s="50" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G17" s="51"/>
       <c r="H17" s="53" t="s">
-        <v>350</v>
-      </c>
-      <c r="I17" s="69" t="s">
-        <v>368</v>
+        <v>352</v>
+      </c>
+      <c r="I17" s="70" t="s">
+        <v>370</v>
       </c>
       <c r="J17" s="55" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="50" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B18" s="50" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C18" s="50">
         <v>5</v>
       </c>
       <c r="D18" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E18" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F18" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G18" s="51"/>
       <c r="H18" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I18" s="51"/>
       <c r="J18" s="57" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="50" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B19" s="50" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C19" s="50">
         <v>6</v>
       </c>
       <c r="D19" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E19" s="50" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H19" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J19" s="50" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="50" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B20" s="50" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C20" s="50">
         <v>7</v>
       </c>
       <c r="D20" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E20" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F20" s="51" t="s">
+        <v>354</v>
+      </c>
+      <c r="H20" s="53" t="s">
         <v>352</v>
       </c>
-      <c r="H20" s="53" t="s">
-        <v>350</v>
-      </c>
       <c r="J20" s="50" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="30" customHeight="1">
       <c r="A21" s="50" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B21" s="50" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C21" s="50">
         <v>1</v>
       </c>
       <c r="D21" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E21" s="52" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G21" s="51"/>
       <c r="H21" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I21" s="51" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="J21" s="52" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="50" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B22" s="50" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C22" s="50">
         <v>1</v>
       </c>
       <c r="D22" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E22" s="50" t="s">
         <v>27</v>
       </c>
       <c r="F22" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G22" s="51"/>
       <c r="H22" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I22" s="51" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="J22" s="50" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="50" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B23" s="50" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C23" s="50">
         <v>2</v>
       </c>
       <c r="D23" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E23" s="50" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="53" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G23" s="51"/>
       <c r="H23" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I23" s="51"/>
       <c r="J23" s="50" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="50" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B24" s="50" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C24" s="50">
         <v>3</v>
       </c>
       <c r="D24" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E24" s="50" t="s">
         <v>27</v>
       </c>
       <c r="F24" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G24" s="51"/>
       <c r="H24" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I24" s="51"/>
       <c r="J24" s="55" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="50" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B25" s="50" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C25" s="50">
         <v>4</v>
       </c>
       <c r="D25" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E25" s="50" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="53" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G25" s="51"/>
       <c r="H25" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I25" s="51"/>
       <c r="J25" s="50" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="50" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B26" s="50" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C26" s="50">
         <v>5</v>
       </c>
       <c r="D26" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E26" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G26" s="51"/>
       <c r="H26" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I26" s="51"/>
       <c r="J26" s="50" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="32" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B27" s="32" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C27" s="32">
         <v>6</v>
       </c>
       <c r="D27" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E27" s="50" t="s">
         <v>27</v>
       </c>
       <c r="F27" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H27" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J27" s="58" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="50" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B28" s="50" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C28" s="50">
         <v>1</v>
       </c>
       <c r="D28" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E28" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G28" s="51"/>
       <c r="H28" s="53"/>
       <c r="I28" s="51" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="J28" s="52" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="50" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B29" s="50" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C29" s="50">
         <v>2</v>
       </c>
       <c r="D29" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E29" s="50" t="s">
         <v>27</v>
       </c>
       <c r="F29" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G29" s="51"/>
       <c r="H29" s="53"/>
       <c r="I29" s="51"/>
       <c r="J29" s="32" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="50" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B30" s="50" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C30" s="50">
         <v>3</v>
       </c>
       <c r="D30" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E30" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G30" s="51"/>
       <c r="H30" s="53"/>
       <c r="I30" s="51"/>
       <c r="J30" s="32" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="50" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B31" s="50" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C31" s="50">
         <v>4</v>
       </c>
       <c r="D31" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E31" s="50" t="s">
         <v>27</v>
       </c>
       <c r="F31" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G31" s="51"/>
       <c r="H31" s="51"/>
       <c r="I31" s="51"/>
       <c r="J31" s="32" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="50" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B32" s="50" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C32" s="50">
         <v>5</v>
       </c>
       <c r="D32" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E32" s="50" t="s">
         <v>27</v>
       </c>
       <c r="F32" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G32" s="51"/>
       <c r="H32" s="51"/>
       <c r="I32" s="51"/>
       <c r="J32" s="58" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="32" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B33" s="32" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C33" s="32">
         <v>6</v>
       </c>
       <c r="D33" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E33" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F33" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J33" s="58" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="50" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B34" s="50" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C34" s="50">
         <v>1</v>
       </c>
       <c r="D34" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E34" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F34" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G34" s="51"/>
       <c r="H34" s="53"/>
       <c r="I34" s="51" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="J34" s="52" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="50" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B35" s="50" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C35" s="50">
         <v>1</v>
       </c>
       <c r="D35" s="50" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E35" s="50"/>
       <c r="F35" s="51"/>
       <c r="G35" s="51"/>
       <c r="H35" s="51"/>
       <c r="I35" s="51" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="J35" s="56" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="50" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B36" s="50" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C36" s="50">
         <v>2</v>
       </c>
       <c r="D36" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E36" s="50" t="s">
         <v>23</v>
       </c>
       <c r="F36" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G36" s="51"/>
       <c r="H36" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I36" s="51"/>
       <c r="J36" s="50" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="50" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B37" s="50" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C37" s="50">
         <v>3</v>
       </c>
       <c r="D37" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E37" s="50" t="s">
         <v>23</v>
       </c>
       <c r="F37" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G37" s="51"/>
       <c r="H37" s="53" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I37" s="51" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="J37" s="50" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="50" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B38" s="50" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C38" s="50">
         <v>4</v>
       </c>
       <c r="D38" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E38" s="50" t="s">
         <v>16</v>
       </c>
       <c r="F38" s="53" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G38" s="51"/>
       <c r="H38" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I38" s="51"/>
       <c r="J38" s="51" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="50" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B39" s="50" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C39" s="50">
         <v>5</v>
       </c>
       <c r="D39" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E39" s="50" t="s">
         <v>16</v>
       </c>
       <c r="F39" s="53" t="s">
+        <v>354</v>
+      </c>
+      <c r="H39" s="53" t="s">
         <v>352</v>
       </c>
-      <c r="H39" s="53" t="s">
-        <v>350</v>
-      </c>
       <c r="J39" s="32" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="50" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B40" s="50" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C40" s="50">
         <v>6</v>
       </c>
       <c r="D40" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E40" s="50" t="s">
         <v>33</v>
       </c>
       <c r="F40" s="51" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G40" s="51"/>
       <c r="H40" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I40" s="51"/>
       <c r="J40" s="50" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="50" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B41" s="50" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C41" s="50">
         <v>7</v>
       </c>
       <c r="D41" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E41" s="50" t="s">
         <v>16</v>
       </c>
       <c r="F41" s="53" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H41" s="53" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J41" s="32" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="50" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B42" s="50" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C42" s="50">
         <v>8</v>
       </c>
       <c r="D42" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E42" s="50" t="s">
         <v>33</v>
       </c>
       <c r="F42" s="51" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="H42" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J42" s="32" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="50" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B43" s="50" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C43" s="50">
         <v>9</v>
       </c>
       <c r="D43" s="50" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E43" s="50"/>
       <c r="F43" s="51"/>
       <c r="I43" s="51" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="J43" s="32" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="50" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B44" s="50" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C44" s="50">
         <v>10</v>
       </c>
       <c r="D44" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E44" s="50" t="s">
         <v>29</v>
       </c>
       <c r="F44" s="51" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="H44" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I44" s="51"/>
       <c r="J44" s="32" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="50" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B45" s="50" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C45" s="50">
         <v>11</v>
       </c>
       <c r="D45" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E45" s="50" t="s">
         <v>16</v>
       </c>
       <c r="F45" s="53" t="s">
+        <v>354</v>
+      </c>
+      <c r="H45" s="53" t="s">
         <v>352</v>
       </c>
-      <c r="H45" s="53" t="s">
-        <v>350</v>
-      </c>
       <c r="J45" s="32" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="50" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B46" s="50" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C46" s="50">
         <v>12</v>
       </c>
       <c r="D46" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E46" s="50" t="s">
         <v>29</v>
       </c>
       <c r="F46" s="51" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="H46" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I46" s="51" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="J46" s="32" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="50" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B47" s="50" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C47" s="50">
         <v>13</v>
       </c>
       <c r="D47" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E47" s="50" t="s">
         <v>29</v>
       </c>
       <c r="F47" s="51" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="H47" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J47" s="32" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="18.75">
       <c r="A48" s="50" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B48" s="50" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C48" s="50">
         <v>14</v>
       </c>
       <c r="D48" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E48" s="52" t="s">
         <v>31</v>
       </c>
       <c r="F48" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G48" s="58" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="H48" s="53" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="I48" s="68"/>
       <c r="J48" s="58" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="50" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B49" s="50" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C49" s="50">
         <v>15</v>
       </c>
       <c r="D49" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E49" s="50" t="s">
         <v>29</v>
       </c>
       <c r="F49" s="51" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="H49" s="53" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J49" s="58" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="50" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B50" s="50" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C50" s="50">
         <v>1</v>
       </c>
       <c r="D50" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E50" s="52" t="s">
         <v>31</v>
       </c>
       <c r="F50" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G50" s="53" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H50" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I50" s="51" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="J50" s="52" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="50" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B51" s="50" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C51" s="50">
         <v>2</v>
       </c>
       <c r="D51" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E51" s="50" t="s">
         <v>16</v>
       </c>
       <c r="F51" s="53" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G51" s="51"/>
       <c r="H51" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I51" s="51"/>
       <c r="J51" s="50" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="50" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B52" s="50" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C52" s="50">
         <v>3</v>
       </c>
       <c r="D52" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E52" s="50" t="s">
         <v>29</v>
       </c>
       <c r="F52" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G52" s="51"/>
       <c r="H52" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I52" s="51"/>
       <c r="J52" s="50" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="50" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B53" s="50" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C53" s="50">
         <v>4</v>
       </c>
       <c r="D53" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E53" s="50" t="s">
         <v>16</v>
       </c>
       <c r="F53" s="53" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G53" s="51"/>
       <c r="H53" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I53" s="51"/>
       <c r="J53" s="52" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="50" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B54" s="50" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C54" s="50">
         <v>5</v>
       </c>
       <c r="D54" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E54" s="52" t="s">
         <v>23</v>
       </c>
       <c r="F54" s="53" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="H54" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J54" s="58" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="50" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B55" s="50" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C55" s="50">
         <v>6</v>
       </c>
       <c r="D55" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E55" s="50" t="s">
         <v>16</v>
       </c>
       <c r="F55" s="53" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G55" s="51"/>
       <c r="H55" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I55" s="51"/>
       <c r="J55" s="53" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="50" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B56" s="50" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C56" s="50">
         <v>7</v>
       </c>
       <c r="D56" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E56" s="50" t="s">
         <v>29</v>
       </c>
       <c r="F56" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G56" s="51"/>
       <c r="H56" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J56" s="58" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="50" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B57" s="50" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C57" s="50">
         <v>8</v>
       </c>
       <c r="D57" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E57" s="50" t="s">
         <v>29</v>
       </c>
       <c r="F57" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G57" s="51"/>
       <c r="H57" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J57" s="58" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="50" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B58" s="50" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C58" s="50">
         <v>9</v>
       </c>
       <c r="D58" s="50" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E58" s="50"/>
       <c r="F58" s="51"/>
       <c r="G58" s="51"/>
       <c r="H58" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I58" s="51"/>
       <c r="J58" s="53" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="50" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B59" s="50" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C59" s="50">
         <v>1</v>
       </c>
       <c r="D59" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E59" s="62" t="s">
         <v>31</v>
       </c>
       <c r="F59" s="53" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G59" s="58" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="H59" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I59" s="51" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="J59" s="52" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="50" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B60" s="50" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C60" s="50">
         <v>2</v>
       </c>
       <c r="D60" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E60" s="62" t="s">
         <v>29</v>
       </c>
       <c r="F60" s="53" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G60" s="51"/>
       <c r="H60" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I60" s="51"/>
       <c r="J60" s="52" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="50" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B61" s="50" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C61" s="50">
         <v>3</v>
       </c>
       <c r="D61" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E61" s="50" t="s">
         <v>16</v>
       </c>
       <c r="F61" s="53" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G61" s="51"/>
       <c r="H61" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I61" s="51"/>
       <c r="J61" s="52" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="50" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B62" s="50" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C62" s="50">
         <v>4</v>
       </c>
       <c r="D62" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E62" s="62" t="s">
         <v>29</v>
       </c>
       <c r="F62" s="53" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G62" s="51"/>
       <c r="H62" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I62" s="51"/>
       <c r="J62" s="52" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="50" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B63" s="50" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C63" s="50">
         <v>5</v>
       </c>
       <c r="D63" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E63" s="50" t="s">
         <v>16</v>
       </c>
       <c r="F63" s="53" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G63" s="51"/>
       <c r="H63" s="53" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I63" s="51"/>
       <c r="J63" s="53" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="50" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B64" s="50" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C64" s="50">
         <v>1</v>
       </c>
       <c r="D64" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E64" s="52" t="s">
         <v>35</v>
       </c>
       <c r="F64" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G64" s="51"/>
       <c r="H64" s="53"/>
       <c r="I64" s="51" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="J64" s="52" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="50" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B65" s="50" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C65" s="50">
         <v>2</v>
       </c>
       <c r="D65" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E65" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F65" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G65" s="51"/>
       <c r="H65" s="53"/>
       <c r="I65" s="51"/>
       <c r="J65" s="52" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="50" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B66" s="50" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C66" s="50">
         <v>3</v>
       </c>
       <c r="D66" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E66" s="52" t="s">
         <v>35</v>
       </c>
       <c r="F66" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G66" s="51"/>
       <c r="H66" s="53"/>
       <c r="I66" s="51"/>
       <c r="J66" s="52" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="50" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B67" s="50" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C67" s="50">
         <v>4</v>
       </c>
       <c r="D67" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E67" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F67" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G67" s="51"/>
       <c r="H67" s="51"/>
       <c r="I67" s="51"/>
       <c r="J67" s="52" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="50" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B68" s="50" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C68" s="50">
         <v>5</v>
       </c>
       <c r="D68" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E68" s="52" t="s">
         <v>35</v>
       </c>
       <c r="F68" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G68" s="51"/>
       <c r="H68" s="51"/>
       <c r="I68" s="51"/>
       <c r="J68" s="52" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="32" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B69" s="32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C69" s="32">
         <v>6</v>
       </c>
       <c r="D69" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E69" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F69" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J69" s="58" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="50" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B70" s="50" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C70" s="50">
         <v>7</v>
       </c>
       <c r="D70" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E70" s="52" t="s">
         <v>35</v>
       </c>
       <c r="F70" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J70" s="58" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="50" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B71" s="50" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C71" s="50">
         <v>8</v>
       </c>
       <c r="D71" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E71" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F71" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J71" s="58" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="50" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B72" s="50" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C72" s="50">
         <v>9</v>
       </c>
       <c r="D72" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E72" s="52" t="s">
         <v>35</v>
       </c>
       <c r="F72" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J72" s="32" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="50" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B73" s="50" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C73" s="50">
         <v>10</v>
       </c>
       <c r="D73" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E73" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F73" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J73" s="32" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" s="50" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B74" s="50" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C74" s="50">
         <v>11</v>
       </c>
       <c r="D74" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E74" s="52" t="s">
         <v>35</v>
       </c>
       <c r="F74" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J74" s="58" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" s="32" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B75" s="32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C75" s="32">
         <v>12</v>
       </c>
       <c r="D75" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E75" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F75" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J75" s="58" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="32" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B76" s="32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C76" s="32">
         <v>13</v>
       </c>
       <c r="D76" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E76" s="58" t="s">
         <v>23</v>
       </c>
       <c r="F76" s="53" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J76" s="58" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="32" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B77" s="32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C77" s="32">
         <v>14</v>
       </c>
       <c r="D77" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E77" s="52" t="s">
         <v>35</v>
       </c>
       <c r="F77" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J77" s="58" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="36">
       <c r="A78" s="50" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B78" s="50" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C78" s="50">
         <v>1</v>
       </c>
       <c r="D78" s="50" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E78" s="52" t="s">
         <v>14</v>
       </c>
       <c r="F78" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G78" s="51"/>
       <c r="H78" s="53"/>
       <c r="I78" s="51" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="J78" s="52" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="36">
       <c r="A79" s="50" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B79" s="50" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C79" s="50">
         <v>2</v>
       </c>
       <c r="D79" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E79" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F79" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G79" s="51"/>
       <c r="H79" s="53"/>
       <c r="I79" s="51"/>
       <c r="J79" s="52" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="36">
       <c r="A80" s="50" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B80" s="50" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C80" s="50">
         <v>3</v>
       </c>
       <c r="D80" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E80" s="52" t="s">
         <v>14</v>
       </c>
       <c r="F80" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G80" s="51"/>
       <c r="H80" s="53" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I80" s="51"/>
       <c r="J80" s="52" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="36">
       <c r="A81" s="50" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B81" s="50" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C81" s="50">
         <v>4</v>
       </c>
       <c r="D81" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E81" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F81" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G81" s="51"/>
       <c r="H81" s="53" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I81" s="51"/>
       <c r="J81" s="52" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="50" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B82" s="50" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C82" s="50">
         <v>1</v>
       </c>
       <c r="D82" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E82" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F82" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G82" s="51"/>
       <c r="H82" s="53"/>
       <c r="I82" s="51" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="J82" s="52" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="50" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B83" s="50" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C83" s="50">
         <v>2</v>
       </c>
       <c r="D83" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E83" s="52" t="s">
         <v>14</v>
       </c>
       <c r="F83" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G83" s="51"/>
       <c r="H83" s="53"/>
       <c r="I83" s="51"/>
       <c r="J83" s="52" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="50" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B84" s="50" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C84" s="50">
         <v>3</v>
       </c>
       <c r="D84" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E84" s="52" t="s">
         <v>14</v>
       </c>
       <c r="F84" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G84" s="51"/>
       <c r="H84" s="53"/>
       <c r="I84" s="51"/>
       <c r="J84" s="52" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="50" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B85" s="50" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C85" s="50">
         <v>4</v>
       </c>
       <c r="D85" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E85" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F85" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G85" s="51"/>
       <c r="H85" s="51"/>
       <c r="I85" s="51"/>
       <c r="J85" s="52" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="18.75" customHeight="1">
       <c r="A86" s="50" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B86" s="50" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C86" s="50">
         <v>5</v>
       </c>
       <c r="D86" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E86" s="52" t="s">
         <v>14</v>
       </c>
       <c r="F86" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G86" s="51"/>
       <c r="H86" s="51"/>
       <c r="I86" s="51"/>
       <c r="J86" s="52" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="50" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B87" s="50" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C87" s="50">
         <v>6</v>
       </c>
       <c r="D87" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E87" s="52" t="s">
         <v>14</v>
       </c>
       <c r="F87" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J87" s="66" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="50" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B88" s="50" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C88" s="50">
         <v>7</v>
       </c>
       <c r="D88" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E88" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F88" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J88" s="58" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="50" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B89" s="50" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C89" s="50">
         <v>8</v>
       </c>
       <c r="D89" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E89" s="52" t="s">
         <v>14</v>
       </c>
       <c r="F89" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J89" s="58" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="50" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B90" s="50" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C90" s="50">
         <v>9</v>
       </c>
       <c r="D90" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E90" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F90" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J90" s="58" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="50" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B91" s="50" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C91" s="50">
         <v>10</v>
       </c>
       <c r="D91" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E91" s="52" t="s">
         <v>14</v>
       </c>
       <c r="F91" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J91" s="58" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="50" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B92" s="50" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C92" s="50">
         <v>1</v>
       </c>
       <c r="D92" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E92" s="50" t="s">
         <v>16</v>
       </c>
       <c r="F92" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G92" s="51"/>
       <c r="H92" s="53" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I92" s="51" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="J92" s="50" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="33" customHeight="1">
       <c r="A93" s="50" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B93" s="50" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C93" s="50">
         <v>1</v>
       </c>
       <c r="D93" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E93" s="50" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F93" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G93" s="51" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="H93" s="53"/>
       <c r="I93" s="51" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J93" s="55" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" s="50" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B94" s="50" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C94" s="50">
         <v>2</v>
       </c>
       <c r="D94" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E94" s="50" t="s">
         <v>16</v>
       </c>
       <c r="F94" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G94" s="51"/>
       <c r="H94" s="53"/>
       <c r="I94" s="51"/>
       <c r="J94" s="55" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="50" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B95" s="50" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C95" s="50">
         <v>1</v>
       </c>
       <c r="D95" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E95" s="50" t="s">
         <v>16</v>
       </c>
       <c r="F95" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G95" s="51"/>
       <c r="H95" s="53"/>
       <c r="I95" s="51" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J95" s="55" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="50" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B96" s="50" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C96" s="50">
         <v>2</v>
       </c>
       <c r="D96" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E96" s="50" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F96" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G96" s="51" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H96" s="53"/>
       <c r="I96" s="51"/>
       <c r="J96" s="50" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="97" spans="1:10">
       <c r="A97" s="50" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B97" s="50" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C97" s="50">
         <v>3</v>
       </c>
       <c r="D97" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E97" s="50" t="s">
         <v>16</v>
       </c>
       <c r="F97" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G97" s="51"/>
       <c r="H97" s="53"/>
       <c r="I97" s="51"/>
       <c r="J97" s="50" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="98" spans="1:10">
       <c r="A98" s="50" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B98" s="50" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C98" s="50">
         <v>4</v>
       </c>
       <c r="D98" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E98" s="50" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F98" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G98" s="51" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H98" s="51"/>
       <c r="I98" s="51"/>
       <c r="J98" s="50" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="99" spans="1:10">
       <c r="A99" s="50" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B99" s="50" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C99" s="50">
         <v>5</v>
       </c>
       <c r="D99" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E99" s="50" t="s">
         <v>16</v>
       </c>
       <c r="F99" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G99" s="51"/>
       <c r="H99" s="51"/>
       <c r="I99" s="51"/>
       <c r="J99" s="50" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="100" spans="1:10">
       <c r="A100" s="50" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B100" s="50" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C100" s="50">
         <v>6</v>
       </c>
       <c r="D100" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E100" s="50" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F100" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G100" s="51" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H100" s="32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J100" s="67" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="101" spans="1:10">
       <c r="A101" s="50" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B101" s="50" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C101" s="50">
         <v>7</v>
       </c>
       <c r="D101" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E101" s="32" t="s">
         <v>25</v>
       </c>
       <c r="F101" s="51" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J101" s="32" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="102" spans="1:10">
       <c r="A102" s="50" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B102" s="50" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C102" s="50">
         <v>8</v>
       </c>
       <c r="D102" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E102" s="50" t="s">
         <v>16</v>
       </c>
       <c r="F102" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J102" s="32" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="103" spans="1:10">
       <c r="A103" s="50" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B103" s="50" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C103" s="50">
         <v>9</v>
       </c>
       <c r="D103" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E103" s="32" t="s">
         <v>23</v>
       </c>
       <c r="F103" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J103" s="32" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="104" spans="1:10">
       <c r="A104" s="50" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B104" s="50" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C104" s="50">
         <v>10</v>
       </c>
       <c r="D104" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E104" s="32" t="s">
         <v>25</v>
       </c>
       <c r="F104" s="51" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J104" s="32" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="105" spans="1:10">
       <c r="A105" s="50" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B105" s="50" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C105" s="50">
         <v>11</v>
       </c>
       <c r="D105" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E105" s="32" t="s">
         <v>23</v>
       </c>
       <c r="F105" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J105" s="32" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="106" spans="1:10">
       <c r="A106" s="50" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B106" s="50" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C106" s="50">
         <v>1</v>
       </c>
       <c r="D106" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E106" s="50" t="s">
         <v>16</v>
       </c>
       <c r="F106" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G106" s="51"/>
       <c r="H106" s="53"/>
       <c r="I106" s="51" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J106" s="50" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="107" spans="1:10">
       <c r="A107" s="50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B107" s="50" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C107" s="50">
         <v>1</v>
       </c>
       <c r="D107" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E107" s="50" t="s">
         <v>37</v>
       </c>
       <c r="F107" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G107" s="51"/>
       <c r="H107" s="53"/>
       <c r="I107" s="51" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J107" s="50" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="108" spans="1:10">
       <c r="A108" s="50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B108" s="50" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C108" s="50">
         <v>2</v>
       </c>
       <c r="D108" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E108" s="56" t="s">
         <v>16</v>
       </c>
       <c r="F108" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G108" s="51"/>
       <c r="H108" s="53"/>
       <c r="I108" s="51"/>
       <c r="J108" s="50" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="109" spans="1:10">
       <c r="A109" s="50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B109" s="50" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C109" s="50">
         <v>3</v>
       </c>
       <c r="D109" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E109" s="50" t="s">
         <v>37</v>
       </c>
       <c r="F109" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G109" s="51"/>
       <c r="H109" s="53"/>
       <c r="I109" s="51"/>
       <c r="J109" s="52" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="110" spans="1:10">
       <c r="A110" s="50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B110" s="50" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C110" s="50">
         <v>4</v>
       </c>
       <c r="D110" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E110" s="52" t="s">
         <v>35</v>
       </c>
       <c r="F110" s="51" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G110" s="53" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="H110" s="51"/>
       <c r="I110" s="51"/>
       <c r="J110" s="52" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="111" spans="1:10">
       <c r="A111" s="50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B111" s="50" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C111" s="50">
         <v>5</v>
       </c>
       <c r="D111" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E111" s="56" t="s">
         <v>16</v>
       </c>
       <c r="F111" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G111" s="51"/>
       <c r="H111" s="51"/>
       <c r="I111" s="51"/>
       <c r="J111" s="52" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="112" spans="1:10">
       <c r="A112" s="50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B112" s="50" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C112" s="50">
         <v>6</v>
       </c>
       <c r="D112" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E112" s="52" t="s">
         <v>35</v>
       </c>
       <c r="F112" s="51" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G112" s="53" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="J112" s="52" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="113" spans="1:10">
       <c r="A113" s="50" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B113" s="50" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C113" s="50">
         <v>1</v>
       </c>
       <c r="D113" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E113" s="52" t="s">
         <v>35</v>
       </c>
       <c r="F113" s="53" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G113" s="51"/>
       <c r="H113" s="53" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I113" s="51" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J113" s="52" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="114" spans="1:10">
       <c r="A114" s="50" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B114" s="50" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C114" s="50">
         <v>2</v>
       </c>
       <c r="D114" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E114" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F114" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G114" s="51"/>
       <c r="H114" s="53"/>
       <c r="I114" s="51"/>
       <c r="J114" s="52" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="115" spans="1:10">
       <c r="A115" s="50" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B115" s="50" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C115" s="50">
         <v>3</v>
       </c>
       <c r="D115" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E115" s="52" t="s">
         <v>37</v>
       </c>
       <c r="F115" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G115" s="51"/>
       <c r="H115" s="53" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I115" s="51"/>
       <c r="J115" s="52" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="116" spans="1:10">
       <c r="A116" s="50" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B116" s="50" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C116" s="50">
         <v>4</v>
       </c>
       <c r="D116" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E116" s="52" t="s">
         <v>23</v>
       </c>
       <c r="F116" s="53" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G116" s="51"/>
       <c r="H116" s="51"/>
       <c r="I116" s="51"/>
       <c r="J116" s="52" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="117" spans="1:10">
       <c r="A117" s="50" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B117" s="50" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C117" s="50">
         <v>5</v>
       </c>
       <c r="D117" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E117" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F117" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G117" s="51"/>
       <c r="H117" s="53"/>
       <c r="I117" s="51"/>
       <c r="J117" s="52" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="118" spans="1:10">
       <c r="A118" s="50" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B118" s="50" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C118" s="50">
         <v>1</v>
       </c>
       <c r="D118" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E118" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F118" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G118" s="51"/>
       <c r="H118" s="53"/>
       <c r="I118" s="51" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J118" s="52" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="119" spans="1:10">
       <c r="A119" s="50" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B119" s="50" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C119" s="50">
         <v>1</v>
       </c>
       <c r="D119" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E119" s="50" t="s">
-        <v>481</v>
+        <v>41</v>
       </c>
       <c r="F119" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G119" s="51"/>
       <c r="H119" s="53" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I119" s="51" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J119" s="50" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="120" spans="1:10">
       <c r="A120" s="50" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B120" s="50" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C120" s="50">
         <v>2</v>
       </c>
       <c r="D120" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E120" s="50" t="s">
         <v>16</v>
       </c>
       <c r="F120" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G120" s="51"/>
       <c r="H120" s="53" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I120" s="51"/>
       <c r="J120" s="50" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="121" spans="1:10">
       <c r="A121" s="50" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B121" s="50" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C121" s="50">
         <v>3</v>
       </c>
       <c r="D121" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E121" s="50" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F121" s="53" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G121" s="51"/>
       <c r="H121" s="53"/>
       <c r="I121" s="51" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J121" s="50" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="122" spans="1:10">
       <c r="A122" s="50" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B122" s="50" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C122" s="50">
         <v>4</v>
       </c>
       <c r="D122" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E122" s="50" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F122" s="53" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G122" s="51"/>
       <c r="H122" s="51"/>
       <c r="I122" s="51"/>
       <c r="J122" s="50" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="123" spans="1:10">
       <c r="A123" s="50" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B123" s="50" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C123" s="50">
         <v>5</v>
       </c>
       <c r="D123" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E123" s="50" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F123" s="53" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G123" s="51"/>
       <c r="H123" s="51"/>
       <c r="I123" s="51"/>
       <c r="J123" s="50" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="124" spans="1:10">
       <c r="A124" s="50" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B124" s="50" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C124" s="50">
         <v>6</v>
       </c>
       <c r="D124" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E124" s="50" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F124" s="53" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="H124" s="53" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J124" s="32" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="125" spans="1:10">
       <c r="A125" s="50" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B125" s="50" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C125" s="50">
         <v>7</v>
       </c>
       <c r="D125" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E125" s="32" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F125" s="51" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I125" s="51" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="J125" s="10" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="126" spans="1:10">
       <c r="A126" s="50" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B126" s="50" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C126" s="50">
         <v>8</v>
       </c>
       <c r="D126" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E126" s="32" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F126" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H126" s="53" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J126" s="58" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="127" spans="1:10">
       <c r="A127" s="50" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B127" s="50" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C127" s="50">
         <v>9</v>
       </c>
       <c r="D127" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E127" s="32" t="s">
         <v>16</v>
       </c>
       <c r="F127" s="51" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="H127" s="53" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J127" s="32" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="128" spans="1:10">
       <c r="A128" s="50" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B128" s="50" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C128" s="50">
         <v>12</v>
       </c>
       <c r="D128" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E128" s="32" t="s">
         <v>18</v>
       </c>
       <c r="F128" s="51" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I128" s="51" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J128" s="10" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="129" spans="1:10">
       <c r="A129" s="50" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B129" s="50" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C129" s="50">
         <v>13</v>
       </c>
       <c r="D129" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E129" s="32" t="s">
         <v>16</v>
       </c>
       <c r="F129" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J129" s="32" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="130" spans="1:10">
       <c r="A130" s="50" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B130" s="50" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C130" s="50">
         <v>14</v>
       </c>
       <c r="D130" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E130" s="32" t="s">
         <v>20</v>
       </c>
       <c r="F130" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J130" s="10" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="131" spans="1:10">
       <c r="A131" s="50" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B131" s="50" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C131" s="50">
         <v>15</v>
       </c>
       <c r="D131" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E131" s="32" t="s">
         <v>16</v>
       </c>
       <c r="F131" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J131" s="32" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="132" spans="1:10">
       <c r="A132" s="50" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B132" s="50" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C132" s="50">
         <v>16</v>
       </c>
       <c r="D132" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E132" s="32" t="s">
         <v>23</v>
       </c>
       <c r="F132" s="51" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J132" s="32" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="133" spans="1:10">
       <c r="A133" s="50" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B133" s="50" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C133" s="50">
         <v>1</v>
       </c>
       <c r="D133" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E133" s="50" t="s">
         <v>18</v>
       </c>
       <c r="F133" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G133" s="51"/>
       <c r="H133" s="53"/>
       <c r="I133" s="51" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J133" s="56" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="134" spans="1:10">
       <c r="A134" s="50" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B134" s="50" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C134" s="50">
         <v>2</v>
       </c>
       <c r="D134" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E134" s="50" t="s">
-        <v>481</v>
+        <v>41</v>
       </c>
       <c r="F134" s="53" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G134" s="51"/>
       <c r="H134" s="53" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I134" s="51"/>
-      <c r="J134" s="70" t="s">
-        <v>500</v>
+      <c r="J134" s="69" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="135" spans="1:10">
       <c r="A135" s="50" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B135" s="50" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C135" s="50">
         <v>3</v>
       </c>
       <c r="D135" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E135" s="50" t="s">
         <v>16</v>
       </c>
       <c r="F135" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G135" s="51"/>
       <c r="H135" s="53"/>
       <c r="I135" s="51"/>
       <c r="J135" s="52" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="136" spans="1:10">
       <c r="A136" s="50" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B136" s="50" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C136" s="50">
         <v>4</v>
       </c>
       <c r="D136" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E136" s="50" t="s">
         <v>18</v>
       </c>
       <c r="F136" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G136" s="51"/>
       <c r="H136" s="51"/>
       <c r="I136" s="51"/>
       <c r="J136" s="53" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="137" spans="1:10">
       <c r="A137" s="50" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B137" s="50" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C137" s="50">
         <v>5</v>
       </c>
       <c r="D137" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E137" s="50" t="s">
         <v>18</v>
       </c>
       <c r="F137" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G137" s="51"/>
       <c r="H137" s="51"/>
       <c r="I137" s="51"/>
       <c r="J137" s="52" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="138" spans="1:10">
       <c r="A138" s="50" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B138" s="50" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C138" s="50">
         <v>6</v>
       </c>
       <c r="D138" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E138" s="50" t="s">
         <v>16</v>
       </c>
       <c r="F138" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J138" s="32" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="139" spans="1:10">
       <c r="A139" s="50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B139" s="50" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C139" s="50">
         <v>1</v>
       </c>
       <c r="D139" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E139" s="52" t="s">
         <v>20</v>
       </c>
       <c r="F139" s="53" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G139" s="51"/>
       <c r="H139" s="53"/>
       <c r="I139" s="51" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="J139" s="52" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="140" spans="1:10">
       <c r="A140" s="50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B140" s="50" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C140" s="50">
         <v>2</v>
       </c>
       <c r="D140" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E140" s="52" t="s">
         <v>18</v>
       </c>
       <c r="F140" s="53" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G140" s="51"/>
       <c r="H140" s="53"/>
       <c r="I140" s="51"/>
       <c r="J140" s="52" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="141" spans="1:10">
       <c r="A141" s="50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B141" s="50" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C141" s="50">
         <v>3</v>
       </c>
       <c r="D141" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E141" s="52" t="s">
         <v>18</v>
       </c>
       <c r="F141" s="53" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G141" s="51"/>
       <c r="H141" s="53"/>
       <c r="I141" s="51"/>
       <c r="J141" s="52" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="142" spans="1:10">
       <c r="A142" s="50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B142" s="50" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C142" s="50">
         <v>4</v>
       </c>
       <c r="D142" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E142" s="52" t="s">
         <v>18</v>
       </c>
       <c r="F142" s="53" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G142" s="51"/>
       <c r="H142" s="51"/>
       <c r="I142" s="51"/>
       <c r="J142" s="52" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="143" spans="1:10">
       <c r="A143" s="50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B143" s="50" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C143" s="50">
         <v>5</v>
       </c>
       <c r="D143" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E143" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F143" s="53" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G143" s="51"/>
       <c r="H143" s="51"/>
       <c r="I143" s="51"/>
       <c r="J143" s="52" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="144" spans="1:10">
       <c r="A144" s="50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B144" s="50" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C144" s="50">
         <v>6</v>
       </c>
       <c r="D144" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E144" s="52" t="s">
         <v>18</v>
       </c>
       <c r="F144" s="53" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J144" s="58" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="145" spans="1:10">
       <c r="A145" s="50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B145" s="50" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C145" s="50">
         <v>7</v>
       </c>
       <c r="D145" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E145" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F145" s="53" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J145" s="58" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="146" spans="1:10">
       <c r="A146" s="50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B146" s="50" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C146" s="50">
         <v>8</v>
       </c>
       <c r="D146" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E146" s="52" t="s">
         <v>18</v>
       </c>
       <c r="F146" s="53" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J146" s="58" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="147" spans="1:10">
       <c r="A147" s="50" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B147" s="50" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C147" s="50">
         <v>1</v>
       </c>
       <c r="D147" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E147" s="52" t="s">
         <v>18</v>
       </c>
       <c r="F147" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G147" s="51"/>
       <c r="H147" s="53"/>
       <c r="I147" s="51" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J147" s="52" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="148" spans="1:10">
       <c r="A148" s="50" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B148" s="50" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C148" s="50">
         <v>2</v>
       </c>
       <c r="D148" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E148" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F148" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G148" s="51"/>
       <c r="H148" s="53"/>
       <c r="I148" s="51"/>
       <c r="J148" s="52" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="149" spans="1:10">
       <c r="A149" s="50" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B149" s="50" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C149" s="50">
         <v>3</v>
       </c>
       <c r="D149" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E149" s="52" t="s">
         <v>18</v>
       </c>
       <c r="F149" s="53" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G149" s="51"/>
       <c r="H149" s="53"/>
       <c r="I149" s="51"/>
       <c r="J149" s="52" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="150" spans="1:10">
       <c r="A150" s="50" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B150" s="50" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C150" s="50">
         <v>4</v>
       </c>
       <c r="D150" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E150" s="52" t="s">
         <v>18</v>
       </c>
       <c r="F150" s="53" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G150" s="51"/>
       <c r="H150" s="51"/>
       <c r="I150" s="51"/>
       <c r="J150" s="52" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="151" spans="1:10">
       <c r="A151" s="50" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B151" s="50" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C151" s="50">
         <v>5</v>
       </c>
       <c r="D151" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E151" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F151" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G151" s="51"/>
       <c r="H151" s="51"/>
       <c r="I151" s="51"/>
       <c r="J151" s="52" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="152" spans="1:10">
       <c r="A152" s="50" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B152" s="50" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C152" s="50">
         <v>6</v>
       </c>
       <c r="D152" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E152" s="52" t="s">
         <v>18</v>
       </c>
       <c r="F152" s="53" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J152" s="58" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="153" spans="1:10">
       <c r="A153" s="50" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B153" s="50" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C153" s="50">
         <v>7</v>
       </c>
       <c r="D153" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E153" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F153" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J153" s="58" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="154" spans="1:10">
       <c r="A154" s="50" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B154" s="50" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C154" s="50">
         <v>1</v>
       </c>
       <c r="D154" s="50" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E154" s="52" t="s">
         <v>14</v>
       </c>
       <c r="F154" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G154" s="51"/>
       <c r="H154" s="53"/>
       <c r="I154" s="51" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J154" s="52" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="155" spans="1:10">
       <c r="A155" s="50" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B155" s="50" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C155" s="50">
         <v>2</v>
       </c>
       <c r="D155" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E155" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F155" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G155" s="51"/>
       <c r="H155" s="53"/>
       <c r="I155" s="51"/>
       <c r="J155" s="52" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="156" spans="1:10">
       <c r="A156" s="50" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B156" s="50" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C156" s="50">
         <v>3</v>
       </c>
       <c r="D156" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E156" s="52" t="s">
         <v>14</v>
       </c>
       <c r="F156" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G156" s="51"/>
       <c r="H156" s="53"/>
       <c r="I156" s="51"/>
-      <c r="J156" s="70" t="s">
-        <v>521</v>
+      <c r="J156" s="69" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="157" spans="1:10">
       <c r="A157" s="50" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B157" s="50" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C157" s="50">
         <v>4</v>
       </c>
       <c r="D157" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E157" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F157" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G157" s="51"/>
       <c r="H157" s="51"/>
       <c r="I157" s="51"/>
       <c r="J157" s="52" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="158" spans="1:10">
       <c r="A158" s="50" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B158" s="50" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C158" s="50">
         <v>5</v>
       </c>
       <c r="D158" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E158" s="52" t="s">
         <v>14</v>
       </c>
       <c r="F158" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G158" s="51"/>
       <c r="H158" s="51"/>
       <c r="I158" s="51"/>
       <c r="J158" s="52" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="159" spans="1:10">
       <c r="A159" s="50" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B159" s="50" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C159" s="50">
         <v>6</v>
       </c>
       <c r="D159" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E159" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F159" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J159" s="58" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="160" spans="1:10">
       <c r="A160" s="50" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B160" s="50" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C160" s="50">
         <v>7</v>
       </c>
       <c r="D160" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E160" s="52" t="s">
         <v>14</v>
       </c>
       <c r="F160" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J160" s="58" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="161" spans="1:10">
       <c r="A161" s="50" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B161" s="50" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C161" s="50">
         <v>8</v>
       </c>
       <c r="D161" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E161" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F161" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J161" s="58" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="162" spans="1:10">
       <c r="A162" s="50" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B162" s="50" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C162" s="50">
         <v>9</v>
       </c>
       <c r="D162" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E162" s="52" t="s">
         <v>14</v>
       </c>
       <c r="F162" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J162" s="58" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="163" spans="1:10">
       <c r="A163" s="50" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B163" s="50" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C163" s="50">
         <v>10</v>
       </c>
       <c r="D163" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E163" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F163" s="51" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J163" s="58" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="164" spans="1:10">
       <c r="A164" s="50" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B164" s="50" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C164" s="50">
         <v>1</v>
       </c>
       <c r="D164" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E164" s="52" t="s">
         <v>10</v>
       </c>
       <c r="F164" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G164" s="51"/>
       <c r="H164" s="53"/>
       <c r="I164" s="51" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J164" s="52" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="165" spans="1:10">
       <c r="A165" s="50" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B165" s="50" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C165" s="50">
         <v>2</v>
       </c>
       <c r="D165" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E165" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F165" s="53" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G165" s="51"/>
       <c r="H165" s="53"/>
       <c r="I165" s="51"/>
       <c r="J165" s="52" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="166" spans="1:10">
       <c r="A166" s="50" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B166" s="50" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C166" s="50">
         <v>3</v>
       </c>
       <c r="D166" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E166" s="52" t="s">
         <v>10</v>
       </c>
       <c r="F166" s="51" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G166" s="51"/>
       <c r="H166" s="53"/>
       <c r="I166" s="51"/>
       <c r="J166" s="52" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="167" spans="1:10">
       <c r="A167" s="50" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B167" s="50" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C167" s="50">
         <v>1</v>
       </c>
       <c r="D167" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E167" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F167" s="53" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G167" s="51"/>
       <c r="H167" s="53"/>
       <c r="I167" s="51" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J167" s="53" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="168" spans="1:10">
       <c r="A168" s="50" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B168" s="50" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C168" s="50">
         <v>2</v>
       </c>
       <c r="D168" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E168" s="50" t="s">
         <v>10</v>
       </c>
       <c r="F168" s="53" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G168" s="51"/>
       <c r="H168" s="53"/>
       <c r="I168" s="51"/>
       <c r="J168" s="52" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="169" spans="1:10">
       <c r="A169" s="50" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B169" s="50" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C169" s="50">
         <v>3</v>
       </c>
       <c r="D169" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E169" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F169" s="53" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G169" s="51"/>
       <c r="H169" s="53"/>
       <c r="I169" s="51"/>
       <c r="J169" s="52" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="170" spans="1:10">
       <c r="A170" s="50" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B170" s="50" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C170" s="50">
         <v>4</v>
       </c>
       <c r="D170" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E170" s="50" t="s">
         <v>10</v>
       </c>
       <c r="F170" s="53" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G170" s="51"/>
       <c r="H170" s="51"/>
       <c r="I170" s="51"/>
       <c r="J170" s="52" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="171" spans="1:10">
       <c r="A171" s="50" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B171" s="50" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C171" s="50">
         <v>5</v>
       </c>
       <c r="D171" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E171" s="52" t="s">
         <v>16</v>
       </c>
       <c r="F171" s="53" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G171" s="51"/>
       <c r="H171" s="51"/>
       <c r="I171" s="51"/>
       <c r="J171" s="52" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="172" spans="1:10">
       <c r="A172" s="50" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B172" s="50" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C172" s="50">
         <v>6</v>
       </c>
       <c r="D172" s="50" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E172" s="50" t="s">
         <v>10</v>
       </c>
       <c r="F172" s="53" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J172" s="58" t="s">
-        <v>537</v>
+        <v>1403</v>
       </c>
     </row>
   </sheetData>
@@ -17317,7 +17313,7 @@
         <v>635</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C22" s="25" t="s">
         <v>623</v>
@@ -17477,7 +17473,7 @@
         <v>671</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C30" s="25" t="s">
         <v>645</v>
@@ -17497,7 +17493,7 @@
         <v>674</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C31" s="25" t="s">
         <v>650</v>
@@ -17517,7 +17513,7 @@
         <v>677</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C32" s="25" t="s">
         <v>678</v>
@@ -17657,7 +17653,7 @@
         <v>709</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C39" s="25" t="s">
         <v>683</v>
@@ -17777,7 +17773,7 @@
         <v>737</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C45" s="25" t="s">
         <v>724</v>
@@ -18090,8 +18086,8 @@
     <col min="27" max="27" width="5.125" style="35" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="5" style="35" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="5.25" style="35" bestFit="1" customWidth="1"/>
-    <col min="30" max="102" width="9" style="9" customWidth="1"/>
-    <col min="103" max="16384" width="9" style="9"/>
+    <col min="30" max="103" width="9" style="9" customWidth="1"/>
+    <col min="104" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="15.4" customHeight="1">
@@ -18402,7 +18398,7 @@
     </row>
     <row r="22" spans="1:21" ht="18" customHeight="1">
       <c r="A22" s="10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N22" s="34">
         <v>0.5</v>
@@ -18478,7 +18474,7 @@
     </row>
     <row r="30" spans="1:21" ht="18" customHeight="1">
       <c r="A30" s="10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F30" s="27">
         <v>0.5</v>
@@ -18489,7 +18485,7 @@
     </row>
     <row r="31" spans="1:21" ht="18" customHeight="1">
       <c r="A31" s="10" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H31" s="27">
         <v>1.5</v>
@@ -18500,7 +18496,7 @@
     </row>
     <row r="32" spans="1:21" ht="18" customHeight="1">
       <c r="A32" s="10" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G32" s="27">
         <v>0.5</v>
@@ -18565,7 +18561,7 @@
     </row>
     <row r="39" spans="1:28" ht="18" customHeight="1">
       <c r="A39" s="10" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="J39" s="33">
         <v>1.5</v>
@@ -18643,7 +18639,7 @@
     </row>
     <row r="45" spans="1:28" ht="18" customHeight="1">
       <c r="A45" s="10" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="W45" s="35">
         <v>0.5</v>
@@ -19123,7 +19119,7 @@
         <v>636</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>814</v>
@@ -19259,7 +19255,7 @@
         <v>672</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>791</v>
@@ -19276,7 +19272,7 @@
         <v>675</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>819</v>
@@ -19293,7 +19289,7 @@
         <v>679</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>862</v>
@@ -19412,7 +19408,7 @@
         <v>710</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>880</v>
@@ -19514,7 +19510,7 @@
         <v>738</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>868</v>
@@ -21273,7 +21269,7 @@
         <v>595</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>997</v>
@@ -22216,7 +22212,7 @@
         <v>624</v>
       </c>
       <c r="B111" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C111" s="10" t="s">
         <v>997</v>
@@ -22423,7 +22419,7 @@
         <v>633</v>
       </c>
       <c r="B120" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C120" s="10" t="s">
         <v>997</v>
@@ -22492,7 +22488,7 @@
         <v>636</v>
       </c>
       <c r="B123" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C123" s="10" t="s">
         <v>997</v>
@@ -23458,7 +23454,7 @@
         <v>656</v>
       </c>
       <c r="B165" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C165" s="10" t="s">
         <v>997</v>
@@ -23550,7 +23546,7 @@
         <v>660</v>
       </c>
       <c r="B169" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C169" s="10" t="s">
         <v>997</v>
@@ -24263,7 +24259,7 @@
         <v>669</v>
       </c>
       <c r="B200" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C200" s="10" t="s">
         <v>997</v>
@@ -24700,7 +24696,7 @@
         <v>679</v>
       </c>
       <c r="B219" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C219" s="10" t="s">
         <v>997</v>
@@ -26195,7 +26191,7 @@
         <v>710</v>
       </c>
       <c r="B284" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C284" s="10" t="s">
         <v>997</v>
@@ -26471,7 +26467,7 @@
         <v>720</v>
       </c>
       <c r="B296" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C296" s="10" t="s">
         <v>997</v>
@@ -27414,7 +27410,7 @@
         <v>747</v>
       </c>
       <c r="B337" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C337" s="47" t="s">
         <v>997</v>
@@ -27918,7 +27914,7 @@
         <v>1144</v>
       </c>
       <c r="G1" s="42" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>542</v>
@@ -29276,7 +29272,7 @@
         <v>997</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>1145</v>
@@ -31656,8 +31652,8 @@
     <cfRule type="duplicateValues" dxfId="149" priority="2366"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A77 A79:A100 A102:A106 A114:A1048576">
-    <cfRule type="duplicateValues" dxfId="148" priority="2331"/>
-    <cfRule type="duplicateValues" dxfId="147" priority="2332"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="2332"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="2331"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A5">
     <cfRule type="duplicateValues" dxfId="146" priority="162"/>
@@ -31684,32 +31680,32 @@
     <cfRule type="duplicateValues" dxfId="137" priority="126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="136" priority="123"/>
-    <cfRule type="duplicateValues" dxfId="135" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16">
     <cfRule type="duplicateValues" dxfId="134" priority="121"/>
     <cfRule type="duplicateValues" dxfId="133" priority="122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
-    <cfRule type="duplicateValues" dxfId="132" priority="119"/>
-    <cfRule type="duplicateValues" dxfId="131" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18">
-    <cfRule type="duplicateValues" dxfId="130" priority="117"/>
-    <cfRule type="duplicateValues" dxfId="129" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:A20">
-    <cfRule type="duplicateValues" dxfId="128" priority="115"/>
-    <cfRule type="duplicateValues" dxfId="127" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
     <cfRule type="duplicateValues" dxfId="126" priority="112"/>
     <cfRule type="duplicateValues" dxfId="125" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A26">
-    <cfRule type="duplicateValues" dxfId="124" priority="110"/>
-    <cfRule type="duplicateValues" dxfId="123" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27">
     <cfRule type="duplicateValues" dxfId="122" priority="140"/>
@@ -31748,20 +31744,20 @@
     <cfRule type="duplicateValues" dxfId="105" priority="632"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40">
-    <cfRule type="duplicateValues" dxfId="104" priority="154"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="154"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41">
     <cfRule type="duplicateValues" dxfId="102" priority="78"/>
     <cfRule type="duplicateValues" dxfId="101" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43">
-    <cfRule type="duplicateValues" dxfId="100" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44">
-    <cfRule type="duplicateValues" dxfId="98" priority="146"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="146"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45">
     <cfRule type="duplicateValues" dxfId="96" priority="90"/>
@@ -31772,8 +31768,8 @@
     <cfRule type="duplicateValues" dxfId="93" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:A48">
-    <cfRule type="duplicateValues" dxfId="92" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:A52">
     <cfRule type="duplicateValues" dxfId="90" priority="106"/>
@@ -31784,32 +31780,32 @@
     <cfRule type="duplicateValues" dxfId="87" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54">
-    <cfRule type="duplicateValues" dxfId="86" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55">
-    <cfRule type="duplicateValues" dxfId="84" priority="133"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="133"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56">
-    <cfRule type="duplicateValues" dxfId="82" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57">
-    <cfRule type="duplicateValues" dxfId="80" priority="148"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="148"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58">
     <cfRule type="duplicateValues" dxfId="78" priority="152"/>
     <cfRule type="duplicateValues" dxfId="77" priority="153"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59">
-    <cfRule type="duplicateValues" dxfId="76" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A60">
-    <cfRule type="duplicateValues" dxfId="74" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61">
     <cfRule type="duplicateValues" dxfId="72" priority="86"/>
@@ -31820,8 +31816,8 @@
     <cfRule type="duplicateValues" dxfId="69" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63">
-    <cfRule type="duplicateValues" dxfId="68" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64">
     <cfRule type="duplicateValues" dxfId="66" priority="60"/>
@@ -31832,8 +31828,8 @@
     <cfRule type="duplicateValues" dxfId="63" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A66">
-    <cfRule type="duplicateValues" dxfId="62" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67">
     <cfRule type="duplicateValues" dxfId="60" priority="150"/>
@@ -31844,8 +31840,8 @@
     <cfRule type="duplicateValues" dxfId="57" priority="866"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69">
-    <cfRule type="duplicateValues" dxfId="56" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70">
     <cfRule type="duplicateValues" dxfId="54" priority="42"/>
@@ -31856,36 +31852,36 @@
     <cfRule type="duplicateValues" dxfId="51" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72:A73">
-    <cfRule type="duplicateValues" dxfId="50" priority="99"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="99"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A74">
     <cfRule type="duplicateValues" dxfId="48" priority="95"/>
     <cfRule type="duplicateValues" dxfId="47" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75:A77">
-    <cfRule type="duplicateValues" dxfId="46" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A78">
-    <cfRule type="duplicateValues" dxfId="44" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A79 A106">
     <cfRule type="duplicateValues" dxfId="42" priority="1727"/>
     <cfRule type="duplicateValues" dxfId="41" priority="1728"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A80">
-    <cfRule type="duplicateValues" dxfId="40" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A82:A83">
     <cfRule type="duplicateValues" dxfId="38" priority="982"/>
     <cfRule type="duplicateValues" dxfId="37" priority="983"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A84">
-    <cfRule type="duplicateValues" dxfId="36" priority="135"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A85">
     <cfRule type="duplicateValues" dxfId="34" priority="13"/>
@@ -31916,12 +31912,12 @@
     <cfRule type="duplicateValues" dxfId="21" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A96">
-    <cfRule type="duplicateValues" dxfId="20" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A98">
-    <cfRule type="duplicateValues" dxfId="18" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A99">
     <cfRule type="duplicateValues" dxfId="16" priority="26"/>
@@ -31936,12 +31932,12 @@
     <cfRule type="duplicateValues" dxfId="11" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A102">
-    <cfRule type="duplicateValues" dxfId="10" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A103">
-    <cfRule type="duplicateValues" dxfId="8" priority="142"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="142"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A104:A105">
     <cfRule type="duplicateValues" dxfId="6" priority="1709"/>
@@ -31952,8 +31948,8 @@
     <cfRule type="duplicateValues" dxfId="3" priority="1944"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A114:A115">
-    <cfRule type="duplicateValues" dxfId="2" priority="131"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="131"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="395"/>
@@ -31990,7 +31986,7 @@
         <v>1349</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>543</v>
@@ -32054,7 +32050,7 @@
         <v>1358</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>1359</v>

--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F415681-28A3-43DB-97AF-9EA1A0879A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{699E4709-88D2-487F-B56E-C29950A8E5C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3562" yWindow="3150" windowWidth="21601" windowHeight="11423" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4785" yWindow="5047" windowWidth="21600" windowHeight="11423" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" r:id="rId1"/>
@@ -7097,9 +7097,6 @@
     <t>王清任</t>
   </si>
   <si>
-    <t>TheoryID</t>
-  </si>
-  <si>
     <t>TheoryName</t>
   </si>
   <si>
@@ -7154,11 +7151,14 @@
     <t>预制方剂</t>
   </si>
   <si>
+    <t>现在你可以预制方剂，开方时搜索并选取方剂名可以填写该方剂的所有药材。</t>
+  </si>
+  <si>
+    <t>TheoryID</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
     <t>yu_zhi_fang_ji</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>现在你可以预制方剂，开方时搜索并选取方剂名可以填写该方剂的所有药材。</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
@@ -9464,8 +9464,8 @@
     <col min="7" max="7" width="25.1328125" style="23" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.265625" style="23" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="33.3984375" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="66" width="9.1328125" style="23" customWidth="1"/>
-    <col min="67" max="16384" width="9.1328125" style="23"/>
+    <col min="10" max="67" width="9.1328125" style="23" customWidth="1"/>
+    <col min="68" max="16384" width="9.1328125" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.399999999999999" customHeight="1">
@@ -11413,10 +11413,10 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1">
       <c r="A1" s="12" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>1606</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>1607</v>
       </c>
       <c r="C1" s="42" t="s">
         <v>270</v>
@@ -11430,10 +11430,10 @@
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1">
       <c r="A2" s="7" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>1608</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>1609</v>
       </c>
       <c r="C2" s="7">
         <v>0</v>
@@ -11442,15 +11442,15 @@
         <v>1565</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1">
       <c r="A3" s="7" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>1611</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>1612</v>
       </c>
       <c r="C3" s="7">
         <v>0</v>
@@ -11459,7 +11459,7 @@
         <v>1565</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1">
@@ -11476,15 +11476,15 @@
         <v>1565</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="C5" s="7">
         <v>0</v>
@@ -11493,7 +11493,7 @@
         <v>1565</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1">
@@ -11586,8 +11586,8 @@
     <col min="14" max="14" width="12" style="36" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.73046875" style="36" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10.86328125" style="36" bestFit="1" customWidth="1"/>
-    <col min="17" max="89" width="9" style="36" customWidth="1"/>
-    <col min="90" max="16384" width="9" style="36"/>
+    <col min="17" max="90" width="9" style="36" customWidth="1"/>
+    <col min="91" max="16384" width="9" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -13764,8 +13764,8 @@
     <col min="8" max="8" width="8.1328125" style="32" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="48" style="32" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="150.46484375" style="32" bestFit="1" customWidth="1"/>
-    <col min="11" max="40" width="8.86328125" style="36" customWidth="1"/>
-    <col min="41" max="16384" width="8.86328125" style="36"/>
+    <col min="11" max="41" width="8.86328125" style="36" customWidth="1"/>
+    <col min="42" max="16384" width="8.86328125" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -23480,8 +23480,8 @@
     <col min="27" max="27" width="5.1328125" style="35" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="5" style="35" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="5.265625" style="35" bestFit="1" customWidth="1"/>
-    <col min="30" max="114" width="9" style="9" customWidth="1"/>
-    <col min="115" max="16384" width="9" style="9"/>
+    <col min="30" max="115" width="9" style="9" customWidth="1"/>
+    <col min="116" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="15.4" customHeight="1">

--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -5704,7 +5704,11 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>gte</t>
+        </is>
+      </c>
       <c r="H2" t="n">
         <v>107</v>
       </c>
@@ -8351,7 +8355,7 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>night</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -8388,11 +8392,7 @@
           <t>026治疗成功</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>clinic</t>
-        </is>
-      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>night</t>
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
@@ -8455,7 +8455,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>night</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">

--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD36A1F-2643-46F9-99C2-AB9641ECCCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C20209-8890-4D3D-BD2E-9438967A9EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Npc" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7048" uniqueCount="1760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7073" uniqueCount="1773">
   <si>
     <t>NpcID</t>
   </si>
@@ -7594,6 +7594,58 @@
   </si>
   <si>
     <t>现在你可以预制方剂，开方时搜索并选取方剂名可以填写该方剂的所有药材。</t>
+  </si>
+  <si>
+    <t>林巧娘</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>马长风</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>魏大脚</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>柳莺儿</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>季云娘</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>贺三姐</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>lin_qiao_niao</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>ma_chang_feng</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>wei_da_jiao</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>liu_ying_er</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>he_san_jie</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>ji_yun_niang</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>哎哟，俺这两天</t>
+    <phoneticPr fontId="19"/>
   </si>
 </sst>
 </file>
@@ -7867,7 +7919,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -8066,6 +8118,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -9911,8 +9964,8 @@
     <col min="7" max="7" width="25.5" style="23" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.75" style="23" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="33.875" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="75" width="9.125" style="23" customWidth="1"/>
-    <col min="76" max="16384" width="9.125" style="23"/>
+    <col min="10" max="76" width="9.125" style="23" customWidth="1"/>
+    <col min="77" max="16384" width="9.125" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.399999999999999" customHeight="1">
@@ -11548,7 +11601,7 @@
         <v>12</v>
       </c>
       <c r="E64" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F64" s="7" t="s">
         <v>102</v>
@@ -11767,66 +11820,128 @@
       </c>
     </row>
     <row r="72" spans="1:9" ht="18" customHeight="1">
-      <c r="A72" s="7"/>
-      <c r="B72" s="7"/>
-      <c r="C72" s="7"/>
-      <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
+      <c r="A72" s="82" t="s">
+        <v>1766</v>
+      </c>
+      <c r="B72" s="82" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E72" s="7">
+        <v>27</v>
+      </c>
       <c r="F72" s="7"/>
       <c r="G72" s="40"/>
       <c r="H72" s="7"/>
       <c r="I72" s="7"/>
     </row>
     <row r="73" spans="1:9" ht="18" customHeight="1">
-      <c r="A73" s="7"/>
-      <c r="B73" s="7"/>
-      <c r="C73" s="7"/>
-      <c r="D73" s="7"/>
-      <c r="E73" s="7"/>
+      <c r="A73" s="82" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B73" s="82" t="s">
+        <v>1761</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E73" s="7">
+        <v>35</v>
+      </c>
       <c r="F73" s="7"/>
       <c r="G73" s="40"/>
       <c r="H73" s="7"/>
       <c r="I73" s="7"/>
     </row>
     <row r="74" spans="1:9" ht="18" customHeight="1">
-      <c r="A74" s="7"/>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
+      <c r="A74" s="82" t="s">
+        <v>1768</v>
+      </c>
+      <c r="B74" s="82" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E74" s="7">
+        <v>42</v>
+      </c>
+      <c r="F74" s="82" t="s">
+        <v>1772</v>
+      </c>
       <c r="G74" s="40"/>
       <c r="H74" s="7"/>
       <c r="I74" s="7"/>
     </row>
     <row r="75" spans="1:9" ht="18" customHeight="1">
-      <c r="A75" s="7"/>
-      <c r="B75" s="7"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
+      <c r="A75" s="82" t="s">
+        <v>1769</v>
+      </c>
+      <c r="B75" s="82" t="s">
+        <v>1763</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E75" s="7">
+        <v>19</v>
+      </c>
       <c r="F75" s="7"/>
       <c r="G75" s="40"/>
       <c r="H75" s="7"/>
       <c r="I75" s="7"/>
     </row>
     <row r="76" spans="1:9" ht="18" customHeight="1">
-      <c r="A76" s="7"/>
-      <c r="B76" s="7"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
+      <c r="A76" s="82" t="s">
+        <v>1770</v>
+      </c>
+      <c r="B76" s="82" t="s">
+        <v>1765</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E76" s="7">
+        <v>38</v>
+      </c>
       <c r="F76" s="7"/>
       <c r="G76" s="40"/>
       <c r="H76" s="7"/>
       <c r="I76" s="7"/>
     </row>
     <row r="77" spans="1:9" ht="18" customHeight="1">
-      <c r="A77" s="7"/>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
-      <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
+      <c r="A77" s="82" t="s">
+        <v>1771</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>1764</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E77" s="7">
+        <v>25</v>
+      </c>
       <c r="F77" s="7"/>
       <c r="G77" s="40"/>
       <c r="H77" s="7"/>
@@ -12067,8 +12182,8 @@
     <col min="16" max="18" width="8.375" style="53" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="10.75" style="53" customWidth="1"/>
     <col min="20" max="20" width="10" style="53" bestFit="1" customWidth="1"/>
-    <col min="21" max="25" width="9" style="54" customWidth="1"/>
-    <col min="26" max="16384" width="9" style="54"/>
+    <col min="21" max="26" width="9" style="54" customWidth="1"/>
+    <col min="27" max="16384" width="9" style="54"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="53" customFormat="1" ht="36" customHeight="1">
@@ -13686,9 +13801,7 @@
       <c r="N43" s="55"/>
       <c r="O43" s="55"/>
       <c r="P43" s="55"/>
-      <c r="Q43" s="55">
-        <v>1000</v>
-      </c>
+      <c r="Q43" s="55"/>
       <c r="R43" s="55"/>
       <c r="S43" s="55" t="b">
         <v>1</v>
@@ -14062,7 +14175,7 @@
       <c r="H53" s="55"/>
       <c r="I53" s="55"/>
       <c r="J53" s="55" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="K53" s="55"/>
       <c r="L53" s="55" t="s">
@@ -14313,7 +14426,7 @@
       </c>
       <c r="T59"/>
     </row>
-    <row r="60" spans="1:20" ht="18.75">
+    <row r="60" spans="1:20" ht="18.75" customHeight="1">
       <c r="A60" s="55" t="s">
         <v>425</v>
       </c>
@@ -14367,8 +14480,8 @@
     <col min="9" max="9" width="48" style="10" customWidth="1"/>
     <col min="10" max="10" width="150.5" style="71" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="73" customWidth="1"/>
-    <col min="12" max="49" width="8.875" style="36" customWidth="1"/>
-    <col min="50" max="16384" width="8.875" style="36"/>
+    <col min="12" max="50" width="8.875" style="36" customWidth="1"/>
+    <col min="51" max="16384" width="8.875" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -27345,8 +27458,8 @@
     <col min="27" max="27" width="5.125" style="35" customWidth="1"/>
     <col min="28" max="28" width="5" style="35" customWidth="1"/>
     <col min="29" max="29" width="5.25" style="35" customWidth="1"/>
-    <col min="30" max="123" width="9" style="9" customWidth="1"/>
-    <col min="124" max="16384" width="9" style="9"/>
+    <col min="30" max="124" width="9" style="9" customWidth="1"/>
+    <col min="125" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="15.4" customHeight="1">

--- a/DataTables/Data.backup_before_detailtext_import.xlsx
+++ b/DataTables/Data.backup_before_detailtext_import.xlsx
@@ -19694,7 +19694,11 @@
           <t>咯噔</t>
         </is>
       </c>
-      <c r="K273" s="50" t="inlineStr"/>
+      <c r="K273" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Music/020/圍剿夜襲.mp3</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="50" t="inlineStr">
@@ -20326,9 +20330,13 @@
           <t>蕲州赈灾药材贪污案惊动朝廷，锦衣卫奉旨查办，地方涉案官员数十人，贪污银钱近万两。</t>
         </is>
       </c>
-      <c r="K289" s="50" t="inlineStr"/>
-    </row>
-    <row r="290" ht="18.75" customHeight="1">
+      <c r="K289" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Music/Story/021/问斩.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
       <c r="A290" s="50" t="inlineStr">
         <is>
           <t>021</t>
@@ -24841,7 +24849,11 @@
           <t>今天是上元佳节，咱们全家去城里逛逛，听说今年的灯节格外热闹。</t>
         </is>
       </c>
-      <c r="K402" s="50" t="inlineStr"/>
+      <c r="K402" s="51" t="inlineStr">
+        <is>
+          <t>res://Assets/Music/Story/027/元宵夜樂.mp3</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="50" t="inlineStr">
